--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Git-hub/MC-SAGARANTEN.WEB-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7A2EB4-9A5E-4836-B430-91F010AEEDFA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,11 @@
     <sheet name="penjualan-paket-tm" sheetId="5" r:id="rId5"/>
     <sheet name="penjualan-direct-selling" sheetId="6" r:id="rId6"/>
     <sheet name="penjualan-hifi" sheetId="7" r:id="rId7"/>
+    <sheet name="index" sheetId="8" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
   <si>
     <t>nama barang</t>
   </si>
@@ -376,18 +380,48 @@
   </si>
   <si>
     <t>355806671163435</t>
+  </si>
+  <si>
+    <t>stok gudang</t>
+  </si>
+  <si>
+    <t>stok dse</t>
+  </si>
+  <si>
+    <t>STOCK AKHIR CSO SAGARANTEN</t>
+  </si>
+  <si>
+    <t>salmo</t>
+  </si>
+  <si>
+    <t>penjualan</t>
+  </si>
+  <si>
+    <t>Spv</t>
+  </si>
+  <si>
+    <t>paket tm</t>
+  </si>
+  <si>
+    <t>direct selling</t>
+  </si>
+  <si>
+    <t>hifi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,8 +444,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,8 +482,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -448,12 +530,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,12 +660,98 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -488,6 +762,353 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CSO"/>
+      <sheetName val="01"/>
+      <sheetName val="02"/>
+      <sheetName val="03"/>
+      <sheetName val="04"/>
+      <sheetName val="05"/>
+      <sheetName val="06"/>
+      <sheetName val="07"/>
+      <sheetName val="08"/>
+      <sheetName val="09"/>
+      <sheetName val="10"/>
+      <sheetName val="11"/>
+      <sheetName val="12"/>
+      <sheetName val="13"/>
+      <sheetName val="14"/>
+      <sheetName val="15"/>
+      <sheetName val="16"/>
+      <sheetName val="17"/>
+      <sheetName val="18"/>
+      <sheetName val="19"/>
+      <sheetName val="20"/>
+      <sheetName val="21"/>
+      <sheetName val="22"/>
+      <sheetName val="23"/>
+      <sheetName val="24"/>
+      <sheetName val="25"/>
+      <sheetName val="26"/>
+      <sheetName val="27"/>
+      <sheetName val="28"/>
+      <sheetName val="29"/>
+      <sheetName val="30"/>
+      <sheetName val="31"/>
+      <sheetName val="SUMMARY"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32">
+        <row r="6">
+          <cell r="B6">
+            <v>2</v>
+          </cell>
+          <cell r="C6">
+            <v>12</v>
+          </cell>
+          <cell r="D6">
+            <v>27</v>
+          </cell>
+          <cell r="E6">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>3</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>110</v>
+          </cell>
+          <cell r="C12">
+            <v>369</v>
+          </cell>
+          <cell r="D12">
+            <v>30</v>
+          </cell>
+          <cell r="E12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>2</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>254</v>
+          </cell>
+          <cell r="C14">
+            <v>342</v>
+          </cell>
+          <cell r="D14">
+            <v>233</v>
+          </cell>
+          <cell r="E14">
+            <v>212</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>21</v>
+          </cell>
+          <cell r="C16">
+            <v>19</v>
+          </cell>
+          <cell r="D16">
+            <v>45</v>
+          </cell>
+          <cell r="E16">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>52</v>
+          </cell>
+          <cell r="C17">
+            <v>144</v>
+          </cell>
+          <cell r="D17">
+            <v>75</v>
+          </cell>
+          <cell r="E17">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>24</v>
+          </cell>
+          <cell r="C18">
+            <v>47</v>
+          </cell>
+          <cell r="D18">
+            <v>2</v>
+          </cell>
+          <cell r="E18">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>3</v>
+          </cell>
+          <cell r="C19">
+            <v>12</v>
+          </cell>
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>31</v>
+          </cell>
+          <cell r="C20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>75</v>
+          </cell>
+          <cell r="C23">
+            <v>65</v>
+          </cell>
+          <cell r="D23">
+            <v>33</v>
+          </cell>
+          <cell r="E23">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -815,12 +1436,15 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
+        <f>index!B4</f>
         <v>1107</v>
       </c>
       <c r="C3">
+        <f>index!C4</f>
         <v>0</v>
       </c>
       <c r="D3" s="1">
+        <f>B3+C3</f>
         <v>1107</v>
       </c>
     </row>
@@ -829,12 +1453,15 @@
         <v>5</v>
       </c>
       <c r="B4">
+        <f>index!B5</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
+        <f>index!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D21" si="0">B4+C4</f>
         <v>0</v>
       </c>
     </row>
@@ -843,13 +1470,16 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>425</v>
+        <f>index!B6</f>
+        <v>1525</v>
       </c>
       <c r="C5">
+        <f>index!C6</f>
         <v>1526</v>
       </c>
       <c r="D5" s="1">
-        <v>1951</v>
+        <f t="shared" si="0"/>
+        <v>3051</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -857,34 +1487,43 @@
         <v>7</v>
       </c>
       <c r="B6">
+        <f>index!B7</f>
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
+        <f>index!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
+        <f>index!B8</f>
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
+        <f>index!C8</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
+        <f>index!B9</f>
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
+        <f>index!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -893,12 +1532,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <f>index!B10</f>
         <v>2462</v>
       </c>
       <c r="C9">
+        <f>index!C10</f>
         <v>0</v>
       </c>
       <c r="D9" s="1">
+        <f t="shared" si="0"/>
         <v>2462</v>
       </c>
     </row>
@@ -907,12 +1549,15 @@
         <v>9</v>
       </c>
       <c r="B10">
+        <f>index!B11</f>
         <v>0</v>
       </c>
       <c r="C10">
+        <f>index!C11</f>
         <v>1</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -921,12 +1566,15 @@
         <v>10</v>
       </c>
       <c r="B11">
+        <f>index!B12</f>
         <v>80</v>
       </c>
       <c r="C11">
+        <f>index!C12</f>
         <v>976</v>
       </c>
       <c r="D11" s="1">
+        <f t="shared" si="0"/>
         <v>1056</v>
       </c>
     </row>
@@ -935,12 +1583,15 @@
         <v>11</v>
       </c>
       <c r="B12">
+        <f>index!B13</f>
         <v>0</v>
       </c>
       <c r="C12">
+        <f>index!C13</f>
         <v>300</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
@@ -949,12 +1600,15 @@
         <v>12</v>
       </c>
       <c r="B13">
+        <f>index!B14</f>
         <v>42</v>
       </c>
       <c r="C13">
+        <f>index!C14</f>
         <v>457</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
         <v>499</v>
       </c>
     </row>
@@ -963,12 +1617,15 @@
         <v>13</v>
       </c>
       <c r="B14">
+        <f>index!B15</f>
         <v>198</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
+        <f>index!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
         <v>198</v>
       </c>
     </row>
@@ -977,12 +1634,15 @@
         <v>14</v>
       </c>
       <c r="B15">
+        <f>index!B16</f>
         <v>165</v>
       </c>
       <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
+        <f>index!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
@@ -991,12 +1651,15 @@
         <v>15</v>
       </c>
       <c r="B16">
+        <f>index!B17</f>
         <v>404</v>
       </c>
       <c r="C16">
+        <f>index!C17</f>
         <v>1</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
         <v>405</v>
       </c>
     </row>
@@ -1005,12 +1668,15 @@
         <v>16</v>
       </c>
       <c r="B17">
+        <f>index!B18</f>
         <v>0</v>
       </c>
       <c r="C17">
+        <f>index!C18</f>
         <v>198</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
         <v>198</v>
       </c>
     </row>
@@ -1019,12 +1685,15 @@
         <v>17</v>
       </c>
       <c r="B18">
+        <f>index!B19</f>
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
+        <f>index!C19</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1033,12 +1702,15 @@
         <v>18</v>
       </c>
       <c r="B19">
+        <f>index!B20</f>
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
+        <f>index!C20</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1047,12 +1719,15 @@
         <v>19</v>
       </c>
       <c r="B20">
+        <f>index!B21</f>
         <v>0</v>
       </c>
       <c r="C20">
+        <f>index!C21</f>
         <v>1032</v>
       </c>
       <c r="D20" s="1">
+        <f t="shared" si="0"/>
         <v>1032</v>
       </c>
     </row>
@@ -1061,12 +1736,15 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <f>index!B22</f>
         <v>72</v>
       </c>
       <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
+        <f>index!C22</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
     </row>
@@ -1117,45 +1795,49 @@
         <v>4</v>
       </c>
       <c r="B2">
+        <f>index!G5</f>
         <v>84</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
+      <c r="C2">
+        <f>index!H5</f>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <f>index!I5</f>
+        <v>23</v>
       </c>
       <c r="E2">
+        <f>index!J5</f>
         <v>119</v>
       </c>
-      <c r="F2">
-        <v>22</v>
-      </c>
       <c r="G2">
-        <v>251</v>
+        <f>SUM(B2:F2)</f>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
+      <c r="B3">
+        <f>index!G6</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>index!H6</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>index!I6</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>index!J6</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G23" si="0">SUM(B3:F3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1163,85 +1845,93 @@
         <v>30</v>
       </c>
       <c r="B4">
+        <f>index!G7</f>
         <v>572</v>
       </c>
       <c r="C4">
+        <f>index!H7</f>
         <v>323</v>
       </c>
       <c r="D4">
+        <f>index!I7</f>
         <v>519</v>
       </c>
       <c r="E4">
+        <f>index!J7</f>
         <v>509</v>
       </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
       <c r="G4">
-        <v>1933</v>
+        <f t="shared" si="0"/>
+        <v>1923</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
+      <c r="B5">
+        <f>index!G8</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>index!H8</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>index!I8</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>index!J8</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
+      <c r="B6">
+        <f>index!G9</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>index!H9</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>index!I9</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>index!J9</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
+      <c r="B7">
+        <f>index!G10</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f>index!H10</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>index!I10</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>index!J10</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1249,21 +1939,23 @@
         <v>8</v>
       </c>
       <c r="B8">
+        <f>index!G11</f>
         <v>120</v>
       </c>
       <c r="C8">
+        <f>index!H11</f>
         <v>300</v>
       </c>
       <c r="D8">
+        <f>index!I11</f>
         <v>120</v>
       </c>
       <c r="E8">
+        <f>index!J11</f>
         <v>300</v>
       </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
       <c r="G8">
+        <f t="shared" si="0"/>
         <v>840</v>
       </c>
     </row>
@@ -1272,21 +1964,23 @@
         <v>31</v>
       </c>
       <c r="B9">
+        <f>index!G12</f>
         <v>5</v>
       </c>
-      <c r="C9" t="s">
-        <v>28</v>
+      <c r="C9">
+        <f>index!H12</f>
+        <v>0</v>
       </c>
       <c r="D9">
+        <f>index!I12</f>
         <v>4</v>
       </c>
       <c r="E9">
+        <f>index!J12</f>
         <v>4</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
       <c r="G9">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
@@ -1295,45 +1989,49 @@
         <v>32</v>
       </c>
       <c r="B10">
+        <f>index!G13</f>
         <v>52</v>
       </c>
       <c r="C10">
-        <v>62</v>
+        <f>index!H13</f>
+        <v>47</v>
       </c>
       <c r="D10">
+        <f>index!I13</f>
         <v>36</v>
       </c>
       <c r="E10">
+        <f>index!J13</f>
         <v>102</v>
       </c>
-      <c r="F10">
-        <v>21</v>
-      </c>
       <c r="G10">
-        <v>273</v>
+        <f t="shared" si="0"/>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
+      <c r="B11">
+        <f>index!G14</f>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>index!H14</f>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f>index!I14</f>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f>index!J14</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1341,22 +2039,24 @@
         <v>34</v>
       </c>
       <c r="B12">
+        <f>index!G15</f>
         <v>44</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <f>index!H15</f>
+        <v>0</v>
       </c>
       <c r="D12">
+        <f>index!I15</f>
         <v>19</v>
       </c>
       <c r="E12">
+        <f>index!J15</f>
         <v>72</v>
       </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
       <c r="G12">
-        <v>145</v>
+        <f t="shared" si="0"/>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1364,22 +2064,24 @@
         <v>35</v>
       </c>
       <c r="B13">
+        <f>index!G16</f>
         <v>99</v>
       </c>
       <c r="C13">
-        <v>46</v>
+        <f>index!H16</f>
+        <v>36</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <f>index!I16</f>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>106</v>
-      </c>
-      <c r="F13">
-        <v>21</v>
+        <f>index!J16</f>
+        <v>101</v>
       </c>
       <c r="G13">
-        <v>322</v>
+        <f t="shared" si="0"/>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1387,22 +2089,24 @@
         <v>36</v>
       </c>
       <c r="B14">
+        <f>index!G17</f>
         <v>46</v>
       </c>
       <c r="C14">
+        <f>index!H17</f>
         <v>50</v>
       </c>
       <c r="D14">
+        <f>index!I17</f>
         <v>39</v>
       </c>
       <c r="E14">
+        <f>index!J17</f>
         <v>48</v>
       </c>
-      <c r="F14">
-        <v>22</v>
-      </c>
       <c r="G14">
-        <v>205</v>
+        <f t="shared" si="0"/>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1410,21 +2114,23 @@
         <v>15</v>
       </c>
       <c r="B15">
+        <f>index!G18</f>
         <v>45</v>
       </c>
       <c r="C15">
+        <f>index!H18</f>
         <v>40</v>
       </c>
       <c r="D15">
+        <f>index!I18</f>
         <v>18</v>
       </c>
       <c r="E15">
+        <f>index!J18</f>
         <v>20</v>
       </c>
-      <c r="F15" t="s">
-        <v>28</v>
-      </c>
       <c r="G15">
+        <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
@@ -1433,21 +2139,23 @@
         <v>16</v>
       </c>
       <c r="B16">
+        <f>index!G19</f>
         <v>11</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
+      <c r="C16">
+        <f>index!H19</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>index!I19</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>index!J19</f>
+        <v>0</v>
       </c>
       <c r="G16">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -1456,21 +2164,23 @@
         <v>17</v>
       </c>
       <c r="B17">
+        <f>index!G20</f>
         <v>1</v>
       </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
+      <c r="C17">
+        <f>index!H20</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>index!I20</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>index!J20</f>
+        <v>0</v>
       </c>
       <c r="G17">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1479,21 +2189,23 @@
         <v>18</v>
       </c>
       <c r="B18">
+        <f>index!G21</f>
         <v>11</v>
       </c>
       <c r="C18">
+        <f>index!H21</f>
         <v>70</v>
       </c>
       <c r="D18">
+        <f>index!I21</f>
         <v>27</v>
       </c>
       <c r="E18">
+        <f>index!J21</f>
         <v>6</v>
       </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
       <c r="G18">
+        <f t="shared" si="0"/>
         <v>114</v>
       </c>
     </row>
@@ -1502,22 +2214,24 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>142</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
+        <f>index!G22</f>
+        <v>132</v>
+      </c>
+      <c r="C19">
+        <f>index!H22</f>
+        <v>0</v>
       </c>
       <c r="D19">
+        <f>index!I22</f>
         <v>91</v>
       </c>
       <c r="E19">
-        <v>71</v>
-      </c>
-      <c r="F19">
-        <v>12</v>
+        <f>index!J22</f>
+        <v>65</v>
       </c>
       <c r="G19">
-        <v>316</v>
+        <f t="shared" si="0"/>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1525,22 +2239,24 @@
         <v>20</v>
       </c>
       <c r="B20">
+        <f>index!G23</f>
         <v>10</v>
       </c>
       <c r="C20">
+        <f>index!H23</f>
         <v>4</v>
       </c>
       <c r="D20">
+        <f>index!I23</f>
         <v>4</v>
       </c>
       <c r="E20">
+        <f>index!J23</f>
         <v>55</v>
       </c>
-      <c r="F20">
-        <v>9</v>
-      </c>
       <c r="G20">
-        <v>82</v>
+        <f t="shared" si="0"/>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1559,8 +2275,9 @@
       <c r="F21" t="s">
         <v>28</v>
       </c>
-      <c r="G21" t="s">
-        <v>28</v>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1579,8 +2296,9 @@
       <c r="F22" t="s">
         <v>28</v>
       </c>
-      <c r="G22" t="s">
-        <v>28</v>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1603,6 +2321,7 @@
         <v>117</v>
       </c>
       <c r="G23">
+        <f t="shared" si="0"/>
         <v>4629</v>
       </c>
     </row>
@@ -1633,7 +2352,8 @@
         <v>39</v>
       </c>
       <c r="B2">
-        <v>45802400</v>
+        <f>index!O3</f>
+        <v>49352400</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1641,7 +2361,8 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>70703400</v>
+        <f>index!O4</f>
+        <v>75753400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1649,7 +2370,8 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>55577000</v>
+        <f>index!O5</f>
+        <v>59427000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1657,7 +2379,8 @@
         <v>42</v>
       </c>
       <c r="B5">
-        <v>68853900</v>
+        <f>index!O6</f>
+        <v>72748900</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1665,7 +2388,8 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>240936700</v>
+        <f>SUM(B2:B5)</f>
+        <v>257281700</v>
       </c>
     </row>
   </sheetData>
@@ -2343,30 +3067,39 @@
         <v>68</v>
       </c>
       <c r="C3">
+        <f>index!AC4</f>
         <v>275</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="39">
+        <f>index!AD4</f>
         <v>6250000</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="39">
+        <f>index!AE4</f>
         <v>6250000</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
+      <c r="F3" s="39" t="str">
+        <f>index!AF4</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G3">
+        <f>index!AG4</f>
         <v>25</v>
       </c>
       <c r="H3">
+        <f>index!AH4</f>
         <v>0</v>
       </c>
       <c r="I3">
+        <f>index!AI4</f>
         <v>0</v>
       </c>
       <c r="J3">
+        <f>index!AJ4</f>
         <v>0</v>
       </c>
       <c r="K3">
+        <f>SUM(G3:J3)</f>
         <v>25</v>
       </c>
     </row>
@@ -2378,30 +3111,39 @@
         <v>68</v>
       </c>
       <c r="C4">
+        <f>index!AC5</f>
         <v>237</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="39">
+        <f>index!AD5</f>
         <v>5585000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="39">
+        <f>index!AE5</f>
         <v>5585000</v>
       </c>
-      <c r="F4" t="s">
-        <v>28</v>
+      <c r="F4" s="39" t="str">
+        <f>index!AF5</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G4">
+        <f>index!AG5</f>
         <v>19</v>
       </c>
       <c r="H4">
+        <f>index!AH5</f>
         <v>1</v>
       </c>
       <c r="I4">
+        <f>index!AI5</f>
         <v>0</v>
       </c>
       <c r="J4">
+        <f>index!AJ5</f>
         <v>1</v>
       </c>
       <c r="K4">
+        <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
         <v>21</v>
       </c>
     </row>
@@ -2413,30 +3155,39 @@
         <v>68</v>
       </c>
       <c r="C5">
+        <f>index!AC6</f>
         <v>286</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="39">
+        <f>index!AD6</f>
         <v>6920000</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="39">
+        <f>index!AE6</f>
         <v>6920000</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
+      <c r="F5" s="39" t="str">
+        <f>index!AF6</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G5">
+        <f>index!AG6</f>
         <v>26</v>
       </c>
       <c r="H5">
+        <f>index!AH6</f>
         <v>0</v>
       </c>
       <c r="I5">
+        <f>index!AI6</f>
         <v>0</v>
       </c>
       <c r="J5">
+        <f>index!AJ6</f>
         <v>2</v>
       </c>
       <c r="K5">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
@@ -2448,59 +3199,77 @@
         <v>68</v>
       </c>
       <c r="C6">
+        <f>index!AC7</f>
         <v>260</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="39">
+        <f>index!AD7</f>
         <v>5875000</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="39">
+        <f>index!AE7</f>
         <v>5875000</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
+      <c r="F6" s="39" t="str">
+        <f>index!AF7</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G6">
+        <f>index!AG7</f>
         <v>16</v>
       </c>
       <c r="H6">
+        <f>index!AH7</f>
         <v>3</v>
       </c>
       <c r="I6">
+        <f>index!AI7</f>
         <v>0</v>
       </c>
       <c r="J6">
+        <f>index!AJ7</f>
         <v>0</v>
       </c>
       <c r="K6">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C7" s="1">
+      <c r="C7" s="39">
+        <f>SUM(C3:C6)</f>
         <v>1058</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="39">
+        <f t="shared" ref="D7:F7" si="1">SUM(D3:D6)</f>
         <v>24630000</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="39">
+        <f t="shared" si="1"/>
         <v>24630000</v>
       </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
         <v>86</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
+        <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
         <v>4</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="1">
+        <f t="shared" ref="I7" si="4">SUM(I3:I6)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" ref="J7" si="5">SUM(J3:J6)</f>
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
+        <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
         <v>93</v>
       </c>
     </row>
@@ -2558,21 +3327,27 @@
         <v>67</v>
       </c>
       <c r="C2">
+        <f>index!AC12</f>
         <v>63</v>
       </c>
       <c r="D2">
+        <f>index!AD12</f>
         <v>630000</v>
       </c>
       <c r="E2">
+        <f>index!AE12</f>
         <v>250000</v>
       </c>
       <c r="F2">
+        <f>index!AF12</f>
         <v>63</v>
       </c>
       <c r="G2">
+        <f>index!AG12</f>
         <v>0</v>
       </c>
       <c r="H2">
+        <f>index!AH12</f>
         <v>63</v>
       </c>
     </row>
@@ -2584,21 +3359,27 @@
         <v>69</v>
       </c>
       <c r="C3">
+        <f>index!AC13</f>
         <v>63</v>
       </c>
       <c r="D3">
+        <f>index!AD13</f>
         <v>630000</v>
       </c>
       <c r="E3">
+        <f>index!AE13</f>
         <v>250000</v>
       </c>
       <c r="F3">
+        <f>index!AF13</f>
         <v>63</v>
       </c>
       <c r="G3">
+        <f>index!AG13</f>
         <v>0</v>
       </c>
       <c r="H3">
+        <f>index!AH13</f>
         <v>63</v>
       </c>
     </row>
@@ -2610,21 +3391,27 @@
         <v>41</v>
       </c>
       <c r="C4">
+        <f>index!AC14</f>
         <v>63</v>
       </c>
       <c r="D4">
+        <f>index!AD14</f>
         <v>630000</v>
       </c>
       <c r="E4">
+        <f>index!AE14</f>
         <v>280000</v>
       </c>
       <c r="F4">
+        <f>index!AF14</f>
         <v>63</v>
       </c>
       <c r="G4">
+        <f>index!AG14</f>
         <v>0</v>
       </c>
       <c r="H4">
+        <f>index!AH14</f>
         <v>63</v>
       </c>
     </row>
@@ -2636,21 +3423,27 @@
         <v>42</v>
       </c>
       <c r="C5">
+        <f>index!AC15</f>
         <v>63</v>
       </c>
       <c r="D5">
+        <f>index!AD15</f>
         <v>630000</v>
       </c>
       <c r="E5">
+        <f>index!AE15</f>
         <v>230000</v>
       </c>
       <c r="F5">
+        <f>index!AF15</f>
         <v>63</v>
       </c>
       <c r="G5">
+        <f>index!AG15</f>
         <v>0</v>
       </c>
       <c r="H5">
+        <f>index!AH15</f>
         <v>63</v>
       </c>
     </row>
@@ -2714,28 +3507,38 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
+        <f>index!AN3</f>
         <v>46157</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>90</v>
+      <c r="C2" s="4" t="str">
+        <f>index!AO3</f>
+        <v>PARHAN</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>index!AP3</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E2" s="4">
+        <f>index!AQ3</f>
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>92</v>
+      <c r="F2" s="7" t="str">
+        <f>index!AR3</f>
+        <v>085882744188</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <f>index!AS3</f>
+        <v>355806671171222</v>
       </c>
       <c r="H2" s="8">
+        <f>index!AT3</f>
         <v>410000</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
+      <c r="J2" s="4">
+        <f>index!AV3</f>
+        <v>0</v>
+      </c>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -2743,28 +3546,38 @@
         <v>2</v>
       </c>
       <c r="B3" s="5">
+        <f>index!AN4</f>
         <v>46157</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>90</v>
+      <c r="C3" s="4" t="str">
+        <f>index!AO4</f>
+        <v>ANDI</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f>index!AP4</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E3" s="4">
+        <f>index!AQ4</f>
         <v>1</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>94</v>
+      <c r="F3" s="7" t="str">
+        <f>index!AR4</f>
+        <v>085882744191</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <f>index!AS4</f>
+        <v>355806671185115</v>
       </c>
       <c r="H3" s="8">
+        <f>index!AT4</f>
         <v>410000</v>
       </c>
       <c r="I3" s="5"/>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4">
+        <f>index!AV4</f>
+        <v>0</v>
+      </c>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2772,28 +3585,38 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
+        <f>index!AN5</f>
         <v>46157</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>90</v>
+      <c r="C4" s="4" t="str">
+        <f>index!AO5</f>
+        <v>ENDEN</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f>index!AP5</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E4" s="4">
+        <f>index!AQ5</f>
         <v>1</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>96</v>
+      <c r="F4" s="7" t="str">
+        <f>index!AR5</f>
+        <v>085882744185</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <f>index!AS5</f>
+        <v>355806671171578</v>
       </c>
       <c r="H4" s="8">
+        <f>index!AT5</f>
         <v>410000</v>
       </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="4"/>
+      <c r="J4" s="4">
+        <f>index!AV5</f>
+        <v>0</v>
+      </c>
       <c r="K4" s="5"/>
       <c r="M4" t="s">
         <v>97</v>
@@ -2804,28 +3627,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
+        <f>index!AN6</f>
         <v>46157</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>90</v>
+      <c r="C5" s="4" t="str">
+        <f>index!AO6</f>
+        <v>PEBRIAN</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>index!AP6</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E5" s="4">
+        <f>index!AQ6</f>
         <v>1</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>99</v>
+      <c r="F5" s="7" t="str">
+        <f>index!AR6</f>
+        <v>085882732616</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f>index!AS6</f>
+        <v>355806671128727</v>
       </c>
       <c r="H5" s="8">
+        <f>index!AT6</f>
         <v>410000</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4">
+        <f>index!AV6</f>
+        <v>0</v>
+      </c>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -2833,25 +3666,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>90</v>
+      <c r="C6" s="4" t="str">
+        <f>index!AO7</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f>index!AP7</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E6" s="4">
+        <f>index!AQ7</f>
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="9"/>
+      <c r="F6" s="7" t="str">
+        <f>index!AR7</f>
+        <v>085882732618</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f>index!AS7</f>
+        <v>355806671214105</v>
+      </c>
+      <c r="H6" s="9">
+        <f>index!AT7</f>
+        <v>0</v>
+      </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="4" t="s">
-        <v>103</v>
+      <c r="J6" s="4" t="str">
+        <f>index!AV7</f>
+        <v>SEGEL</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -2860,25 +3702,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>90</v>
+      <c r="C7" s="4" t="str">
+        <f>index!AO8</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f>index!AP8</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E7" s="4">
+        <f>index!AQ8</f>
         <v>1</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="9"/>
+      <c r="F7" s="7" t="str">
+        <f>index!AR8</f>
+        <v>085882732619</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f>index!AS8</f>
+        <v>355806671185537</v>
+      </c>
+      <c r="H7" s="9">
+        <f>index!AT8</f>
+        <v>0</v>
+      </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="4" t="s">
-        <v>103</v>
+      <c r="J7" s="4" t="str">
+        <f>index!AV8</f>
+        <v>SEGEL</v>
       </c>
       <c r="K7" s="5"/>
     </row>
@@ -2887,25 +3738,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>90</v>
+      <c r="C8" s="4" t="str">
+        <f>index!AO9</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D8" s="6" t="str">
+        <f>index!AP9</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E8" s="4">
+        <f>index!AQ9</f>
         <v>1</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="8"/>
+      <c r="F8" s="7" t="str">
+        <f>index!AR9</f>
+        <v>085882732617</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f>index!AS9</f>
+        <v>355806671185602</v>
+      </c>
+      <c r="H8" s="8">
+        <f>index!AT9</f>
+        <v>0</v>
+      </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="4" t="s">
-        <v>103</v>
+      <c r="J8" s="4" t="str">
+        <f>index!AV9</f>
+        <v>SEGEL</v>
       </c>
       <c r="K8" s="5"/>
     </row>
@@ -2914,25 +3774,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>90</v>
+      <c r="C9" s="4" t="str">
+        <f>index!AO10</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D9" s="6" t="str">
+        <f>index!AP10</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E9" s="4">
+        <f>index!AQ10</f>
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="8"/>
+      <c r="F9" s="7" t="str">
+        <f>index!AR10</f>
+        <v>085882732615</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f>index!AS10</f>
+        <v>355806671135482</v>
+      </c>
+      <c r="H9" s="8">
+        <f>index!AT10</f>
+        <v>0</v>
+      </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="4" t="s">
-        <v>103</v>
+      <c r="J9" s="4" t="str">
+        <f>index!AV10</f>
+        <v>SEGEL</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -2941,25 +3810,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>90</v>
+      <c r="C10" s="4" t="str">
+        <f>index!AO11</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f>index!AP11</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E10" s="4">
+        <f>index!AQ11</f>
         <v>1</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="8"/>
+      <c r="F10" s="7" t="str">
+        <f>index!AR11</f>
+        <v>085882732613</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <f>index!AS11</f>
+        <v>355806671185370</v>
+      </c>
+      <c r="H10" s="8">
+        <f>index!AT11</f>
+        <v>0</v>
+      </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="4" t="s">
-        <v>103</v>
+      <c r="J10" s="4" t="str">
+        <f>index!AV11</f>
+        <v>SEGEL</v>
       </c>
       <c r="K10" s="5"/>
     </row>
@@ -2968,25 +3846,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>90</v>
+      <c r="C11" s="4" t="str">
+        <f>index!AO12</f>
+        <v>GUDANG</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f>index!AP12</f>
+        <v>HIFI HKM</v>
       </c>
       <c r="E11" s="4">
+        <f>index!AQ12</f>
         <v>1</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="9"/>
+      <c r="F11" s="7" t="str">
+        <f>index!AR12</f>
+        <v>085882732611</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <f>index!AS12</f>
+        <v>355806671163435</v>
+      </c>
+      <c r="H11" s="9">
+        <f>index!AT12</f>
+        <v>0</v>
+      </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="4" t="s">
-        <v>103</v>
+      <c r="J11" s="4" t="str">
+        <f>index!AV12</f>
+        <v>SEGEL</v>
       </c>
       <c r="K11" s="5"/>
     </row>
@@ -2995,14 +3882,35 @@
         <v>11</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="4">
+        <f>index!AO13</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <f>index!AP13</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f>index!AQ13</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <f>index!AR13</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <f>index!AS13</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <f>index!AT13</f>
+        <v>0</v>
+      </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="4">
+        <f>index!AV13</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -3010,14 +3918,35 @@
         <v>12</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="9"/>
+      <c r="C13" s="4">
+        <f>index!AO14</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>index!AP14</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>index!AQ14</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="7">
+        <f>index!AR14</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <f>index!AS14</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>index!AT14</f>
+        <v>0</v>
+      </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="4">
+        <f>index!AV14</f>
+        <v>0</v>
+      </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -3025,14 +3954,35 @@
         <v>13</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
+      <c r="C14" s="4">
+        <f>index!AO15</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>index!AP15</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>index!AQ15</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="7">
+        <f>index!AR15</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <f>index!AS15</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <f>index!AT15</f>
+        <v>0</v>
+      </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="4">
+        <f>index!AV15</f>
+        <v>0</v>
+      </c>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -3040,14 +3990,35 @@
         <v>14</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="4">
+        <f>index!AO16</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
+        <f>index!AP16</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>index!AQ16</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
+        <f>index!AR16</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <f>index!AS16</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>index!AT16</f>
+        <v>0</v>
+      </c>
       <c r="I15" s="10"/>
-      <c r="J15" s="4"/>
+      <c r="J15" s="4">
+        <f>index!AV16</f>
+        <v>0</v>
+      </c>
       <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -3055,14 +4026,35 @@
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="9"/>
+      <c r="C16" s="4">
+        <f>index!AO17</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <f>index!AP17</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>index!AQ17</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
+        <f>index!AR17</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <f>index!AS17</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <f>index!AT17</f>
+        <v>0</v>
+      </c>
       <c r="I16" s="10"/>
-      <c r="J16" s="4"/>
+      <c r="J16" s="4">
+        <f>index!AV17</f>
+        <v>0</v>
+      </c>
       <c r="K16" s="10"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -3070,14 +4062,35 @@
         <v>16</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="9"/>
+      <c r="C17" s="4">
+        <f>index!AO18</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <f>index!AP18</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <f>index!AQ18</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <f>index!AR18</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <f>index!AS18</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <f>index!AT18</f>
+        <v>0</v>
+      </c>
       <c r="I17" s="10"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="4">
+        <f>index!AV18</f>
+        <v>0</v>
+      </c>
       <c r="K17" s="10"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -3088,4 +4101,2362 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
+  <dimension ref="A1:AW26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" t="s">
+        <v>115</v>
+      </c>
+      <c r="N1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="19"/>
+      <c r="N2" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="31">
+        <v>1</v>
+      </c>
+      <c r="S2" s="31">
+        <v>2</v>
+      </c>
+      <c r="T2" s="31">
+        <v>3</v>
+      </c>
+      <c r="U2" s="31">
+        <v>4</v>
+      </c>
+      <c r="V2" s="31">
+        <v>8</v>
+      </c>
+      <c r="W2" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
+      <c r="N3" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="38">
+        <v>49352400</v>
+      </c>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="35"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="37"/>
+      <c r="AC3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="5">
+        <v>46157</v>
+      </c>
+      <c r="AO3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT3" s="8">
+        <v>410000</v>
+      </c>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="5"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="15">
+        <v>1107</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15">
+        <f>C4+B4</f>
+        <v>1107</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="38">
+        <v>75753400</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" s="38">
+        <f>[1]SUMMARY!B6</f>
+        <v>2</v>
+      </c>
+      <c r="S4" s="38">
+        <f>[1]SUMMARY!C6</f>
+        <v>12</v>
+      </c>
+      <c r="T4" s="38">
+        <f>[1]SUMMARY!D6</f>
+        <v>27</v>
+      </c>
+      <c r="U4" s="38">
+        <f>[1]SUMMARY!E6</f>
+        <v>48</v>
+      </c>
+      <c r="V4" s="38">
+        <v>10</v>
+      </c>
+      <c r="W4" s="38">
+        <f>SUM(R4:V4)</f>
+        <v>99</v>
+      </c>
+      <c r="X4" s="4">
+        <v>11000</v>
+      </c>
+      <c r="Y4" s="38">
+        <f>W4*X4</f>
+        <v>1089000</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC4">
+        <v>275</v>
+      </c>
+      <c r="AD4" s="39">
+        <v>6250000</v>
+      </c>
+      <c r="AE4" s="39">
+        <v>6250000</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG4">
+        <v>25</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>25</v>
+      </c>
+      <c r="AM4" s="4">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="5">
+        <v>46157</v>
+      </c>
+      <c r="AO4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>410000</v>
+      </c>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="4"/>
+      <c r="AW4" s="5"/>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="15">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15">
+        <f t="shared" ref="D5:D22" si="0">C5+B5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="26">
+        <v>84</v>
+      </c>
+      <c r="H5" s="26">
+        <v>0</v>
+      </c>
+      <c r="I5" s="26">
+        <v>23</v>
+      </c>
+      <c r="J5" s="26">
+        <v>119</v>
+      </c>
+      <c r="K5" s="26">
+        <v>22</v>
+      </c>
+      <c r="L5" s="27">
+        <f t="shared" ref="L5:L25" si="1">SUM(G5:K5)</f>
+        <v>248</v>
+      </c>
+      <c r="N5" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="38">
+        <v>59427000</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="38">
+        <f>[1]SUMMARY!B7</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="38">
+        <f>[1]SUMMARY!C7</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="38">
+        <f>[1]SUMMARY!D7</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="38">
+        <f>[1]SUMMARY!E7</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="38">
+        <v>0</v>
+      </c>
+      <c r="W5" s="38">
+        <f t="shared" ref="W5:W22" si="2">SUM(R5:V5)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>30000</v>
+      </c>
+      <c r="Y5" s="38">
+        <f t="shared" ref="Y5:Y22" si="3">W5*X5</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC5">
+        <v>237</v>
+      </c>
+      <c r="AD5" s="39">
+        <v>5585000</v>
+      </c>
+      <c r="AE5" s="39">
+        <v>5585000</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG5">
+        <v>19</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>21</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="5">
+        <v>46157</v>
+      </c>
+      <c r="AO5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS5" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT5" s="8">
+        <v>410000</v>
+      </c>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="4"/>
+      <c r="AW5" s="5"/>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="15">
+        <v>1525</v>
+      </c>
+      <c r="C6" s="16">
+        <v>1526</v>
+      </c>
+      <c r="D6" s="15">
+        <f t="shared" si="0"/>
+        <v>3051</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26">
+        <v>0</v>
+      </c>
+      <c r="I6" s="26">
+        <v>0</v>
+      </c>
+      <c r="J6" s="26">
+        <v>0</v>
+      </c>
+      <c r="K6" s="26">
+        <v>0</v>
+      </c>
+      <c r="L6" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" s="38">
+        <v>72748900</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="38">
+        <f>[1]SUMMARY!B8</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="38">
+        <f>[1]SUMMARY!C8</f>
+        <v>3</v>
+      </c>
+      <c r="T6" s="38">
+        <f>[1]SUMMARY!D8</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="38">
+        <f>[1]SUMMARY!E8</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="38">
+        <v>0</v>
+      </c>
+      <c r="W6" s="38">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="X6" s="4">
+        <v>25000</v>
+      </c>
+      <c r="Y6" s="38">
+        <f t="shared" si="3"/>
+        <v>75000</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC6">
+        <v>286</v>
+      </c>
+      <c r="AD6" s="39">
+        <v>6920000</v>
+      </c>
+      <c r="AE6" s="39">
+        <v>6920000</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG6">
+        <v>26</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>2</v>
+      </c>
+      <c r="AK6">
+        <v>28</v>
+      </c>
+      <c r="AM6" s="4">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="5">
+        <v>46157</v>
+      </c>
+      <c r="AO6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT6" s="8">
+        <v>410000</v>
+      </c>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="4"/>
+      <c r="AW6" s="5"/>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="26">
+        <v>572</v>
+      </c>
+      <c r="H7" s="26">
+        <v>323</v>
+      </c>
+      <c r="I7" s="26">
+        <v>519</v>
+      </c>
+      <c r="J7" s="26">
+        <v>509</v>
+      </c>
+      <c r="K7" s="26">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27">
+        <f t="shared" si="1"/>
+        <v>1933</v>
+      </c>
+      <c r="N7" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="38">
+        <f>SUM(O3:O6)</f>
+        <v>257281700</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="38">
+        <f>[1]SUMMARY!B9</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="38">
+        <f>[1]SUMMARY!C9</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="38">
+        <f>[1]SUMMARY!D9</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="38">
+        <f>[1]SUMMARY!E9</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="38">
+        <v>0</v>
+      </c>
+      <c r="W7" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>30000</v>
+      </c>
+      <c r="Y7" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC7">
+        <v>260</v>
+      </c>
+      <c r="AD7" s="39">
+        <v>5875000</v>
+      </c>
+      <c r="AE7" s="39">
+        <v>5875000</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG7">
+        <v>16</v>
+      </c>
+      <c r="AH7">
+        <v>3</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>19</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>5</v>
+      </c>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP7" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AS7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW7" s="5"/>
+    </row>
+    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26">
+        <v>0</v>
+      </c>
+      <c r="J8" s="26">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26">
+        <v>0</v>
+      </c>
+      <c r="L8" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="38">
+        <f>[1]SUMMARY!B10</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="38">
+        <f>[1]SUMMARY!C10</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="38">
+        <f>[1]SUMMARY!D10</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="38">
+        <f>[1]SUMMARY!E10</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="38">
+        <v>0</v>
+      </c>
+      <c r="W8" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="39">
+        <v>1058</v>
+      </c>
+      <c r="AD8" s="39">
+        <v>24630000</v>
+      </c>
+      <c r="AE8" s="39">
+        <v>24630000</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG8">
+        <v>86</v>
+      </c>
+      <c r="AH8">
+        <v>4</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>3</v>
+      </c>
+      <c r="AK8">
+        <v>93</v>
+      </c>
+      <c r="AM8" s="4">
+        <v>6</v>
+      </c>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AS8" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT8" s="9"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW8" s="5"/>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26">
+        <v>0</v>
+      </c>
+      <c r="H9" s="26">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26">
+        <v>0</v>
+      </c>
+      <c r="J9" s="26">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26">
+        <v>0</v>
+      </c>
+      <c r="L9" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="38">
+        <f>[1]SUMMARY!B11</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="38">
+        <f>[1]SUMMARY!C11</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="38">
+        <f>[1]SUMMARY!D11</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="38">
+        <f>[1]SUMMARY!E11</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="38">
+        <v>0</v>
+      </c>
+      <c r="W9" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>7</v>
+      </c>
+      <c r="AN9" s="5"/>
+      <c r="AO9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT9" s="8"/>
+      <c r="AU9" s="5"/>
+      <c r="AV9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW9" s="5"/>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15">
+        <v>2462</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
+        <f t="shared" si="0"/>
+        <v>2462</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="26">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
+        <v>0</v>
+      </c>
+      <c r="J10" s="26">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0</v>
+      </c>
+      <c r="L10" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="38">
+        <f>[1]SUMMARY!B12</f>
+        <v>110</v>
+      </c>
+      <c r="S10" s="38">
+        <f>[1]SUMMARY!C12</f>
+        <v>369</v>
+      </c>
+      <c r="T10" s="38">
+        <f>[1]SUMMARY!D12</f>
+        <v>30</v>
+      </c>
+      <c r="U10" s="38">
+        <f>[1]SUMMARY!E12</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="38">
+        <v>0</v>
+      </c>
+      <c r="W10" s="38">
+        <f t="shared" si="2"/>
+        <v>509</v>
+      </c>
+      <c r="X10" s="4">
+        <v>600</v>
+      </c>
+      <c r="Y10" s="38">
+        <f t="shared" si="3"/>
+        <v>305400</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM10" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT10" s="8"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW10" s="5"/>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="26">
+        <v>120</v>
+      </c>
+      <c r="H11" s="26">
+        <v>300</v>
+      </c>
+      <c r="I11" s="26">
+        <v>120</v>
+      </c>
+      <c r="J11" s="26">
+        <v>300</v>
+      </c>
+      <c r="K11" s="26">
+        <v>0</v>
+      </c>
+      <c r="L11" s="27">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="Q11" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="38">
+        <f>[1]SUMMARY!B13</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="38">
+        <f>[1]SUMMARY!C13</f>
+        <v>2</v>
+      </c>
+      <c r="T11" s="38">
+        <f>[1]SUMMARY!D13</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="38">
+        <f>[1]SUMMARY!E13</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="38">
+        <v>0</v>
+      </c>
+      <c r="W11" s="38">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="X11" s="4">
+        <v>22500</v>
+      </c>
+      <c r="Y11" s="38">
+        <f t="shared" si="3"/>
+        <v>45000</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM11" s="4">
+        <v>9</v>
+      </c>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AS11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT11" s="8"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW11" s="5"/>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15">
+        <v>80</v>
+      </c>
+      <c r="C12" s="16">
+        <v>976</v>
+      </c>
+      <c r="D12" s="15">
+        <f>C12+B12</f>
+        <v>1056</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="26">
+        <v>5</v>
+      </c>
+      <c r="H12" s="26">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26">
+        <v>4</v>
+      </c>
+      <c r="J12" s="26">
+        <v>4</v>
+      </c>
+      <c r="K12" s="26">
+        <v>0</v>
+      </c>
+      <c r="L12" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="38">
+        <f>[1]SUMMARY!B14</f>
+        <v>254</v>
+      </c>
+      <c r="S12" s="38">
+        <f>[1]SUMMARY!C14</f>
+        <v>342</v>
+      </c>
+      <c r="T12" s="38">
+        <f>[1]SUMMARY!D14</f>
+        <v>233</v>
+      </c>
+      <c r="U12" s="38">
+        <f>[1]SUMMARY!E14</f>
+        <v>212</v>
+      </c>
+      <c r="V12" s="38">
+        <v>0</v>
+      </c>
+      <c r="W12" s="38">
+        <f t="shared" si="2"/>
+        <v>1041</v>
+      </c>
+      <c r="X12" s="4">
+        <v>13200</v>
+      </c>
+      <c r="Y12" s="38">
+        <f t="shared" si="3"/>
+        <v>13741200</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC12">
+        <v>63</v>
+      </c>
+      <c r="AD12">
+        <v>630000</v>
+      </c>
+      <c r="AE12">
+        <v>250000</v>
+      </c>
+      <c r="AF12">
+        <v>63</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>63</v>
+      </c>
+      <c r="AM12" s="4">
+        <v>10</v>
+      </c>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ12" s="4">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT12" s="9"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW12" s="5"/>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="16">
+        <v>300</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="26">
+        <v>52</v>
+      </c>
+      <c r="H13" s="26">
+        <v>47</v>
+      </c>
+      <c r="I13" s="26">
+        <v>36</v>
+      </c>
+      <c r="J13" s="26">
+        <v>102</v>
+      </c>
+      <c r="K13" s="26">
+        <v>21</v>
+      </c>
+      <c r="L13" s="27">
+        <f t="shared" si="1"/>
+        <v>258</v>
+      </c>
+      <c r="Q13" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="38">
+        <f>[1]SUMMARY!B15</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="38">
+        <f>[1]SUMMARY!C15</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="38">
+        <f>[1]SUMMARY!D15</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="38">
+        <f>[1]SUMMARY!E15</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="38">
+        <v>0</v>
+      </c>
+      <c r="W13" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="4">
+        <v>20000</v>
+      </c>
+      <c r="Y13" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC13">
+        <v>63</v>
+      </c>
+      <c r="AD13">
+        <v>630000</v>
+      </c>
+      <c r="AE13">
+        <v>250000</v>
+      </c>
+      <c r="AF13">
+        <v>63</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>63</v>
+      </c>
+      <c r="AM13" s="4">
+        <v>11</v>
+      </c>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="6"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="9"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="4"/>
+      <c r="AW13" s="5"/>
+    </row>
+    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15">
+        <v>42</v>
+      </c>
+      <c r="C14" s="16">
+        <v>457</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" si="0"/>
+        <v>499</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26">
+        <v>0</v>
+      </c>
+      <c r="J14" s="26">
+        <v>0</v>
+      </c>
+      <c r="K14" s="26">
+        <v>0</v>
+      </c>
+      <c r="L14" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14" s="38">
+        <f>[1]SUMMARY!B16</f>
+        <v>21</v>
+      </c>
+      <c r="S14" s="38">
+        <f>[1]SUMMARY!C16</f>
+        <v>19</v>
+      </c>
+      <c r="T14" s="38">
+        <f>[1]SUMMARY!D16</f>
+        <v>45</v>
+      </c>
+      <c r="U14" s="38">
+        <f>[1]SUMMARY!E16</f>
+        <v>43</v>
+      </c>
+      <c r="V14" s="38">
+        <v>0</v>
+      </c>
+      <c r="W14" s="38">
+        <f t="shared" si="2"/>
+        <v>128</v>
+      </c>
+      <c r="X14" s="4">
+        <v>14500</v>
+      </c>
+      <c r="Y14" s="38">
+        <f t="shared" si="3"/>
+        <v>1856000</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC14">
+        <v>63</v>
+      </c>
+      <c r="AD14">
+        <v>630000</v>
+      </c>
+      <c r="AE14">
+        <v>280000</v>
+      </c>
+      <c r="AF14">
+        <v>63</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>63</v>
+      </c>
+      <c r="AM14" s="4">
+        <v>12</v>
+      </c>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="6"/>
+      <c r="AQ14" s="4"/>
+      <c r="AR14" s="7"/>
+      <c r="AS14" s="7"/>
+      <c r="AT14" s="9"/>
+      <c r="AU14" s="5"/>
+      <c r="AV14" s="4"/>
+      <c r="AW14" s="5"/>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="15">
+        <v>198</v>
+      </c>
+      <c r="C15" s="16">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="26">
+        <v>44</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26">
+        <v>19</v>
+      </c>
+      <c r="J15" s="26">
+        <v>72</v>
+      </c>
+      <c r="K15" s="26">
+        <v>0</v>
+      </c>
+      <c r="L15" s="27">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" s="38">
+        <f>[1]SUMMARY!B17</f>
+        <v>52</v>
+      </c>
+      <c r="S15" s="38">
+        <f>[1]SUMMARY!C17</f>
+        <v>144</v>
+      </c>
+      <c r="T15" s="38">
+        <f>[1]SUMMARY!D17</f>
+        <v>75</v>
+      </c>
+      <c r="U15" s="38">
+        <f>[1]SUMMARY!E17</f>
+        <v>33</v>
+      </c>
+      <c r="V15" s="38">
+        <v>0</v>
+      </c>
+      <c r="W15" s="38">
+        <f t="shared" si="2"/>
+        <v>304</v>
+      </c>
+      <c r="X15" s="4">
+        <v>17250</v>
+      </c>
+      <c r="Y15" s="38">
+        <f t="shared" si="3"/>
+        <v>5244000</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC15">
+        <v>63</v>
+      </c>
+      <c r="AD15">
+        <v>630000</v>
+      </c>
+      <c r="AE15">
+        <v>230000</v>
+      </c>
+      <c r="AF15">
+        <v>63</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>63</v>
+      </c>
+      <c r="AM15" s="4">
+        <v>13</v>
+      </c>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="6"/>
+      <c r="AQ15" s="4"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="7"/>
+      <c r="AT15" s="8"/>
+      <c r="AU15" s="5"/>
+      <c r="AV15" s="4"/>
+      <c r="AW15" s="5"/>
+    </row>
+    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="15">
+        <v>165</v>
+      </c>
+      <c r="C16" s="16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="26">
+        <v>99</v>
+      </c>
+      <c r="H16" s="26">
+        <v>36</v>
+      </c>
+      <c r="I16" s="26">
+        <v>40</v>
+      </c>
+      <c r="J16" s="26">
+        <v>101</v>
+      </c>
+      <c r="K16" s="26">
+        <v>21</v>
+      </c>
+      <c r="L16" s="27">
+        <f t="shared" si="1"/>
+        <v>297</v>
+      </c>
+      <c r="Q16" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="38">
+        <f>[1]SUMMARY!B18</f>
+        <v>24</v>
+      </c>
+      <c r="S16" s="38">
+        <f>[1]SUMMARY!C18</f>
+        <v>47</v>
+      </c>
+      <c r="T16" s="38">
+        <f>[1]SUMMARY!D18</f>
+        <v>2</v>
+      </c>
+      <c r="U16" s="38">
+        <f>[1]SUMMARY!E18</f>
+        <v>3</v>
+      </c>
+      <c r="V16" s="38">
+        <v>0</v>
+      </c>
+      <c r="W16" s="38">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="X16" s="4">
+        <v>23000</v>
+      </c>
+      <c r="Y16" s="38">
+        <f t="shared" si="3"/>
+        <v>1748000</v>
+      </c>
+      <c r="AM16" s="4">
+        <v>14</v>
+      </c>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="6"/>
+      <c r="AQ16" s="4"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="7"/>
+      <c r="AT16" s="9"/>
+      <c r="AU16" s="10"/>
+      <c r="AV16" s="4"/>
+      <c r="AW16" s="10"/>
+    </row>
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="15">
+        <v>404</v>
+      </c>
+      <c r="C17" s="16">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
+        <f t="shared" si="0"/>
+        <v>405</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="26">
+        <v>46</v>
+      </c>
+      <c r="H17" s="26">
+        <v>50</v>
+      </c>
+      <c r="I17" s="26">
+        <v>39</v>
+      </c>
+      <c r="J17" s="26">
+        <v>48</v>
+      </c>
+      <c r="K17" s="26">
+        <v>22</v>
+      </c>
+      <c r="L17" s="27">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="R17" s="38">
+        <f>[1]SUMMARY!B19</f>
+        <v>3</v>
+      </c>
+      <c r="S17" s="38">
+        <f>[1]SUMMARY!C19</f>
+        <v>12</v>
+      </c>
+      <c r="T17" s="38">
+        <f>[1]SUMMARY!D19</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="38">
+        <f>[1]SUMMARY!E19</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="38">
+        <v>0</v>
+      </c>
+      <c r="W17" s="38">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="X17" s="4">
+        <v>30000</v>
+      </c>
+      <c r="Y17" s="38">
+        <f t="shared" si="3"/>
+        <v>450000</v>
+      </c>
+      <c r="AM17" s="4">
+        <v>15</v>
+      </c>
+      <c r="AN17" s="5"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="6"/>
+      <c r="AQ17" s="4"/>
+      <c r="AR17" s="7"/>
+      <c r="AS17" s="7"/>
+      <c r="AT17" s="9"/>
+      <c r="AU17" s="10"/>
+      <c r="AV17" s="4"/>
+      <c r="AW17" s="10"/>
+    </row>
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0</v>
+      </c>
+      <c r="C18" s="16">
+        <v>198</v>
+      </c>
+      <c r="D18" s="15">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="26">
+        <v>45</v>
+      </c>
+      <c r="H18" s="26">
+        <v>40</v>
+      </c>
+      <c r="I18" s="26">
+        <v>18</v>
+      </c>
+      <c r="J18" s="26">
+        <v>20</v>
+      </c>
+      <c r="K18" s="26">
+        <v>0</v>
+      </c>
+      <c r="L18" s="27">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="Q18" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="R18" s="38">
+        <f>[1]SUMMARY!B20</f>
+        <v>31</v>
+      </c>
+      <c r="S18" s="38">
+        <f>[1]SUMMARY!C20</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="38">
+        <f>[1]SUMMARY!D20</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="38">
+        <f>[1]SUMMARY!E20</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="38">
+        <v>0</v>
+      </c>
+      <c r="W18" s="38">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="X18" s="4">
+        <v>6900</v>
+      </c>
+      <c r="Y18" s="38">
+        <f t="shared" si="3"/>
+        <v>213900</v>
+      </c>
+      <c r="AM18" s="4">
+        <v>16</v>
+      </c>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="6"/>
+      <c r="AQ18" s="4"/>
+      <c r="AR18" s="7"/>
+      <c r="AS18" s="7"/>
+      <c r="AT18" s="9"/>
+      <c r="AU18" s="10"/>
+      <c r="AV18" s="4"/>
+      <c r="AW18" s="10"/>
+    </row>
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="26">
+        <v>11</v>
+      </c>
+      <c r="H19" s="26">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26">
+        <v>0</v>
+      </c>
+      <c r="J19" s="26">
+        <v>0</v>
+      </c>
+      <c r="K19" s="26">
+        <v>0</v>
+      </c>
+      <c r="L19" s="27">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="Q19" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="38">
+        <f>[1]SUMMARY!B21</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="38">
+        <f>[1]SUMMARY!C21</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="38">
+        <f>[1]SUMMARY!D21</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="38">
+        <f>[1]SUMMARY!E21</f>
+        <v>9</v>
+      </c>
+      <c r="V19" s="38">
+        <v>0</v>
+      </c>
+      <c r="W19" s="38">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="X19" s="4">
+        <v>7000</v>
+      </c>
+      <c r="Y19" s="38">
+        <f t="shared" si="3"/>
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15">
+        <v>0</v>
+      </c>
+      <c r="C20" s="16">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="26">
+        <v>1</v>
+      </c>
+      <c r="H20" s="26">
+        <v>0</v>
+      </c>
+      <c r="I20" s="26">
+        <v>0</v>
+      </c>
+      <c r="J20" s="26">
+        <v>0</v>
+      </c>
+      <c r="K20" s="26">
+        <v>0</v>
+      </c>
+      <c r="L20" s="27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="R20" s="38">
+        <f>[1]SUMMARY!B22</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="38">
+        <f>[1]SUMMARY!C22</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="38">
+        <f>[1]SUMMARY!D22</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="38">
+        <f>[1]SUMMARY!E22</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="38">
+        <v>0</v>
+      </c>
+      <c r="W20" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="4">
+        <v>12000</v>
+      </c>
+      <c r="Y20" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="15">
+        <v>0</v>
+      </c>
+      <c r="C21" s="16">
+        <v>1032</v>
+      </c>
+      <c r="D21" s="15">
+        <f t="shared" si="0"/>
+        <v>1032</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="26">
+        <v>11</v>
+      </c>
+      <c r="H21" s="26">
+        <v>70</v>
+      </c>
+      <c r="I21" s="26">
+        <v>27</v>
+      </c>
+      <c r="J21" s="26">
+        <v>6</v>
+      </c>
+      <c r="K21" s="26">
+        <v>0</v>
+      </c>
+      <c r="L21" s="27">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="Q21" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="38">
+        <f>[1]SUMMARY!B23</f>
+        <v>75</v>
+      </c>
+      <c r="S21" s="38">
+        <f>[1]SUMMARY!C23</f>
+        <v>65</v>
+      </c>
+      <c r="T21" s="38">
+        <f>[1]SUMMARY!D23</f>
+        <v>33</v>
+      </c>
+      <c r="U21" s="38">
+        <f>[1]SUMMARY!E23</f>
+        <v>15</v>
+      </c>
+      <c r="V21" s="38">
+        <v>0</v>
+      </c>
+      <c r="W21" s="38">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+      <c r="X21" s="4">
+        <v>9600</v>
+      </c>
+      <c r="Y21" s="38">
+        <f t="shared" si="3"/>
+        <v>1804800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A22" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="15">
+        <v>72</v>
+      </c>
+      <c r="C22" s="16">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="26">
+        <v>132</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26">
+        <v>91</v>
+      </c>
+      <c r="J22" s="26">
+        <v>65</v>
+      </c>
+      <c r="K22" s="26">
+        <v>12</v>
+      </c>
+      <c r="L22" s="27">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="Q22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="38">
+        <f>[1]SUMMARY!B24</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="38">
+        <f>[1]SUMMARY!C24</f>
+        <v>0</v>
+      </c>
+      <c r="T22" s="38">
+        <f>[1]SUMMARY!D24</f>
+        <v>0</v>
+      </c>
+      <c r="U22" s="38">
+        <f>[1]SUMMARY!E24</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="38">
+        <v>0</v>
+      </c>
+      <c r="W22" s="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="4">
+        <v>13200</v>
+      </c>
+      <c r="Y22" s="38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="F23" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="26">
+        <v>10</v>
+      </c>
+      <c r="H23" s="26">
+        <v>4</v>
+      </c>
+      <c r="I23" s="26">
+        <v>4</v>
+      </c>
+      <c r="J23" s="26">
+        <v>55</v>
+      </c>
+      <c r="K23" s="26">
+        <v>9</v>
+      </c>
+      <c r="L23" s="27">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="38">
+        <v>0</v>
+      </c>
+      <c r="S23" s="38">
+        <v>0</v>
+      </c>
+      <c r="T23" s="38">
+        <v>0</v>
+      </c>
+      <c r="U23" s="38">
+        <v>0</v>
+      </c>
+      <c r="V23" s="38">
+        <v>0</v>
+      </c>
+      <c r="W23" s="38">
+        <v>0</v>
+      </c>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="F24" s="25"/>
+      <c r="G24" s="26">
+        <v>0</v>
+      </c>
+      <c r="H24" s="26">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26">
+        <v>0</v>
+      </c>
+      <c r="J24" s="26">
+        <v>0</v>
+      </c>
+      <c r="K24" s="26">
+        <v>0</v>
+      </c>
+      <c r="L24" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="38">
+        <v>0</v>
+      </c>
+      <c r="S24" s="38">
+        <v>0</v>
+      </c>
+      <c r="T24" s="38">
+        <v>0</v>
+      </c>
+      <c r="U24" s="38">
+        <v>0</v>
+      </c>
+      <c r="V24" s="38">
+        <v>0</v>
+      </c>
+      <c r="W24" s="38">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="F25" s="25"/>
+      <c r="G25" s="26">
+        <v>0</v>
+      </c>
+      <c r="H25" s="26">
+        <v>0</v>
+      </c>
+      <c r="I25" s="26">
+        <v>0</v>
+      </c>
+      <c r="J25" s="26">
+        <v>0</v>
+      </c>
+      <c r="K25" s="26">
+        <v>0</v>
+      </c>
+      <c r="L25" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="R25" s="24">
+        <f>SUM(R4:R24)</f>
+        <v>572</v>
+      </c>
+      <c r="S25" s="24">
+        <f t="shared" ref="S25:Y25" si="4">SUM(S4:S24)</f>
+        <v>1015</v>
+      </c>
+      <c r="T25" s="24">
+        <f t="shared" si="4"/>
+        <v>445</v>
+      </c>
+      <c r="U25" s="24">
+        <f t="shared" si="4"/>
+        <v>363</v>
+      </c>
+      <c r="V25" s="24">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="W25" s="24">
+        <f t="shared" si="4"/>
+        <v>2405</v>
+      </c>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24">
+        <f t="shared" si="4"/>
+        <v>26635300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="F26" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="29">
+        <f t="shared" ref="G26:L26" si="5">SUM(G5:G25)</f>
+        <v>1232</v>
+      </c>
+      <c r="H26" s="29">
+        <f t="shared" si="5"/>
+        <v>870</v>
+      </c>
+      <c r="I26" s="29">
+        <f t="shared" si="5"/>
+        <v>940</v>
+      </c>
+      <c r="J26" s="29">
+        <f t="shared" si="5"/>
+        <v>1401</v>
+      </c>
+      <c r="K26" s="29">
+        <f t="shared" si="5"/>
+        <v>117</v>
+      </c>
+      <c r="L26" s="29">
+        <f t="shared" si="5"/>
+        <v>4560</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="W2:W3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="AF4:AI7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ4:AJ7">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7A2EB4-9A5E-4836-B430-91F010AEEDFA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,21 @@
   <externalReferences>
     <externalReference r:id="rId9"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -414,12 +422,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -637,8 +645,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="43">
@@ -651,21 +659,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -673,16 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -698,28 +691,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -727,16 +702,49 @@
     <xf numFmtId="168" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -1112,9 +1120,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1152,7 +1160,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1258,7 +1266,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1400,7 +1408,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1409,15 +1417,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1431,7 +1439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1448,7 +1456,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1465,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1482,7 +1490,7 @@
         <v>3051</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1499,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1513,7 +1521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1527,7 +1535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1552,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1561,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1578,7 +1586,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1612,7 +1620,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1629,7 +1637,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1646,7 +1654,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1663,7 +1671,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1680,7 +1688,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1697,7 +1705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1714,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1731,7 +1739,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1756,18 +1764,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1790,7 +1798,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1815,7 +1823,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1840,7 +1848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1865,7 +1873,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1890,7 +1898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1912,7 +1920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1934,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1984,7 +1992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -2009,7 +2017,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -2034,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2059,7 +2067,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -2084,7 +2092,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -2109,7 +2117,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2134,7 +2142,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2159,7 +2167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2184,7 +2192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2209,7 +2217,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2234,7 +2242,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2259,7 +2267,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -2280,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -2301,7 +2309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2333,13 +2341,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2347,7 +2355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -2356,7 +2364,7 @@
         <v>49352400</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2365,7 +2373,7 @@
         <v>75753400</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -2374,7 +2382,7 @@
         <v>59427000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2383,7 +2391,7 @@
         <v>72748900</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2400,17 +2408,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -2436,7 +2444,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>51</v>
       </c>
@@ -2450,7 +2458,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2467,16 +2475,18 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>96</v>
+        <f>SUM(B3:E3)</f>
+        <v>86</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
-        <v>1056000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <f>F3*G3</f>
+        <v>946000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2493,16 +2503,18 @@
         <v>0</v>
       </c>
       <c r="F4">
+        <f t="shared" ref="F4:F23" si="0">SUM(B4:E4)</f>
         <v>0</v>
       </c>
       <c r="G4">
         <v>30000</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H4:H23" si="1">F4*G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -2519,16 +2531,18 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G5">
         <v>25000</v>
       </c>
       <c r="H5">
+        <f t="shared" si="1"/>
         <v>75000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2545,16 +2559,18 @@
         <v>0</v>
       </c>
       <c r="F6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G6">
         <v>30000</v>
       </c>
       <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>0</v>
       </c>
@@ -2568,13 +2584,15 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>0</v>
       </c>
@@ -2588,13 +2606,15 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2611,16 +2631,18 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <f t="shared" si="0"/>
         <v>509</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
+        <f t="shared" si="1"/>
         <v>305400</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2637,16 +2659,18 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G10">
         <v>22500</v>
       </c>
       <c r="H10">
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2663,16 +2687,18 @@
         <v>212</v>
       </c>
       <c r="F11">
+        <f t="shared" si="0"/>
         <v>1026</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
+        <f t="shared" si="1"/>
         <v>13543200</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2689,16 +2715,18 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G12">
         <v>20000</v>
       </c>
       <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2715,16 +2743,18 @@
         <v>43</v>
       </c>
       <c r="F13">
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
+        <f t="shared" si="1"/>
         <v>1711000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2741,16 +2771,18 @@
         <v>28</v>
       </c>
       <c r="F14">
+        <f t="shared" si="0"/>
         <v>279</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
+        <f t="shared" si="1"/>
         <v>4812750</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2767,16 +2799,18 @@
         <v>3</v>
       </c>
       <c r="F15">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
+        <f t="shared" si="1"/>
         <v>1748000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2793,16 +2827,18 @@
         <v>0</v>
       </c>
       <c r="F16">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
+        <f t="shared" si="1"/>
         <v>450000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2819,16 +2855,18 @@
         <v>0</v>
       </c>
       <c r="F17">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
+        <f t="shared" si="1"/>
         <v>213900</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2845,16 +2883,18 @@
         <v>9</v>
       </c>
       <c r="F18">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="G18">
         <v>7000</v>
       </c>
       <c r="H18">
+        <f t="shared" si="1"/>
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2871,16 +2911,18 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2897,16 +2939,18 @@
         <v>9</v>
       </c>
       <c r="F20">
+        <f t="shared" si="0"/>
         <v>172</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
+        <f t="shared" si="1"/>
         <v>1651200</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2923,16 +2967,18 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G21">
         <v>13200</v>
       </c>
       <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>0</v>
       </c>
@@ -2946,13 +2992,15 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>0</v>
       </c>
@@ -2966,33 +3014,41 @@
         <v>0</v>
       </c>
       <c r="F23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24">
+        <f t="shared" ref="B24:G24" si="2">SUM(B3:B23)</f>
         <v>562</v>
       </c>
       <c r="C24">
+        <f t="shared" si="2"/>
         <v>980</v>
       </c>
       <c r="D24">
+        <f t="shared" si="2"/>
         <v>432</v>
       </c>
       <c r="E24">
+        <f t="shared" si="2"/>
         <v>352</v>
       </c>
       <c r="F24">
-        <v>2336</v>
+        <f t="shared" si="2"/>
+        <v>2326</v>
       </c>
       <c r="H24">
-        <v>25674450</v>
+        <f>SUM(H3:H23)</f>
+        <v>25564450</v>
       </c>
     </row>
   </sheetData>
@@ -3003,20 +3059,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -3030,7 +3086,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>59</v>
       </c>
@@ -3059,7 +3115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -3070,15 +3126,15 @@
         <f>index!AC4</f>
         <v>275</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="28">
         <f>index!AD4</f>
         <v>6250000</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="28">
         <f>index!AE4</f>
         <v>6250000</v>
       </c>
-      <c r="F3" s="39" t="str">
+      <c r="F3" s="28" t="str">
         <f>index!AF4</f>
         <v xml:space="preserve"> -   </v>
       </c>
@@ -3103,7 +3159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -3114,15 +3170,15 @@
         <f>index!AC5</f>
         <v>237</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="28">
         <f>index!AD5</f>
         <v>5585000</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="28">
         <f>index!AE5</f>
         <v>5585000</v>
       </c>
-      <c r="F4" s="39" t="str">
+      <c r="F4" s="28" t="str">
         <f>index!AF5</f>
         <v xml:space="preserve"> -   </v>
       </c>
@@ -3147,7 +3203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -3158,15 +3214,15 @@
         <f>index!AC6</f>
         <v>286</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="28">
         <f>index!AD6</f>
         <v>6920000</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="28">
         <f>index!AE6</f>
         <v>6920000</v>
       </c>
-      <c r="F5" s="39" t="str">
+      <c r="F5" s="28" t="str">
         <f>index!AF6</f>
         <v xml:space="preserve"> -   </v>
       </c>
@@ -3191,7 +3247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3202,15 +3258,15 @@
         <f>index!AC7</f>
         <v>260</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="28">
         <f>index!AD7</f>
         <v>5875000</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="28">
         <f>index!AE7</f>
         <v>5875000</v>
       </c>
-      <c r="F6" s="39" t="str">
+      <c r="F6" s="28" t="str">
         <f>index!AF7</f>
         <v xml:space="preserve"> -   </v>
       </c>
@@ -3235,16 +3291,16 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C7" s="39">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
         <v>1058</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="28">
         <f t="shared" ref="D7:F7" si="1">SUM(D3:D6)</f>
         <v>24630000</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="28">
         <f t="shared" si="1"/>
         <v>24630000</v>
       </c>
@@ -3280,20 +3336,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -3319,7 +3375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -3335,8 +3391,7 @@
         <v>630000</v>
       </c>
       <c r="E2">
-        <f>index!AE12</f>
-        <v>250000</v>
+        <v>630000</v>
       </c>
       <c r="F2">
         <f>index!AF12</f>
@@ -3351,7 +3406,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -3367,8 +3422,7 @@
         <v>630000</v>
       </c>
       <c r="E3">
-        <f>index!AE13</f>
-        <v>250000</v>
+        <v>630000</v>
       </c>
       <c r="F3">
         <f>index!AF13</f>
@@ -3383,7 +3437,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -3399,8 +3453,7 @@
         <v>630000</v>
       </c>
       <c r="E4">
-        <f>index!AE14</f>
-        <v>280000</v>
+        <v>630000</v>
       </c>
       <c r="F4">
         <f>index!AF14</f>
@@ -3415,7 +3468,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -3431,8 +3484,7 @@
         <v>630000</v>
       </c>
       <c r="E5">
-        <f>index!AE15</f>
-        <v>230000</v>
+        <v>630000</v>
       </c>
       <c r="F5">
         <f>index!AF15</f>
@@ -3445,6 +3497,32 @@
       <c r="H5">
         <f>index!AH15</f>
         <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <f>SUM(C2:C5)</f>
+        <v>252</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:H6" si="0">SUM(D2:D5)</f>
+        <v>2520000</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>2520000</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3455,19 +3533,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.87109375" customWidth="1"/>
+    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -3502,7 +3580,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3534,14 +3612,17 @@
         <f>index!AT3</f>
         <v>410000</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5">
+        <f>index!AU3</f>
+        <v>46158</v>
+      </c>
       <c r="J2" s="4">
         <f>index!AV3</f>
         <v>0</v>
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3580,7 +3661,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3622,7 +3703,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3661,7 +3742,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3697,7 +3778,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3733,7 +3814,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3769,7 +3850,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3805,7 +3886,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3841,7 +3922,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3877,7 +3958,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3913,7 +3994,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3949,7 +4030,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3985,7 +4066,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -4021,7 +4102,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -4057,7 +4138,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -4093,7 +4174,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>97</v>
       </c>
@@ -4106,13 +4187,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>114</v>
       </c>
@@ -4132,56 +4214,56 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19"/>
-      <c r="N2" s="40" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="40"/>
+      <c r="N2" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="41" t="s">
+      <c r="O2" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="Q2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="31">
+      <c r="R2" s="26">
         <v>1</v>
       </c>
-      <c r="S2" s="31">
+      <c r="S2" s="26">
         <v>2</v>
       </c>
-      <c r="T2" s="31">
+      <c r="T2" s="26">
         <v>3</v>
       </c>
-      <c r="U2" s="31">
+      <c r="U2" s="26">
         <v>4</v>
       </c>
-      <c r="V2" s="31">
+      <c r="V2" s="26">
         <v>8</v>
       </c>
-      <c r="W2" s="32" t="s">
+      <c r="W2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="33" t="s">
+      <c r="X2" s="32" t="s">
         <v>49</v>
       </c>
       <c r="Y2" s="34" t="s">
@@ -4233,43 +4315,43 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23"/>
-      <c r="N3" s="42" t="s">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18"/>
+      <c r="N3" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3" s="27">
         <v>49352400</v>
       </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="31" t="s">
+      <c r="Q3" s="25"/>
+      <c r="R3" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="31" t="s">
+      <c r="S3" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="T3" s="31" t="s">
+      <c r="T3" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="V3" s="31" t="s">
+      <c r="V3" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="35"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="37"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="35"/>
       <c r="AC3" t="s">
         <v>59</v>
       </c>
@@ -4321,25 +4403,27 @@
       <c r="AT3" s="8">
         <v>410000</v>
       </c>
-      <c r="AU3" s="5"/>
+      <c r="AU3" s="5">
+        <v>46158</v>
+      </c>
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>1107</v>
       </c>
-      <c r="C4" s="16">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="14">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
         <f>C4+B4</f>
         <v>1107</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="19" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -4360,42 +4444,42 @@
       <c r="L4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="N4" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="27">
         <v>75753400</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="27">
         <f>[1]SUMMARY!B6</f>
         <v>2</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="27">
         <f>[1]SUMMARY!C6</f>
         <v>12</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="27">
         <f>[1]SUMMARY!D6</f>
         <v>27</v>
       </c>
-      <c r="U4" s="38">
+      <c r="U4" s="27">
         <f>[1]SUMMARY!E6</f>
         <v>48</v>
       </c>
-      <c r="V4" s="38">
+      <c r="V4" s="27">
         <v>10</v>
       </c>
-      <c r="W4" s="38">
+      <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
         <v>99</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
-      <c r="Y4" s="38">
+      <c r="Y4" s="27">
         <f>W4*X4</f>
         <v>1089000</v>
       </c>
@@ -4408,10 +4492,10 @@
       <c r="AC4">
         <v>275</v>
       </c>
-      <c r="AD4" s="39">
+      <c r="AD4" s="28">
         <v>6250000</v>
       </c>
-      <c r="AE4" s="39">
+      <c r="AE4" s="28">
         <v>6250000</v>
       </c>
       <c r="AF4" t="s">
@@ -4460,78 +4544,78 @@
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15">
-        <v>0</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="B5" s="13">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
         <f t="shared" ref="D5:D22" si="0">C5+B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="21">
         <v>84</v>
       </c>
-      <c r="H5" s="26">
-        <v>0</v>
-      </c>
-      <c r="I5" s="26">
+      <c r="H5" s="21">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21">
         <v>23</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="21">
         <v>119</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="21">
         <v>22</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="22">
         <f t="shared" ref="L5:L25" si="1">SUM(G5:K5)</f>
         <v>248</v>
       </c>
-      <c r="N5" s="42" t="s">
+      <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5" s="27">
         <v>59427000</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="27">
         <f>[1]SUMMARY!B7</f>
         <v>0</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="27">
         <f>[1]SUMMARY!C7</f>
         <v>0</v>
       </c>
-      <c r="T5" s="38">
+      <c r="T5" s="27">
         <f>[1]SUMMARY!D7</f>
         <v>0</v>
       </c>
-      <c r="U5" s="38">
+      <c r="U5" s="27">
         <f>[1]SUMMARY!E7</f>
         <v>0</v>
       </c>
-      <c r="V5" s="38">
-        <v>0</v>
-      </c>
-      <c r="W5" s="38">
+      <c r="V5" s="27">
+        <v>0</v>
+      </c>
+      <c r="W5" s="27">
         <f t="shared" ref="W5:W22" si="2">SUM(R5:V5)</f>
         <v>0</v>
       </c>
       <c r="X5" s="4">
         <v>30000</v>
       </c>
-      <c r="Y5" s="38">
+      <c r="Y5" s="27">
         <f t="shared" ref="Y5:Y22" si="3">W5*X5</f>
         <v>0</v>
       </c>
@@ -4544,10 +4628,10 @@
       <c r="AC5">
         <v>237</v>
       </c>
-      <c r="AD5" s="39">
+      <c r="AD5" s="28">
         <v>5585000</v>
       </c>
-      <c r="AE5" s="39">
+      <c r="AE5" s="28">
         <v>5585000</v>
       </c>
       <c r="AF5" t="s">
@@ -4596,78 +4680,78 @@
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="13">
         <v>1525</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="14">
         <v>1526</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <f t="shared" si="0"/>
         <v>3051</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="26">
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>0</v>
-      </c>
-      <c r="I6" s="26">
-        <v>0</v>
-      </c>
-      <c r="J6" s="26">
-        <v>0</v>
-      </c>
-      <c r="K6" s="26">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27">
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21">
+        <v>0</v>
+      </c>
+      <c r="K6" s="21">
+        <v>0</v>
+      </c>
+      <c r="L6" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6" s="27">
         <v>72748900</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="27">
         <f>[1]SUMMARY!B8</f>
         <v>0</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="27">
         <f>[1]SUMMARY!C8</f>
         <v>3</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="27">
         <f>[1]SUMMARY!D8</f>
         <v>0</v>
       </c>
-      <c r="U6" s="38">
+      <c r="U6" s="27">
         <f>[1]SUMMARY!E8</f>
         <v>0</v>
       </c>
-      <c r="V6" s="38">
-        <v>0</v>
-      </c>
-      <c r="W6" s="38">
+      <c r="V6" s="27">
+        <v>0</v>
+      </c>
+      <c r="W6" s="27">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
-      <c r="Y6" s="38">
+      <c r="Y6" s="27">
         <f t="shared" si="3"/>
         <v>75000</v>
       </c>
@@ -4680,10 +4764,10 @@
       <c r="AC6">
         <v>286</v>
       </c>
-      <c r="AD6" s="39">
+      <c r="AD6" s="28">
         <v>6920000</v>
       </c>
-      <c r="AE6" s="39">
+      <c r="AE6" s="28">
         <v>6920000</v>
       </c>
       <c r="AF6" t="s">
@@ -4732,79 +4816,79 @@
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="15">
-        <v>0</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="25" t="s">
+      <c r="B7" s="13">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="21">
         <v>572</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="21">
         <v>323</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="21">
         <v>519</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="21">
         <v>509</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="21">
         <v>10</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="22">
         <f t="shared" si="1"/>
         <v>1933</v>
       </c>
-      <c r="N7" s="42" t="s">
+      <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
         <v>257281700</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="27">
         <f>[1]SUMMARY!B9</f>
         <v>0</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="27">
         <f>[1]SUMMARY!C9</f>
         <v>0</v>
       </c>
-      <c r="T7" s="38">
+      <c r="T7" s="27">
         <f>[1]SUMMARY!D9</f>
         <v>0</v>
       </c>
-      <c r="U7" s="38">
+      <c r="U7" s="27">
         <f>[1]SUMMARY!E9</f>
         <v>0</v>
       </c>
-      <c r="V7" s="38">
-        <v>0</v>
-      </c>
-      <c r="W7" s="38">
+      <c r="V7" s="27">
+        <v>0</v>
+      </c>
+      <c r="W7" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X7" s="4">
         <v>30000</v>
       </c>
-      <c r="Y7" s="38">
+      <c r="Y7" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4817,10 +4901,10 @@
       <c r="AC7">
         <v>260</v>
       </c>
-      <c r="AD7" s="39">
+      <c r="AD7" s="28">
         <v>5875000</v>
       </c>
-      <c r="AE7" s="39">
+      <c r="AE7" s="28">
         <v>5875000</v>
       </c>
       <c r="AF7" t="s">
@@ -4867,76 +4951,76 @@
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15">
-        <v>0</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="25" t="s">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="26">
-        <v>0</v>
-      </c>
-      <c r="H8" s="26">
-        <v>0</v>
-      </c>
-      <c r="I8" s="26">
-        <v>0</v>
-      </c>
-      <c r="J8" s="26">
-        <v>0</v>
-      </c>
-      <c r="K8" s="26">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27">
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>0</v>
+      </c>
+      <c r="L8" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="38">
+      <c r="Q8" s="23"/>
+      <c r="R8" s="27">
         <f>[1]SUMMARY!B10</f>
         <v>0</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="27">
         <f>[1]SUMMARY!C10</f>
         <v>0</v>
       </c>
-      <c r="T8" s="38">
+      <c r="T8" s="27">
         <f>[1]SUMMARY!D10</f>
         <v>0</v>
       </c>
-      <c r="U8" s="38">
+      <c r="U8" s="27">
         <f>[1]SUMMARY!E10</f>
         <v>0</v>
       </c>
-      <c r="V8" s="38">
-        <v>0</v>
-      </c>
-      <c r="W8" s="38">
+      <c r="V8" s="27">
+        <v>0</v>
+      </c>
+      <c r="W8" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="38">
+      <c r="X8" s="19"/>
+      <c r="Y8" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC8" s="39">
+      <c r="AC8" s="28">
         <v>1058</v>
       </c>
-      <c r="AD8" s="39">
+      <c r="AD8" s="28">
         <v>24630000</v>
       </c>
-      <c r="AE8" s="39">
+      <c r="AE8" s="28">
         <v>24630000</v>
       </c>
       <c r="AF8" t="s">
@@ -4983,64 +5067,64 @@
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26">
-        <v>0</v>
-      </c>
-      <c r="H9" s="26">
-        <v>0</v>
-      </c>
-      <c r="I9" s="26">
-        <v>0</v>
-      </c>
-      <c r="J9" s="26">
-        <v>0</v>
-      </c>
-      <c r="K9" s="26">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21">
+        <v>0</v>
+      </c>
+      <c r="K9" s="21">
+        <v>0</v>
+      </c>
+      <c r="L9" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="38">
+      <c r="Q9" s="20"/>
+      <c r="R9" s="27">
         <f>[1]SUMMARY!B11</f>
         <v>0</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="27">
         <f>[1]SUMMARY!C11</f>
         <v>0</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="27">
         <f>[1]SUMMARY!D11</f>
         <v>0</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="27">
         <f>[1]SUMMARY!E11</f>
         <v>0</v>
       </c>
-      <c r="V9" s="38">
-        <v>0</v>
-      </c>
-      <c r="W9" s="38">
+      <c r="V9" s="27">
+        <v>0</v>
+      </c>
+      <c r="W9" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X9" s="4"/>
-      <c r="Y9" s="38">
+      <c r="Y9" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5070,70 +5154,70 @@
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <v>2462</v>
       </c>
-      <c r="C10" s="16">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
         <f t="shared" si="0"/>
         <v>2462</v>
       </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="26">
-        <v>0</v>
-      </c>
-      <c r="H10" s="26">
-        <v>0</v>
-      </c>
-      <c r="I10" s="26">
-        <v>0</v>
-      </c>
-      <c r="J10" s="26">
-        <v>0</v>
-      </c>
-      <c r="K10" s="26">
-        <v>0</v>
-      </c>
-      <c r="L10" s="27">
+      <c r="F10" s="23"/>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0</v>
+      </c>
+      <c r="K10" s="21">
+        <v>0</v>
+      </c>
+      <c r="L10" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="25" t="s">
+      <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="27">
         <f>[1]SUMMARY!B12</f>
         <v>110</v>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="27">
         <f>[1]SUMMARY!C12</f>
         <v>369</v>
       </c>
-      <c r="T10" s="38">
+      <c r="T10" s="27">
         <f>[1]SUMMARY!D12</f>
         <v>30</v>
       </c>
-      <c r="U10" s="38">
+      <c r="U10" s="27">
         <f>[1]SUMMARY!E12</f>
         <v>0</v>
       </c>
-      <c r="V10" s="38">
-        <v>0</v>
-      </c>
-      <c r="W10" s="38">
+      <c r="V10" s="27">
+        <v>0</v>
+      </c>
+      <c r="W10" s="27">
         <f t="shared" si="2"/>
         <v>509</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
-      <c r="Y10" s="38">
+      <c r="Y10" s="27">
         <f t="shared" si="3"/>
         <v>305400</v>
       </c>
@@ -5166,72 +5250,72 @@
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
-        <v>0</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="B11" s="13">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14">
         <v>1</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="21">
         <v>120</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="21">
         <v>300</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="21">
         <v>120</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="21">
         <v>300</v>
       </c>
-      <c r="K11" s="26">
-        <v>0</v>
-      </c>
-      <c r="L11" s="27">
+      <c r="K11" s="21">
+        <v>0</v>
+      </c>
+      <c r="L11" s="22">
         <f t="shared" si="1"/>
         <v>840</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="Q11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="27">
         <f>[1]SUMMARY!B13</f>
         <v>0</v>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="27">
         <f>[1]SUMMARY!C13</f>
         <v>2</v>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="27">
         <f>[1]SUMMARY!D13</f>
         <v>0</v>
       </c>
-      <c r="U11" s="38">
+      <c r="U11" s="27">
         <f>[1]SUMMARY!E13</f>
         <v>0</v>
       </c>
-      <c r="V11" s="38">
-        <v>0</v>
-      </c>
-      <c r="W11" s="38">
+      <c r="V11" s="27">
+        <v>0</v>
+      </c>
+      <c r="W11" s="27">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="X11" s="4">
         <v>22500</v>
       </c>
-      <c r="Y11" s="38">
+      <c r="Y11" s="27">
         <f t="shared" si="3"/>
         <v>45000</v>
       </c>
@@ -5285,72 +5369,72 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="13">
         <v>80</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <v>976</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="13">
         <f>C12+B12</f>
         <v>1056</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="26">
-        <v>0</v>
-      </c>
-      <c r="I12" s="26">
+      <c r="H12" s="21">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21">
         <v>4</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="21">
         <v>4</v>
       </c>
-      <c r="K12" s="26">
-        <v>0</v>
-      </c>
-      <c r="L12" s="27">
+      <c r="K12" s="21">
+        <v>0</v>
+      </c>
+      <c r="L12" s="22">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="27">
         <f>[1]SUMMARY!B14</f>
         <v>254</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="27">
         <f>[1]SUMMARY!C14</f>
         <v>342</v>
       </c>
-      <c r="T12" s="38">
+      <c r="T12" s="27">
         <f>[1]SUMMARY!D14</f>
         <v>233</v>
       </c>
-      <c r="U12" s="38">
+      <c r="U12" s="27">
         <f>[1]SUMMARY!E14</f>
         <v>212</v>
       </c>
-      <c r="V12" s="38">
-        <v>0</v>
-      </c>
-      <c r="W12" s="38">
+      <c r="V12" s="27">
+        <v>0</v>
+      </c>
+      <c r="W12" s="27">
         <f t="shared" si="2"/>
         <v>1041</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
-      <c r="Y12" s="38">
+      <c r="Y12" s="27">
         <f t="shared" si="3"/>
         <v>13741200</v>
       </c>
@@ -5404,72 +5488,72 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="15">
-        <v>0</v>
-      </c>
-      <c r="C13" s="16">
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14">
         <v>300</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="21">
         <v>52</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="21">
         <v>47</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="21">
         <v>36</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="21">
         <v>102</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="21">
         <v>21</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="22">
         <f t="shared" si="1"/>
         <v>258</v>
       </c>
-      <c r="Q13" s="25" t="s">
+      <c r="Q13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="R13" s="38">
+      <c r="R13" s="27">
         <f>[1]SUMMARY!B15</f>
         <v>0</v>
       </c>
-      <c r="S13" s="38">
+      <c r="S13" s="27">
         <f>[1]SUMMARY!C15</f>
         <v>0</v>
       </c>
-      <c r="T13" s="38">
+      <c r="T13" s="27">
         <f>[1]SUMMARY!D15</f>
         <v>0</v>
       </c>
-      <c r="U13" s="38">
+      <c r="U13" s="27">
         <f>[1]SUMMARY!E15</f>
         <v>0</v>
       </c>
-      <c r="V13" s="38">
-        <v>0</v>
-      </c>
-      <c r="W13" s="38">
+      <c r="V13" s="27">
+        <v>0</v>
+      </c>
+      <c r="W13" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
         <v>20000</v>
       </c>
-      <c r="Y13" s="38">
+      <c r="Y13" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5511,72 +5595,72 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="13">
         <v>42</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <v>457</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <f t="shared" si="0"/>
         <v>499</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="26">
-        <v>0</v>
-      </c>
-      <c r="H14" s="26">
-        <v>0</v>
-      </c>
-      <c r="I14" s="26">
-        <v>0</v>
-      </c>
-      <c r="J14" s="26">
-        <v>0</v>
-      </c>
-      <c r="K14" s="26">
-        <v>0</v>
-      </c>
-      <c r="L14" s="27">
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21">
+        <v>0</v>
+      </c>
+      <c r="L14" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="25" t="s">
+      <c r="Q14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="27">
         <f>[1]SUMMARY!B16</f>
         <v>21</v>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="27">
         <f>[1]SUMMARY!C16</f>
         <v>19</v>
       </c>
-      <c r="T14" s="38">
+      <c r="T14" s="27">
         <f>[1]SUMMARY!D16</f>
         <v>45</v>
       </c>
-      <c r="U14" s="38">
+      <c r="U14" s="27">
         <f>[1]SUMMARY!E16</f>
         <v>43</v>
       </c>
-      <c r="V14" s="38">
-        <v>0</v>
-      </c>
-      <c r="W14" s="38">
+      <c r="V14" s="27">
+        <v>0</v>
+      </c>
+      <c r="W14" s="27">
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
-      <c r="Y14" s="38">
+      <c r="Y14" s="27">
         <f t="shared" si="3"/>
         <v>1856000</v>
       </c>
@@ -5618,72 +5702,72 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="13">
         <v>198</v>
       </c>
-      <c r="C15" s="16">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
         <f t="shared" si="0"/>
         <v>198</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="21">
         <v>44</v>
       </c>
-      <c r="H15" s="26">
-        <v>0</v>
-      </c>
-      <c r="I15" s="26">
+      <c r="H15" s="21">
+        <v>0</v>
+      </c>
+      <c r="I15" s="21">
         <v>19</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="21">
         <v>72</v>
       </c>
-      <c r="K15" s="26">
-        <v>0</v>
-      </c>
-      <c r="L15" s="27">
+      <c r="K15" s="21">
+        <v>0</v>
+      </c>
+      <c r="L15" s="22">
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
-      <c r="Q15" s="25" t="s">
+      <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="R15" s="38">
+      <c r="R15" s="27">
         <f>[1]SUMMARY!B17</f>
         <v>52</v>
       </c>
-      <c r="S15" s="38">
+      <c r="S15" s="27">
         <f>[1]SUMMARY!C17</f>
         <v>144</v>
       </c>
-      <c r="T15" s="38">
+      <c r="T15" s="27">
         <f>[1]SUMMARY!D17</f>
         <v>75</v>
       </c>
-      <c r="U15" s="38">
+      <c r="U15" s="27">
         <f>[1]SUMMARY!E17</f>
         <v>33</v>
       </c>
-      <c r="V15" s="38">
-        <v>0</v>
-      </c>
-      <c r="W15" s="38">
+      <c r="V15" s="27">
+        <v>0</v>
+      </c>
+      <c r="W15" s="27">
         <f t="shared" si="2"/>
         <v>304</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
-      <c r="Y15" s="38">
+      <c r="Y15" s="27">
         <f t="shared" si="3"/>
         <v>5244000</v>
       </c>
@@ -5725,72 +5809,72 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>165</v>
       </c>
-      <c r="C16" s="16">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="21">
         <v>99</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="21">
         <v>36</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="21">
         <v>40</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="21">
         <v>101</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="21">
         <v>21</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="22">
         <f t="shared" si="1"/>
         <v>297</v>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="R16" s="38">
+      <c r="R16" s="27">
         <f>[1]SUMMARY!B18</f>
         <v>24</v>
       </c>
-      <c r="S16" s="38">
+      <c r="S16" s="27">
         <f>[1]SUMMARY!C18</f>
         <v>47</v>
       </c>
-      <c r="T16" s="38">
+      <c r="T16" s="27">
         <f>[1]SUMMARY!D18</f>
         <v>2</v>
       </c>
-      <c r="U16" s="38">
+      <c r="U16" s="27">
         <f>[1]SUMMARY!E18</f>
         <v>3</v>
       </c>
-      <c r="V16" s="38">
-        <v>0</v>
-      </c>
-      <c r="W16" s="38">
+      <c r="V16" s="27">
+        <v>0</v>
+      </c>
+      <c r="W16" s="27">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="X16" s="4">
         <v>23000</v>
       </c>
-      <c r="Y16" s="38">
+      <c r="Y16" s="27">
         <f t="shared" si="3"/>
         <v>1748000</v>
       </c>
@@ -5808,72 +5892,72 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>404</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="13">
         <f t="shared" si="0"/>
         <v>405</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="21">
         <v>46</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="21">
         <v>50</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="21">
         <v>39</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="21">
         <v>48</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="21">
         <v>22</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="22">
         <f t="shared" si="1"/>
         <v>205</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="R17" s="38">
+      <c r="R17" s="27">
         <f>[1]SUMMARY!B19</f>
         <v>3</v>
       </c>
-      <c r="S17" s="38">
+      <c r="S17" s="27">
         <f>[1]SUMMARY!C19</f>
         <v>12</v>
       </c>
-      <c r="T17" s="38">
+      <c r="T17" s="27">
         <f>[1]SUMMARY!D19</f>
         <v>0</v>
       </c>
-      <c r="U17" s="38">
+      <c r="U17" s="27">
         <f>[1]SUMMARY!E19</f>
         <v>0</v>
       </c>
-      <c r="V17" s="38">
-        <v>0</v>
-      </c>
-      <c r="W17" s="38">
+      <c r="V17" s="27">
+        <v>0</v>
+      </c>
+      <c r="W17" s="27">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
-      <c r="Y17" s="38">
+      <c r="Y17" s="27">
         <f t="shared" si="3"/>
         <v>450000</v>
       </c>
@@ -5891,72 +5975,72 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="15">
-        <v>0</v>
-      </c>
-      <c r="C18" s="16">
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14">
         <v>198</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="13">
         <f t="shared" si="0"/>
         <v>198</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="21">
         <v>45</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="21">
         <v>40</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="21">
         <v>18</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="21">
         <v>20</v>
       </c>
-      <c r="K18" s="26">
-        <v>0</v>
-      </c>
-      <c r="L18" s="27">
+      <c r="K18" s="21">
+        <v>0</v>
+      </c>
+      <c r="L18" s="22">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="Q18" s="25" t="s">
+      <c r="Q18" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="27">
         <f>[1]SUMMARY!B20</f>
         <v>31</v>
       </c>
-      <c r="S18" s="38">
+      <c r="S18" s="27">
         <f>[1]SUMMARY!C20</f>
         <v>0</v>
       </c>
-      <c r="T18" s="38">
+      <c r="T18" s="27">
         <f>[1]SUMMARY!D20</f>
         <v>0</v>
       </c>
-      <c r="U18" s="38">
+      <c r="U18" s="27">
         <f>[1]SUMMARY!E20</f>
         <v>0</v>
       </c>
-      <c r="V18" s="38">
-        <v>0</v>
-      </c>
-      <c r="W18" s="38">
+      <c r="V18" s="27">
+        <v>0</v>
+      </c>
+      <c r="W18" s="27">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="X18" s="4">
         <v>6900</v>
       </c>
-      <c r="Y18" s="38">
+      <c r="Y18" s="27">
         <f t="shared" si="3"/>
         <v>213900</v>
       </c>
@@ -5974,457 +6058,457 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="15">
-        <v>0</v>
-      </c>
-      <c r="C19" s="16">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="25" t="s">
+      <c r="B19" s="13">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="21">
         <v>11</v>
       </c>
-      <c r="H19" s="26">
-        <v>0</v>
-      </c>
-      <c r="I19" s="26">
-        <v>0</v>
-      </c>
-      <c r="J19" s="26">
-        <v>0</v>
-      </c>
-      <c r="K19" s="26">
-        <v>0</v>
-      </c>
-      <c r="L19" s="27">
+      <c r="H19" s="21">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
+      <c r="L19" s="22">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="Q19" s="25" t="s">
+      <c r="Q19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="R19" s="38">
+      <c r="R19" s="27">
         <f>[1]SUMMARY!B21</f>
         <v>0</v>
       </c>
-      <c r="S19" s="38">
+      <c r="S19" s="27">
         <f>[1]SUMMARY!C21</f>
         <v>0</v>
       </c>
-      <c r="T19" s="38">
+      <c r="T19" s="27">
         <f>[1]SUMMARY!D21</f>
         <v>0</v>
       </c>
-      <c r="U19" s="38">
+      <c r="U19" s="27">
         <f>[1]SUMMARY!E21</f>
         <v>9</v>
       </c>
-      <c r="V19" s="38">
-        <v>0</v>
-      </c>
-      <c r="W19" s="38">
+      <c r="V19" s="27">
+        <v>0</v>
+      </c>
+      <c r="W19" s="27">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="X19" s="4">
         <v>7000</v>
       </c>
-      <c r="Y19" s="38">
+      <c r="Y19" s="27">
         <f t="shared" si="3"/>
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="15">
-        <v>0</v>
-      </c>
-      <c r="C20" s="16">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="25" t="s">
+      <c r="B20" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="26">
-        <v>0</v>
-      </c>
-      <c r="I20" s="26">
-        <v>0</v>
-      </c>
-      <c r="J20" s="26">
-        <v>0</v>
-      </c>
-      <c r="K20" s="26">
-        <v>0</v>
-      </c>
-      <c r="L20" s="27">
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <v>0</v>
+      </c>
+      <c r="K20" s="21">
+        <v>0</v>
+      </c>
+      <c r="L20" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="R20" s="38">
+      <c r="R20" s="27">
         <f>[1]SUMMARY!B22</f>
         <v>0</v>
       </c>
-      <c r="S20" s="38">
+      <c r="S20" s="27">
         <f>[1]SUMMARY!C22</f>
         <v>0</v>
       </c>
-      <c r="T20" s="38">
+      <c r="T20" s="27">
         <f>[1]SUMMARY!D22</f>
         <v>0</v>
       </c>
-      <c r="U20" s="38">
+      <c r="U20" s="27">
         <f>[1]SUMMARY!E22</f>
         <v>0</v>
       </c>
-      <c r="V20" s="38">
-        <v>0</v>
-      </c>
-      <c r="W20" s="38">
+      <c r="V20" s="27">
+        <v>0</v>
+      </c>
+      <c r="W20" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X20" s="4">
         <v>12000</v>
       </c>
-      <c r="Y20" s="38">
+      <c r="Y20" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="15">
-        <v>0</v>
-      </c>
-      <c r="C21" s="16">
+      <c r="B21" s="13">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14">
         <v>1032</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <f t="shared" si="0"/>
         <v>1032</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="21">
         <v>11</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="21">
         <v>70</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="21">
         <v>27</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="21">
         <v>6</v>
       </c>
-      <c r="K21" s="26">
-        <v>0</v>
-      </c>
-      <c r="L21" s="27">
+      <c r="K21" s="21">
+        <v>0</v>
+      </c>
+      <c r="L21" s="22">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
-      <c r="Q21" s="25" t="s">
+      <c r="Q21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="R21" s="38">
+      <c r="R21" s="27">
         <f>[1]SUMMARY!B23</f>
         <v>75</v>
       </c>
-      <c r="S21" s="38">
+      <c r="S21" s="27">
         <f>[1]SUMMARY!C23</f>
         <v>65</v>
       </c>
-      <c r="T21" s="38">
+      <c r="T21" s="27">
         <f>[1]SUMMARY!D23</f>
         <v>33</v>
       </c>
-      <c r="U21" s="38">
+      <c r="U21" s="27">
         <f>[1]SUMMARY!E23</f>
         <v>15</v>
       </c>
-      <c r="V21" s="38">
-        <v>0</v>
-      </c>
-      <c r="W21" s="38">
+      <c r="V21" s="27">
+        <v>0</v>
+      </c>
+      <c r="W21" s="27">
         <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
-      <c r="Y21" s="38">
+      <c r="Y21" s="27">
         <f t="shared" si="3"/>
         <v>1804800</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <v>72</v>
       </c>
-      <c r="C22" s="16">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="21">
         <v>132</v>
       </c>
-      <c r="H22" s="26">
-        <v>0</v>
-      </c>
-      <c r="I22" s="26">
+      <c r="H22" s="21">
+        <v>0</v>
+      </c>
+      <c r="I22" s="21">
         <v>91</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="21">
         <v>65</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="21">
         <v>12</v>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="22">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="Q22" s="25" t="s">
+      <c r="Q22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="27">
         <f>[1]SUMMARY!B24</f>
         <v>0</v>
       </c>
-      <c r="S22" s="38">
+      <c r="S22" s="27">
         <f>[1]SUMMARY!C24</f>
         <v>0</v>
       </c>
-      <c r="T22" s="38">
+      <c r="T22" s="27">
         <f>[1]SUMMARY!D24</f>
         <v>0</v>
       </c>
-      <c r="U22" s="38">
+      <c r="U22" s="27">
         <f>[1]SUMMARY!E24</f>
         <v>0</v>
       </c>
-      <c r="V22" s="38">
-        <v>0</v>
-      </c>
-      <c r="W22" s="38">
+      <c r="V22" s="27">
+        <v>0</v>
+      </c>
+      <c r="W22" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X22" s="4">
         <v>13200</v>
       </c>
-      <c r="Y22" s="38">
+      <c r="Y22" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="F23" s="25" t="s">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="21">
         <v>10</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="21">
         <v>4</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="21">
         <v>4</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23" s="21">
         <v>55</v>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="21">
         <v>9</v>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="22">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="38">
-        <v>0</v>
-      </c>
-      <c r="S23" s="38">
-        <v>0</v>
-      </c>
-      <c r="T23" s="38">
-        <v>0</v>
-      </c>
-      <c r="U23" s="38">
-        <v>0</v>
-      </c>
-      <c r="V23" s="38">
-        <v>0</v>
-      </c>
-      <c r="W23" s="38">
+      <c r="Q23" s="20"/>
+      <c r="R23" s="27">
+        <v>0</v>
+      </c>
+      <c r="S23" s="27">
+        <v>0</v>
+      </c>
+      <c r="T23" s="27">
+        <v>0</v>
+      </c>
+      <c r="U23" s="27">
+        <v>0</v>
+      </c>
+      <c r="V23" s="27">
+        <v>0</v>
+      </c>
+      <c r="W23" s="27">
         <v>0</v>
       </c>
       <c r="X23" s="4"/>
-      <c r="Y23" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="F24" s="25"/>
-      <c r="G24" s="26">
-        <v>0</v>
-      </c>
-      <c r="H24" s="26">
-        <v>0</v>
-      </c>
-      <c r="I24" s="26">
-        <v>0</v>
-      </c>
-      <c r="J24" s="26">
-        <v>0</v>
-      </c>
-      <c r="K24" s="26">
-        <v>0</v>
-      </c>
-      <c r="L24" s="27">
+      <c r="Y23" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="F24" s="20"/>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>0</v>
+      </c>
+      <c r="I24" s="21">
+        <v>0</v>
+      </c>
+      <c r="J24" s="21">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21">
+        <v>0</v>
+      </c>
+      <c r="L24" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="38">
-        <v>0</v>
-      </c>
-      <c r="S24" s="38">
-        <v>0</v>
-      </c>
-      <c r="T24" s="38">
-        <v>0</v>
-      </c>
-      <c r="U24" s="38">
-        <v>0</v>
-      </c>
-      <c r="V24" s="38">
-        <v>0</v>
-      </c>
-      <c r="W24" s="38">
+      <c r="Q24" s="20"/>
+      <c r="R24" s="27">
+        <v>0</v>
+      </c>
+      <c r="S24" s="27">
+        <v>0</v>
+      </c>
+      <c r="T24" s="27">
+        <v>0</v>
+      </c>
+      <c r="U24" s="27">
+        <v>0</v>
+      </c>
+      <c r="V24" s="27">
+        <v>0</v>
+      </c>
+      <c r="W24" s="27">
         <v>0</v>
       </c>
       <c r="X24" s="4"/>
-      <c r="Y24" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="F25" s="25"/>
-      <c r="G25" s="26">
-        <v>0</v>
-      </c>
-      <c r="H25" s="26">
-        <v>0</v>
-      </c>
-      <c r="I25" s="26">
-        <v>0</v>
-      </c>
-      <c r="J25" s="26">
-        <v>0</v>
-      </c>
-      <c r="K25" s="26">
-        <v>0</v>
-      </c>
-      <c r="L25" s="27">
+      <c r="Y24" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="F25" s="20"/>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0</v>
+      </c>
+      <c r="I25" s="21">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21">
+        <v>0</v>
+      </c>
+      <c r="L25" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="28" t="s">
+      <c r="Q25" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="R25" s="24">
+      <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
         <v>572</v>
       </c>
-      <c r="S25" s="24">
+      <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="4">SUM(S4:S24)</f>
         <v>1015</v>
       </c>
-      <c r="T25" s="24">
+      <c r="T25" s="19">
         <f t="shared" si="4"/>
         <v>445</v>
       </c>
-      <c r="U25" s="24">
+      <c r="U25" s="19">
         <f t="shared" si="4"/>
         <v>363</v>
       </c>
-      <c r="V25" s="24">
+      <c r="V25" s="19">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="W25" s="24">
+      <c r="W25" s="19">
         <f t="shared" si="4"/>
         <v>2405</v>
       </c>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24">
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19">
         <f t="shared" si="4"/>
         <v>26635300</v>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="F26" s="28" t="s">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="24">
         <f t="shared" ref="G26:L26" si="5">SUM(G5:G25)</f>
         <v>1232</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="24">
         <f t="shared" si="5"/>
         <v>870</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="24">
         <f t="shared" si="5"/>
         <v>940</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="24">
         <f t="shared" si="5"/>
         <v>1401</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="24">
         <f t="shared" si="5"/>
         <v>117</v>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="24">
         <f t="shared" si="5"/>
         <v>4560</v>
       </c>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7A2EB4-9A5E-4836-B430-91F010AEEDFA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="I2" s="5">
         <f>index!AU3</f>
-        <v>46158</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4">
         <f>index!AV3</f>
@@ -3654,7 +3654,10 @@
         <f>index!AT4</f>
         <v>410000</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5">
+        <f>index!AU4</f>
+        <v>0</v>
+      </c>
       <c r="J3" s="4">
         <f>index!AV4</f>
         <v>0</v>
@@ -3693,7 +3696,10 @@
         <f>index!AT5</f>
         <v>410000</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5">
+        <f>index!AU5</f>
+        <v>0</v>
+      </c>
       <c r="J4" s="4">
         <f>index!AV5</f>
         <v>0</v>
@@ -3735,7 +3741,10 @@
         <f>index!AT6</f>
         <v>410000</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5">
+        <f>index!AU6</f>
+        <v>0</v>
+      </c>
       <c r="J5" s="4">
         <f>index!AV6</f>
         <v>0</v>
@@ -3771,7 +3780,10 @@
         <f>index!AT7</f>
         <v>0</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5">
+        <f>index!AU7</f>
+        <v>0</v>
+      </c>
       <c r="J6" s="4" t="str">
         <f>index!AV7</f>
         <v>SEGEL</v>
@@ -3807,7 +3819,10 @@
         <f>index!AT8</f>
         <v>0</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5">
+        <f>index!AU8</f>
+        <v>0</v>
+      </c>
       <c r="J7" s="4" t="str">
         <f>index!AV8</f>
         <v>SEGEL</v>
@@ -3843,7 +3858,10 @@
         <f>index!AT9</f>
         <v>0</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5">
+        <f>index!AU9</f>
+        <v>0</v>
+      </c>
       <c r="J8" s="4" t="str">
         <f>index!AV9</f>
         <v>SEGEL</v>
@@ -3879,7 +3897,10 @@
         <f>index!AT10</f>
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5">
+        <f>index!AU10</f>
+        <v>0</v>
+      </c>
       <c r="J9" s="4" t="str">
         <f>index!AV10</f>
         <v>SEGEL</v>
@@ -3915,7 +3936,10 @@
         <f>index!AT11</f>
         <v>0</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5">
+        <f>index!AU11</f>
+        <v>0</v>
+      </c>
       <c r="J10" s="4" t="str">
         <f>index!AV11</f>
         <v>SEGEL</v>
@@ -3951,7 +3975,10 @@
         <f>index!AT12</f>
         <v>0</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5">
+        <f>index!AU12</f>
+        <v>0</v>
+      </c>
       <c r="J11" s="4" t="str">
         <f>index!AV12</f>
         <v>SEGEL</v>
@@ -3987,7 +4014,10 @@
         <f>index!AT13</f>
         <v>0</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5">
+        <f>index!AU13</f>
+        <v>0</v>
+      </c>
       <c r="J12" s="4">
         <f>index!AV13</f>
         <v>0</v>
@@ -4023,7 +4053,10 @@
         <f>index!AT14</f>
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5">
+        <f>index!AU14</f>
+        <v>0</v>
+      </c>
       <c r="J13" s="4">
         <f>index!AV14</f>
         <v>0</v>
@@ -4059,7 +4092,10 @@
         <f>index!AT15</f>
         <v>0</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5">
+        <f>index!AU15</f>
+        <v>0</v>
+      </c>
       <c r="J14" s="4">
         <f>index!AV15</f>
         <v>0</v>
@@ -4095,7 +4131,10 @@
         <f>index!AT16</f>
         <v>0</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="5">
+        <f>index!AU16</f>
+        <v>0</v>
+      </c>
       <c r="J15" s="4">
         <f>index!AV16</f>
         <v>0</v>
@@ -4131,7 +4170,10 @@
         <f>index!AT17</f>
         <v>0</v>
       </c>
-      <c r="I16" s="10"/>
+      <c r="I16" s="5">
+        <f>index!AU17</f>
+        <v>0</v>
+      </c>
       <c r="J16" s="4">
         <f>index!AV17</f>
         <v>0</v>
@@ -4167,7 +4209,10 @@
         <f>index!AT18</f>
         <v>0</v>
       </c>
-      <c r="I17" s="10"/>
+      <c r="I17" s="5">
+        <f>index!AU18</f>
+        <v>0</v>
+      </c>
       <c r="J17" s="4">
         <f>index!AV18</f>
         <v>0</v>
@@ -4403,9 +4448,7 @@
       <c r="AT3" s="8">
         <v>410000</v>
       </c>
-      <c r="AU3" s="5">
-        <v>46158</v>
-      </c>
+      <c r="AU3" s="5"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
     </row>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7A2EB4-9A5E-4836-B430-91F010AEEDFA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="penjualan-hifi" sheetId="7" r:id="rId7"/>
     <sheet name="index" sheetId="8" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="128">
   <si>
     <t>nama barang</t>
   </si>
@@ -415,6 +412,18 @@
   </si>
   <si>
     <t>hifi</t>
+  </si>
+  <si>
+    <t>Muhammad Parhan</t>
+  </si>
+  <si>
+    <t>15-May-2026</t>
+  </si>
+  <si>
+    <t>21-May-2026</t>
+  </si>
+  <si>
+    <t>CSM</t>
   </si>
 </sst>
 </file>
@@ -772,353 +781,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="CSO"/>
-      <sheetName val="01"/>
-      <sheetName val="02"/>
-      <sheetName val="03"/>
-      <sheetName val="04"/>
-      <sheetName val="05"/>
-      <sheetName val="06"/>
-      <sheetName val="07"/>
-      <sheetName val="08"/>
-      <sheetName val="09"/>
-      <sheetName val="10"/>
-      <sheetName val="11"/>
-      <sheetName val="12"/>
-      <sheetName val="13"/>
-      <sheetName val="14"/>
-      <sheetName val="15"/>
-      <sheetName val="16"/>
-      <sheetName val="17"/>
-      <sheetName val="18"/>
-      <sheetName val="19"/>
-      <sheetName val="20"/>
-      <sheetName val="21"/>
-      <sheetName val="22"/>
-      <sheetName val="23"/>
-      <sheetName val="24"/>
-      <sheetName val="25"/>
-      <sheetName val="26"/>
-      <sheetName val="27"/>
-      <sheetName val="28"/>
-      <sheetName val="29"/>
-      <sheetName val="30"/>
-      <sheetName val="31"/>
-      <sheetName val="SUMMARY"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32">
-        <row r="6">
-          <cell r="B6">
-            <v>2</v>
-          </cell>
-          <cell r="C6">
-            <v>12</v>
-          </cell>
-          <cell r="D6">
-            <v>27</v>
-          </cell>
-          <cell r="E6">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0</v>
-          </cell>
-          <cell r="C7">
-            <v>0</v>
-          </cell>
-          <cell r="D7">
-            <v>0</v>
-          </cell>
-          <cell r="E7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>0</v>
-          </cell>
-          <cell r="C8">
-            <v>3</v>
-          </cell>
-          <cell r="D8">
-            <v>0</v>
-          </cell>
-          <cell r="E8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>0</v>
-          </cell>
-          <cell r="C9">
-            <v>0</v>
-          </cell>
-          <cell r="D9">
-            <v>0</v>
-          </cell>
-          <cell r="E9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>0</v>
-          </cell>
-          <cell r="C10">
-            <v>0</v>
-          </cell>
-          <cell r="D10">
-            <v>0</v>
-          </cell>
-          <cell r="E10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>0</v>
-          </cell>
-          <cell r="C11">
-            <v>0</v>
-          </cell>
-          <cell r="D11">
-            <v>0</v>
-          </cell>
-          <cell r="E11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>110</v>
-          </cell>
-          <cell r="C12">
-            <v>369</v>
-          </cell>
-          <cell r="D12">
-            <v>30</v>
-          </cell>
-          <cell r="E12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>0</v>
-          </cell>
-          <cell r="C13">
-            <v>2</v>
-          </cell>
-          <cell r="D13">
-            <v>0</v>
-          </cell>
-          <cell r="E13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>254</v>
-          </cell>
-          <cell r="C14">
-            <v>342</v>
-          </cell>
-          <cell r="D14">
-            <v>233</v>
-          </cell>
-          <cell r="E14">
-            <v>212</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>0</v>
-          </cell>
-          <cell r="C15">
-            <v>0</v>
-          </cell>
-          <cell r="D15">
-            <v>0</v>
-          </cell>
-          <cell r="E15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>21</v>
-          </cell>
-          <cell r="C16">
-            <v>19</v>
-          </cell>
-          <cell r="D16">
-            <v>45</v>
-          </cell>
-          <cell r="E16">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>52</v>
-          </cell>
-          <cell r="C17">
-            <v>144</v>
-          </cell>
-          <cell r="D17">
-            <v>75</v>
-          </cell>
-          <cell r="E17">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>24</v>
-          </cell>
-          <cell r="C18">
-            <v>47</v>
-          </cell>
-          <cell r="D18">
-            <v>2</v>
-          </cell>
-          <cell r="E18">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>3</v>
-          </cell>
-          <cell r="C19">
-            <v>12</v>
-          </cell>
-          <cell r="D19">
-            <v>0</v>
-          </cell>
-          <cell r="E19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>31</v>
-          </cell>
-          <cell r="C20">
-            <v>0</v>
-          </cell>
-          <cell r="D20">
-            <v>0</v>
-          </cell>
-          <cell r="E20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>0</v>
-          </cell>
-          <cell r="C21">
-            <v>0</v>
-          </cell>
-          <cell r="D21">
-            <v>0</v>
-          </cell>
-          <cell r="E21">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>0</v>
-          </cell>
-          <cell r="C22">
-            <v>0</v>
-          </cell>
-          <cell r="D22">
-            <v>0</v>
-          </cell>
-          <cell r="E22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>75</v>
-          </cell>
-          <cell r="C23">
-            <v>65</v>
-          </cell>
-          <cell r="D23">
-            <v>33</v>
-          </cell>
-          <cell r="E23">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>0</v>
-          </cell>
-          <cell r="C24">
-            <v>0</v>
-          </cell>
-          <cell r="D24">
-            <v>0</v>
-          </cell>
-          <cell r="E24">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
@@ -1445,7 +1107,7 @@
       </c>
       <c r="B3" s="1">
         <f>index!B4</f>
-        <v>1107</v>
+        <v>1007</v>
       </c>
       <c r="C3">
         <f>index!C4</f>
@@ -1453,7 +1115,7 @@
       </c>
       <c r="D3" s="1">
         <f>B3+C3</f>
-        <v>1107</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1575,7 +1237,7 @@
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1583,7 +1245,7 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1056</v>
+        <v>996</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1609,7 +1271,7 @@
       </c>
       <c r="B13">
         <f>index!B14</f>
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <f>index!C14</f>
@@ -1617,7 +1279,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>499</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1626,7 +1288,7 @@
       </c>
       <c r="B14">
         <f>index!B15</f>
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="C14">
         <f>index!C15</f>
@@ -1634,7 +1296,7 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1660,11 +1322,11 @@
       </c>
       <c r="B16">
         <f>index!B17</f>
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C16">
         <f>index!C17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
@@ -1808,43 +1470,43 @@
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>226</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <f>index!G6</f>
-        <v>0</v>
-      </c>
-      <c r="C3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C3" t="str">
         <f>index!H6</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D3" t="str">
         <f>index!I6</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E3" t="str">
         <f>index!J6</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G23" si="0">SUM(B3:F3)</f>
+        <f t="shared" ref="G3:G22" si="0">SUM(B3:F3)</f>
         <v>0</v>
       </c>
     </row>
@@ -1854,15 +1516,15 @@
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
@@ -1870,28 +1532,28 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1923</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <f>index!G8</f>
-        <v>0</v>
-      </c>
-      <c r="C5">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C5" t="str">
         <f>index!H8</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D5" t="str">
         <f>index!I8</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E5" t="str">
         <f>index!J8</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
@@ -1899,21 +1561,21 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6">
+      <c r="B6" t="str">
         <f>index!G9</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C6" t="str">
         <f>index!H9</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D6" t="str">
         <f>index!I9</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E6" t="str">
         <f>index!J9</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
@@ -1921,21 +1583,21 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7">
+      <c r="B7" t="str">
         <f>index!G10</f>
-        <v>0</v>
-      </c>
-      <c r="C7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C7" t="str">
         <f>index!H10</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D7" t="str">
         <f>index!I10</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E7" t="str">
         <f>index!J10</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
@@ -1948,7 +1610,7 @@
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
@@ -1956,7 +1618,7 @@
       </c>
       <c r="D8">
         <f>index!I11</f>
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <f>index!J11</f>
@@ -1964,7 +1626,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>810</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1975,9 +1637,9 @@
         <f>index!G12</f>
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="str">
         <f>index!H12</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="D9">
         <f>index!I12</f>
@@ -1998,7 +1660,7 @@
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
@@ -2014,28 +1676,28 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>237</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <f>index!G14</f>
-        <v>0</v>
-      </c>
-      <c r="C11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C11" t="str">
         <f>index!H14</f>
-        <v>0</v>
-      </c>
-      <c r="D11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D11" t="str">
         <f>index!I14</f>
-        <v>0</v>
-      </c>
-      <c r="E11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E11" t="str">
         <f>index!J14</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
@@ -2050,13 +1712,13 @@
         <f>index!G15</f>
         <v>44</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="str">
         <f>index!H15</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
@@ -2064,7 +1726,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -2077,7 +1739,7 @@
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
@@ -2085,11 +1747,11 @@
       </c>
       <c r="E13">
         <f>index!J16</f>
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2102,11 +1764,11 @@
       </c>
       <c r="C14">
         <f>index!H17</f>
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D14">
         <f>index!I17</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <f>index!J17</f>
@@ -2114,7 +1776,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -2148,23 +1810,23 @@
       </c>
       <c r="B16">
         <f>index!G19</f>
-        <v>11</v>
-      </c>
-      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="C16" t="str">
         <f>index!H19</f>
-        <v>0</v>
-      </c>
-      <c r="D16">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D16" t="str">
         <f>index!I19</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E16" t="str">
         <f>index!J19</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -2175,17 +1837,17 @@
         <f>index!G20</f>
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="str">
         <f>index!H20</f>
-        <v>0</v>
-      </c>
-      <c r="D17">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D17" t="str">
         <f>index!I20</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E17" t="str">
         <f>index!J20</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
@@ -2225,9 +1887,9 @@
         <f>index!G22</f>
         <v>132</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="str">
         <f>index!H22</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -2314,23 +1976,28 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>1242</v>
+        <f>SUM(B2:B22)</f>
+        <v>1234</v>
       </c>
       <c r="C23">
-        <v>905</v>
+        <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
+        <v>943</v>
       </c>
       <c r="D23">
-        <v>953</v>
+        <f t="shared" si="1"/>
+        <v>964</v>
       </c>
       <c r="E23">
-        <v>1412</v>
+        <f t="shared" si="1"/>
+        <v>1385</v>
       </c>
       <c r="F23">
-        <v>117</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G23">
-        <f t="shared" si="0"/>
-        <v>4629</v>
+        <f t="shared" si="1"/>
+        <v>4526</v>
       </c>
     </row>
   </sheetData>
@@ -2357,11 +2024,11 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>49352400</v>
+        <v>54302400</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2370,7 +2037,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>75753400</v>
+        <v>78757400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2379,7 +2046,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>59427000</v>
+        <v>62427000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2388,7 +2055,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>72748900</v>
+        <v>77532500</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2397,7 +2064,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>257281700</v>
+        <v>273019300</v>
       </c>
     </row>
   </sheetData>
@@ -2463,27 +2130,31 @@
         <v>4</v>
       </c>
       <c r="B3">
+        <f>index!R4</f>
         <v>2</v>
       </c>
       <c r="C3">
+        <f>index!S4</f>
         <v>12</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <f>index!T4</f>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <f>index!U4</f>
+        <v>58</v>
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>946000</v>
+        <v>1144000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -2491,15 +2162,19 @@
         <v>29</v>
       </c>
       <c r="B4">
+        <f>index!R5</f>
         <v>0</v>
       </c>
       <c r="C4">
+        <f>index!S5</f>
         <v>0</v>
       </c>
       <c r="D4">
+        <f>index!T5</f>
         <v>0</v>
       </c>
       <c r="E4">
+        <f>index!U5</f>
         <v>0</v>
       </c>
       <c r="F4">
@@ -2519,15 +2194,19 @@
         <v>30</v>
       </c>
       <c r="B5">
+        <f>index!R6</f>
         <v>0</v>
       </c>
       <c r="C5">
+        <f>index!S6</f>
         <v>3</v>
       </c>
       <c r="D5">
+        <f>index!T6</f>
         <v>0</v>
       </c>
       <c r="E5">
+        <f>index!U6</f>
         <v>0</v>
       </c>
       <c r="F5">
@@ -2547,15 +2226,19 @@
         <v>7</v>
       </c>
       <c r="B6">
+        <f>index!R7</f>
         <v>0</v>
       </c>
       <c r="C6">
+        <f>index!S7</f>
         <v>0</v>
       </c>
       <c r="D6">
+        <f>index!T7</f>
         <v>0</v>
       </c>
       <c r="E6">
+        <f>index!U7</f>
         <v>0</v>
       </c>
       <c r="F6">
@@ -2572,15 +2255,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7">
+        <f>index!R8</f>
         <v>0</v>
       </c>
       <c r="C7">
+        <f>index!S8</f>
         <v>0</v>
       </c>
       <c r="D7">
+        <f>index!T8</f>
         <v>0</v>
       </c>
       <c r="E7">
+        <f>index!U8</f>
         <v>0</v>
       </c>
       <c r="F7">
@@ -2594,15 +2281,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8">
+        <f>index!R9</f>
         <v>0</v>
       </c>
       <c r="C8">
+        <f>index!S9</f>
         <v>0</v>
       </c>
       <c r="D8">
+        <f>index!T9</f>
         <v>0</v>
       </c>
       <c r="E8">
+        <f>index!U9</f>
         <v>0</v>
       </c>
       <c r="F8">
@@ -2619,27 +2310,31 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>110</v>
+        <f>index!R10</f>
+        <v>120</v>
       </c>
       <c r="C9">
+        <f>index!S10</f>
         <v>369</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <f>index!T10</f>
+        <v>50</v>
       </c>
       <c r="E9">
+        <f>index!U10</f>
         <v>0</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>305400</v>
+        <v>323400</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -2647,15 +2342,19 @@
         <v>31</v>
       </c>
       <c r="B10">
+        <f>index!R11</f>
         <v>0</v>
       </c>
       <c r="C10">
+        <f>index!S11</f>
         <v>2</v>
       </c>
       <c r="D10">
+        <f>index!T11</f>
         <v>0</v>
       </c>
       <c r="E10">
+        <f>index!U11</f>
         <v>0</v>
       </c>
       <c r="F10">
@@ -2675,27 +2374,31 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>254</v>
+        <f>index!R12</f>
+        <v>279</v>
       </c>
       <c r="C11">
-        <v>327</v>
+        <f>index!S12</f>
+        <v>342</v>
       </c>
       <c r="D11">
+        <f>index!T12</f>
         <v>233</v>
       </c>
       <c r="E11">
+        <f>index!U12</f>
         <v>212</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1026</v>
+        <v>1066</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>13543200</v>
+        <v>14071200</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -2703,15 +2406,19 @@
         <v>33</v>
       </c>
       <c r="B12">
+        <f>index!R13</f>
         <v>0</v>
       </c>
       <c r="C12">
+        <f>index!S13</f>
         <v>0</v>
       </c>
       <c r="D12">
+        <f>index!T13</f>
         <v>0</v>
       </c>
       <c r="E12">
+        <f>index!U13</f>
         <v>0</v>
       </c>
       <c r="F12">
@@ -2731,27 +2438,31 @@
         <v>34</v>
       </c>
       <c r="B13">
+        <f>index!R14</f>
         <v>21</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <f>index!S14</f>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>45</v>
+        <f>index!T14</f>
+        <v>51</v>
       </c>
       <c r="E13">
+        <f>index!U14</f>
         <v>43</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>1711000</v>
+        <v>1943000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -2759,27 +2470,31 @@
         <v>35</v>
       </c>
       <c r="B14">
+        <f>index!R15</f>
         <v>52</v>
       </c>
       <c r="C14">
-        <v>134</v>
+        <f>index!S15</f>
+        <v>153</v>
       </c>
       <c r="D14">
-        <v>65</v>
+        <f>index!T15</f>
+        <v>75</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <f>index!U15</f>
+        <v>39</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>4812750</v>
+        <v>5502750</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -2787,27 +2502,31 @@
         <v>36</v>
       </c>
       <c r="B15">
+        <f>index!R16</f>
         <v>24</v>
       </c>
       <c r="C15">
-        <v>47</v>
+        <f>index!S16</f>
+        <v>53</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <f>index!T16</f>
+        <v>5</v>
       </c>
       <c r="E15">
+        <f>index!U16</f>
         <v>3</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>1748000</v>
+        <v>1955000</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -2815,15 +2534,19 @@
         <v>15</v>
       </c>
       <c r="B16">
+        <f>index!R17</f>
         <v>3</v>
       </c>
       <c r="C16">
+        <f>index!S17</f>
         <v>12</v>
       </c>
       <c r="D16">
+        <f>index!T17</f>
         <v>0</v>
       </c>
       <c r="E16">
+        <f>index!U17</f>
         <v>0</v>
       </c>
       <c r="F16">
@@ -2843,27 +2566,31 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>31</v>
+        <f>index!R18</f>
+        <v>32</v>
       </c>
       <c r="C17">
+        <f>index!S18</f>
         <v>0</v>
       </c>
       <c r="D17">
+        <f>index!T18</f>
         <v>0</v>
       </c>
       <c r="E17">
+        <f>index!U18</f>
         <v>0</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>213900</v>
+        <v>220800</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2871,15 +2598,19 @@
         <v>17</v>
       </c>
       <c r="B18">
+        <f>index!R19</f>
         <v>0</v>
       </c>
       <c r="C18">
+        <f>index!S19</f>
         <v>0</v>
       </c>
       <c r="D18">
+        <f>index!T19</f>
         <v>0</v>
       </c>
       <c r="E18">
+        <f>index!U19</f>
         <v>9</v>
       </c>
       <c r="F18">
@@ -2899,15 +2630,19 @@
         <v>18</v>
       </c>
       <c r="B19">
+        <f>index!R20</f>
         <v>0</v>
       </c>
       <c r="C19">
+        <f>index!S20</f>
         <v>0</v>
       </c>
       <c r="D19">
+        <f>index!T20</f>
         <v>0</v>
       </c>
       <c r="E19">
+        <f>index!U20</f>
         <v>0</v>
       </c>
       <c r="F19">
@@ -2927,27 +2662,31 @@
         <v>19</v>
       </c>
       <c r="B20">
+        <f>index!R21</f>
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <f>index!S21</f>
         <v>65</v>
       </c>
-      <c r="C20">
-        <v>65</v>
-      </c>
       <c r="D20">
+        <f>index!T21</f>
         <v>33</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <f>index!U21</f>
+        <v>15</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>1651200</v>
+        <v>1804800</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -2955,15 +2694,19 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <f>index!R22</f>
         <v>0</v>
       </c>
       <c r="C21">
+        <f>index!S22</f>
         <v>0</v>
       </c>
       <c r="D21">
+        <f>index!T22</f>
         <v>0</v>
       </c>
       <c r="E21">
+        <f>index!U22</f>
         <v>0</v>
       </c>
       <c r="F21">
@@ -2980,15 +2723,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22">
+        <f>index!R23</f>
         <v>0</v>
       </c>
       <c r="C22">
+        <f>index!S23</f>
         <v>0</v>
       </c>
       <c r="D22">
+        <f>index!T23</f>
         <v>0</v>
       </c>
       <c r="E22">
+        <f>index!U23</f>
         <v>0</v>
       </c>
       <c r="F22">
@@ -3002,15 +2749,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B23">
+        <f>index!R24</f>
         <v>0</v>
       </c>
       <c r="C23">
+        <f>index!S24</f>
         <v>0</v>
       </c>
       <c r="D23">
+        <f>index!T24</f>
         <v>0</v>
       </c>
       <c r="E23">
+        <f>index!U24</f>
         <v>0</v>
       </c>
       <c r="F23">
@@ -3028,27 +2779,27 @@
       </c>
       <c r="B24">
         <f t="shared" ref="B24:G24" si="2">SUM(B3:B23)</f>
-        <v>562</v>
+        <v>608</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1030</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2326</v>
+        <v>2496</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>25564450</v>
+        <v>27597950</v>
       </c>
     </row>
   </sheetData>
@@ -3128,11 +2879,11 @@
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>6250000</v>
+        <v>6750000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>6250000</v>
+        <v>6750000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -3140,7 +2891,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -3156,7 +2907,7 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -3172,11 +2923,11 @@
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>5585000</v>
+        <v>6085000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>5585000</v>
+        <v>6085000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -3184,7 +2935,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -3200,7 +2951,7 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -3216,11 +2967,11 @@
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>6920000</v>
+        <v>7420000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>6920000</v>
+        <v>7420000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -3228,7 +2979,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -3244,7 +2995,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -3297,12 +3048,12 @@
         <v>1058</v>
       </c>
       <c r="D7" s="28">
-        <f t="shared" ref="D7:F7" si="1">SUM(D3:D6)</f>
-        <v>24630000</v>
+        <f>SUM(D3:D6)</f>
+        <v>26130000</v>
       </c>
       <c r="E7" s="28">
-        <f t="shared" si="1"/>
-        <v>24630000</v>
+        <f t="shared" ref="D7:F7" si="1">SUM(E3:E6)</f>
+        <v>26130000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3310,7 +3061,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3326,7 +3077,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3584,9 +3335,9 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="5" t="str">
         <f>index!AN3</f>
-        <v>46157</v>
+        <v>15-May-2026</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>index!AO3</f>
@@ -3626,9 +3377,9 @@
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="5" t="str">
         <f>index!AN4</f>
-        <v>46157</v>
+        <v>15-May-2026</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>index!AO4</f>
@@ -3668,9 +3419,9 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="5" t="str">
         <f>index!AN5</f>
-        <v>46157</v>
+        <v>15-May-2026</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>index!AO5</f>
@@ -3713,9 +3464,9 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="5" t="str">
         <f>index!AN6</f>
-        <v>46157</v>
+        <v>15-May-2026</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>index!AO6</f>
@@ -3755,10 +3506,13 @@
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="5" t="str">
+        <f>index!AN7</f>
+        <v>21-May-2026</v>
+      </c>
       <c r="C6" s="4" t="str">
         <f>index!AO7</f>
-        <v>GUDANG</v>
+        <v>PARHAN</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>index!AP7</f>
@@ -3778,15 +3532,15 @@
       </c>
       <c r="H6" s="9">
         <f>index!AT7</f>
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I6" s="5">
         <f>index!AU7</f>
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="str">
+      <c r="J6" s="4">
         <f>index!AV7</f>
-        <v>SEGEL</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -3794,10 +3548,13 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5" t="str">
+        <f>index!AN8</f>
+        <v>21-May-2026</v>
+      </c>
       <c r="C7" s="4" t="str">
         <f>index!AO8</f>
-        <v>GUDANG</v>
+        <v>ANDI</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>index!AP8</f>
@@ -3817,15 +3574,15 @@
       </c>
       <c r="H7" s="9">
         <f>index!AT8</f>
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I7" s="5">
         <f>index!AU8</f>
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="str">
+      <c r="J7" s="4">
         <f>index!AV8</f>
-        <v>SEGEL</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5"/>
     </row>
@@ -3833,10 +3590,13 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="5" t="str">
+        <f>index!AN9</f>
+        <v>21-May-2026</v>
+      </c>
       <c r="C8" s="4" t="str">
         <f>index!AO9</f>
-        <v>GUDANG</v>
+        <v>ENDEN</v>
       </c>
       <c r="D8" s="6" t="str">
         <f>index!AP9</f>
@@ -3856,15 +3616,15 @@
       </c>
       <c r="H8" s="8">
         <f>index!AT9</f>
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I8" s="5">
         <f>index!AU9</f>
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="str">
+      <c r="J8" s="4">
         <f>index!AV9</f>
-        <v>SEGEL</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5"/>
     </row>
@@ -3872,10 +3632,13 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="5" t="str">
+        <f>index!AN10</f>
+        <v>21-May-2026</v>
+      </c>
       <c r="C9" s="4" t="str">
         <f>index!AO10</f>
-        <v>GUDANG</v>
+        <v>PEBRIAN</v>
       </c>
       <c r="D9" s="6" t="str">
         <f>index!AP10</f>
@@ -3895,15 +3658,15 @@
       </c>
       <c r="H9" s="8">
         <f>index!AT10</f>
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I9" s="5">
         <f>index!AU10</f>
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="str">
+      <c r="J9" s="4">
         <f>index!AV10</f>
-        <v>SEGEL</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -3911,10 +3674,13 @@
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="str">
+        <f>index!AN11</f>
+        <v>21-May-2026</v>
+      </c>
       <c r="C10" s="4" t="str">
         <f>index!AO11</f>
-        <v>GUDANG</v>
+        <v>CSM</v>
       </c>
       <c r="D10" s="6" t="str">
         <f>index!AP11</f>
@@ -3934,15 +3700,15 @@
       </c>
       <c r="H10" s="8">
         <f>index!AT11</f>
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I10" s="5">
         <f>index!AU11</f>
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="str">
+      <c r="J10" s="4">
         <f>index!AV11</f>
-        <v>SEGEL</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5"/>
     </row>
@@ -3950,7 +3716,10 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5">
+        <f>index!AN12</f>
+        <v>0</v>
+      </c>
       <c r="C11" s="4" t="str">
         <f>index!AO12</f>
         <v>GUDANG</v>
@@ -4235,7 +4004,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4376,7 +4148,7 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>49352400</v>
+        <v>54302400</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4427,8 +4199,8 @@
       <c r="AM3" s="4">
         <v>1</v>
       </c>
-      <c r="AN3" s="5">
-        <v>46157</v>
+      <c r="AN3" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AO3" s="4" t="s">
         <v>89</v>
@@ -4457,14 +4229,14 @@
         <v>4</v>
       </c>
       <c r="B4" s="13">
-        <v>1107</v>
+        <v>1007</v>
       </c>
       <c r="C4" s="14">
         <v>0</v>
       </c>
       <c r="D4" s="13">
         <f>C4+B4</f>
-        <v>1107</v>
+        <v>1007</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>21</v>
@@ -4491,40 +4263,36 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>75753400</v>
+        <v>78757400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <f>[1]SUMMARY!B6</f>
         <v>2</v>
       </c>
       <c r="S4" s="27">
-        <f>[1]SUMMARY!C6</f>
         <v>12</v>
       </c>
       <c r="T4" s="27">
-        <f>[1]SUMMARY!D6</f>
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="U4" s="27">
-        <f>[1]SUMMARY!E6</f>
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="V4" s="27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>1089000</v>
+        <v>1144000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4536,16 +4304,16 @@
         <v>275</v>
       </c>
       <c r="AD4" s="28">
-        <v>6250000</v>
+        <v>6750000</v>
       </c>
       <c r="AE4" s="28">
-        <v>6250000</v>
+        <v>6750000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4562,8 +4330,8 @@
       <c r="AM4" s="4">
         <v>2</v>
       </c>
-      <c r="AN4" s="5">
-        <v>46157</v>
+      <c r="AN4" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AO4" s="4" t="s">
         <v>22</v>
@@ -4608,58 +4376,52 @@
         <v>84</v>
       </c>
       <c r="H5" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I5" s="21">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="J5" s="21">
-        <v>119</v>
-      </c>
-      <c r="K5" s="21">
-        <v>22</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="K5" s="21"/>
       <c r="L5" s="22">
-        <f t="shared" ref="L5:L25" si="1">SUM(G5:K5)</f>
-        <v>248</v>
+        <f>SUM(G5:K5)</f>
+        <v>311</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>59427000</v>
+        <v>62427000</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
       </c>
       <c r="R5" s="27">
-        <f>[1]SUMMARY!B7</f>
         <v>0</v>
       </c>
       <c r="S5" s="27">
-        <f>[1]SUMMARY!C7</f>
         <v>0</v>
       </c>
       <c r="T5" s="27">
-        <f>[1]SUMMARY!D7</f>
         <v>0</v>
       </c>
       <c r="U5" s="27">
-        <f>[1]SUMMARY!E7</f>
         <v>0</v>
       </c>
       <c r="V5" s="27">
         <v>0</v>
       </c>
       <c r="W5" s="27">
-        <f t="shared" ref="W5:W22" si="2">SUM(R5:V5)</f>
+        <f t="shared" ref="W5:W22" si="1">SUM(R5:V5)</f>
         <v>0</v>
       </c>
       <c r="X5" s="4">
         <v>30000</v>
       </c>
       <c r="Y5" s="27">
-        <f t="shared" ref="Y5:Y22" si="3">W5*X5</f>
+        <f t="shared" ref="Y5:Y22" si="2">W5*X5</f>
         <v>0</v>
       </c>
       <c r="AA5" t="s">
@@ -4672,16 +4434,16 @@
         <v>237</v>
       </c>
       <c r="AD5" s="28">
-        <v>5585000</v>
+        <v>6085000</v>
       </c>
       <c r="AE5" s="28">
-        <v>5585000</v>
+        <v>6085000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4698,8 +4460,8 @@
       <c r="AM5" s="4">
         <v>3</v>
       </c>
-      <c r="AN5" s="5">
-        <v>46157</v>
+      <c r="AN5" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AO5" s="4" t="s">
         <v>24</v>
@@ -4740,62 +4502,56 @@
       <c r="F6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21">
-        <v>0</v>
-      </c>
-      <c r="J6" s="21">
-        <v>0</v>
-      </c>
-      <c r="K6" s="21">
-        <v>0</v>
-      </c>
+      <c r="G6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="21"/>
       <c r="L6" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L5:L25" si="3">SUM(G6:K6)</f>
         <v>0</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>72748900</v>
+        <v>77532500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <f>[1]SUMMARY!B8</f>
         <v>0</v>
       </c>
       <c r="S6" s="27">
-        <f>[1]SUMMARY!C8</f>
         <v>3</v>
       </c>
       <c r="T6" s="27">
-        <f>[1]SUMMARY!D8</f>
         <v>0</v>
       </c>
       <c r="U6" s="27">
-        <f>[1]SUMMARY!E8</f>
         <v>0</v>
       </c>
       <c r="V6" s="27">
         <v>0</v>
       </c>
       <c r="W6" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>75000</v>
       </c>
       <c r="AA6" t="s">
@@ -4808,16 +4564,16 @@
         <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>6920000</v>
+        <v>7420000</v>
       </c>
       <c r="AE6" s="28">
-        <v>6920000</v>
+        <v>7420000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4834,8 +4590,8 @@
       <c r="AM6" s="4">
         <v>4</v>
       </c>
-      <c r="AN6" s="5">
-        <v>46157</v>
+      <c r="AN6" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AO6" s="4" t="s">
         <v>25</v>
@@ -4877,62 +4633,56 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="H7" s="21">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="I7" s="21">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="J7" s="21">
         <v>509</v>
       </c>
-      <c r="K7" s="21">
-        <v>10</v>
-      </c>
+      <c r="K7" s="21"/>
       <c r="L7" s="22">
-        <f t="shared" si="1"/>
-        <v>1933</v>
+        <f t="shared" si="3"/>
+        <v>1857</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>257281700</v>
+        <v>273019300</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
       </c>
       <c r="R7" s="27">
-        <f>[1]SUMMARY!B9</f>
         <v>0</v>
       </c>
       <c r="S7" s="27">
-        <f>[1]SUMMARY!C9</f>
         <v>0</v>
       </c>
       <c r="T7" s="27">
-        <f>[1]SUMMARY!D9</f>
         <v>0</v>
       </c>
       <c r="U7" s="27">
-        <f>[1]SUMMARY!E9</f>
         <v>0</v>
       </c>
       <c r="V7" s="27">
         <v>0</v>
       </c>
       <c r="W7" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X7" s="4">
         <v>30000</v>
       </c>
       <c r="Y7" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA7" t="s">
@@ -4971,9 +4721,11 @@
       <c r="AM7" s="4">
         <v>5</v>
       </c>
-      <c r="AN7" s="5"/>
+      <c r="AN7" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="AO7" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="AP7" s="6" t="s">
         <v>90</v>
@@ -4987,11 +4739,11 @@
       <c r="AS7" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AT7" s="9"/>
+      <c r="AT7" s="9">
+        <v>410000</v>
+      </c>
       <c r="AU7" s="5"/>
-      <c r="AV7" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="AV7" s="4"/>
       <c r="AW7" s="5"/>
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.2">
@@ -5009,87 +4761,90 @@
       <c r="F8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="21">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21">
-        <v>0</v>
-      </c>
-      <c r="K8" s="21">
-        <v>0</v>
-      </c>
+      <c r="G8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="21"/>
       <c r="L8" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="27">
-        <f>[1]SUMMARY!B10</f>
         <v>0</v>
       </c>
       <c r="S8" s="27">
-        <f>[1]SUMMARY!C10</f>
         <v>0</v>
       </c>
       <c r="T8" s="27">
-        <f>[1]SUMMARY!D10</f>
         <v>0</v>
       </c>
       <c r="U8" s="27">
-        <f>[1]SUMMARY!E10</f>
         <v>0</v>
       </c>
       <c r="V8" s="27">
         <v>0</v>
       </c>
       <c r="W8" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8" s="19"/>
       <c r="Y8" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC8" s="28">
         <v>1058</v>
       </c>
       <c r="AD8" s="28">
-        <v>24630000</v>
+        <f>SUM(AD4:AD7)</f>
+        <v>26130000</v>
       </c>
       <c r="AE8" s="28">
-        <v>24630000</v>
+        <f>SUM(AE4:AE7)</f>
+        <v>26130000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
-        <v>86</v>
+        <f>SUM(AG4:AG7)</f>
+        <v>92</v>
       </c>
       <c r="AH8">
+        <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
         <v>4</v>
       </c>
       <c r="AI8">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ8">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AK8">
+        <f t="shared" si="4"/>
         <v>93</v>
       </c>
       <c r="AM8" s="4">
         <v>6</v>
       </c>
-      <c r="AN8" s="5"/>
+      <c r="AN8" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="AO8" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="AP8" s="6" t="s">
         <v>90</v>
@@ -5103,11 +4858,11 @@
       <c r="AS8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AT8" s="9"/>
+      <c r="AT8" s="9">
+        <v>410000</v>
+      </c>
       <c r="AU8" s="5"/>
-      <c r="AV8" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="AV8" s="4"/>
       <c r="AW8" s="5"/>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.2">
@@ -5123,60 +4878,56 @@
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
-        <v>0</v>
-      </c>
-      <c r="K9" s="21">
-        <v>0</v>
-      </c>
+      <c r="G9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="21"/>
       <c r="L9" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
-        <f>[1]SUMMARY!B11</f>
         <v>0</v>
       </c>
       <c r="S9" s="27">
-        <f>[1]SUMMARY!C11</f>
         <v>0</v>
       </c>
       <c r="T9" s="27">
-        <f>[1]SUMMARY!D11</f>
         <v>0</v>
       </c>
       <c r="U9" s="27">
-        <f>[1]SUMMARY!E11</f>
         <v>0</v>
       </c>
       <c r="V9" s="27">
         <v>0</v>
       </c>
       <c r="W9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AM9" s="4">
         <v>7</v>
       </c>
-      <c r="AN9" s="5"/>
+      <c r="AN9" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="AO9" s="4" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="AP9" s="6" t="s">
         <v>90</v>
@@ -5190,11 +4941,11 @@
       <c r="AS9" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="AT9" s="8"/>
+      <c r="AT9" s="8">
+        <v>410000</v>
+      </c>
       <c r="AU9" s="5"/>
-      <c r="AV9" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="AV9" s="4"/>
       <c r="AW9" s="5"/>
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.2">
@@ -5212,57 +4963,51 @@
         <v>2462</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21">
-        <v>0</v>
-      </c>
-      <c r="K10" s="21">
-        <v>0</v>
-      </c>
+      <c r="G10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="21"/>
       <c r="L10" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <f>[1]SUMMARY!B12</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="S10" s="27">
-        <f>[1]SUMMARY!C12</f>
         <v>369</v>
       </c>
       <c r="T10" s="27">
-        <f>[1]SUMMARY!D12</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="U10" s="27">
-        <f>[1]SUMMARY!E12</f>
         <v>0</v>
       </c>
       <c r="V10" s="27">
         <v>0</v>
       </c>
       <c r="W10" s="27">
-        <f t="shared" si="2"/>
-        <v>509</v>
+        <f>SUM(R10:V10)</f>
+        <v>539</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
-        <f t="shared" si="3"/>
-        <v>305400</v>
+        <f t="shared" si="2"/>
+        <v>323400</v>
       </c>
       <c r="AA10" t="s">
         <v>121</v>
@@ -5270,9 +5015,11 @@
       <c r="AM10" s="4">
         <v>8</v>
       </c>
-      <c r="AN10" s="5"/>
+      <c r="AN10" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="AO10" s="4" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AP10" s="6" t="s">
         <v>90</v>
@@ -5286,11 +5033,11 @@
       <c r="AS10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AT10" s="8"/>
+      <c r="AT10" s="8">
+        <v>410000</v>
+      </c>
       <c r="AU10" s="5"/>
-      <c r="AV10" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.2">
@@ -5311,55 +5058,49 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H11" s="21">
         <v>300</v>
       </c>
       <c r="I11" s="21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J11" s="21">
         <v>300</v>
       </c>
-      <c r="K11" s="21">
-        <v>0</v>
-      </c>
+      <c r="K11" s="21"/>
       <c r="L11" s="22">
-        <f t="shared" si="1"/>
-        <v>840</v>
+        <f t="shared" si="3"/>
+        <v>810</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
       </c>
       <c r="R11" s="27">
-        <f>[1]SUMMARY!B13</f>
         <v>0</v>
       </c>
       <c r="S11" s="27">
-        <f>[1]SUMMARY!C13</f>
         <v>2</v>
       </c>
       <c r="T11" s="27">
-        <f>[1]SUMMARY!D13</f>
         <v>0</v>
       </c>
       <c r="U11" s="27">
-        <f>[1]SUMMARY!E13</f>
         <v>0</v>
       </c>
       <c r="V11" s="27">
         <v>0</v>
       </c>
       <c r="W11" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="X11" s="4">
         <v>22500</v>
       </c>
       <c r="Y11" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>45000</v>
       </c>
       <c r="AA11" t="s">
@@ -5389,9 +5130,11 @@
       <c r="AM11" s="4">
         <v>9</v>
       </c>
-      <c r="AN11" s="5"/>
+      <c r="AN11" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="AO11" s="4" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="AP11" s="6" t="s">
         <v>90</v>
@@ -5405,11 +5148,11 @@
       <c r="AS11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AT11" s="8"/>
+      <c r="AT11" s="8">
+        <v>410000</v>
+      </c>
       <c r="AU11" s="5"/>
-      <c r="AV11" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.2">
@@ -5417,14 +5160,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C12" s="14">
         <v>976</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1056</v>
+        <v>996</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5432,8 +5175,8 @@
       <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="21">
-        <v>0</v>
+      <c r="H12" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I12" s="21">
         <v>4</v>
@@ -5441,45 +5184,39 @@
       <c r="J12" s="21">
         <v>4</v>
       </c>
-      <c r="K12" s="21">
-        <v>0</v>
-      </c>
+      <c r="K12" s="21"/>
       <c r="L12" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <f>[1]SUMMARY!B14</f>
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="S12" s="27">
-        <f>[1]SUMMARY!C14</f>
         <v>342</v>
       </c>
       <c r="T12" s="27">
-        <f>[1]SUMMARY!D14</f>
         <v>233</v>
       </c>
       <c r="U12" s="27">
-        <f>[1]SUMMARY!E14</f>
         <v>212</v>
       </c>
       <c r="V12" s="27">
         <v>0</v>
       </c>
       <c r="W12" s="27">
-        <f t="shared" si="2"/>
-        <v>1041</v>
+        <f t="shared" si="1"/>
+        <v>1066</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
-        <f t="shared" si="3"/>
-        <v>13741200</v>
+        <f t="shared" si="2"/>
+        <v>14071200</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5494,7 +5231,7 @@
         <v>630000</v>
       </c>
       <c r="AE12">
-        <v>250000</v>
+        <v>630000</v>
       </c>
       <c r="AF12">
         <v>63</v>
@@ -5549,7 +5286,7 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="H13" s="21">
         <v>47</v>
@@ -5560,44 +5297,38 @@
       <c r="J13" s="21">
         <v>102</v>
       </c>
-      <c r="K13" s="21">
-        <v>21</v>
-      </c>
+      <c r="K13" s="21"/>
       <c r="L13" s="22">
-        <f t="shared" si="1"/>
-        <v>258</v>
+        <f t="shared" si="3"/>
+        <v>272</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
       </c>
       <c r="R13" s="27">
-        <f>[1]SUMMARY!B15</f>
         <v>0</v>
       </c>
       <c r="S13" s="27">
-        <f>[1]SUMMARY!C15</f>
         <v>0</v>
       </c>
       <c r="T13" s="27">
-        <f>[1]SUMMARY!D15</f>
         <v>0</v>
       </c>
       <c r="U13" s="27">
-        <f>[1]SUMMARY!E15</f>
         <v>0</v>
       </c>
       <c r="V13" s="27">
         <v>0</v>
       </c>
       <c r="W13" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
         <v>20000</v>
       </c>
       <c r="Y13" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA13" t="s">
@@ -5613,7 +5344,7 @@
         <v>630000</v>
       </c>
       <c r="AE13">
-        <v>250000</v>
+        <v>630000</v>
       </c>
       <c r="AF13">
         <v>63</v>
@@ -5643,69 +5374,63 @@
         <v>12</v>
       </c>
       <c r="B14" s="13">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C14" s="14">
         <v>457</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="0"/>
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="21">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
-        <v>0</v>
-      </c>
+      <c r="G14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="21"/>
       <c r="L14" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q14" s="20" t="s">
         <v>34</v>
       </c>
       <c r="R14" s="27">
-        <f>[1]SUMMARY!B16</f>
         <v>21</v>
       </c>
       <c r="S14" s="27">
-        <f>[1]SUMMARY!C16</f>
         <v>19</v>
       </c>
       <c r="T14" s="27">
-        <f>[1]SUMMARY!D16</f>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="U14" s="27">
-        <f>[1]SUMMARY!E16</f>
         <v>43</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
       </c>
       <c r="W14" s="27">
-        <f t="shared" si="2"/>
-        <v>128</v>
+        <f t="shared" si="1"/>
+        <v>134</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
-        <f t="shared" si="3"/>
-        <v>1856000</v>
+        <f t="shared" si="2"/>
+        <v>1943000</v>
       </c>
       <c r="AA14" t="s">
         <v>77</v>
@@ -5720,7 +5445,7 @@
         <v>630000</v>
       </c>
       <c r="AE14">
-        <v>280000</v>
+        <v>630000</v>
       </c>
       <c r="AF14">
         <v>63</v>
@@ -5750,14 +5475,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="13">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="C15" s="14">
         <v>0</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5765,54 +5490,48 @@
       <c r="G15" s="21">
         <v>44</v>
       </c>
-      <c r="H15" s="21">
-        <v>0</v>
+      <c r="H15" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I15" s="21">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J15" s="21">
         <v>72</v>
       </c>
-      <c r="K15" s="21">
-        <v>0</v>
-      </c>
+      <c r="K15" s="21"/>
       <c r="L15" s="22">
-        <f t="shared" si="1"/>
-        <v>135</v>
+        <f t="shared" si="3"/>
+        <v>159</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <f>[1]SUMMARY!B17</f>
         <v>52</v>
       </c>
       <c r="S15" s="27">
-        <f>[1]SUMMARY!C17</f>
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="T15" s="27">
-        <f>[1]SUMMARY!D17</f>
         <v>75</v>
       </c>
       <c r="U15" s="27">
-        <f>[1]SUMMARY!E17</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="V15" s="27">
         <v>0</v>
       </c>
       <c r="W15" s="27">
-        <f t="shared" si="2"/>
-        <v>304</v>
+        <f t="shared" si="1"/>
+        <v>319</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
-        <f t="shared" si="3"/>
-        <v>5244000</v>
+        <f t="shared" si="2"/>
+        <v>5502750</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5827,7 +5546,7 @@
         <v>630000</v>
       </c>
       <c r="AE15">
-        <v>230000</v>
+        <v>630000</v>
       </c>
       <c r="AF15">
         <v>63</v>
@@ -5873,53 +5592,71 @@
         <v>99</v>
       </c>
       <c r="H16" s="21">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I16" s="21">
         <v>40</v>
       </c>
       <c r="J16" s="21">
-        <v>101</v>
-      </c>
-      <c r="K16" s="21">
-        <v>21</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="K16" s="21"/>
       <c r="L16" s="22">
-        <f t="shared" si="1"/>
-        <v>297</v>
+        <f t="shared" si="3"/>
+        <v>321</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
       </c>
       <c r="R16" s="27">
-        <f>[1]SUMMARY!B18</f>
         <v>24</v>
       </c>
       <c r="S16" s="27">
-        <f>[1]SUMMARY!C18</f>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T16" s="27">
-        <f>[1]SUMMARY!D18</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U16" s="27">
-        <f>[1]SUMMARY!E18</f>
         <v>3</v>
       </c>
       <c r="V16" s="27">
         <v>0</v>
       </c>
       <c r="W16" s="27">
-        <f t="shared" si="2"/>
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>85</v>
       </c>
       <c r="X16" s="4">
         <v>23000</v>
       </c>
       <c r="Y16" s="27">
-        <f t="shared" si="3"/>
-        <v>1748000</v>
+        <f t="shared" si="2"/>
+        <v>1955000</v>
+      </c>
+      <c r="AC16">
+        <f>SUM(AC12:AC15)</f>
+        <v>252</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" ref="AD16:AH16" si="5">SUM(AD12:AD15)</f>
+        <v>2520000</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="5"/>
+        <v>2520000</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="5"/>
+        <v>252</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="5"/>
+        <v>252</v>
       </c>
       <c r="AM16" s="4">
         <v>14</v>
@@ -5940,10 +5677,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="13">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="13">
         <f t="shared" si="0"/>
@@ -5956,52 +5693,46 @@
         <v>46</v>
       </c>
       <c r="H17" s="21">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I17" s="21">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J17" s="21">
         <v>48</v>
       </c>
-      <c r="K17" s="21">
-        <v>22</v>
-      </c>
+      <c r="K17" s="21"/>
       <c r="L17" s="22">
-        <f t="shared" si="1"/>
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>174</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
       </c>
       <c r="R17" s="27">
-        <f>[1]SUMMARY!B19</f>
         <v>3</v>
       </c>
       <c r="S17" s="27">
-        <f>[1]SUMMARY!C19</f>
         <v>12</v>
       </c>
       <c r="T17" s="27">
-        <f>[1]SUMMARY!D19</f>
         <v>0</v>
       </c>
       <c r="U17" s="27">
-        <f>[1]SUMMARY!E19</f>
         <v>0</v>
       </c>
       <c r="V17" s="27">
         <v>0</v>
       </c>
       <c r="W17" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
       <c r="Y17" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>450000</v>
       </c>
       <c r="AM17" s="4">
@@ -6047,45 +5778,39 @@
       <c r="J18" s="21">
         <v>20</v>
       </c>
-      <c r="K18" s="21">
-        <v>0</v>
-      </c>
+      <c r="K18" s="21"/>
       <c r="L18" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
       <c r="Q18" s="20" t="s">
         <v>16</v>
       </c>
       <c r="R18" s="27">
-        <f>[1]SUMMARY!B20</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S18" s="27">
-        <f>[1]SUMMARY!C20</f>
         <v>0</v>
       </c>
       <c r="T18" s="27">
-        <f>[1]SUMMARY!D20</f>
         <v>0</v>
       </c>
       <c r="U18" s="27">
-        <f>[1]SUMMARY!E20</f>
         <v>0</v>
       </c>
       <c r="V18" s="27">
         <v>0</v>
       </c>
       <c r="W18" s="27">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>32</v>
       </c>
       <c r="X18" s="4">
         <v>6900</v>
       </c>
       <c r="Y18" s="27">
-        <f t="shared" si="3"/>
-        <v>213900</v>
+        <f t="shared" si="2"/>
+        <v>220800</v>
       </c>
       <c r="AM18" s="4">
         <v>16</v>
@@ -6119,55 +5844,49 @@
         <v>16</v>
       </c>
       <c r="G19" s="21">
-        <v>11</v>
-      </c>
-      <c r="H19" s="21">
-        <v>0</v>
-      </c>
-      <c r="I19" s="21">
-        <v>0</v>
-      </c>
-      <c r="J19" s="21">
-        <v>0</v>
-      </c>
-      <c r="K19" s="21">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="21"/>
       <c r="L19" s="22">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>17</v>
       </c>
       <c r="R19" s="27">
-        <f>[1]SUMMARY!B21</f>
         <v>0</v>
       </c>
       <c r="S19" s="27">
-        <f>[1]SUMMARY!C21</f>
         <v>0</v>
       </c>
       <c r="T19" s="27">
-        <f>[1]SUMMARY!D21</f>
         <v>0</v>
       </c>
       <c r="U19" s="27">
-        <f>[1]SUMMARY!E21</f>
         <v>9</v>
       </c>
       <c r="V19" s="27">
         <v>0</v>
       </c>
       <c r="W19" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X19" s="4">
         <v>7000</v>
       </c>
       <c r="Y19" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>63000</v>
       </c>
     </row>
@@ -6191,53 +5910,47 @@
       <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="21">
-        <v>0</v>
-      </c>
-      <c r="I20" s="21">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21">
-        <v>0</v>
-      </c>
-      <c r="K20" s="21">
-        <v>0</v>
-      </c>
+      <c r="H20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="21"/>
       <c r="L20" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q20" s="20" t="s">
         <v>18</v>
       </c>
       <c r="R20" s="27">
-        <f>[1]SUMMARY!B22</f>
         <v>0</v>
       </c>
       <c r="S20" s="27">
-        <f>[1]SUMMARY!C22</f>
         <v>0</v>
       </c>
       <c r="T20" s="27">
-        <f>[1]SUMMARY!D22</f>
         <v>0</v>
       </c>
       <c r="U20" s="27">
-        <f>[1]SUMMARY!E22</f>
         <v>0</v>
       </c>
       <c r="V20" s="27">
         <v>0</v>
       </c>
       <c r="W20" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X20" s="4">
         <v>12000</v>
       </c>
       <c r="Y20" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6270,44 +5983,38 @@
       <c r="J21" s="21">
         <v>6</v>
       </c>
-      <c r="K21" s="21">
-        <v>0</v>
-      </c>
+      <c r="K21" s="21"/>
       <c r="L21" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>114</v>
       </c>
       <c r="Q21" s="20" t="s">
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <f>[1]SUMMARY!B23</f>
         <v>75</v>
       </c>
       <c r="S21" s="27">
-        <f>[1]SUMMARY!C23</f>
         <v>65</v>
       </c>
       <c r="T21" s="27">
-        <f>[1]SUMMARY!D23</f>
         <v>33</v>
       </c>
       <c r="U21" s="27">
-        <f>[1]SUMMARY!E23</f>
         <v>15</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>188</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1804800</v>
       </c>
     </row>
@@ -6331,8 +6038,8 @@
       <c r="G22" s="21">
         <v>132</v>
       </c>
-      <c r="H22" s="21">
-        <v>0</v>
+      <c r="H22" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I22" s="21">
         <v>91</v>
@@ -6340,44 +6047,38 @@
       <c r="J22" s="21">
         <v>65</v>
       </c>
-      <c r="K22" s="21">
-        <v>12</v>
-      </c>
+      <c r="K22" s="21"/>
       <c r="L22" s="22">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <f t="shared" si="3"/>
+        <v>288</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
       </c>
       <c r="R22" s="27">
-        <f>[1]SUMMARY!B24</f>
         <v>0</v>
       </c>
       <c r="S22" s="27">
-        <f>[1]SUMMARY!C24</f>
         <v>0</v>
       </c>
       <c r="T22" s="27">
-        <f>[1]SUMMARY!D24</f>
         <v>0</v>
       </c>
       <c r="U22" s="27">
-        <f>[1]SUMMARY!E24</f>
         <v>0</v>
       </c>
       <c r="V22" s="27">
         <v>0</v>
       </c>
       <c r="W22" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X22" s="4">
         <v>13200</v>
       </c>
       <c r="Y22" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -6397,12 +6098,10 @@
       <c r="J23" s="21">
         <v>55</v>
       </c>
-      <c r="K23" s="21">
-        <v>9</v>
-      </c>
+      <c r="K23" s="21"/>
       <c r="L23" s="22">
-        <f t="shared" si="1"/>
-        <v>82</v>
+        <f t="shared" si="3"/>
+        <v>73</v>
       </c>
       <c r="Q23" s="20"/>
       <c r="R23" s="27">
@@ -6446,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q24" s="20"/>
@@ -6491,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q25" s="23" t="s">
@@ -6499,32 +6198,32 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>572</v>
+        <v>608</v>
       </c>
       <c r="S25" s="19">
-        <f t="shared" ref="S25:Y25" si="4">SUM(S4:S24)</f>
-        <v>1015</v>
+        <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
+        <v>1030</v>
       </c>
       <c r="T25" s="19">
-        <f t="shared" si="4"/>
-        <v>445</v>
+        <f t="shared" si="6"/>
+        <v>479</v>
       </c>
       <c r="U25" s="19">
-        <f t="shared" si="4"/>
-        <v>363</v>
+        <f t="shared" si="6"/>
+        <v>379</v>
       </c>
       <c r="V25" s="19">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="W25" s="19">
-        <f t="shared" si="4"/>
-        <v>2405</v>
+        <f t="shared" si="6"/>
+        <v>2496</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
-        <f t="shared" si="4"/>
-        <v>26635300</v>
+        <f t="shared" si="6"/>
+        <v>27597950</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.2">
@@ -6532,28 +6231,28 @@
         <v>27</v>
       </c>
       <c r="G26" s="24">
-        <f t="shared" ref="G26:L26" si="5">SUM(G5:G25)</f>
-        <v>1232</v>
+        <f t="shared" ref="G26:L26" si="7">SUM(G5:G25)</f>
+        <v>1234</v>
       </c>
       <c r="H26" s="24">
-        <f t="shared" si="5"/>
-        <v>870</v>
+        <f t="shared" si="7"/>
+        <v>943</v>
       </c>
       <c r="I26" s="24">
-        <f t="shared" si="5"/>
-        <v>940</v>
+        <f t="shared" si="7"/>
+        <v>964</v>
       </c>
       <c r="J26" s="24">
-        <f t="shared" si="5"/>
-        <v>1401</v>
+        <f t="shared" si="7"/>
+        <v>1385</v>
       </c>
       <c r="K26" s="24">
-        <f t="shared" si="5"/>
-        <v>117</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="L26" s="24">
-        <f t="shared" si="5"/>
-        <v>4560</v>
+        <f>SUM(L5:L25)</f>
+        <v>4526</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Git-hub/MC-SAGARANTEN.WEB-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7A2EB4-9A5E-4836-B430-91F010AEEDFA}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62656D4D-4838-4DA6-8E4E-60A664803232}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="127">
   <si>
     <t>nama barang</t>
   </si>
@@ -417,13 +409,13 @@
     <t>Muhammad Parhan</t>
   </si>
   <si>
-    <t>15-May-2026</t>
-  </si>
-  <si>
-    <t>21-May-2026</t>
-  </si>
-  <si>
     <t>CSM</t>
+  </si>
+  <si>
+    <t>REWARD</t>
+  </si>
+  <si>
+    <t>RETURE</t>
   </si>
 </sst>
 </file>
@@ -431,8 +423,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -654,8 +646,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="43">
@@ -717,16 +709,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -752,8 +744,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
-    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -782,9 +774,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -822,7 +814,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -928,7 +920,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1070,7 +1062,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1079,15 +1071,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1101,13 +1093,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
         <f>index!B4</f>
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="C3">
         <f>index!C4</f>
@@ -1115,10 +1107,10 @@
       </c>
       <c r="D3" s="1">
         <f>B3+C3</f>
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1135,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1152,7 +1144,7 @@
         <v>3051</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1169,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1183,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1197,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1214,7 +1206,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1231,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1248,7 +1240,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1265,7 +1257,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1282,7 +1274,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1299,7 +1291,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1316,7 +1308,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1333,7 +1325,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1350,7 +1342,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1367,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1384,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1401,7 +1393,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1426,18 +1418,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1460,13 +1452,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
@@ -1474,7 +1466,7 @@
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
@@ -1482,135 +1474,135 @@
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3">
         <f>index!G6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C3" t="str">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <f>index!H6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D3" t="str">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <f>index!I6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E3" t="str">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <f>index!J6</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G22" si="0">SUM(B3:F3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5">
         <f>index!G8</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C5" t="str">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <f>index!H8</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D5" t="str">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <f>index!I8</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <f>index!J8</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" t="str">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6">
         <f>index!G9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C6" t="str">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <f>index!H9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D6" t="str">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <f>index!I9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E6" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <f>index!J9</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" t="str">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7">
         <f>index!G10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C7" t="str">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <f>index!H10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <f>index!I10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <f>index!J10</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
@@ -1626,10 +1618,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>810</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1637,9 +1629,9 @@
         <f>index!G12</f>
         <v>5</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9">
         <f>index!H12</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f>index!I12</f>
@@ -1654,7 +1646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1664,11 +1656,11 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
@@ -1676,35 +1668,35 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11">
         <f>index!G14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C11" t="str">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <f>index!H14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D11" t="str">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <f>index!I14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E11" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <f>index!J14</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1712,9 +1704,9 @@
         <f>index!G15</f>
         <v>44</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12">
         <f>index!H15</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
@@ -1729,21 +1721,21 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1751,10 +1743,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1779,7 +1771,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1804,32 +1796,32 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16">
         <f>index!G19</f>
-        <v>10</v>
-      </c>
-      <c r="C16" t="str">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <f>index!H19</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D16" t="str">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <f>index!I19</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E16" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <f>index!J19</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1837,24 +1829,24 @@
         <f>index!G20</f>
         <v>1</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17">
         <f>index!H20</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D17" t="str">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <f>index!I20</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <f>index!J20</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1879,7 +1871,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1887,9 +1879,9 @@
         <f>index!G22</f>
         <v>132</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19">
         <f>index!H22</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -1897,14 +1889,14 @@
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1929,7 +1921,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1950,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1971,25 +1963,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1234</v>
+        <v>1175</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>943</v>
+        <v>891</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>964</v>
+        <v>906</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1385</v>
+        <v>1368</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1997,7 +1989,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4526</v>
+        <v>4340</v>
       </c>
     </row>
   </sheetData>
@@ -2008,13 +2000,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2022,49 +2014,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>123</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>54302400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>56815800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>78757400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85327400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>62427000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>65993500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>77532500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>82649500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>273019300</v>
+        <v>290786200</v>
       </c>
     </row>
   </sheetData>
@@ -2075,17 +2067,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -2111,7 +2103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>51</v>
       </c>
@@ -2125,13 +2117,13 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <f>index!R4</f>
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <f>index!S4</f>
@@ -2139,7 +2131,7 @@
       </c>
       <c r="D3">
         <f>index!T4</f>
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <f>index!U4</f>
@@ -2147,17 +2139,17 @@
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>1144000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1639000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2189,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -2221,7 +2213,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2253,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!R8</f>
         <v>0</v>
@@ -2279,7 +2271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!R9</f>
         <v>0</v>
@@ -2305,13 +2297,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
         <f>index!R10</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C9">
         <f>index!S10</f>
@@ -2327,17 +2319,17 @@
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>323400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>329400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2369,7 +2361,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2379,11 +2371,11 @@
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E11">
         <f>index!U12</f>
@@ -2391,17 +2383,17 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>14071200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>14427600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2433,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2465,21 +2457,21 @@
         <v>1943000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14">
         <f>index!R15</f>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
@@ -2487,17 +2479,17 @@
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>5502750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>6106500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2529,7 +2521,7 @@
         <v>1955000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2561,13 +2553,13 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
         <f>index!R18</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <f>index!S18</f>
@@ -2583,17 +2575,17 @@
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>220800</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>289800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2625,7 +2617,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2657,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2675,21 +2667,21 @@
       </c>
       <c r="E20">
         <f>index!U21</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>1804800</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1862400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2721,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B22">
         <f>index!R23</f>
         <v>0</v>
@@ -2747,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B23">
         <f>index!R24</f>
         <v>0</v>
@@ -2773,33 +2765,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24">
-        <f t="shared" ref="B24:G24" si="2">SUM(B3:B23)</f>
-        <v>608</v>
+        <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
+        <v>658</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>479</v>
+        <v>526</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2496</v>
+        <v>2629</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>27597950</v>
+        <v>29185700</v>
       </c>
     </row>
   </sheetData>
@@ -2810,20 +2802,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2837,7 +2829,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>59</v>
       </c>
@@ -2866,7 +2858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2879,11 +2871,11 @@
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>6750000</v>
+        <v>7250000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>6750000</v>
+        <v>7250000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2891,7 +2883,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2907,10 +2899,10 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -2923,11 +2915,11 @@
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>6085000</v>
+        <v>6585000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>6085000</v>
+        <v>6585000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2935,7 +2927,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2951,10 +2943,10 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2967,11 +2959,11 @@
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>7420000</v>
+        <v>7670000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>7420000</v>
+        <v>7670000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2979,7 +2971,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2995,10 +2987,10 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3011,11 +3003,11 @@
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>5875000</v>
+        <v>6125000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>5875000</v>
+        <v>6125000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3023,7 +3015,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3039,21 +3031,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
         <v>1058</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>26130000</v>
+        <v>27630000</v>
       </c>
       <c r="E7" s="28">
-        <f t="shared" ref="D7:F7" si="1">SUM(E3:E6)</f>
-        <v>26130000</v>
+        <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
+        <v>27630000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3061,7 +3053,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3077,7 +3069,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3088,19 +3080,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -3126,7 +3118,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -3157,7 +3149,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -3188,7 +3180,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -3219,7 +3211,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -3250,7 +3242,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3284,19 +3276,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.87109375" customWidth="1"/>
-    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -3331,13 +3323,13 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="5">
         <f>index!AN3</f>
-        <v>15-May-2026</v>
+        <v>46157</v>
       </c>
       <c r="C2" s="4" t="str">
         <f>index!AO3</f>
@@ -3373,13 +3365,13 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="5">
         <f>index!AN4</f>
-        <v>15-May-2026</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>index!AO4</f>
@@ -3415,13 +3407,13 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="str">
+      <c r="B4" s="5">
         <f>index!AN5</f>
-        <v>15-May-2026</v>
+        <v>46157</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>index!AO5</f>
@@ -3460,13 +3452,13 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="5">
         <f>index!AN6</f>
-        <v>15-May-2026</v>
+        <v>46157</v>
       </c>
       <c r="C5" s="4" t="str">
         <f>index!AO6</f>
@@ -3502,13 +3494,13 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="str">
+      <c r="B6" s="5">
         <f>index!AN7</f>
-        <v>21-May-2026</v>
+        <v>46163</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>index!AO7</f>
@@ -3538,19 +3530,19 @@
         <f>index!AU7</f>
         <v>0</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="4" t="str">
         <f>index!AV7</f>
-        <v>0</v>
+        <v>SEGEL</v>
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="str">
+      <c r="B7" s="5">
         <f>index!AN8</f>
-        <v>21-May-2026</v>
+        <v>46163</v>
       </c>
       <c r="C7" s="4" t="str">
         <f>index!AO8</f>
@@ -3580,19 +3572,19 @@
         <f>index!AU8</f>
         <v>0</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="4" t="str">
         <f>index!AV8</f>
-        <v>0</v>
+        <v>SEGEL</v>
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="str">
+      <c r="B8" s="5">
         <f>index!AN9</f>
-        <v>21-May-2026</v>
+        <v>46163</v>
       </c>
       <c r="C8" s="4" t="str">
         <f>index!AO9</f>
@@ -3622,19 +3614,19 @@
         <f>index!AU9</f>
         <v>0</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="4" t="str">
         <f>index!AV9</f>
-        <v>0</v>
+        <v>SEGEL</v>
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="str">
+      <c r="B9" s="5">
         <f>index!AN10</f>
-        <v>21-May-2026</v>
+        <v>46163</v>
       </c>
       <c r="C9" s="4" t="str">
         <f>index!AO10</f>
@@ -3664,19 +3656,19 @@
         <f>index!AU10</f>
         <v>0</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="4" t="str">
         <f>index!AV10</f>
-        <v>0</v>
+        <v>SEGEL</v>
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="str">
+      <c r="B10" s="5">
         <f>index!AN11</f>
-        <v>21-May-2026</v>
+        <v>46163</v>
       </c>
       <c r="C10" s="4" t="str">
         <f>index!AO11</f>
@@ -3700,25 +3692,25 @@
       </c>
       <c r="H10" s="8">
         <f>index!AT11</f>
-        <v>410000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
         <f>index!AU11</f>
         <v>0</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="4" t="str">
         <f>index!AV11</f>
-        <v>0</v>
+        <v>REWARD</v>
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5">
         <f>index!AN12</f>
-        <v>0</v>
+        <v>46164</v>
       </c>
       <c r="C11" s="4" t="str">
         <f>index!AO12</f>
@@ -3750,11 +3742,11 @@
       </c>
       <c r="J11" s="4" t="str">
         <f>index!AV12</f>
-        <v>SEGEL</v>
+        <v>RETURE</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3793,7 +3785,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3832,7 +3824,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3871,7 +3863,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3910,7 +3902,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3949,7 +3941,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J19" t="s">
         <v>97</v>
       </c>
@@ -4001,17 +3993,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>114</v>
       </c>
@@ -4031,7 +4023,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="36" t="s">
         <v>0</v>
       </c>
@@ -4132,7 +4124,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A3" s="37"/>
       <c r="B3" s="37"/>
       <c r="C3" s="37"/>
@@ -4148,7 +4140,7 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>54302400</v>
+        <v>56815800</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4199,8 +4191,8 @@
       <c r="AM3" s="4">
         <v>1</v>
       </c>
-      <c r="AN3" s="5" t="s">
-        <v>124</v>
+      <c r="AN3" s="5">
+        <v>46157</v>
       </c>
       <c r="AO3" s="4" t="s">
         <v>89</v>
@@ -4224,19 +4216,19 @@
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="13">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="C4" s="14">
         <v>0</v>
       </c>
       <c r="D4" s="13">
         <f>C4+B4</f>
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>21</v>
@@ -4263,19 +4255,19 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>78757400</v>
+        <v>85327400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="S4" s="27">
         <v>12</v>
       </c>
       <c r="T4" s="27">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="U4" s="27">
         <v>58</v>
@@ -4285,14 +4277,14 @@
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>1144000</v>
+        <v>1639000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4304,16 +4296,16 @@
         <v>275</v>
       </c>
       <c r="AD4" s="28">
-        <v>6750000</v>
+        <v>7250000</v>
       </c>
       <c r="AE4" s="28">
-        <v>6750000</v>
+        <v>7250000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4330,8 +4322,8 @@
       <c r="AM4" s="4">
         <v>2</v>
       </c>
-      <c r="AN4" s="5" t="s">
-        <v>124</v>
+      <c r="AN4" s="5">
+        <v>46157</v>
       </c>
       <c r="AO4" s="4" t="s">
         <v>22</v>
@@ -4355,7 +4347,7 @@
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4373,27 +4365,29 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H5" s="21">
         <v>50</v>
       </c>
       <c r="I5" s="21">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J5" s="21">
         <v>109</v>
       </c>
-      <c r="K5" s="21"/>
+      <c r="K5" s="21">
+        <v>22</v>
+      </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>62427000</v>
+        <v>65993500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4434,16 +4428,16 @@
         <v>237</v>
       </c>
       <c r="AD5" s="28">
-        <v>6085000</v>
+        <v>6585000</v>
       </c>
       <c r="AE5" s="28">
-        <v>6085000</v>
+        <v>6585000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4460,8 +4454,8 @@
       <c r="AM5" s="4">
         <v>3</v>
       </c>
-      <c r="AN5" s="5" t="s">
-        <v>124</v>
+      <c r="AN5" s="5">
+        <v>46157</v>
       </c>
       <c r="AO5" s="4" t="s">
         <v>24</v>
@@ -4485,7 +4479,7 @@
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4502,28 +4496,30 @@
       <c r="F6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="21"/>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21">
+        <v>0</v>
+      </c>
+      <c r="K6" s="21">
+        <v>0</v>
+      </c>
       <c r="L6" s="22">
-        <f t="shared" ref="L5:L25" si="3">SUM(G6:K6)</f>
+        <f t="shared" ref="L6:L25" si="3">SUM(G6:K6)</f>
         <v>0</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>77532500</v>
+        <v>82649500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4564,16 +4560,16 @@
         <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>7420000</v>
+        <v>7670000</v>
       </c>
       <c r="AE6" s="28">
-        <v>7420000</v>
+        <v>7670000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4590,8 +4586,8 @@
       <c r="AM6" s="4">
         <v>4</v>
       </c>
-      <c r="AN6" s="5" t="s">
-        <v>124</v>
+      <c r="AN6" s="5">
+        <v>46157</v>
       </c>
       <c r="AO6" s="4" t="s">
         <v>25</v>
@@ -4615,7 +4611,7 @@
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4633,28 +4629,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="H7" s="21">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="I7" s="21">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="J7" s="21">
-        <v>509</v>
-      </c>
-      <c r="K7" s="21"/>
+        <v>498</v>
+      </c>
+      <c r="K7" s="21">
+        <v>10</v>
+      </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1857</v>
+        <v>1801</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>273019300</v>
+        <v>290786200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4695,16 +4693,16 @@
         <v>260</v>
       </c>
       <c r="AD7" s="28">
-        <v>5875000</v>
+        <v>6125000</v>
       </c>
       <c r="AE7" s="28">
-        <v>5875000</v>
+        <v>6125000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4721,8 +4719,8 @@
       <c r="AM7" s="4">
         <v>5</v>
       </c>
-      <c r="AN7" s="5" t="s">
-        <v>125</v>
+      <c r="AN7" s="5">
+        <v>46163</v>
       </c>
       <c r="AO7" s="4" t="s">
         <v>89</v>
@@ -4743,10 +4741,12 @@
         <v>410000</v>
       </c>
       <c r="AU7" s="5"/>
-      <c r="AV7" s="4"/>
+      <c r="AV7" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4761,19 +4761,21 @@
       <c r="F8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="21"/>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21">
+        <v>0</v>
+      </c>
       <c r="L8" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4808,18 +4810,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>26130000</v>
+        <v>27630000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>26130000</v>
+        <v>27630000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4840,8 +4842,8 @@
       <c r="AM8" s="4">
         <v>6</v>
       </c>
-      <c r="AN8" s="5" t="s">
-        <v>125</v>
+      <c r="AN8" s="5">
+        <v>46163</v>
       </c>
       <c r="AO8" s="4" t="s">
         <v>22</v>
@@ -4862,10 +4864,12 @@
         <v>410000</v>
       </c>
       <c r="AU8" s="5"/>
-      <c r="AV8" s="4"/>
+      <c r="AV8" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4878,19 +4882,21 @@
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="21"/>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21">
+        <v>0</v>
+      </c>
+      <c r="K9" s="21">
+        <v>0</v>
+      </c>
       <c r="L9" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4923,8 +4929,8 @@
       <c r="AM9" s="4">
         <v>7</v>
       </c>
-      <c r="AN9" s="5" t="s">
-        <v>125</v>
+      <c r="AN9" s="5">
+        <v>46163</v>
       </c>
       <c r="AO9" s="4" t="s">
         <v>24</v>
@@ -4945,10 +4951,12 @@
         <v>410000</v>
       </c>
       <c r="AU9" s="5"/>
-      <c r="AV9" s="4"/>
+      <c r="AV9" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -4963,19 +4971,21 @@
         <v>2462</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="21"/>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0</v>
+      </c>
+      <c r="K10" s="21">
+        <v>0</v>
+      </c>
       <c r="L10" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4984,7 +4994,7 @@
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="S10" s="27">
         <v>369</v>
@@ -5000,14 +5010,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="2"/>
-        <v>323400</v>
+        <v>329400</v>
       </c>
       <c r="AA10" t="s">
         <v>121</v>
@@ -5015,8 +5025,8 @@
       <c r="AM10" s="4">
         <v>8</v>
       </c>
-      <c r="AN10" s="5" t="s">
-        <v>125</v>
+      <c r="AN10" s="5">
+        <v>46163</v>
       </c>
       <c r="AO10" s="4" t="s">
         <v>25</v>
@@ -5037,10 +5047,12 @@
         <v>410000</v>
       </c>
       <c r="AU10" s="5"/>
-      <c r="AV10" s="4"/>
+      <c r="AV10" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5058,7 +5070,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H11" s="21">
         <v>300</v>
@@ -5069,10 +5081,12 @@
       <c r="J11" s="21">
         <v>300</v>
       </c>
-      <c r="K11" s="21"/>
+      <c r="K11" s="21">
+        <v>0</v>
+      </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5130,11 +5144,11 @@
       <c r="AM11" s="4">
         <v>9</v>
       </c>
-      <c r="AN11" s="5" t="s">
-        <v>125</v>
+      <c r="AN11" s="5">
+        <v>46163</v>
       </c>
       <c r="AO11" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AP11" s="6" t="s">
         <v>90</v>
@@ -5148,14 +5162,14 @@
       <c r="AS11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AT11" s="8">
-        <v>410000</v>
-      </c>
+      <c r="AT11" s="8"/>
       <c r="AU11" s="5"/>
-      <c r="AV11" s="4"/>
+      <c r="AV11" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
@@ -5175,8 +5189,8 @@
       <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="21" t="s">
-        <v>28</v>
+      <c r="H12" s="21">
+        <v>0</v>
       </c>
       <c r="I12" s="21">
         <v>4</v>
@@ -5184,7 +5198,9 @@
       <c r="J12" s="21">
         <v>4</v>
       </c>
-      <c r="K12" s="21"/>
+      <c r="K12" s="21">
+        <v>0</v>
+      </c>
       <c r="L12" s="22">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -5196,10 +5212,10 @@
         <v>279</v>
       </c>
       <c r="S12" s="27">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="T12" s="27">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="U12" s="27">
         <v>212</v>
@@ -5209,14 +5225,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>14071200</v>
+        <v>14427600</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5245,7 +5261,9 @@
       <c r="AM12" s="4">
         <v>10</v>
       </c>
-      <c r="AN12" s="5"/>
+      <c r="AN12" s="5">
+        <v>46164</v>
+      </c>
       <c r="AO12" s="4" t="s">
         <v>100</v>
       </c>
@@ -5264,11 +5282,11 @@
       <c r="AT12" s="9"/>
       <c r="AU12" s="5"/>
       <c r="AV12" s="4" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5289,18 +5307,20 @@
         <v>87</v>
       </c>
       <c r="H13" s="21">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I13" s="21">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J13" s="21">
         <v>102</v>
       </c>
-      <c r="K13" s="21"/>
+      <c r="K13" s="21">
+        <v>21</v>
+      </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5369,7 +5389,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5386,19 +5406,21 @@
       <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="21"/>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21">
+        <v>0</v>
+      </c>
       <c r="L14" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5470,7 +5492,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5490,8 +5512,8 @@
       <c r="G15" s="21">
         <v>44</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>28</v>
+      <c r="H15" s="21">
+        <v>0</v>
       </c>
       <c r="I15" s="21">
         <v>43</v>
@@ -5499,7 +5521,9 @@
       <c r="J15" s="21">
         <v>72</v>
       </c>
-      <c r="K15" s="21"/>
+      <c r="K15" s="21">
+        <v>0</v>
+      </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
         <v>159</v>
@@ -5508,13 +5532,13 @@
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="S15" s="27">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="T15" s="27">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="U15" s="27">
         <v>39</v>
@@ -5524,14 +5548,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>5502750</v>
+        <v>6106500</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5571,7 +5595,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5589,21 +5613,23 @@
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H16" s="21">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I16" s="21">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J16" s="21">
         <v>95</v>
       </c>
-      <c r="K16" s="21"/>
+      <c r="K16" s="21">
+        <v>21</v>
+      </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5672,7 +5698,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5701,10 +5727,12 @@
       <c r="J17" s="21">
         <v>48</v>
       </c>
-      <c r="K17" s="21"/>
+      <c r="K17" s="21">
+        <v>22</v>
+      </c>
       <c r="L17" s="22">
         <f t="shared" si="3"/>
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -5749,7 +5777,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5778,7 +5806,9 @@
       <c r="J18" s="21">
         <v>20</v>
       </c>
-      <c r="K18" s="21"/>
+      <c r="K18" s="21">
+        <v>0</v>
+      </c>
       <c r="L18" s="22">
         <f t="shared" si="3"/>
         <v>123</v>
@@ -5787,7 +5817,7 @@
         <v>16</v>
       </c>
       <c r="R18" s="27">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="S18" s="27">
         <v>0</v>
@@ -5803,14 +5833,14 @@
       </c>
       <c r="W18" s="27">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="X18" s="4">
         <v>6900</v>
       </c>
       <c r="Y18" s="27">
         <f t="shared" si="2"/>
-        <v>220800</v>
+        <v>289800</v>
       </c>
       <c r="AM18" s="4">
         <v>16</v>
@@ -5826,7 +5856,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5844,21 +5874,23 @@
         <v>16</v>
       </c>
       <c r="G19" s="21">
-        <v>10</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
       <c r="L19" s="22">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>17</v>
@@ -5890,7 +5922,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5910,16 +5942,18 @@
       <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="21"/>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <v>0</v>
+      </c>
+      <c r="K20" s="21">
+        <v>0</v>
+      </c>
       <c r="L20" s="22">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -5954,7 +5988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -5983,7 +6017,9 @@
       <c r="J21" s="21">
         <v>6</v>
       </c>
-      <c r="K21" s="21"/>
+      <c r="K21" s="21">
+        <v>0</v>
+      </c>
       <c r="L21" s="22">
         <f t="shared" si="3"/>
         <v>114</v>
@@ -6001,24 +6037,24 @@
         <v>33</v>
       </c>
       <c r="U21" s="27">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>1804800</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+        <v>1862400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6038,19 +6074,21 @@
       <c r="G22" s="21">
         <v>132</v>
       </c>
-      <c r="H22" s="21" t="s">
-        <v>28</v>
+      <c r="H22" s="21">
+        <v>0</v>
       </c>
       <c r="I22" s="21">
         <v>91</v>
       </c>
       <c r="J22" s="21">
-        <v>65</v>
-      </c>
-      <c r="K22" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="K22" s="21">
+        <v>12</v>
+      </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6082,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6098,10 +6136,12 @@
       <c r="J23" s="21">
         <v>55</v>
       </c>
-      <c r="K23" s="21"/>
+      <c r="K23" s="21">
+        <v>9</v>
+      </c>
       <c r="L23" s="22">
         <f t="shared" si="3"/>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="20"/>
       <c r="R23" s="27">
@@ -6127,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6172,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6198,19 +6238,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>608</v>
+        <v>658</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>479</v>
+        <v>526</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6218,41 +6258,41 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2496</v>
+        <v>2629</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>27597950</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+        <v>29185700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
-        <f t="shared" ref="G26:L26" si="7">SUM(G5:G25)</f>
-        <v>1234</v>
+        <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
+        <v>1175</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>943</v>
+        <v>891</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>964</v>
+        <v>906</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1385</v>
+        <v>1368</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4526</v>
+        <v>4457</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62656D4D-4838-4DA6-8E4E-60A664803232}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A9F184-7C14-47F2-86D9-0A96B9A7D609}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="128">
   <si>
     <t>nama barang</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>RETURE</t>
+  </si>
+  <si>
+    <t>paste disisni</t>
   </si>
 </sst>
 </file>
@@ -650,7 +653,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -741,6 +744,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1099,11 +1105,11 @@
       </c>
       <c r="B3" s="1">
         <f>index!B4</f>
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C3">
         <f>index!C4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
         <f>B3+C3</f>
@@ -1229,15 +1235,15 @@
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>996</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1280,7 +1286,7 @@
       </c>
       <c r="B14">
         <f>index!B15</f>
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <f>index!C15</f>
@@ -1288,7 +1294,7 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1297,7 +1303,7 @@
       </c>
       <c r="B15">
         <f>index!B16</f>
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C15">
         <f>index!C16</f>
@@ -1305,7 +1311,7 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1314,11 +1320,11 @@
       </c>
       <c r="B16">
         <f>index!B17</f>
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C16">
         <f>index!C17</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
@@ -1382,7 +1388,7 @@
       </c>
       <c r="B20">
         <f>index!B21</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C20">
         <f>index!C21</f>
@@ -1390,7 +1396,7 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>1032</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1458,23 +1464,23 @@
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>279</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1508,15 +1514,15 @@
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
@@ -1524,7 +1530,7 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1791</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1656,7 +1662,7 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
@@ -1664,11 +1670,11 @@
       </c>
       <c r="E10">
         <f>index!J13</f>
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1727,23 +1733,23 @@
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>286</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1764,11 +1770,11 @@
       </c>
       <c r="E14">
         <f>index!J17</f>
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>174</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1877,7 +1883,7 @@
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
@@ -1885,7 +1891,7 @@
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
@@ -1893,7 +1899,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>282</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1969,19 +1975,19 @@
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1175</v>
+        <v>1189</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>891</v>
+        <v>840</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>906</v>
+        <v>867</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1989,7 +1995,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4340</v>
+        <v>4314</v>
       </c>
     </row>
   </sheetData>
@@ -2020,7 +2026,7 @@
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>56815800</v>
+        <v>59365800</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2029,7 +2035,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>85327400</v>
+        <v>88846400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2038,7 +2044,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>65993500</v>
+        <v>71812500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2047,7 +2053,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>82649500</v>
+        <v>86149500</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2056,7 +2062,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>290786200</v>
+        <v>306174200</v>
       </c>
     </row>
   </sheetData>
@@ -2123,30 +2129,30 @@
       </c>
       <c r="B3">
         <f>index!R4</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <f>index!S4</f>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <f>index!T4</f>
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E3">
         <f>index!U4</f>
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>1639000</v>
+        <v>2101000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -2371,7 +2377,7 @@
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
@@ -2383,14 +2389,14 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>14427600</v>
+        <v>14625600</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2463,30 +2469,30 @@
       </c>
       <c r="B14">
         <f>index!R15</f>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>6106500</v>
+        <v>6779250</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2655,7 +2661,7 @@
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
@@ -2663,7 +2669,7 @@
       </c>
       <c r="D20">
         <f>index!T21</f>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <f>index!U21</f>
@@ -2671,14 +2677,14 @@
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>1862400</v>
+        <v>2092800</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -2771,27 +2777,27 @@
       </c>
       <c r="B24">
         <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>658</v>
+        <v>693</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2629</v>
+        <v>2749</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>29185700</v>
+        <v>30748850</v>
       </c>
     </row>
   </sheetData>
@@ -2871,11 +2877,11 @@
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>7250000</v>
+        <v>7500000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>7250000</v>
+        <v>7500000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2883,7 +2889,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2899,7 +2905,7 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -2915,11 +2921,11 @@
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>6585000</v>
+        <v>6835000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>6585000</v>
+        <v>6835000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2927,7 +2933,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2943,7 +2949,7 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -2959,11 +2965,11 @@
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>7670000</v>
+        <v>8170000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>7670000</v>
+        <v>8170000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2987,7 +2993,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -3041,11 +3047,11 @@
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>27630000</v>
+        <v>28630000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>27630000</v>
+        <v>28630000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3053,7 +3059,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3069,7 +3075,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4140,7 +4146,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>56815800</v>
+        <f>56815800+O9</f>
+        <v>59365800</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4221,10 +4228,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="13">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C4" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="13">
         <f>C4+B4</f>
@@ -4255,36 +4262,37 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>85327400</v>
+        <f>85327400+O10</f>
+        <v>88846400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
+        <v>27</v>
+      </c>
+      <c r="S4" s="27">
         <v>22</v>
       </c>
-      <c r="S4" s="27">
-        <v>12</v>
-      </c>
       <c r="T4" s="27">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="U4" s="27">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>1639000</v>
+        <v>2101000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4296,16 +4304,16 @@
         <v>275</v>
       </c>
       <c r="AD4" s="28">
-        <v>7250000</v>
+        <v>7500000</v>
       </c>
       <c r="AE4" s="28">
-        <v>7250000</v>
+        <v>7500000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4365,29 +4373,30 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H5" s="21">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5" s="21">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J5" s="21">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>65993500</v>
+        <f>65993500+O11</f>
+        <v>71812500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4428,16 +4437,16 @@
         <v>237</v>
       </c>
       <c r="AD5" s="28">
-        <v>6585000</v>
+        <v>6835000</v>
       </c>
       <c r="AE5" s="28">
-        <v>6585000</v>
+        <v>6835000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4519,7 +4528,8 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>82649500</v>
+        <f>82649500+O12</f>
+        <v>86149500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4560,16 +4570,16 @@
         <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>7670000</v>
+        <v>8170000</v>
       </c>
       <c r="AE6" s="28">
-        <v>7670000</v>
+        <v>8170000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4629,13 +4639,13 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="H7" s="21">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="I7" s="21">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="J7" s="21">
         <v>498</v>
@@ -4645,14 +4655,14 @@
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1801</v>
+        <v>1757</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>290786200</v>
+        <v>306174200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4810,18 +4820,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>27630000</v>
+        <v>28630000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>27630000</v>
+        <v>28630000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4901,6 +4911,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="N9" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="O9">
+        <v>2550000</v>
+      </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
         <v>0</v>
@@ -4990,6 +5006,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="O10">
+        <v>3519000</v>
+      </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
@@ -5087,6 +5106,9 @@
       <c r="L11" s="22">
         <f t="shared" si="3"/>
         <v>800</v>
+      </c>
+      <c r="O11">
+        <v>5819000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5174,14 +5196,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="C12" s="14">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>996</v>
+        <v>1278</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5205,6 +5227,9 @@
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
+      <c r="O12">
+        <v>3500000</v>
+      </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
@@ -5212,7 +5237,7 @@
         <v>279</v>
       </c>
       <c r="S12" s="27">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="T12" s="27">
         <v>245</v>
@@ -5225,14 +5250,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>14427600</v>
+        <v>14625600</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5307,20 +5332,20 @@
         <v>87</v>
       </c>
       <c r="H13" s="21">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I13" s="21">
         <v>24</v>
       </c>
       <c r="J13" s="21">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="K13" s="21">
         <v>21</v>
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5497,14 +5522,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="13">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="C15" s="14">
         <v>0</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5532,30 +5557,30 @@
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="S15" s="27">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="T15" s="27">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U15" s="27">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="V15" s="27">
         <v>0</v>
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>6106500</v>
+        <v>6779250</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5600,36 +5625,36 @@
         <v>14</v>
       </c>
       <c r="B16" s="13">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C16" s="14">
         <v>0</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="H16" s="21">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I16" s="21">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J16" s="21">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="K16" s="21">
         <v>21</v>
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5703,10 +5728,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="13">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="13">
         <f t="shared" si="0"/>
@@ -5725,14 +5750,14 @@
         <v>36</v>
       </c>
       <c r="J17" s="21">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="K17" s="21">
         <v>22</v>
       </c>
       <c r="L17" s="22">
         <f t="shared" si="3"/>
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -5993,14 +6018,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="13">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C21" s="14">
         <v>1032</v>
       </c>
       <c r="D21" s="13">
         <f t="shared" si="0"/>
-        <v>1032</v>
+        <v>1332</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
@@ -6028,13 +6053,13 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="S21" s="27">
         <v>65</v>
       </c>
       <c r="T21" s="27">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U21" s="27">
         <v>21</v>
@@ -6044,14 +6069,14 @@
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>1862400</v>
+        <v>2092800</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.35">
@@ -6072,13 +6097,13 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H22" s="21">
         <v>0</v>
       </c>
       <c r="I22" s="21">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J22" s="21">
         <v>59</v>
@@ -6088,7 +6113,7 @@
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6238,19 +6263,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>658</v>
+        <v>693</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6258,12 +6283,12 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2629</v>
+        <v>2749</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>29185700</v>
+        <v>30748850</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.35">
@@ -6272,19 +6297,19 @@
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1175</v>
+        <v>1189</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>891</v>
+        <v>840</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>906</v>
+        <v>867</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1368</v>
+        <v>1418</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6292,7 +6317,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4457</v>
+        <v>4431</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A9F184-7C14-47F2-86D9-0A96B9A7D609}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{307D1ECE-E19F-4C79-99CE-93E19C7C59F8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -712,6 +712,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -744,9 +747,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3051</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1278</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B13">
         <f>index!B14</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f>index!C14</f>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>469</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14">
         <f>index!B15</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f>index!C15</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B15">
         <f>index!B16</f>
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="C15">
         <f>index!C16</f>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="B20">
         <f>index!B21</f>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C20">
         <f>index!C21</f>
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>1332</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1464,15 +1464,15 @@
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>237</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1522,15 +1522,15 @@
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1747</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>248</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1712,11 +1712,11 @@
       </c>
       <c r="C12">
         <f>index!H15</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1737,11 +1737,11 @@
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>337</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C14">
         <f>index!H17</f>
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D14">
         <f>index!I17</f>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -1895,11 +1895,11 @@
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>258</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1189</v>
+        <v>1174</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>840</v>
+        <v>1023</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1418</v>
+        <v>1390</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4314</v>
+        <v>4466</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>59365800</v>
+        <v>63565800</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>88846400</v>
+        <v>96751400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>71812500</v>
+        <v>78062500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>86149500</v>
+        <v>95059500</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>306174200</v>
+        <v>333439200</v>
       </c>
     </row>
   </sheetData>
@@ -2129,15 +2129,15 @@
       </c>
       <c r="B3">
         <f>index!R4</f>
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <f>index!S4</f>
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <f>index!T4</f>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <f>index!U4</f>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>2101000</v>
+        <v>2376000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -2377,11 +2377,11 @@
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E11">
         <f>index!U12</f>
@@ -2389,14 +2389,14 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>14625600</v>
+        <v>14968800</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D13">
         <f>index!T14</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <f>index!U14</f>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>1943000</v>
+        <v>1986500</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -2473,11 +2473,11 @@
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
@@ -2485,14 +2485,14 @@
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>6779250</v>
+        <v>7038000</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
@@ -2673,18 +2673,18 @@
       </c>
       <c r="E20">
         <f>index!U21</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>2092800</v>
+        <v>2246400</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -2777,27 +2777,27 @@
       </c>
       <c r="B24">
         <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1100</v>
+        <v>1139</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2749</v>
+        <v>2834</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>30748850</v>
+        <v>31822900</v>
       </c>
     </row>
   </sheetData>
@@ -2965,11 +2965,11 @@
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>8170000</v>
+        <v>8420000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>8170000</v>
+        <v>8420000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -3009,11 +3009,11 @@
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>6125000</v>
+        <v>6625000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>6125000</v>
+        <v>6625000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>28630000</v>
+        <v>29380000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>28630000</v>
+        <v>29380000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4030,27 +4030,27 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
       <c r="N2" s="29" t="s">
         <v>37</v>
       </c>
@@ -4075,13 +4075,13 @@
       <c r="V2" s="26">
         <v>8</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="32" t="s">
+      <c r="X2" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" s="34" t="s">
+      <c r="Y2" s="35" t="s">
         <v>50</v>
       </c>
       <c r="AA2" t="s">
@@ -4131,10 +4131,10 @@
       </c>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
       <c r="F3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17"/>
@@ -4146,8 +4146,7 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <f>56815800+O9</f>
-        <v>59365800</v>
+        <v>63565800</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4165,9 +4164,9 @@
       <c r="V3" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="42"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="35"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="36"/>
       <c r="AC3" t="s">
         <v>59</v>
       </c>
@@ -4262,20 +4261,19 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <f>85327400+O10</f>
-        <v>88846400</v>
+        <v>96751400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S4" s="27">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="T4" s="27">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="U4" s="27">
         <v>80</v>
@@ -4285,14 +4283,14 @@
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>2101000</v>
+        <v>2376000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4373,13 +4371,13 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H5" s="21">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5" s="21">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J5" s="21">
         <v>87</v>
@@ -4389,14 +4387,13 @@
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <f>65993500+O11</f>
-        <v>71812500</v>
+        <v>78062500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4496,11 +4493,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3051</v>
+        <v>3036</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4528,8 +4525,7 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <f>82649500+O12</f>
-        <v>86149500</v>
+        <v>95059500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4570,16 +4566,16 @@
         <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>8170000</v>
+        <v>8420000</v>
       </c>
       <c r="AE6" s="28">
-        <v>8170000</v>
+        <v>8420000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4645,24 +4641,24 @@
         <v>268</v>
       </c>
       <c r="I7" s="21">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="J7" s="21">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1757</v>
+        <v>1724</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>306174200</v>
+        <v>333439200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4703,16 +4699,16 @@
         <v>260</v>
       </c>
       <c r="AD7" s="28">
-        <v>6125000</v>
+        <v>6625000</v>
       </c>
       <c r="AE7" s="28">
-        <v>6125000</v>
+        <v>6625000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4820,18 +4816,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>28630000</v>
+        <v>29380000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>28630000</v>
+        <v>29380000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4911,7 +4907,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N9" s="43" t="s">
+      <c r="N9" s="32" t="s">
         <v>127</v>
       </c>
       <c r="O9">
@@ -5196,14 +5192,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="C12" s="14">
         <v>978</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1278</v>
+        <v>1188</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5237,10 +5233,10 @@
         <v>279</v>
       </c>
       <c r="S12" s="27">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="T12" s="27">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="U12" s="27">
         <v>212</v>
@@ -5250,14 +5246,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1108</v>
+        <v>1134</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>14625600</v>
+        <v>14968800</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5332,10 +5328,10 @@
         <v>87</v>
       </c>
       <c r="H13" s="21">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I13" s="21">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J13" s="21">
         <v>120</v>
@@ -5345,7 +5341,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5419,14 +5415,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C14" s="14">
         <v>457</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="0"/>
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>33</v>
@@ -5460,7 +5456,7 @@
         <v>19</v>
       </c>
       <c r="T14" s="27">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U14" s="27">
         <v>43</v>
@@ -5470,14 +5466,14 @@
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>1943000</v>
+        <v>1986500</v>
       </c>
       <c r="AA14" t="s">
         <v>77</v>
@@ -5522,14 +5518,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="13">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C15" s="14">
         <v>0</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5538,10 +5534,10 @@
         <v>44</v>
       </c>
       <c r="H15" s="21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I15" s="21">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J15" s="21">
         <v>72</v>
@@ -5551,7 +5547,7 @@
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
@@ -5560,10 +5556,10 @@
         <v>77</v>
       </c>
       <c r="S15" s="27">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="T15" s="27">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="U15" s="27">
         <v>45</v>
@@ -5573,14 +5569,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>6779250</v>
+        <v>7038000</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5625,14 +5621,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="13">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="C16" s="14">
         <v>0</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
@@ -5641,10 +5637,10 @@
         <v>134</v>
       </c>
       <c r="H16" s="21">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="I16" s="21">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J16" s="21">
         <v>119</v>
@@ -5654,7 +5650,7 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5744,7 +5740,7 @@
         <v>46</v>
       </c>
       <c r="H17" s="21">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I17" s="21">
         <v>36</v>
@@ -5757,7 +5753,7 @@
       </c>
       <c r="L17" s="22">
         <f t="shared" si="3"/>
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -6018,14 +6014,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="13">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C21" s="14">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="D21" s="13">
         <f t="shared" si="0"/>
-        <v>1332</v>
+        <v>1242</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
@@ -6053,7 +6049,7 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S21" s="27">
         <v>65</v>
@@ -6062,21 +6058,21 @@
         <v>42</v>
       </c>
       <c r="U21" s="27">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2092800</v>
+        <v>2246400</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.35">
@@ -6097,23 +6093,23 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H22" s="21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I22" s="21">
         <v>82</v>
       </c>
       <c r="J22" s="21">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6263,19 +6259,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1100</v>
+        <v>1139</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6283,12 +6279,12 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2749</v>
+        <v>2834</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>30748850</v>
+        <v>31822900</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.35">
@@ -6297,19 +6293,19 @@
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1189</v>
+        <v>1174</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>840</v>
+        <v>1023</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1418</v>
+        <v>1390</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6317,7 +6313,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4431</v>
+        <v>4583</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{307D1ECE-E19F-4C79-99CE-93E19C7C59F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,16 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -426,8 +434,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -649,8 +657,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
@@ -715,16 +723,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -750,8 +758,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -780,9 +788,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -820,7 +828,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -926,7 +934,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1068,7 +1076,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1077,15 +1085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1116,7 +1124,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1133,7 +1141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1143,14 +1151,14 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1167,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1181,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1195,7 +1203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1212,7 +1220,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1229,13 +1237,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1243,10 +1251,10 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1263,7 +1271,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1280,7 +1288,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1297,13 +1305,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
         <f>index!B16</f>
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C15">
         <f>index!C16</f>
@@ -1311,10 +1319,10 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1331,7 +1339,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1348,7 +1356,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1365,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1382,13 +1390,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!B21</f>
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="C20">
         <f>index!C21</f>
@@ -1396,10 +1404,10 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1424,18 +1432,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1458,32 +1466,32 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1508,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1522,18 +1530,18 @@
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1558,7 +1566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1580,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1602,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1627,7 +1635,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1652,17 +1660,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
@@ -1670,14 +1678,14 @@
       </c>
       <c r="E10">
         <f>index!J13</f>
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1702,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1727,7 +1735,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1737,7 +1745,7 @@
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
@@ -1745,20 +1753,20 @@
       </c>
       <c r="E13">
         <f>index!J16</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>36</v>
       </c>
       <c r="B14">
         <f>index!G17</f>
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <f>index!H17</f>
@@ -1770,14 +1778,14 @@
       </c>
       <c r="E14">
         <f>index!J17</f>
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>234</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1802,7 +1810,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1827,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1852,7 +1860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1866,7 +1874,7 @@
       </c>
       <c r="D18">
         <f>index!I21</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <f>index!J21</f>
@@ -1874,16 +1882,16 @@
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
@@ -1895,14 +1903,14 @@
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>332</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1927,7 +1935,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1948,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1969,25 +1977,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1174</v>
+        <v>1274</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>1023</v>
+        <v>983</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>879</v>
+        <v>841</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1390</v>
+        <v>1422</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1995,7 +2003,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4466</v>
+        <v>4520</v>
       </c>
     </row>
   </sheetData>
@@ -2006,13 +2014,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2020,49 +2028,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>123</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>63565800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>65965800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>96751400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>101851400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>78062500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81582500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>95059500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98259500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>333439200</v>
+        <v>347659200</v>
       </c>
     </row>
   </sheetData>
@@ -2073,17 +2081,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -2109,7 +2117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>51</v>
       </c>
@@ -2123,39 +2131,39 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <f>index!R4</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <f>index!S4</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <f>index!T4</f>
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E3">
         <f>index!U4</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>2376000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2926000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2187,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -2219,7 +2227,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2251,7 +2259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!R8</f>
         <v>0</v>
@@ -2277,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!R9</f>
         <v>0</v>
@@ -2303,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>329400</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2367,7 +2375,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2377,7 +2385,7 @@
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
@@ -2385,21 +2393,21 @@
       </c>
       <c r="E11">
         <f>index!U12</f>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1134</v>
+        <v>1152</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>14968800</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>15206400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2431,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2463,7 +2471,7 @@
         <v>1986500</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2473,7 +2481,7 @@
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
@@ -2481,21 +2489,21 @@
       </c>
       <c r="E14">
         <f>index!U15</f>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>7038000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>7348500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2527,7 +2535,7 @@
         <v>1955000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2559,7 +2567,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2591,7 +2599,7 @@
         <v>289800</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2623,7 +2631,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2637,7 +2645,7 @@
       </c>
       <c r="D19">
         <f>index!T20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <f>index!U20</f>
@@ -2645,23 +2653,23 @@
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
@@ -2673,21 +2681,21 @@
       </c>
       <c r="E20">
         <f>index!U21</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>2246400</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2719,7 +2727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <f>index!R23</f>
         <v>0</v>
@@ -2745,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <f>index!R24</f>
         <v>0</v>
@@ -2771,33 +2779,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24">
         <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1139</v>
+        <v>1179</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2834</v>
+        <v>2942</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>31822900</v>
+        <v>33146600</v>
       </c>
     </row>
   </sheetData>
@@ -2808,20 +2816,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2835,7 +2843,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>59</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2908,7 +2916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -2952,7 +2960,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2965,11 +2973,11 @@
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>8420000</v>
+        <v>8920000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>8420000</v>
+        <v>8920000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2977,7 +2985,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2993,10 +3001,10 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3009,11 +3017,11 @@
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>6625000</v>
+        <v>6875000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>6625000</v>
+        <v>6875000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3037,21 +3045,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
         <v>1058</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>29380000</v>
+        <v>30130000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>29380000</v>
+        <v>30130000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3059,7 +3067,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3075,7 +3083,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3086,19 +3094,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -3124,7 +3132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -3155,7 +3163,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -3186,7 +3194,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -3217,7 +3225,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -3248,7 +3256,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3282,19 +3290,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.87109375" customWidth="1"/>
+    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -3329,7 +3337,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3371,7 +3379,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3413,7 +3421,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3458,7 +3466,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3500,7 +3508,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3542,7 +3550,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3584,7 +3592,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3626,7 +3634,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3668,7 +3676,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3710,7 +3718,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3752,7 +3760,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3791,7 +3799,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3830,7 +3838,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3869,7 +3877,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3908,7 +3916,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3947,7 +3955,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3986,7 +3994,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>97</v>
       </c>
@@ -3999,17 +4007,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>114</v>
       </c>
@@ -4029,7 +4037,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4130,7 +4138,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -4146,7 +4154,7 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>63565800</v>
+        <v>65965800</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4222,7 +4230,7 @@
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4261,36 +4269,36 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>96751400</v>
+        <v>101851400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="S4" s="27">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="T4" s="27">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="U4" s="27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>2376000</v>
+        <v>2926000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4353,7 +4361,7 @@
       <c r="AV4" s="4"/>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4371,29 +4379,29 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
+        <v>57</v>
+      </c>
+      <c r="H5" s="21">
+        <v>20</v>
+      </c>
+      <c r="I5" s="21">
+        <v>18</v>
+      </c>
+      <c r="J5" s="21">
         <v>67</v>
-      </c>
-      <c r="H5" s="21">
-        <v>30</v>
-      </c>
-      <c r="I5" s="21">
-        <v>28</v>
-      </c>
-      <c r="J5" s="21">
-        <v>87</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>78062500</v>
+        <v>81582500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4485,7 +4493,7 @@
       <c r="AV5" s="4"/>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4493,11 +4501,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3036</v>
+        <v>3069</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4525,7 +4533,7 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>95059500</v>
+        <v>98259500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4566,16 +4574,16 @@
         <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>8420000</v>
+        <v>8920000</v>
       </c>
       <c r="AE6" s="28">
-        <v>8420000</v>
+        <v>8920000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4617,7 +4625,7 @@
       <c r="AV6" s="4"/>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4641,24 +4649,24 @@
         <v>268</v>
       </c>
       <c r="I7" s="21">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="J7" s="21">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1724</v>
+        <v>1691</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>333439200</v>
+        <v>347659200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4699,16 +4707,16 @@
         <v>260</v>
       </c>
       <c r="AD7" s="28">
-        <v>6625000</v>
+        <v>6875000</v>
       </c>
       <c r="AE7" s="28">
-        <v>6625000</v>
+        <v>6875000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4752,7 +4760,7 @@
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4816,18 +4824,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>29380000</v>
+        <v>30130000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>29380000</v>
+        <v>30130000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4875,7 +4883,7 @@
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4968,7 +4976,7 @@
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -5067,7 +5075,7 @@
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5187,19 +5195,19 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="C12" s="14">
         <v>978</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1188</v>
+        <v>1128</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5233,27 +5241,27 @@
         <v>279</v>
       </c>
       <c r="S12" s="27">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="T12" s="27">
         <v>254</v>
       </c>
       <c r="U12" s="27">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="V12" s="27">
         <v>0</v>
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1134</v>
+        <v>1152</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>14968800</v>
+        <v>15206400</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5307,7 +5315,7 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5325,23 +5333,23 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="H13" s="21">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I13" s="21">
         <v>45</v>
       </c>
       <c r="J13" s="21">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="K13" s="21">
         <v>21</v>
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5410,7 +5418,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5513,7 +5521,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5556,27 +5564,27 @@
         <v>77</v>
       </c>
       <c r="S15" s="27">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="T15" s="27">
         <v>91</v>
       </c>
       <c r="U15" s="27">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V15" s="27">
         <v>0</v>
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7038000</v>
+        <v>7348500</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5616,19 +5624,19 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="13">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C16" s="14">
         <v>0</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
@@ -5637,20 +5645,20 @@
         <v>134</v>
       </c>
       <c r="H16" s="21">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I16" s="21">
         <v>42</v>
       </c>
       <c r="J16" s="21">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K16" s="21">
         <v>21</v>
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5719,7 +5727,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5737,7 +5745,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="21">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H17" s="21">
         <v>74</v>
@@ -5746,14 +5754,14 @@
         <v>36</v>
       </c>
       <c r="J17" s="21">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K17" s="21">
         <v>22</v>
       </c>
       <c r="L17" s="22">
         <f t="shared" si="3"/>
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -5798,7 +5806,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5877,7 +5885,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5943,7 +5951,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5989,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U20" s="27">
         <v>0</v>
@@ -5999,29 +6007,29 @@
       </c>
       <c r="W20" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X20" s="4">
         <v>12000</v>
       </c>
       <c r="Y20" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="13">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="C21" s="14">
         <v>1002</v>
       </c>
       <c r="D21" s="13">
         <f t="shared" si="0"/>
-        <v>1242</v>
+        <v>1152</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
@@ -6033,7 +6041,7 @@
         <v>70</v>
       </c>
       <c r="I21" s="21">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J21" s="21">
         <v>6</v>
@@ -6043,13 +6051,13 @@
       </c>
       <c r="L21" s="22">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="Q21" s="20" t="s">
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="S21" s="27">
         <v>65</v>
@@ -6058,24 +6066,24 @@
         <v>42</v>
       </c>
       <c r="U21" s="27">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2246400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6093,7 +6101,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="H22" s="21">
         <v>90</v>
@@ -6102,14 +6110,14 @@
         <v>82</v>
       </c>
       <c r="J22" s="21">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>344</v>
+        <v>418</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6141,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6188,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6233,7 +6241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6259,19 +6267,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1139</v>
+        <v>1179</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6279,33 +6287,33 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2834</v>
+        <v>2942</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>31822900</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+        <v>33146600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1174</v>
+        <v>1274</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>1023</v>
+        <v>983</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>879</v>
+        <v>841</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1390</v>
+        <v>1422</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6313,7 +6321,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4583</v>
+        <v>4637</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FD02756-EE61-4BE2-9305-178C1618323C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="6" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="126">
   <si>
     <t>nama barang</t>
   </si>
@@ -345,18 +337,12 @@
     <t>355806671128727</t>
   </si>
   <si>
-    <t>GUDANG</t>
-  </si>
-  <si>
     <t>085882732618</t>
   </si>
   <si>
     <t>355806671214105</t>
   </si>
   <si>
-    <t>SEGEL</t>
-  </si>
-  <si>
     <t>085882732619</t>
   </si>
   <si>
@@ -417,9 +403,6 @@
     <t>Muhammad Parhan</t>
   </si>
   <si>
-    <t>CSM</t>
-  </si>
-  <si>
     <t>REWARD</t>
   </si>
   <si>
@@ -427,6 +410,9 @@
   </si>
   <si>
     <t>paste disisni</t>
+  </si>
+  <si>
+    <t>On Hand Dse</t>
   </si>
 </sst>
 </file>
@@ -434,8 +420,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -657,8 +643,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
@@ -723,16 +709,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -758,8 +744,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
-    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -788,9 +774,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -828,7 +814,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -934,7 +920,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1076,7 +1062,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1085,15 +1071,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1107,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1124,7 +1110,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1141,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1151,14 +1137,14 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1544</v>
+        <v>1511</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3069</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1175,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1189,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1203,13 +1189,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <f>index!B10</f>
-        <v>2462</v>
+        <v>2312</v>
       </c>
       <c r="C9">
         <f>index!C10</f>
@@ -1217,10 +1203,10 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>2462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1237,13 +1223,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1251,10 +1237,10 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1271,7 +1257,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1288,7 +1274,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1305,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1322,7 +1308,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1339,7 +1325,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1356,7 +1342,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1373,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1390,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1407,7 +1393,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1432,18 +1418,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1466,7 +1452,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1476,7 +1462,7 @@
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
@@ -1484,14 +1470,14 @@
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1516,13 +1502,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
@@ -1530,18 +1516,18 @@
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1566,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1588,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1610,7 +1596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1606,7 @@
       </c>
       <c r="C8">
         <f>index!H11</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="D8">
         <f>index!I11</f>
@@ -1632,10 +1618,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1660,7 +1646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1670,11 +1656,11 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
@@ -1682,10 +1668,10 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>354</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1710,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1728,14 +1714,14 @@
       </c>
       <c r="E12">
         <f>index!J15</f>
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1745,11 +1731,11 @@
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1757,10 +1743,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1785,7 +1771,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1795,7 +1781,7 @@
       </c>
       <c r="C15">
         <f>index!H18</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <f>index!I18</f>
@@ -1807,10 +1793,10 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1835,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1860,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1885,17 +1871,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -1907,10 +1893,10 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>406</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1935,7 +1921,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1956,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1977,25 +1963,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>983</v>
+        <v>1148</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1422</v>
+        <v>1365</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -2003,7 +1989,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4520</v>
+        <v>4610</v>
       </c>
     </row>
   </sheetData>
@@ -2014,13 +2000,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2028,49 +2014,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>65965800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>69115800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>101851400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>109801400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>81582500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>87282500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>98259500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>103959500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>347659200</v>
+        <v>370159200</v>
       </c>
     </row>
   </sheetData>
@@ -2081,17 +2067,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -2117,7 +2103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>51</v>
       </c>
@@ -2131,7 +2117,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2141,7 +2127,7 @@
       </c>
       <c r="C3">
         <f>index!S4</f>
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <f>index!T4</f>
@@ -2149,21 +2135,21 @@
       </c>
       <c r="E3">
         <f>index!U4</f>
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>2926000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>3256000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2195,13 +2181,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5">
         <f>index!R6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <f>index!S6</f>
@@ -2217,17 +2203,17 @@
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>25000</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2259,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!R8</f>
         <v>0</v>
@@ -2285,7 +2271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!R9</f>
         <v>0</v>
@@ -2311,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2343,7 +2329,7 @@
         <v>329400</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2375,7 +2361,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2389,7 +2375,7 @@
       </c>
       <c r="D11">
         <f>index!T12</f>
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="E11">
         <f>index!U12</f>
@@ -2397,17 +2383,17 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>15206400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>15404400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2439,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2457,21 +2443,21 @@
       </c>
       <c r="E13">
         <f>index!U14</f>
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>1986500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2204000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2481,11 +2467,11 @@
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
@@ -2493,17 +2479,17 @@
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>7348500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>7693500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2535,7 +2521,7 @@
         <v>1955000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2531,7 @@
       </c>
       <c r="C16">
         <f>index!S17</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <f>index!T17</f>
@@ -2557,17 +2543,17 @@
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2599,7 +2585,7 @@
         <v>289800</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2631,7 +2617,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2663,17 +2649,17 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D20">
         <f>index!T21</f>
@@ -2685,17 +2671,17 @@
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2688000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2727,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B22">
         <f>index!R23</f>
         <v>0</v>
@@ -2753,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B23">
         <f>index!R24</f>
         <v>0</v>
@@ -2779,33 +2765,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24">
         <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1179</v>
+        <v>1224</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>451</v>
+        <v>486</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>2942</v>
+        <v>3059</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>33146600</v>
+        <v>34725100</v>
       </c>
     </row>
   </sheetData>
@@ -2816,20 +2802,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2843,7 +2829,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>59</v>
       </c>
@@ -2872,7 +2858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2881,7 +2867,7 @@
       </c>
       <c r="C3">
         <f>index!AC4</f>
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
@@ -2916,7 +2902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -2925,15 +2911,15 @@
       </c>
       <c r="C4">
         <f>index!AC5</f>
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>6835000</v>
+        <v>7335000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>6835000</v>
+        <v>7335000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2941,7 +2927,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2957,10 +2943,10 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2969,15 +2955,15 @@
       </c>
       <c r="C5">
         <f>index!AC6</f>
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2985,7 +2971,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -3001,10 +2987,10 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3013,15 +2999,15 @@
       </c>
       <c r="C6">
         <f>index!AC7</f>
-        <v>260</v>
+        <v>359</v>
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>6875000</v>
+        <v>8125000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>6875000</v>
+        <v>8125000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3029,7 +3015,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3045,21 +3031,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
-        <v>1058</v>
+        <v>1430</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>30130000</v>
+        <v>32130000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>30130000</v>
+        <v>32130000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3067,7 +3053,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3083,7 +3069,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3094,19 +3080,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -3132,7 +3118,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -3163,7 +3149,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -3194,7 +3180,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -3225,7 +3211,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -3256,7 +3242,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3290,19 +3276,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.87109375" customWidth="1"/>
-    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -3337,7 +3323,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3373,13 +3359,13 @@
         <f>index!AU3</f>
         <v>0</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="4" t="str">
         <f>index!AV3</f>
-        <v>0</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3415,13 +3401,13 @@
         <f>index!AU4</f>
         <v>0</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="4" t="str">
         <f>index!AV4</f>
-        <v>0</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3457,16 +3443,16 @@
         <f>index!AU5</f>
         <v>0</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="4" t="str">
         <f>index!AV5</f>
-        <v>0</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K4" s="5"/>
       <c r="M4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3502,13 +3488,13 @@
         <f>index!AU6</f>
         <v>0</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="4" t="str">
         <f>index!AV6</f>
-        <v>0</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3546,11 +3532,11 @@
       </c>
       <c r="J6" s="4" t="str">
         <f>index!AV7</f>
-        <v>SEGEL</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3588,11 +3574,11 @@
       </c>
       <c r="J7" s="4" t="str">
         <f>index!AV8</f>
-        <v>SEGEL</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3630,11 +3616,11 @@
       </c>
       <c r="J8" s="4" t="str">
         <f>index!AV9</f>
-        <v>SEGEL</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3672,11 +3658,11 @@
       </c>
       <c r="J9" s="4" t="str">
         <f>index!AV10</f>
-        <v>SEGEL</v>
+        <v>On Hand Dse</v>
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3686,7 +3672,7 @@
       </c>
       <c r="C10" s="4" t="str">
         <f>index!AO11</f>
-        <v>CSM</v>
+        <v>REWARD</v>
       </c>
       <c r="D10" s="6" t="str">
         <f>index!AP11</f>
@@ -3718,7 +3704,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3728,7 +3714,7 @@
       </c>
       <c r="C11" s="4" t="str">
         <f>index!AO12</f>
-        <v>GUDANG</v>
+        <v>RETURE</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>index!AP12</f>
@@ -3760,7 +3746,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3799,7 +3785,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3838,7 +3824,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3877,7 +3863,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3916,7 +3902,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3955,7 +3941,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3994,7 +3980,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J19" t="s">
         <v>97</v>
       </c>
@@ -4007,37 +3993,37 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" t="s">
         <v>115</v>
       </c>
-      <c r="N1" t="s">
-        <v>117</v>
-      </c>
       <c r="Q1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA1" t="s">
         <v>118</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AM1" t="s">
         <v>120</v>
       </c>
-      <c r="AM1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4051,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="40"/>
@@ -4138,7 +4124,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -4154,7 +4140,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>65965800</v>
+        <f>65965800+O9</f>
+        <v>69115800</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4170,7 +4157,7 @@
         <v>53</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W3" s="43"/>
       <c r="X3" s="34"/>
@@ -4227,10 +4214,12 @@
         <v>410000</v>
       </c>
       <c r="AU3" s="5"/>
-      <c r="AV3" s="4"/>
+      <c r="AV3" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4269,7 +4258,8 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>101851400</v>
+        <f>101851400+O10</f>
+        <v>109801400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
@@ -4278,27 +4268,27 @@
         <v>42</v>
       </c>
       <c r="S4" s="27">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="T4" s="27">
         <v>82</v>
       </c>
       <c r="U4" s="27">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>2926000</v>
+        <v>3256000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4307,7 +4297,7 @@
         <v>68</v>
       </c>
       <c r="AC4">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="AD4" s="28">
         <v>7500000</v>
@@ -4358,10 +4348,12 @@
         <v>410000</v>
       </c>
       <c r="AU4" s="5"/>
-      <c r="AV4" s="4"/>
+      <c r="AV4" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4382,26 +4374,27 @@
         <v>57</v>
       </c>
       <c r="H5" s="21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I5" s="21">
         <v>18</v>
       </c>
       <c r="J5" s="21">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>81582500</v>
+        <f>81582500+O11</f>
+        <v>87282500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4439,19 +4432,19 @@
         <v>68</v>
       </c>
       <c r="AC5">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="AD5" s="28">
-        <v>6835000</v>
+        <v>7335000</v>
       </c>
       <c r="AE5" s="28">
-        <v>6835000</v>
+        <v>7335000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4490,10 +4483,12 @@
         <v>410000</v>
       </c>
       <c r="AU5" s="5"/>
-      <c r="AV5" s="4"/>
+      <c r="AV5" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4501,11 +4496,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1544</v>
+        <v>1511</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3069</v>
+        <v>3036</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4533,13 +4528,14 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>98259500</v>
+        <f>98259500+O12</f>
+        <v>103959500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="27">
         <v>3</v>
@@ -4555,14 +4551,14 @@
       </c>
       <c r="W6" s="27">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
         <f t="shared" si="2"/>
-        <v>75000</v>
+        <v>125000</v>
       </c>
       <c r="AA6" t="s">
         <v>41</v>
@@ -4571,19 +4567,19 @@
         <v>68</v>
       </c>
       <c r="AC6">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="AD6" s="28">
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="AE6" s="28">
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4622,10 +4618,12 @@
         <v>410000</v>
       </c>
       <c r="AU6" s="5"/>
-      <c r="AV6" s="4"/>
+      <c r="AV6" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4643,30 +4641,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H7" s="21">
         <v>268</v>
       </c>
       <c r="I7" s="21">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="J7" s="21">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1691</v>
+        <v>1656</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>347659200</v>
+        <v>370159200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4704,19 +4702,19 @@
         <v>68</v>
       </c>
       <c r="AC7">
-        <v>260</v>
+        <v>359</v>
       </c>
       <c r="AD7" s="28">
-        <v>6875000</v>
+        <v>8125000</v>
       </c>
       <c r="AE7" s="28">
-        <v>6875000</v>
+        <v>8125000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4746,21 +4744,21 @@
         <v>1</v>
       </c>
       <c r="AR7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS7" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="AS7" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="AT7" s="9">
         <v>410000</v>
       </c>
       <c r="AU7" s="5"/>
       <c r="AV7" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4820,22 +4818,23 @@
         <v>0</v>
       </c>
       <c r="AC8" s="28">
-        <v>1058</v>
+        <f>SUM(AC4:AC7)</f>
+        <v>1430</v>
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>30130000</v>
+        <v>32130000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>30130000</v>
+        <v>32130000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4869,21 +4868,21 @@
         <v>1</v>
       </c>
       <c r="AR8" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AS8" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AT8" s="9">
         <v>410000</v>
       </c>
       <c r="AU8" s="5"/>
       <c r="AV8" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4916,10 +4915,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O9">
-        <v>2550000</v>
+        <v>3150000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4962,33 +4961,33 @@
         <v>1</v>
       </c>
       <c r="AR9" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS9" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AT9" s="8">
         <v>410000</v>
       </c>
       <c r="AU9" s="5"/>
       <c r="AV9" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="13">
-        <v>2462</v>
+        <v>2312</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
-        <v>2462</v>
+        <v>2312</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="21">
@@ -5011,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>3519000</v>
+        <v>7950000</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
@@ -5043,7 +5042,7 @@
         <v>329400</v>
       </c>
       <c r="AA10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AM10" s="4">
         <v>8</v>
@@ -5061,21 +5060,21 @@
         <v>1</v>
       </c>
       <c r="AR10" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AT10" s="8">
         <v>410000</v>
       </c>
       <c r="AU10" s="5"/>
       <c r="AV10" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5096,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="21">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="I11" s="21">
         <v>100</v>
@@ -5109,10 +5108,10 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="O11">
-        <v>5819000</v>
+        <v>5700000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5174,7 +5173,7 @@
         <v>46163</v>
       </c>
       <c r="AO11" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AP11" s="6" t="s">
         <v>90</v>
@@ -5183,31 +5182,31 @@
         <v>1</v>
       </c>
       <c r="AR11" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS11" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="5"/>
       <c r="AV11" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C12" s="14">
         <v>978</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1128</v>
+        <v>1038</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5232,7 +5231,7 @@
         <v>13</v>
       </c>
       <c r="O12">
-        <v>3500000</v>
+        <v>5700000</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
@@ -5244,7 +5243,7 @@
         <v>404</v>
       </c>
       <c r="T12" s="27">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="U12" s="27">
         <v>215</v>
@@ -5254,14 +5253,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>15206400</v>
+        <v>15404400</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5294,7 +5293,7 @@
         <v>46164</v>
       </c>
       <c r="AO12" s="4" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="AP12" s="6" t="s">
         <v>90</v>
@@ -5303,19 +5302,19 @@
         <v>1</v>
       </c>
       <c r="AR12" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AS12" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AT12" s="9"/>
       <c r="AU12" s="5"/>
       <c r="AV12" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5336,10 +5335,10 @@
         <v>117</v>
       </c>
       <c r="H13" s="21">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="I13" s="21">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J13" s="21">
         <v>147</v>
@@ -5349,7 +5348,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5418,7 +5417,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5467,21 +5466,21 @@
         <v>54</v>
       </c>
       <c r="U14" s="27">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>1986500</v>
+        <v>2204000</v>
       </c>
       <c r="AA14" t="s">
         <v>77</v>
@@ -5521,7 +5520,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5548,14 +5547,14 @@
         <v>40</v>
       </c>
       <c r="J15" s="21">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K15" s="21">
         <v>0</v>
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
@@ -5564,10 +5563,10 @@
         <v>77</v>
       </c>
       <c r="S15" s="27">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="T15" s="27">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="U15" s="27">
         <v>48</v>
@@ -5577,14 +5576,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7348500</v>
+        <v>7693500</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5624,7 +5623,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5645,10 +5644,10 @@
         <v>134</v>
       </c>
       <c r="H16" s="21">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I16" s="21">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5658,7 +5657,7 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5727,7 +5726,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5770,7 +5769,7 @@
         <v>3</v>
       </c>
       <c r="S17" s="27">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T17" s="27">
         <v>0</v>
@@ -5783,14 +5782,14 @@
       </c>
       <c r="W17" s="27">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
       <c r="Y17" s="27">
         <f t="shared" si="2"/>
-        <v>450000</v>
+        <v>600000</v>
       </c>
       <c r="AM17" s="4">
         <v>15</v>
@@ -5806,7 +5805,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5827,7 +5826,7 @@
         <v>45</v>
       </c>
       <c r="H18" s="21">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I18" s="21">
         <v>18</v>
@@ -5840,7 +5839,7 @@
       </c>
       <c r="L18" s="22">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="20" t="s">
         <v>16</v>
@@ -5885,7 +5884,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5951,7 +5950,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -6017,7 +6016,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -6057,10 +6056,10 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="S21" s="27">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T21" s="27">
         <v>42</v>
@@ -6073,17 +6072,17 @@
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+        <v>2688000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6101,10 +6100,10 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H22" s="21">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I22" s="21">
         <v>82</v>
@@ -6117,7 +6116,7 @@
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6149,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6196,7 +6195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6241,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6267,19 +6266,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1179</v>
+        <v>1224</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>451</v>
+        <v>486</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6287,33 +6286,33 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2942</v>
+        <v>3059</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>33146600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+        <v>34725100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>983</v>
+        <v>1148</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1422</v>
+        <v>1365</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6321,7 +6320,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4637</v>
+        <v>4727</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{DEBA2040-E3D9-49C9-998E-3302C635B836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FD02756-EE61-4BE2-9305-178C1618323C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCD213A-17C5-4614-B396-8486F20744ED}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="6" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B9" s="1">
         <f>index!B10</f>
-        <v>2312</v>
+        <v>2250</v>
       </c>
       <c r="C9">
         <f>index!C10</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>2312</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="C11">
         <f>index!C12</f>
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C14">
         <f>index!C15</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C15">
         <f>index!C16</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1458,23 +1458,23 @@
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1646</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D8">
         <f>index!I11</f>
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <f>index!J11</f>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1885,15 +1885,15 @@
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>376</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1969,19 +1969,19 @@
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>1148</v>
+        <v>1117</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>835</v>
+        <v>771</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1326</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4610</v>
+        <v>4436</v>
       </c>
     </row>
   </sheetData>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>69115800</v>
+        <v>72215900</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>109801400</v>
+        <v>115428500</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>87282500</v>
+        <v>90282500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>103959500</v>
+        <v>107886300</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>370159200</v>
+        <v>385813200</v>
       </c>
     </row>
   </sheetData>
@@ -2123,30 +2123,30 @@
       </c>
       <c r="B3">
         <f>index!R4</f>
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C3">
         <f>index!S4</f>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <f>index!T4</f>
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <f>index!U4</f>
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F3">
         <f>SUM(B3:E3)</f>
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="G3">
         <v>11000</v>
       </c>
       <c r="H3">
         <f>F3*G3</f>
-        <v>3256000</v>
+        <v>3762000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B9">
         <f>index!R10</f>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C9">
         <f>index!S10</f>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D9">
         <f>index!T10</f>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <f>index!U10</f>
@@ -2319,14 +2319,14 @@
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>329400</v>
+        <v>395400</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="B11">
         <f>index!R12</f>
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
@@ -2383,14 +2383,14 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1167</v>
+        <v>1187</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>15404400</v>
+        <v>15668400</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D13">
         <f>index!T14</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <f>index!U14</f>
@@ -2447,14 +2447,14 @@
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>2204000</v>
+        <v>2291000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B14">
         <f>index!R15</f>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <f>index!S15</f>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
@@ -2479,14 +2479,14 @@
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>7693500</v>
+        <v>7917750</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2663,22 +2663,22 @@
       </c>
       <c r="D20">
         <f>index!T21</f>
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E20">
         <f>index!U21</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>2688000</v>
+        <v>2870400</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -2771,27 +2771,27 @@
       </c>
       <c r="B24">
         <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1224</v>
+        <v>1244</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>609</v>
+        <v>735</v>
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>3059</v>
+        <v>3273</v>
       </c>
       <c r="H24">
         <f>SUM(H3:H23)</f>
-        <v>34725100</v>
+        <v>36054750</v>
       </c>
     </row>
   </sheetData>
@@ -2867,15 +2867,15 @@
       </c>
       <c r="C3">
         <f>index!AC4</f>
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -2911,15 +2911,15 @@
       </c>
       <c r="C4">
         <f>index!AC5</f>
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>7335000</v>
+        <v>7585000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>7335000</v>
+        <v>7585000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -2999,15 +2999,15 @@
       </c>
       <c r="C6">
         <f>index!AC7</f>
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>8125000</v>
+        <v>8375000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>8125000</v>
+        <v>8375000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
-        <v>1430</v>
+        <v>1463</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>32130000</v>
+        <v>32880000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>32130000</v>
+        <v>32880000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4140,8 +4140,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <f>65965800+O9</f>
-        <v>69115800</v>
+        <f>65965900+O9</f>
+        <v>72215900</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4259,36 +4259,36 @@
       </c>
       <c r="O4" s="27">
         <f>101851400+O10</f>
-        <v>109801400</v>
+        <v>115428500</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="S4" s="27">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="T4" s="27">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="U4" s="27">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>3256000</v>
+        <v>3762000</v>
       </c>
       <c r="AA4" t="s">
         <v>67</v>
@@ -4297,19 +4297,19 @@
         <v>68</v>
       </c>
       <c r="AC4">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="AD4" s="28">
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="AE4" s="28">
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4371,30 +4371,30 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H5" s="21">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21">
         <v>10</v>
       </c>
-      <c r="I5" s="21">
-        <v>18</v>
-      </c>
       <c r="J5" s="21">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
         <f>81582500+O11</f>
-        <v>87282500</v>
+        <v>90282500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4432,19 +4432,19 @@
         <v>68</v>
       </c>
       <c r="AC5">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AD5" s="28">
-        <v>7335000</v>
+        <v>7585000</v>
       </c>
       <c r="AE5" s="28">
-        <v>7335000</v>
+        <v>7585000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="O6" s="27">
         <f>98259500+O12</f>
-        <v>103959500</v>
+        <v>107886300</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4644,27 +4644,27 @@
         <v>515</v>
       </c>
       <c r="H7" s="21">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="I7" s="21">
         <v>420</v>
       </c>
       <c r="J7" s="21">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1656</v>
+        <v>1634</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>370159200</v>
+        <v>385813200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4702,19 +4702,19 @@
         <v>68</v>
       </c>
       <c r="AC7">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AD7" s="28">
-        <v>8125000</v>
+        <v>8375000</v>
       </c>
       <c r="AE7" s="28">
-        <v>8125000</v>
+        <v>8375000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4818,23 +4818,22 @@
         <v>0</v>
       </c>
       <c r="AC8" s="28">
-        <f>SUM(AC4:AC7)</f>
-        <v>1430</v>
+        <v>1058</v>
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>32130000</v>
+        <v>32880000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>32130000</v>
+        <v>32880000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4918,7 +4917,7 @@
         <v>124</v>
       </c>
       <c r="O9">
-        <v>3150000</v>
+        <v>6250000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4980,14 +4979,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="13">
-        <v>2312</v>
+        <v>2250</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
-        <v>2312</v>
+        <v>2250</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="21">
@@ -5010,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>7950000</v>
+        <v>13577100</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="S10" s="27">
         <v>369</v>
       </c>
       <c r="T10" s="27">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U10" s="27">
         <v>0</v>
@@ -5032,14 +5031,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="2"/>
-        <v>329400</v>
+        <v>395400</v>
       </c>
       <c r="AA10" t="s">
         <v>119</v>
@@ -5092,13 +5091,13 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H11" s="21">
         <v>450</v>
       </c>
       <c r="I11" s="21">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J11" s="21">
         <v>300</v>
@@ -5108,10 +5107,10 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>950</v>
+        <v>902</v>
       </c>
       <c r="O11">
-        <v>5700000</v>
+        <v>8700000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5202,11 +5201,11 @@
         <v>60</v>
       </c>
       <c r="C12" s="14">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5231,16 +5230,16 @@
         <v>13</v>
       </c>
       <c r="O12">
-        <v>5700000</v>
+        <v>9626800</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="S12" s="27">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="T12" s="27">
         <v>269</v>
@@ -5253,14 +5252,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1167</v>
+        <v>1187</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>15404400</v>
+        <v>15668400</v>
       </c>
       <c r="AA12" t="s">
         <v>75</v>
@@ -5332,10 +5331,10 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H13" s="21">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I13" s="21">
         <v>60</v>
@@ -5348,7 +5347,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5463,7 +5462,7 @@
         <v>19</v>
       </c>
       <c r="T14" s="27">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="U14" s="27">
         <v>58</v>
@@ -5473,14 +5472,14 @@
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>2204000</v>
+        <v>2291000</v>
       </c>
       <c r="AA14" t="s">
         <v>77</v>
@@ -5528,11 +5527,11 @@
         <v>0</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5544,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="21">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J15" s="21">
         <v>57</v>
@@ -5554,19 +5553,19 @@
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="S15" s="27">
         <v>220</v>
       </c>
       <c r="T15" s="27">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="U15" s="27">
         <v>48</v>
@@ -5576,14 +5575,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7693500</v>
+        <v>7917750</v>
       </c>
       <c r="AA15" t="s">
         <v>78</v>
@@ -5631,23 +5630,23 @@
         <v>60</v>
       </c>
       <c r="C16" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H16" s="21">
         <v>50</v>
       </c>
       <c r="I16" s="21">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5657,7 +5656,7 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -6062,24 +6061,24 @@
         <v>85</v>
       </c>
       <c r="T21" s="27">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U21" s="27">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2688000</v>
+        <v>2870400</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.35">
@@ -6106,17 +6105,17 @@
         <v>70</v>
       </c>
       <c r="I22" s="21">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J22" s="21">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6266,19 +6265,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1224</v>
+        <v>1244</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>609</v>
+        <v>735</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6286,12 +6285,12 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>3059</v>
+        <v>3273</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>34725100</v>
+        <v>36054750</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.35">
@@ -6300,19 +6299,19 @@
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>1148</v>
+        <v>1117</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>835</v>
+        <v>771</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1365</v>
+        <v>1326</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6320,7 +6319,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4727</v>
+        <v>4553</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCD213A-17C5-4614-B396-8486F20744ED}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="5" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
     <sheet name="stok-barang-dse" sheetId="2" r:id="rId2"/>
     <sheet name="penjualan-salmo" sheetId="3" r:id="rId3"/>
-    <sheet name="penjualan-reguler" sheetId="4" r:id="rId4"/>
+    <sheet name="penjualan-reguler-new" sheetId="4" r:id="rId4"/>
     <sheet name="penjualan-paket-tm" sheetId="5" r:id="rId5"/>
     <sheet name="penjualan-direct-selling" sheetId="6" r:id="rId6"/>
     <sheet name="penjualan-hifi" sheetId="7" r:id="rId7"/>
@@ -27,15 +27,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
   <si>
     <t>nama barang</t>
   </si>
@@ -169,18 +177,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Skbplara08</t>
-  </si>
-  <si>
-    <t>Skbplara04</t>
-  </si>
-  <si>
-    <t>Skbplara11</t>
-  </si>
-  <si>
-    <t>Dsesgrn01</t>
-  </si>
-  <si>
     <t>Total Penjualan</t>
   </si>
   <si>
@@ -413,6 +409,24 @@
   </si>
   <si>
     <t>On Hand Dse</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Total PCS</t>
+  </si>
+  <si>
+    <t>Harga</t>
+  </si>
+  <si>
+    <t>Total Rp</t>
+  </si>
+  <si>
+    <t>TOTAL SP</t>
+  </si>
+  <si>
+    <t>VOUCHER</t>
   </si>
 </sst>
 </file>
@@ -420,8 +434,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -643,8 +657,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
@@ -709,16 +723,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -744,8 +758,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -774,9 +788,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -814,7 +828,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -920,7 +934,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1062,7 +1076,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1071,15 +1085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1110,7 +1124,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1127,7 +1141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1137,14 +1151,14 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1161,7 +1175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1175,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1189,13 +1203,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <f>index!B10</f>
-        <v>2250</v>
+        <v>2462</v>
       </c>
       <c r="C9">
         <f>index!C10</f>
@@ -1203,10 +1217,10 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1223,24 +1237,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1257,7 +1271,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1274,7 +1288,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1284,14 +1298,14 @@
       </c>
       <c r="C14">
         <f>index!C15</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1301,14 +1315,14 @@
       </c>
       <c r="C15">
         <f>index!C16</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1325,7 +1339,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1342,7 +1356,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1359,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1376,7 +1390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1393,7 +1407,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1418,18 +1432,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1452,32 +1466,32 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1502,32 +1516,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1552,7 +1566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1574,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1596,21 +1610,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="D8">
         <f>index!I11</f>
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <f>index!J11</f>
@@ -1618,10 +1632,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>902</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1646,21 +1660,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
@@ -1668,10 +1682,10 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1696,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1710,32 +1724,32 @@
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1743,10 +1757,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1771,7 +1785,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1781,7 +1795,7 @@
       </c>
       <c r="C15">
         <f>index!H18</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <f>index!I18</f>
@@ -1793,10 +1807,10 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1821,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1846,7 +1860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1871,32 +1885,32 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1921,7 +1935,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1942,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1963,25 +1977,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1222</v>
+        <v>1274</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>1117</v>
+        <v>983</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1326</v>
+        <v>1422</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1989,7 +2003,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4436</v>
+        <v>4520</v>
       </c>
     </row>
   </sheetData>
@@ -2000,13 +2014,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2014,49 +2028,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>72215900</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>65965900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>115428500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>101851400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>90282500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81582500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>107886300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98259500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>385813200</v>
+        <v>347659300</v>
       </c>
     </row>
   </sheetData>
@@ -2067,731 +2081,606 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>42</v>
+      </c>
+      <c r="C2">
+        <v>42</v>
+      </c>
+      <c r="D2">
+        <v>82</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <f>SUM(B2:E2)</f>
+        <v>266</v>
+      </c>
+      <c r="G2">
+        <v>11000</v>
+      </c>
+      <c r="H2">
+        <f>F2*G2</f>
+        <v>2926000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <f>index!R4</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>index!S4</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <f>index!T4</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <f>index!U4</f>
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <f>SUM(B3:E3)</f>
-        <v>342</v>
+        <f t="shared" ref="F3:F5" si="0">SUM(B3:E3)</f>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>11000</v>
+        <v>30000</v>
       </c>
       <c r="H3">
-        <f>F3*G3</f>
-        <v>3762000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H3:H5" si="1">F3*G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <f>index!R5</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f>index!S5</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <f>index!T5</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>index!U5</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F23" si="0">SUM(B4:E4)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H23" si="1">F4*G4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <f>index!R6</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>index!S6</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <f>index!T6</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>index!U6</f>
         <v>0</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="B6">
-        <f>index!R7</f>
-        <v>0</v>
+        <f>SUM(B2:B5)</f>
+        <v>42</v>
       </c>
       <c r="C6">
-        <f>index!S7</f>
-        <v>0</v>
+        <f t="shared" ref="C6:H6" si="2">SUM(C2:C5)</f>
+        <v>45</v>
       </c>
       <c r="D6">
-        <f>index!T7</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>82</v>
       </c>
       <c r="E6">
-        <f>index!U7</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>100</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>30000</v>
+        <f t="shared" si="2"/>
+        <v>269</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B7">
-        <f>index!R8</f>
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <f>index!S8</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <f>index!T8</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <f>index!U8</f>
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <f>index!R9</f>
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <f>index!S9</f>
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <f>index!T9</f>
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <f>index!U9</f>
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>3001000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <f>index!R10</f>
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C9">
-        <f>index!S10</f>
         <v>369</v>
       </c>
       <c r="D9">
-        <f>index!T10</f>
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E9">
-        <f>index!U10</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
-        <v>659</v>
+        <f>SUM(B9:E9)</f>
+        <v>549</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <f t="shared" si="1"/>
-        <v>395400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <f>F9*G9</f>
+        <v>329400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
       <c r="B10">
-        <f>index!R11</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>index!S11</f>
         <v>2</v>
       </c>
       <c r="D10">
-        <f>index!T11</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>index!U11</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F10:F21" si="3">SUM(B10:E10)</f>
         <v>2</v>
       </c>
       <c r="G10">
         <v>22500</v>
       </c>
       <c r="H10">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H10:H21" si="4">F10*G10</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
       <c r="B11">
-        <f>index!R12</f>
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C11">
-        <f>index!S12</f>
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D11">
-        <f>index!T12</f>
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="E11">
-        <f>index!U12</f>
         <v>215</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
-        <v>1187</v>
+        <f t="shared" si="3"/>
+        <v>1152</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
-        <v>15668400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>15206400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
       <c r="B12">
-        <f>index!R13</f>
         <v>0</v>
       </c>
       <c r="C12">
-        <f>index!S13</f>
         <v>0</v>
       </c>
       <c r="D12">
-        <f>index!T13</f>
         <v>0</v>
       </c>
       <c r="E12">
-        <f>index!U13</f>
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12">
         <v>20000</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13">
-        <f>index!R14</f>
         <v>21</v>
       </c>
       <c r="C13">
-        <f>index!S14</f>
         <v>19</v>
       </c>
       <c r="D13">
-        <f>index!T14</f>
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E13">
-        <f>index!U14</f>
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
-        <v>158</v>
+        <f t="shared" si="3"/>
+        <v>137</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
-        <v>2291000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>1986500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14">
-        <f>index!R15</f>
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C14">
-        <f>index!S15</f>
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D14">
-        <f>index!T15</f>
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E14">
-        <f>index!U15</f>
         <v>48</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
-        <v>459</v>
+        <f t="shared" si="3"/>
+        <v>426</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
-        <f t="shared" si="1"/>
-        <v>7917750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>7348500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15">
-        <f>index!R16</f>
         <v>24</v>
       </c>
       <c r="C15">
-        <f>index!S16</f>
         <v>53</v>
       </c>
       <c r="D15">
-        <f>index!T16</f>
         <v>5</v>
       </c>
       <c r="E15">
-        <f>index!U16</f>
         <v>3</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1955000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <f>index!R17</f>
         <v>3</v>
       </c>
       <c r="C16">
-        <f>index!S17</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <f>index!T17</f>
         <v>0</v>
       </c>
       <c r="E16">
-        <f>index!U17</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
-        <f t="shared" si="1"/>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <f>index!R18</f>
         <v>42</v>
       </c>
       <c r="C17">
-        <f>index!S18</f>
         <v>0</v>
       </c>
       <c r="D17">
-        <f>index!T18</f>
         <v>0</v>
       </c>
       <c r="E17">
-        <f>index!U18</f>
         <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>289800</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <f>index!R19</f>
         <v>0</v>
       </c>
       <c r="C18">
-        <f>index!S19</f>
         <v>0</v>
       </c>
       <c r="D18">
-        <f>index!T19</f>
         <v>0</v>
       </c>
       <c r="E18">
-        <f>index!U19</f>
         <v>9</v>
       </c>
       <c r="F18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="G18">
         <v>7000</v>
       </c>
       <c r="H18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <f>index!R20</f>
         <v>0</v>
       </c>
       <c r="C19">
-        <f>index!S20</f>
         <v>0</v>
       </c>
       <c r="D19">
-        <f>index!T20</f>
         <v>6</v>
       </c>
       <c r="E19">
-        <f>index!U20</f>
         <v>0</v>
       </c>
       <c r="F19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <f>index!R21</f>
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C20">
-        <f>index!S21</f>
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D20">
-        <f>index!T21</f>
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E20">
-        <f>index!U21</f>
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <f t="shared" si="0"/>
-        <v>299</v>
+        <f t="shared" si="3"/>
+        <v>250</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
-        <f t="shared" si="1"/>
-        <v>2870400</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <f>index!R22</f>
         <v>0</v>
       </c>
       <c r="C21">
-        <f>index!S22</f>
         <v>0</v>
       </c>
       <c r="D21">
-        <f>index!T22</f>
         <v>0</v>
       </c>
       <c r="E21">
-        <f>index!U22</f>
         <v>0</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G21">
         <v>13200</v>
       </c>
       <c r="H21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
       <c r="B22">
-        <f>index!R23</f>
-        <v>0</v>
+        <f>SUM(B9:B21)</f>
+        <v>686</v>
       </c>
       <c r="C22">
-        <f>index!S23</f>
-        <v>0</v>
+        <f t="shared" ref="C22:H22" si="5">SUM(C9:C21)</f>
+        <v>1134</v>
       </c>
       <c r="D22">
-        <f>index!T23</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>502</v>
       </c>
       <c r="E22">
-        <f>index!U23</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>351</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2673</v>
       </c>
       <c r="H22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B23">
-        <f>index!R24</f>
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <f>index!S24</f>
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <f>index!T24</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <f>index!U24</f>
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24">
-        <f t="shared" ref="B24:F24" si="2">SUM(B3:B23)</f>
-        <v>780</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="2"/>
-        <v>1244</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="2"/>
-        <v>735</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="2"/>
-        <v>514</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="2"/>
-        <v>3273</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>30145600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H24">
-        <f>SUM(H3:H23)</f>
-        <v>36054750</v>
+        <f>H6+H22</f>
+        <v>33146600</v>
       </c>
     </row>
   </sheetData>
@@ -2802,80 +2691,80 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>61</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>62</v>
-      </c>
-      <c r="G2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" t="s">
-        <v>66</v>
       </c>
       <c r="K2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <f>index!AC4</f>
-        <v>341</v>
+        <v>275</v>
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>7750000</v>
+        <v>7500000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>7750000</v>
+        <v>7500000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2883,7 +2772,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2899,27 +2788,27 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <f>index!AC5</f>
-        <v>339</v>
+        <v>237</v>
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>7585000</v>
+        <v>6835000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>7585000</v>
+        <v>6835000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2927,7 +2816,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2943,27 +2832,27 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <f>index!AC6</f>
-        <v>413</v>
+        <v>286</v>
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>9170000</v>
+        <v>8920000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>9170000</v>
+        <v>8920000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2971,7 +2860,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2987,27 +2876,27 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <f>index!AC7</f>
-        <v>370</v>
+        <v>260</v>
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>8375000</v>
+        <v>6875000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>8375000</v>
+        <v>6875000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -3015,7 +2904,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -3031,21 +2920,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
-        <v>1463</v>
+        <v>1058</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>32880000</v>
+        <v>30130000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>32880000</v>
+        <v>30130000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -3053,7 +2942,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -3069,7 +2958,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3079,51 +2968,51 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
         <v>70</v>
-      </c>
-      <c r="B1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" t="s">
-        <v>74</v>
       </c>
       <c r="H1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <f>index!AC12</f>
@@ -3149,12 +3038,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <f>index!AC13</f>
@@ -3180,9 +3069,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -3211,9 +3100,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -3242,7 +3131,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3266,6 +3155,17 @@
       <c r="H6">
         <f t="shared" si="0"/>
         <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E8" s="28">
+        <v>30130000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <f>E6+E8</f>
+        <v>32650000</v>
       </c>
     </row>
   </sheetData>
@@ -3276,54 +3176,54 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.87109375" customWidth="1"/>
+    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3365,7 +3265,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3407,7 +3307,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3449,10 +3349,10 @@
       </c>
       <c r="K4" s="5"/>
       <c r="M4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3494,7 +3394,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3536,7 +3436,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3578,7 +3478,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3620,7 +3520,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3662,7 +3562,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3704,7 +3604,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3746,7 +3646,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3785,7 +3685,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3824,7 +3724,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3863,7 +3763,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3902,7 +3802,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3941,7 +3841,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3980,9 +3880,9 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3993,37 +3893,37 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" t="s">
         <v>112</v>
       </c>
-      <c r="F1" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="AA1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM1" t="s">
         <v>116</v>
       </c>
-      <c r="AA1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4037,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G2" s="40"/>
       <c r="H2" s="40"/>
@@ -4070,61 +3970,61 @@
         <v>8</v>
       </c>
       <c r="W2" s="42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="X2" s="33" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Y2" s="35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AB2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AD2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AM2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AS2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="AT2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AV2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AR2" s="3" t="s">
+      <c r="AW2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AS2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AV2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW2" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -4140,51 +4040,50 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <f>65965900+O9</f>
-        <v>72215900</v>
+        <v>65965900</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>39</v>
       </c>
       <c r="T3" s="26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="U3" s="26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="W3" s="43"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="36"/>
       <c r="AC3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG3" t="s">
         <v>59</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AH3" t="s">
         <v>60</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AI3" t="s">
         <v>61</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AJ3" t="s">
         <v>62</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>66</v>
       </c>
       <c r="AK3" t="s">
         <v>27</v>
@@ -4196,30 +4095,30 @@
         <v>46157</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AP3" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ3" s="4">
         <v>1</v>
       </c>
       <c r="AR3" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AS3" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AT3" s="8">
         <v>410000</v>
       </c>
       <c r="AU3" s="5"/>
       <c r="AV3" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4258,58 +4157,57 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <f>101851400+O10</f>
-        <v>115428500</v>
+        <v>101851400</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="S4" s="27">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="T4" s="27">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="U4" s="27">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>3762000</v>
+        <v>2926000</v>
       </c>
       <c r="AA4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AB4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AC4">
-        <v>341</v>
+        <v>275</v>
       </c>
       <c r="AD4" s="28">
-        <v>7750000</v>
+        <v>7500000</v>
       </c>
       <c r="AE4" s="28">
-        <v>7750000</v>
+        <v>7500000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4333,27 +4231,27 @@
         <v>22</v>
       </c>
       <c r="AP4" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ4" s="4">
         <v>1</v>
       </c>
       <c r="AR4" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AS4" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AT4" s="8">
         <v>410000</v>
       </c>
       <c r="AU4" s="5"/>
       <c r="AV4" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4371,30 +4269,29 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H5" s="21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I5" s="21">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J5" s="21">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <f>81582500+O11</f>
-        <v>90282500</v>
+        <v>81582500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4426,25 +4323,25 @@
         <v>0</v>
       </c>
       <c r="AA5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AC5">
-        <v>339</v>
+        <v>237</v>
       </c>
       <c r="AD5" s="28">
-        <v>7585000</v>
+        <v>6835000</v>
       </c>
       <c r="AE5" s="28">
-        <v>7585000</v>
+        <v>6835000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4468,27 +4365,27 @@
         <v>24</v>
       </c>
       <c r="AP5" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ5" s="4">
         <v>1</v>
       </c>
       <c r="AR5" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AS5" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AT5" s="8">
         <v>410000</v>
       </c>
       <c r="AU5" s="5"/>
       <c r="AV5" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4496,11 +4393,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1511</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3036</v>
+        <v>3069</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4528,14 +4425,13 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <f>98259500+O12</f>
-        <v>107886300</v>
+        <v>98259500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="27">
         <v>3</v>
@@ -4551,35 +4447,35 @@
       </c>
       <c r="W6" s="27">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
         <f t="shared" si="2"/>
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="AA6" t="s">
         <v>41</v>
       </c>
       <c r="AB6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AC6">
-        <v>413</v>
+        <v>286</v>
       </c>
       <c r="AD6" s="28">
-        <v>9170000</v>
+        <v>8920000</v>
       </c>
       <c r="AE6" s="28">
-        <v>9170000</v>
+        <v>8920000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4603,27 +4499,27 @@
         <v>25</v>
       </c>
       <c r="AP6" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ6" s="4">
         <v>1</v>
       </c>
       <c r="AR6" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AS6" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AT6" s="8">
         <v>410000</v>
       </c>
       <c r="AU6" s="5"/>
       <c r="AV6" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4641,30 +4537,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H7" s="21">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I7" s="21">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="J7" s="21">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1634</v>
+        <v>1691</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>385813200</v>
+        <v>347659300</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4699,22 +4595,22 @@
         <v>42</v>
       </c>
       <c r="AB7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AC7">
-        <v>370</v>
+        <v>260</v>
       </c>
       <c r="AD7" s="28">
-        <v>8375000</v>
+        <v>6875000</v>
       </c>
       <c r="AE7" s="28">
-        <v>8375000</v>
+        <v>6875000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4735,30 +4631,30 @@
         <v>46163</v>
       </c>
       <c r="AO7" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AP7" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ7" s="4">
         <v>1</v>
       </c>
       <c r="AR7" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AS7" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="AT7" s="9">
         <v>410000</v>
       </c>
       <c r="AU7" s="5"/>
       <c r="AV7" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4822,18 +4718,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>32880000</v>
+        <v>30130000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>32880000</v>
+        <v>30130000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4861,27 +4757,27 @@
         <v>22</v>
       </c>
       <c r="AP8" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ8" s="4">
         <v>1</v>
       </c>
       <c r="AR8" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AS8" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AT8" s="9">
         <v>410000</v>
       </c>
       <c r="AU8" s="5"/>
       <c r="AV8" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4914,10 +4810,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O9">
-        <v>6250000</v>
+        <v>2550000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4954,39 +4850,39 @@
         <v>24</v>
       </c>
       <c r="AP9" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ9" s="4">
         <v>1</v>
       </c>
       <c r="AR9" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AS9" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AT9" s="8">
         <v>410000</v>
       </c>
       <c r="AU9" s="5"/>
       <c r="AV9" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="13">
-        <v>2250</v>
+        <v>2462</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
-        <v>2250</v>
+        <v>2462</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="21">
@@ -5009,19 +4905,19 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>13577100</v>
+        <v>3519000</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="S10" s="27">
         <v>369</v>
       </c>
       <c r="T10" s="27">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U10" s="27">
         <v>0</v>
@@ -5031,17 +4927,17 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>659</v>
+        <v>549</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="2"/>
-        <v>395400</v>
+        <v>329400</v>
       </c>
       <c r="AA10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AM10" s="4">
         <v>8</v>
@@ -5053,27 +4949,27 @@
         <v>25</v>
       </c>
       <c r="AP10" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ10" s="4">
         <v>1</v>
       </c>
       <c r="AR10" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AT10" s="8">
         <v>410000</v>
       </c>
       <c r="AU10" s="5"/>
       <c r="AV10" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5091,13 +4987,13 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H11" s="21">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="I11" s="21">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J11" s="21">
         <v>300</v>
@@ -5107,10 +5003,10 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>902</v>
+        <v>800</v>
       </c>
       <c r="O11">
-        <v>8700000</v>
+        <v>5819000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5142,25 +5038,25 @@
         <v>45000</v>
       </c>
       <c r="AA11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG11" t="s">
         <v>70</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>74</v>
       </c>
       <c r="AH11" t="s">
         <v>27</v>
@@ -5172,40 +5068,40 @@
         <v>46163</v>
       </c>
       <c r="AO11" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AP11" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ11" s="4">
         <v>1</v>
       </c>
       <c r="AR11" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AS11" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="5"/>
       <c r="AV11" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C12" s="14">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1041</v>
+        <v>1128</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5230,19 +5126,19 @@
         <v>13</v>
       </c>
       <c r="O12">
-        <v>9626800</v>
+        <v>3500000</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="S12" s="27">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="T12" s="27">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="U12" s="27">
         <v>215</v>
@@ -5252,20 +5148,20 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1187</v>
+        <v>1152</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>15668400</v>
+        <v>15206400</v>
       </c>
       <c r="AA12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AB12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AC12">
         <v>63</v>
@@ -5292,28 +5188,28 @@
         <v>46164</v>
       </c>
       <c r="AO12" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AP12" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ12" s="4">
         <v>1</v>
       </c>
       <c r="AR12" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AS12" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AT12" s="9"/>
       <c r="AU12" s="5"/>
       <c r="AV12" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5331,13 +5227,13 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H13" s="21">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I13" s="21">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J13" s="21">
         <v>147</v>
@@ -5347,7 +5243,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>430</v>
+        <v>375</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5379,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AB13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AC13">
         <v>63</v>
@@ -5416,7 +5312,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5462,27 +5358,27 @@
         <v>19</v>
       </c>
       <c r="T14" s="27">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="U14" s="27">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>2291000</v>
+        <v>1986500</v>
       </c>
       <c r="AA14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AB14" t="s">
         <v>41</v>
@@ -5519,7 +5415,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5527,11 +5423,11 @@
         <v>0</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5543,29 +5439,29 @@
         <v>12</v>
       </c>
       <c r="I15" s="21">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J15" s="21">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K15" s="21">
         <v>0</v>
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="S15" s="27">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="T15" s="27">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="U15" s="27">
         <v>48</v>
@@ -5575,17 +5471,17 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7917750</v>
+        <v>7348500</v>
       </c>
       <c r="AA15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AB15" t="s">
         <v>42</v>
@@ -5622,7 +5518,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5630,23 +5526,23 @@
         <v>60</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H16" s="21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I16" s="21">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5656,7 +5552,7 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5725,7 +5621,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5768,7 +5664,7 @@
         <v>3</v>
       </c>
       <c r="S17" s="27">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T17" s="27">
         <v>0</v>
@@ -5781,14 +5677,14 @@
       </c>
       <c r="W17" s="27">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
       <c r="Y17" s="27">
         <f t="shared" si="2"/>
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="AM17" s="4">
         <v>15</v>
@@ -5804,7 +5700,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5825,7 +5721,7 @@
         <v>45</v>
       </c>
       <c r="H18" s="21">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I18" s="21">
         <v>18</v>
@@ -5838,7 +5734,7 @@
       </c>
       <c r="L18" s="22">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="Q18" s="20" t="s">
         <v>16</v>
@@ -5883,7 +5779,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5949,7 +5845,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -6015,7 +5911,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -6055,33 +5951,33 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="S21" s="27">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="T21" s="27">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="U21" s="27">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2870400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6099,23 +5995,23 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H22" s="21">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I22" s="21">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J22" s="21">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>369</v>
+        <v>418</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6147,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6194,7 +6090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6239,7 +6135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6261,23 +6157,23 @@
         <v>0</v>
       </c>
       <c r="Q25" s="23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>780</v>
+        <v>728</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1244</v>
+        <v>1179</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>735</v>
+        <v>584</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6285,33 +6181,33 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>3273</v>
+        <v>2942</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>36054750</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+        <v>33146600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1222</v>
+        <v>1274</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>1117</v>
+        <v>983</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1326</v>
+        <v>1422</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6319,7 +6215,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4553</v>
+        <v>4637</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08007BF8-341C-8C4F-A873-A2E05A0208D3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="5" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="3" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="132">
   <si>
     <t>nama barang</t>
   </si>
@@ -1151,11 +1151,11 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1544</v>
+        <v>1511</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3069</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B9" s="1">
         <f>index!B10</f>
-        <v>2462</v>
+        <v>2250</v>
       </c>
       <c r="C9">
         <f>index!C10</f>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>2462</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1243,15 +1243,15 @@
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1128</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1298,11 +1298,11 @@
       </c>
       <c r="C14">
         <f>index!C15</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1315,11 +1315,11 @@
       </c>
       <c r="C15">
         <f>index!C16</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>162</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1681</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1616,15 +1616,15 @@
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="D8">
         <f>index!I11</f>
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <f>index!J11</f>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1666,15 +1666,15 @@
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>354</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1724,15 +1724,15 @@
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>168</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1741,15 +1741,15 @@
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>352</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C15">
         <f>index!H18</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <f>index!I18</f>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1891,23 +1891,23 @@
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>406</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1983,19 +1983,19 @@
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1274</v>
+        <v>1222</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>983</v>
+        <v>1117</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>841</v>
+        <v>771</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1422</v>
+        <v>1326</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4520</v>
+        <v>4436</v>
       </c>
     </row>
   </sheetData>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>65965900</v>
+        <v>72215900</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>101851400</v>
+        <v>115428500</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>81582500</v>
+        <v>90282500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>98259500</v>
+        <v>107886300</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>347659300</v>
+        <v>385813200</v>
       </c>
     </row>
   </sheetData>
@@ -2134,14 +2134,12 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <f>SUM(B2:E2)</f>
         <v>266</v>
       </c>
       <c r="G2">
         <v>11000</v>
       </c>
       <c r="H2">
-        <f>F2*G2</f>
         <v>2926000</v>
       </c>
     </row>
@@ -2162,14 +2160,12 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F5" si="0">SUM(B3:E3)</f>
         <v>0</v>
       </c>
       <c r="G3">
         <v>30000</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H5" si="1">F3*G3</f>
         <v>0</v>
       </c>
     </row>
@@ -2190,14 +2186,12 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G4">
         <v>25000</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
         <v>75000</v>
       </c>
     </row>
@@ -2218,14 +2212,12 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G5">
         <v>30000</v>
       </c>
       <c r="H5">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2234,27 +2226,21 @@
         <v>126</v>
       </c>
       <c r="B6">
-        <f>SUM(B2:B5)</f>
         <v>42</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:H6" si="2">SUM(C2:C5)</f>
         <v>45</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="E6">
-        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="F6">
-        <f t="shared" si="2"/>
         <v>269</v>
       </c>
       <c r="H6">
-        <f t="shared" si="2"/>
         <v>3001000</v>
       </c>
     </row>
@@ -2301,14 +2287,12 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <f>SUM(B9:E9)</f>
         <v>549</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <f>F9*G9</f>
         <v>329400</v>
       </c>
     </row>
@@ -2329,14 +2313,12 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:F21" si="3">SUM(B10:E10)</f>
         <v>2</v>
       </c>
       <c r="G10">
         <v>22500</v>
       </c>
       <c r="H10">
-        <f t="shared" ref="H10:H21" si="4">F10*G10</f>
         <v>45000</v>
       </c>
     </row>
@@ -2357,14 +2339,12 @@
         <v>215</v>
       </c>
       <c r="F11">
-        <f t="shared" si="3"/>
         <v>1152</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
-        <f t="shared" si="4"/>
         <v>15206400</v>
       </c>
     </row>
@@ -2385,14 +2365,12 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12">
         <v>20000</v>
       </c>
       <c r="H12">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -2413,14 +2391,12 @@
         <v>43</v>
       </c>
       <c r="F13">
-        <f t="shared" si="3"/>
         <v>137</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
-        <f t="shared" si="4"/>
         <v>1986500</v>
       </c>
     </row>
@@ -2441,14 +2417,12 @@
         <v>48</v>
       </c>
       <c r="F14">
-        <f t="shared" si="3"/>
         <v>426</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
-        <f t="shared" si="4"/>
         <v>7348500</v>
       </c>
     </row>
@@ -2469,14 +2443,12 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
-        <f t="shared" si="4"/>
         <v>1955000</v>
       </c>
     </row>
@@ -2497,14 +2469,12 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
         <v>450000</v>
       </c>
     </row>
@@ -2525,14 +2495,12 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
-        <f t="shared" si="4"/>
         <v>289800</v>
       </c>
     </row>
@@ -2553,14 +2521,12 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="G18">
         <v>7000</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
         <v>63000</v>
       </c>
     </row>
@@ -2581,14 +2547,12 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
-        <f t="shared" si="4"/>
         <v>72000</v>
       </c>
     </row>
@@ -2609,14 +2573,12 @@
         <v>33</v>
       </c>
       <c r="F20">
-        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
         <v>2400000</v>
       </c>
     </row>
@@ -2637,14 +2599,12 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G21">
         <v>13200</v>
       </c>
       <c r="H21">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -2653,33 +2613,26 @@
         <v>50</v>
       </c>
       <c r="B22">
-        <f>SUM(B9:B21)</f>
         <v>686</v>
       </c>
       <c r="C22">
-        <f t="shared" ref="C22:H22" si="5">SUM(C9:C21)</f>
         <v>1134</v>
       </c>
       <c r="D22">
-        <f t="shared" si="5"/>
         <v>502</v>
       </c>
       <c r="E22">
-        <f t="shared" si="5"/>
         <v>351</v>
       </c>
       <c r="F22">
-        <f t="shared" si="5"/>
         <v>2673</v>
       </c>
       <c r="H22">
-        <f t="shared" si="5"/>
         <v>30145600</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H24">
-        <f>H6+H22</f>
         <v>33146600</v>
       </c>
     </row>
@@ -2756,15 +2709,15 @@
       </c>
       <c r="C3">
         <f>index!AC4</f>
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2772,7 +2725,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2788,7 +2741,7 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2800,15 +2753,15 @@
       </c>
       <c r="C4">
         <f>index!AC5</f>
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>6835000</v>
+        <v>7585000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>6835000</v>
+        <v>7585000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2816,7 +2769,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2832,7 +2785,7 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2844,15 +2797,15 @@
       </c>
       <c r="C5">
         <f>index!AC6</f>
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2860,7 +2813,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2876,7 +2829,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2888,15 +2841,15 @@
       </c>
       <c r="C6">
         <f>index!AC7</f>
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>6875000</v>
+        <v>8375000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>6875000</v>
+        <v>8375000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -2904,7 +2857,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -2920,21 +2873,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
-        <v>1058</v>
+        <v>1463</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>30130000</v>
+        <v>32880000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>30130000</v>
+        <v>32880000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -2942,7 +2895,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -2958,7 +2911,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2968,7 +2921,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
@@ -3155,17 +3108,6 @@
       <c r="H6">
         <f t="shared" si="0"/>
         <v>252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E8" s="28">
-        <v>30130000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E9">
-        <f>E6+E8</f>
-        <v>32650000</v>
       </c>
     </row>
   </sheetData>
@@ -4040,7 +3982,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <v>65965900</v>
+        <f>65965900+O9</f>
+        <v>72215900</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4157,36 +4100,37 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <v>101851400</v>
+        <f>101851400+O10</f>
+        <v>115428500</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="S4" s="27">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="T4" s="27">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="U4" s="27">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>2926000</v>
+        <v>3762000</v>
       </c>
       <c r="AA4" t="s">
         <v>63</v>
@@ -4195,19 +4139,19 @@
         <v>64</v>
       </c>
       <c r="AC4">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="AD4" s="28">
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="AE4" s="28">
-        <v>7500000</v>
+        <v>7750000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4269,29 +4213,30 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H5" s="21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5" s="21">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J5" s="21">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <v>81582500</v>
+        <f>81582500+O11</f>
+        <v>90282500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4329,19 +4274,19 @@
         <v>64</v>
       </c>
       <c r="AC5">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="AD5" s="28">
-        <v>6835000</v>
+        <v>7585000</v>
       </c>
       <c r="AE5" s="28">
-        <v>6835000</v>
+        <v>7585000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4393,11 +4338,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1544</v>
+        <v>1511</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3069</v>
+        <v>3036</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4425,13 +4370,14 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <v>98259500</v>
+        <f>98259500+O12</f>
+        <v>107886300</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="27">
         <v>3</v>
@@ -4447,14 +4393,14 @@
       </c>
       <c r="W6" s="27">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
         <f t="shared" si="2"/>
-        <v>75000</v>
+        <v>125000</v>
       </c>
       <c r="AA6" t="s">
         <v>41</v>
@@ -4463,19 +4409,19 @@
         <v>64</v>
       </c>
       <c r="AC6">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="AD6" s="28">
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="AE6" s="28">
-        <v>8920000</v>
+        <v>9170000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4537,30 +4483,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H7" s="21">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="I7" s="21">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="J7" s="21">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1691</v>
+        <v>1634</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>347659300</v>
+        <v>385813200</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4598,19 +4544,19 @@
         <v>64</v>
       </c>
       <c r="AC7">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="AD7" s="28">
-        <v>6875000</v>
+        <v>8375000</v>
       </c>
       <c r="AE7" s="28">
-        <v>6875000</v>
+        <v>8375000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4718,18 +4664,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>30130000</v>
+        <v>32880000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>30130000</v>
+        <v>32880000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4813,7 +4759,7 @@
         <v>120</v>
       </c>
       <c r="O9">
-        <v>2550000</v>
+        <v>6250000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4875,14 +4821,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="13">
-        <v>2462</v>
+        <v>2250</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
-        <v>2462</v>
+        <v>2250</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="21">
@@ -4905,19 +4851,19 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>3519000</v>
+        <v>13577100</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="S10" s="27">
         <v>369</v>
       </c>
       <c r="T10" s="27">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U10" s="27">
         <v>0</v>
@@ -4927,14 +4873,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>549</v>
+        <v>659</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="2"/>
-        <v>329400</v>
+        <v>395400</v>
       </c>
       <c r="AA10" t="s">
         <v>115</v>
@@ -4987,13 +4933,13 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H11" s="21">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="I11" s="21">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J11" s="21">
         <v>300</v>
@@ -5003,10 +4949,10 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>800</v>
+        <v>902</v>
       </c>
       <c r="O11">
-        <v>5819000</v>
+        <v>8700000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5094,14 +5040,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C12" s="14">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1128</v>
+        <v>1041</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5126,19 +5072,19 @@
         <v>13</v>
       </c>
       <c r="O12">
-        <v>3500000</v>
+        <v>9626800</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="S12" s="27">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="T12" s="27">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="U12" s="27">
         <v>215</v>
@@ -5148,14 +5094,14 @@
       </c>
       <c r="W12" s="27">
         <f t="shared" si="1"/>
-        <v>1152</v>
+        <v>1187</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="2"/>
-        <v>15206400</v>
+        <v>15668400</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
@@ -5227,13 +5173,13 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H13" s="21">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I13" s="21">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J13" s="21">
         <v>147</v>
@@ -5243,7 +5189,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>375</v>
+        <v>430</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5358,24 +5304,24 @@
         <v>19</v>
       </c>
       <c r="T14" s="27">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="U14" s="27">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>1986500</v>
+        <v>2291000</v>
       </c>
       <c r="AA14" t="s">
         <v>73</v>
@@ -5423,11 +5369,11 @@
         <v>0</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5439,29 +5385,29 @@
         <v>12</v>
       </c>
       <c r="I15" s="21">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J15" s="21">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K15" s="21">
         <v>0</v>
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="S15" s="27">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="T15" s="27">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="U15" s="27">
         <v>48</v>
@@ -5471,14 +5417,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7348500</v>
+        <v>7917750</v>
       </c>
       <c r="AA15" t="s">
         <v>74</v>
@@ -5526,23 +5472,23 @@
         <v>60</v>
       </c>
       <c r="C16" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H16" s="21">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I16" s="21">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5552,7 +5498,7 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5664,7 +5610,7 @@
         <v>3</v>
       </c>
       <c r="S17" s="27">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T17" s="27">
         <v>0</v>
@@ -5677,14 +5623,14 @@
       </c>
       <c r="W17" s="27">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
       <c r="Y17" s="27">
         <f t="shared" si="2"/>
-        <v>450000</v>
+        <v>600000</v>
       </c>
       <c r="AM17" s="4">
         <v>15</v>
@@ -5721,7 +5667,7 @@
         <v>45</v>
       </c>
       <c r="H18" s="21">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I18" s="21">
         <v>18</v>
@@ -5734,7 +5680,7 @@
       </c>
       <c r="L18" s="22">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="20" t="s">
         <v>16</v>
@@ -5951,30 +5897,30 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="S21" s="27">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T21" s="27">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U21" s="27">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2400000</v>
+        <v>2870400</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.2">
@@ -5995,23 +5941,23 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H22" s="21">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I22" s="21">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J22" s="21">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>418</v>
+        <v>369</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6161,19 +6107,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>728</v>
+        <v>780</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1179</v>
+        <v>1244</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>584</v>
+        <v>735</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>451</v>
+        <v>514</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6181,12 +6127,12 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>2942</v>
+        <v>3273</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>33146600</v>
+        <v>36054750</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.2">
@@ -6195,19 +6141,19 @@
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1274</v>
+        <v>1222</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>983</v>
+        <v>1117</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>841</v>
+        <v>771</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1422</v>
+        <v>1326</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6215,7 +6161,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4637</v>
+        <v>4553</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08007BF8-341C-8C4F-A873-A2E05A0208D3}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B20D7BF6-3803-7F47-AC31-3301A05A9FBF}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="3" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
   <si>
     <t>nama barang</t>
   </si>
@@ -661,7 +661,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,6 +755,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2080,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
@@ -2244,6 +2247,7 @@
         <v>3001000</v>
       </c>
     </row>
+    <row r="7" spans="1:8" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>127</v>
@@ -2631,12 +2635,10 @@
         <v>30145600</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H24">
-        <v>33146600</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:XFD7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B20D7BF6-3803-7F47-AC31-3301A05A9FBF}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{411ACDE1-1E2E-498D-8727-C9A7FF11DFCA}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="6" activeTab="3" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,8 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -434,8 +426,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -657,8 +649,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="45">
@@ -723,16 +715,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -756,13 +751,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
-    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -791,9 +783,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -831,7 +823,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -937,7 +929,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1079,7 +1071,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1088,15 +1080,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1127,7 +1119,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1144,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1154,14 +1146,14 @@
       </c>
       <c r="C5">
         <f>index!C6</f>
-        <v>1511</v>
+        <v>1445</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1178,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1192,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1206,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1223,7 +1215,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1240,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1257,7 +1249,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1274,7 +1266,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1291,7 +1283,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1308,7 +1300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1325,7 +1317,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1342,7 +1334,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1359,7 +1351,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1376,7 +1368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1393,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1410,7 +1402,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1435,18 +1427,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1469,13 +1461,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <f>index!G5</f>
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <f>index!H5</f>
@@ -1483,18 +1475,18 @@
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1519,32 +1511,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>420</v>
+        <v>376</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>432</v>
+        <v>267</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1569,7 +1561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1591,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1613,17 +1605,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="D8">
         <f>index!I11</f>
@@ -1635,10 +1627,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>902</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1663,7 +1655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1688,7 +1680,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1713,7 +1705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1723,11 +1715,11 @@
       </c>
       <c r="C12">
         <f>index!H15</f>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
@@ -1735,16 +1727,16 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13">
         <f>index!G16</f>
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C13">
         <f>index!H16</f>
@@ -1752,7 +1744,7 @@
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1760,10 +1752,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1788,7 +1780,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1813,7 +1805,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1838,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1863,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1888,32 +1880,32 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1938,7 +1930,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1959,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1980,25 +1972,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1222</v>
+        <v>1133</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>1117</v>
+        <v>858</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>771</v>
+        <v>681</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1326</v>
+        <v>1145</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -2006,7 +1998,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4436</v>
+        <v>3817</v>
       </c>
     </row>
   </sheetData>
@@ -2017,13 +2009,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2031,49 +2023,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>117</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>72215900</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>79465900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>115428500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>128661600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>90282500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100370500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>107886300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>119569800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>385813200</v>
+        <v>428067800</v>
       </c>
     </row>
   </sheetData>
@@ -2084,17 +2076,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>122</v>
       </c>
@@ -2120,135 +2112,165 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>42</v>
+        <f>index!R4</f>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <f>index!S4</f>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>82</v>
+        <f>index!T4</f>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <f>index!U4</f>
+        <v>148</v>
       </c>
       <c r="F2">
-        <v>266</v>
+        <f>SUM(B2:E2)</f>
+        <v>367</v>
       </c>
       <c r="G2">
         <v>11000</v>
       </c>
       <c r="H2">
-        <v>2926000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <f>F2*G2</f>
+        <v>4037000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
       <c r="B3">
+        <f>index!R5</f>
         <v>0</v>
       </c>
       <c r="C3">
+        <f>index!S5</f>
         <v>0</v>
       </c>
       <c r="D3">
+        <f>index!T5</f>
         <v>0</v>
       </c>
       <c r="E3">
+        <f>index!U5</f>
         <v>0</v>
       </c>
       <c r="F3">
+        <f t="shared" ref="F3:F5" si="0">SUM(B3:E3)</f>
         <v>0</v>
       </c>
       <c r="G3">
         <v>30000</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" ref="H3:H5" si="1">F3*G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <f>index!R6</f>
+        <v>2</v>
       </c>
       <c r="C4">
+        <f>index!S6</f>
         <v>3</v>
       </c>
       <c r="D4">
+        <f>index!T6</f>
         <v>0</v>
       </c>
       <c r="E4">
+        <f>index!U6</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>25000</v>
       </c>
       <c r="H4">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
+        <f>index!R7</f>
         <v>0</v>
       </c>
       <c r="C5">
+        <f>index!S7</f>
         <v>0</v>
       </c>
       <c r="D5">
+        <f>index!T7</f>
         <v>0</v>
       </c>
       <c r="E5">
+        <f>index!U7</f>
         <v>0</v>
       </c>
       <c r="F5">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G5">
         <v>30000</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>126</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <f>SUM(B2:B5)</f>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <f t="shared" ref="C6:H6" si="2">SUM(C2:C5)</f>
+        <v>65</v>
       </c>
       <c r="D6">
-        <v>82</v>
+        <f t="shared" si="2"/>
+        <v>95</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <f t="shared" si="2"/>
+        <v>148</v>
       </c>
       <c r="F6">
-        <v>269</v>
+        <f t="shared" si="2"/>
+        <v>372</v>
       </c>
       <c r="H6">
-        <v>3001000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>4162000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="33" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -2274,365 +2296,449 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>130</v>
+        <f>index!R10</f>
+        <v>160</v>
       </c>
       <c r="C9">
-        <v>369</v>
+        <f>index!S10</f>
+        <v>519</v>
       </c>
       <c r="D9">
-        <v>50</v>
+        <f>index!T10</f>
+        <v>150</v>
       </c>
       <c r="E9">
+        <f>index!U10</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <v>549</v>
+        <f>SUM(B9:E9)</f>
+        <v>829</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
-        <v>329400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <f>F9*G9</f>
+        <v>497400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
       <c r="B10">
+        <f>index!R11</f>
         <v>0</v>
       </c>
       <c r="C10">
+        <f>index!S11</f>
         <v>2</v>
       </c>
       <c r="D10">
+        <f>index!T11</f>
         <v>0</v>
       </c>
       <c r="E10">
+        <f>index!U11</f>
         <v>0</v>
       </c>
       <c r="F10">
+        <f t="shared" ref="F10:F21" si="3">SUM(B10:E10)</f>
         <v>2</v>
       </c>
       <c r="G10">
         <v>22500</v>
       </c>
       <c r="H10">
+        <f t="shared" ref="H10:H21" si="4">F10*G10</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
       <c r="B11">
-        <v>279</v>
+        <f>index!R12</f>
+        <v>289</v>
       </c>
       <c r="C11">
-        <v>404</v>
+        <f>index!S12</f>
+        <v>414</v>
       </c>
       <c r="D11">
-        <v>254</v>
+        <f>index!T12</f>
+        <v>269</v>
       </c>
       <c r="E11">
+        <f>index!U12</f>
         <v>215</v>
       </c>
       <c r="F11">
-        <v>1152</v>
+        <f t="shared" si="3"/>
+        <v>1187</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
-        <v>15206400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>15668400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
       <c r="B12">
+        <f>index!R13</f>
         <v>0</v>
       </c>
       <c r="C12">
+        <f>index!S13</f>
         <v>0</v>
       </c>
       <c r="D12">
+        <f>index!T13</f>
         <v>0</v>
       </c>
       <c r="E12">
+        <f>index!U13</f>
         <v>0</v>
       </c>
       <c r="F12">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12">
         <v>20000</v>
       </c>
       <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13">
+        <f>index!R14</f>
         <v>21</v>
       </c>
       <c r="C13">
-        <v>19</v>
+        <f>index!S14</f>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>54</v>
+        <f>index!T14</f>
+        <v>76</v>
       </c>
       <c r="E13">
-        <v>43</v>
+        <f>index!U14</f>
+        <v>58</v>
       </c>
       <c r="F13">
-        <v>137</v>
+        <f t="shared" si="3"/>
+        <v>184</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
-        <v>1986500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>2668000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14">
-        <v>77</v>
+        <f>index!R15</f>
+        <v>97</v>
       </c>
       <c r="C14">
-        <v>210</v>
+        <f>index!S15</f>
+        <v>220</v>
       </c>
       <c r="D14">
-        <v>91</v>
+        <f>index!T15</f>
+        <v>120</v>
       </c>
       <c r="E14">
+        <f>index!U15</f>
         <v>48</v>
       </c>
       <c r="F14">
-        <v>426</v>
+        <f t="shared" si="3"/>
+        <v>485</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
-        <v>7348500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>8366250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15">
+        <f>index!R16</f>
         <v>24</v>
       </c>
       <c r="C15">
+        <f>index!S16</f>
         <v>53</v>
       </c>
       <c r="D15">
+        <f>index!T16</f>
         <v>5</v>
       </c>
       <c r="E15">
+        <f>index!U16</f>
         <v>3</v>
       </c>
       <c r="F15">
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
+        <f t="shared" si="4"/>
         <v>1955000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
+        <f>index!R17</f>
         <v>3</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <f>index!S17</f>
+        <v>17</v>
       </c>
       <c r="D16">
+        <f>index!T17</f>
         <v>0</v>
       </c>
       <c r="E16">
+        <f>index!U17</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
+        <f>index!R18</f>
         <v>42</v>
       </c>
       <c r="C17">
+        <f>index!S18</f>
         <v>0</v>
       </c>
       <c r="D17">
+        <f>index!T18</f>
         <v>0</v>
       </c>
       <c r="E17">
+        <f>index!U18</f>
         <v>0</v>
       </c>
       <c r="F17">
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
+        <f t="shared" si="4"/>
         <v>289800</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
+        <f>index!R19</f>
         <v>0</v>
       </c>
       <c r="C18">
+        <f>index!S19</f>
         <v>0</v>
       </c>
       <c r="D18">
+        <f>index!T19</f>
         <v>0</v>
       </c>
       <c r="E18">
+        <f>index!U19</f>
         <v>9</v>
       </c>
       <c r="F18">
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="G18">
         <v>7000</v>
       </c>
       <c r="H18">
+        <f t="shared" si="4"/>
         <v>63000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
+        <f>index!R20</f>
         <v>0</v>
       </c>
       <c r="C19">
+        <f>index!S20</f>
         <v>0</v>
       </c>
       <c r="D19">
+        <f>index!T20</f>
         <v>6</v>
       </c>
       <c r="E19">
+        <f>index!U20</f>
         <v>0</v>
       </c>
       <c r="F19">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
+        <f t="shared" si="4"/>
         <v>72000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>110</v>
+        <f>index!R21</f>
+        <v>136</v>
       </c>
       <c r="C20">
-        <v>65</v>
+        <f>index!S21</f>
+        <v>140</v>
       </c>
       <c r="D20">
-        <v>42</v>
+        <f>index!T21</f>
+        <v>60</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <f>index!U21</f>
+        <v>49</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <f t="shared" si="3"/>
+        <v>385</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>3696000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
+        <f>index!R22</f>
         <v>0</v>
       </c>
       <c r="C21">
+        <f>index!S22</f>
         <v>0</v>
       </c>
       <c r="D21">
+        <f>index!T22</f>
         <v>0</v>
       </c>
       <c r="E21">
+        <f>index!U22</f>
         <v>0</v>
       </c>
       <c r="F21">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G21">
         <v>13200</v>
       </c>
       <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22">
+        <f>SUM(B9:B21)</f>
+        <v>772</v>
+      </c>
+      <c r="C22">
+        <f t="shared" ref="C22:H22" si="5">SUM(C9:C21)</f>
+        <v>1394</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="5"/>
         <v>686</v>
       </c>
-      <c r="C22">
-        <v>1134</v>
-      </c>
-      <c r="D22">
-        <v>502</v>
-      </c>
       <c r="E22">
-        <v>351</v>
+        <f t="shared" si="5"/>
+        <v>382</v>
       </c>
       <c r="F22">
-        <v>2673</v>
+        <f t="shared" si="5"/>
+        <v>3234</v>
       </c>
       <c r="H22">
-        <v>30145600</v>
+        <f t="shared" si="5"/>
+        <v>33920850</v>
       </c>
     </row>
   </sheetData>
@@ -2646,20 +2752,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -2673,7 +2779,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>55</v>
       </c>
@@ -2702,7 +2808,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -2711,15 +2817,15 @@
       </c>
       <c r="C3">
         <f>index!AC4</f>
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D3" s="28">
         <f>index!AD4</f>
-        <v>7750000</v>
+        <v>8750000</v>
       </c>
       <c r="E3" s="28">
         <f>index!AE4</f>
-        <v>7750000</v>
+        <v>8750000</v>
       </c>
       <c r="F3" s="28" t="str">
         <f>index!AF4</f>
@@ -2727,7 +2833,7 @@
       </c>
       <c r="G3">
         <f>index!AG4</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3">
         <f>index!AH4</f>
@@ -2743,10 +2849,10 @@
       </c>
       <c r="K3">
         <f>SUM(G3:J3)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -2755,15 +2861,15 @@
       </c>
       <c r="C4">
         <f>index!AC5</f>
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="D4" s="28">
         <f>index!AD5</f>
-        <v>7585000</v>
+        <v>8335000</v>
       </c>
       <c r="E4" s="28">
         <f>index!AE5</f>
-        <v>7585000</v>
+        <v>8335000</v>
       </c>
       <c r="F4" s="28" t="str">
         <f>index!AF5</f>
@@ -2771,7 +2877,7 @@
       </c>
       <c r="G4">
         <f>index!AG5</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <f>index!AH5</f>
@@ -2787,10 +2893,10 @@
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2799,15 +2905,15 @@
       </c>
       <c r="C5">
         <f>index!AC6</f>
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="D5" s="28">
         <f>index!AD6</f>
-        <v>9170000</v>
+        <v>10170000</v>
       </c>
       <c r="E5" s="28">
         <f>index!AE6</f>
-        <v>9170000</v>
+        <v>10170000</v>
       </c>
       <c r="F5" s="28" t="str">
         <f>index!AF6</f>
@@ -2815,7 +2921,7 @@
       </c>
       <c r="G5">
         <f>index!AG6</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5">
         <f>index!AH6</f>
@@ -2831,10 +2937,10 @@
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2843,15 +2949,15 @@
       </c>
       <c r="C6">
         <f>index!AC7</f>
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="D6" s="28">
         <f>index!AD7</f>
-        <v>8375000</v>
+        <v>12125000</v>
       </c>
       <c r="E6" s="28">
         <f>index!AE7</f>
-        <v>8375000</v>
+        <v>12125000</v>
       </c>
       <c r="F6" s="28" t="str">
         <f>index!AF7</f>
@@ -2859,7 +2965,7 @@
       </c>
       <c r="G6">
         <f>index!AG7</f>
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H6">
         <f>index!AH7</f>
@@ -2875,21 +2981,21 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
-        <v>1463</v>
+        <v>1749</v>
       </c>
       <c r="D7" s="28">
         <f>SUM(D3:D6)</f>
-        <v>32880000</v>
+        <v>39380000</v>
       </c>
       <c r="E7" s="28">
         <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>32880000</v>
+        <v>39380000</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
@@ -2897,7 +3003,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
@@ -2913,7 +3019,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +3030,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -2962,7 +3068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -2993,7 +3099,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -3024,7 +3130,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3055,7 +3161,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -3086,7 +3192,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3120,19 +3226,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.87109375" customWidth="1"/>
-    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
@@ -3167,7 +3273,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3209,7 +3315,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3251,7 +3357,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3296,7 +3402,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3338,7 +3444,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3380,7 +3486,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3422,7 +3528,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3464,7 +3570,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3506,7 +3612,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3548,7 +3654,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3590,7 +3696,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3629,7 +3735,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3668,7 +3774,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3707,7 +3813,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3746,7 +3852,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3785,7 +3891,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3824,7 +3930,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J19" t="s">
         <v>93</v>
       </c>
@@ -3837,17 +3943,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -3867,28 +3973,28 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37" t="s">
+    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
       <c r="N2" s="29" t="s">
         <v>37</v>
       </c>
@@ -3913,13 +4019,13 @@
       <c r="V2" s="26">
         <v>8</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="W2" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="33" t="s">
+      <c r="X2" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Y2" s="36" t="s">
         <v>46</v>
       </c>
       <c r="AA2" t="s">
@@ -3968,11 +4074,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
       <c r="F3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17"/>
@@ -3984,8 +4090,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <f>65965900+O9</f>
-        <v>72215900</v>
+        <f>65965900+O9+O14+O19</f>
+        <v>79465900</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4003,9 +4109,9 @@
       <c r="V3" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="W3" s="43"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="36"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="37"/>
       <c r="AC3" t="s">
         <v>55</v>
       </c>
@@ -4063,7 +4169,7 @@
       </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4102,37 +4208,37 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <f>101851400+O10</f>
-        <v>115428500</v>
+        <f>101851400+O10+O15+O20</f>
+        <v>128661600</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="S4" s="27">
         <v>62</v>
       </c>
       <c r="T4" s="27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U4" s="27">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>3762000</v>
+        <v>4037000</v>
       </c>
       <c r="AA4" t="s">
         <v>63</v>
@@ -4141,19 +4247,19 @@
         <v>64</v>
       </c>
       <c r="AC4">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="AD4" s="28">
-        <v>7750000</v>
+        <v>8750000</v>
       </c>
       <c r="AE4" s="28">
-        <v>7750000</v>
+        <v>8750000</v>
       </c>
       <c r="AF4" t="s">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -4197,7 +4303,7 @@
       </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4215,30 +4321,30 @@
         <v>4</v>
       </c>
       <c r="G5" s="21">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H5" s="21">
         <v>0</v>
       </c>
       <c r="I5" s="21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J5" s="21">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K5" s="21">
         <v>22</v>
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <f>81582500+O11</f>
-        <v>90282500</v>
+        <f>81582500+O11+O16+O21</f>
+        <v>100370500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4276,19 +4382,19 @@
         <v>64</v>
       </c>
       <c r="AC5">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="AD5" s="28">
-        <v>7585000</v>
+        <v>8335000</v>
       </c>
       <c r="AE5" s="28">
-        <v>7585000</v>
+        <v>8335000</v>
       </c>
       <c r="AF5" t="s">
         <v>28</v>
       </c>
       <c r="AG5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -4332,7 +4438,7 @@
       </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4340,11 +4446,11 @@
         <v>1525</v>
       </c>
       <c r="C6" s="14">
-        <v>1511</v>
+        <v>1445</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>3036</v>
+        <v>2970</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -4372,8 +4478,8 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <f>98259500+O12</f>
-        <v>107886300</v>
+        <f>98259500+O12+O17+O22</f>
+        <v>119569800</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4411,19 +4517,19 @@
         <v>64</v>
       </c>
       <c r="AC6">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="AD6" s="28">
-        <v>9170000</v>
+        <v>10170000</v>
       </c>
       <c r="AE6" s="28">
-        <v>9170000</v>
+        <v>10170000</v>
       </c>
       <c r="AF6" t="s">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -4467,7 +4573,7 @@
       </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4485,30 +4591,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="H7" s="21">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="I7" s="21">
-        <v>420</v>
+        <v>376</v>
       </c>
       <c r="J7" s="21">
-        <v>432</v>
+        <v>267</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>1634</v>
+        <v>1348</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>385813200</v>
+        <v>428067800</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4546,19 +4652,19 @@
         <v>64</v>
       </c>
       <c r="AC7">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="AD7" s="28">
-        <v>8375000</v>
+        <v>12125000</v>
       </c>
       <c r="AE7" s="28">
-        <v>8375000</v>
+        <v>12125000</v>
       </c>
       <c r="AF7" t="s">
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4602,7 +4708,7 @@
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4666,18 +4772,18 @@
       </c>
       <c r="AD8" s="28">
         <f>SUM(AD4:AD7)</f>
-        <v>32880000</v>
+        <v>39380000</v>
       </c>
       <c r="AE8" s="28">
         <f>SUM(AE4:AE7)</f>
-        <v>32880000</v>
+        <v>39380000</v>
       </c>
       <c r="AF8" t="s">
         <v>28</v>
       </c>
       <c r="AG8">
         <f>SUM(AG4:AG7)</f>
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
@@ -4725,7 +4831,7 @@
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4818,7 +4924,7 @@
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -4859,10 +4965,10 @@
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="S10" s="27">
-        <v>369</v>
+        <v>519</v>
       </c>
       <c r="T10" s="27">
         <v>150</v>
@@ -4875,14 +4981,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>659</v>
+        <v>829</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="2"/>
-        <v>395400</v>
+        <v>497400</v>
       </c>
       <c r="AA10" t="s">
         <v>115</v>
@@ -4917,7 +5023,7 @@
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -4935,10 +5041,10 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H11" s="21">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="I11" s="21">
         <v>62</v>
@@ -4951,7 +5057,7 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>902</v>
+        <v>732</v>
       </c>
       <c r="O11">
         <v>8700000</v>
@@ -5037,7 +5143,7 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
@@ -5157,7 +5263,7 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5260,7 +5366,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5296,6 +5402,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="O14">
+        <v>4050000</v>
+      </c>
       <c r="Q14" s="20" t="s">
         <v>34</v>
       </c>
@@ -5303,10 +5412,10 @@
         <v>21</v>
       </c>
       <c r="S14" s="27">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="T14" s="27">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="U14" s="27">
         <v>58</v>
@@ -5316,14 +5425,14 @@
       </c>
       <c r="W14" s="27">
         <f t="shared" si="1"/>
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
         <f t="shared" si="2"/>
-        <v>2291000</v>
+        <v>2668000</v>
       </c>
       <c r="AA14" t="s">
         <v>73</v>
@@ -5363,7 +5472,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5384,10 +5493,10 @@
         <v>44</v>
       </c>
       <c r="H15" s="21">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I15" s="21">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J15" s="21">
         <v>57</v>
@@ -5397,19 +5506,22 @@
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>147</v>
+        <v>121</v>
+      </c>
+      <c r="O15">
+        <v>4048900</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="S15" s="27">
         <v>220</v>
       </c>
       <c r="T15" s="27">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="U15" s="27">
         <v>48</v>
@@ -5419,14 +5531,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="1"/>
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="2"/>
-        <v>7917750</v>
+        <v>8366250</v>
       </c>
       <c r="AA15" t="s">
         <v>74</v>
@@ -5466,7 +5578,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5484,13 +5596,13 @@
         <v>35</v>
       </c>
       <c r="G16" s="21">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H16" s="21">
         <v>50</v>
       </c>
       <c r="I16" s="21">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5500,7 +5612,10 @@
       </c>
       <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>314</v>
+      </c>
+      <c r="O16">
+        <v>3938000</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5569,7 +5684,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5604,6 +5719,9 @@
       <c r="L17" s="22">
         <f t="shared" si="3"/>
         <v>301</v>
+      </c>
+      <c r="O17">
+        <v>3263400</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -5648,7 +5766,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5727,7 +5845,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5762,6 +5880,9 @@
       <c r="L19" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+      <c r="O19">
+        <v>3200000</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>17</v>
@@ -5793,7 +5914,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5829,6 +5950,9 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
+      <c r="O20">
+        <v>9184200</v>
+      </c>
       <c r="Q20" s="20" t="s">
         <v>18</v>
       </c>
@@ -5859,7 +5983,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -5895,37 +6019,40 @@
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
+      <c r="O21">
+        <v>6150000</v>
+      </c>
       <c r="Q21" s="20" t="s">
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="S21" s="27">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="T21" s="27">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="U21" s="27">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
         <f t="shared" si="1"/>
-        <v>299</v>
+        <v>385</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="2"/>
-        <v>2870400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+        <v>3696000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -5943,23 +6070,26 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="H22" s="21">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="I22" s="21">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J22" s="21">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K22" s="21">
         <v>12</v>
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>369</v>
+        <v>283</v>
+      </c>
+      <c r="O22">
+        <v>8420100</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -5991,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6038,7 +6168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6083,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6109,19 +6239,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>780</v>
+        <v>836</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1244</v>
+        <v>1459</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="6"/>
-        <v>735</v>
+        <v>781</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="6"/>
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="6"/>
@@ -6129,33 +6259,33 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="6"/>
-        <v>3273</v>
+        <v>3606</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="6"/>
-        <v>36054750</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+        <v>38082850</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1222</v>
+        <v>1133</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>1117</v>
+        <v>858</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
-        <v>771</v>
+        <v>681</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="7"/>
-        <v>1326</v>
+        <v>1145</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="7"/>
@@ -6163,7 +6293,7 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4553</v>
+        <v>3934</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{411ACDE1-1E2E-498D-8727-C9A7FF11DFCA}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9301B34B-6E72-44D5-898F-ED87BB99D573}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1041</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B20">
         <f>index!B21</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <f>index!C21</f>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>1152</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>409</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C12">
         <f>index!H15</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>271</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>858</v>
+        <v>948</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>3817</v>
+        <v>3907</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>79465900</v>
+        <v>79565900</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>128661600</v>
+        <v>130361600</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>100370500</v>
+        <v>102820500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>119569800</v>
+        <v>121169800</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>428067800</v>
+        <v>433917800</v>
       </c>
     </row>
   </sheetData>
@@ -3942,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
@@ -4090,8 +4090,8 @@
         <v>39</v>
       </c>
       <c r="O3" s="27">
-        <f>65965900+O9+O14+O19</f>
-        <v>79465900</v>
+        <f>65965900+O9+O14+O19+O24</f>
+        <v>79565900</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4208,8 +4208,8 @@
         <v>40</v>
       </c>
       <c r="O4" s="27">
-        <f>101851400+O10+O15+O20</f>
-        <v>128661600</v>
+        <f>101851400+O10+O15+O20+O25</f>
+        <v>130361600</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
@@ -4343,8 +4343,8 @@
         <v>41</v>
       </c>
       <c r="O5" s="27">
-        <f>81582500+O11+O16+O21</f>
-        <v>100370500</v>
+        <f>81582500+O11+O16+O21+O26</f>
+        <v>102820500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4478,8 +4478,8 @@
         <v>42</v>
       </c>
       <c r="O6" s="27">
-        <f>98259500+O12+O17+O22</f>
-        <v>119569800</v>
+        <f>98259500+O12+O17+O22+O27</f>
+        <v>121169800</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>428067800</v>
+        <v>433917800</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -5148,14 +5148,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C12" s="14">
         <v>981</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1041</v>
+        <v>1011</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5284,7 +5284,7 @@
         <v>107</v>
       </c>
       <c r="H13" s="21">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I13" s="21">
         <v>60</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5493,7 +5493,7 @@
         <v>44</v>
       </c>
       <c r="H15" s="21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I15" s="21">
         <v>18</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O15">
         <v>4048900</v>
@@ -5988,14 +5988,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="13">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C21" s="14">
         <v>1002</v>
       </c>
       <c r="D21" s="13">
         <f t="shared" si="0"/>
-        <v>1152</v>
+        <v>1092</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
@@ -6073,7 +6073,7 @@
         <v>131</v>
       </c>
       <c r="H22" s="21">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="I22" s="21">
         <v>64</v>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L22" s="22">
         <f t="shared" si="3"/>
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="O22">
         <v>8420100</v>
@@ -6189,6 +6189,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="O24">
+        <v>100000</v>
+      </c>
       <c r="Q24" s="20"/>
       <c r="R24" s="27">
         <v>0</v>
@@ -6233,6 +6236,9 @@
       <c r="L25" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1700000</v>
       </c>
       <c r="Q25" s="23" t="s">
         <v>50</v>
@@ -6277,7 +6283,7 @@
       </c>
       <c r="H26" s="24">
         <f t="shared" si="7"/>
-        <v>858</v>
+        <v>948</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="7"/>
@@ -6293,7 +6299,15 @@
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>3934</v>
+        <v>4024</v>
+      </c>
+      <c r="O26">
+        <v>2450000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="O27">
+        <v>1600000</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9301B34B-6E72-44D5-898F-ED87BB99D573}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52040D7D-2062-5E48-AB67-46D7CEE52431}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
@@ -27,15 +27,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="127">
   <si>
     <t>nama barang</t>
   </si>
@@ -395,9 +403,6 @@
   </si>
   <si>
     <t>RETURE</t>
-  </si>
-  <si>
-    <t>paste disisni</t>
   </si>
   <si>
     <t>On Hand Dse</t>
@@ -426,8 +431,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -649,11 +654,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -715,19 +720,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -751,10 +754,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -783,9 +789,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -823,7 +829,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -929,7 +935,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1071,7 +1077,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1080,15 +1086,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1125,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1153,7 +1159,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1184,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1198,13 +1204,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <f>index!B10</f>
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C9">
         <f>index!C10</f>
@@ -1212,10 +1218,10 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1232,13 +1238,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
         <f>index!B12</f>
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C11">
         <f>index!C12</f>
@@ -1246,10 +1252,10 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1266,7 +1272,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1276,20 +1282,20 @@
       </c>
       <c r="C13">
         <f>index!C14</f>
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
         <f>index!B15</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <f>index!C15</f>
@@ -1297,16 +1303,16 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
         <f>index!B16</f>
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="C15">
         <f>index!C16</f>
@@ -1314,10 +1320,10 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1334,7 +1340,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1344,14 +1350,14 @@
       </c>
       <c r="C17">
         <f>index!C18</f>
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1385,13 +1391,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!B21</f>
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="C20">
         <f>index!C21</f>
@@ -1399,16 +1405,16 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
         <f>index!B22</f>
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="C21">
         <f>index!C22</f>
@@ -1416,7 +1422,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -1427,18 +1433,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1461,7 +1467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1469,9 +1475,9 @@
         <f>index!G5</f>
         <v>37</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
         <f>index!H5</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="D2">
         <f>index!I5</f>
@@ -1486,132 +1492,132 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <f>index!G6</f>
-        <v>0</v>
-      </c>
-      <c r="C3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C3" t="str">
         <f>index!H6</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D3" t="str">
         <f>index!I6</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E3" t="str">
         <f>index!J6</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G22" si="0">SUM(B3:F3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
         <f>index!G8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <f>index!H8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <f>index!I8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <f>index!J8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="str">
         <f>index!G9</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C6" t="str">
         <f>index!H9</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D6" t="str">
         <f>index!I9</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E6" t="str">
         <f>index!J9</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="str">
         <f>index!G10</f>
-        <v>0</v>
-      </c>
-      <c r="C7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C7" t="str">
         <f>index!H10</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D7" t="str">
         <f>index!I10</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E7" t="str">
         <f>index!J10</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
@@ -1627,10 +1633,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>732</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1638,9 +1644,9 @@
         <f>index!G12</f>
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="str">
         <f>index!H12</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="D9">
         <f>index!I12</f>
@@ -1655,7 +1661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1665,47 +1671,47 @@
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <f>index!J13</f>
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>429</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <f>index!G14</f>
-        <v>0</v>
-      </c>
-      <c r="C11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="C11" t="str">
         <f>index!H14</f>
-        <v>0</v>
-      </c>
-      <c r="D11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D11" t="str">
         <f>index!I14</f>
-        <v>0</v>
-      </c>
-      <c r="E11">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E11" t="str">
         <f>index!J14</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1715,11 +1721,11 @@
       </c>
       <c r="C12">
         <f>index!H15</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
@@ -1727,10 +1733,10 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1740,11 +1746,11 @@
       </c>
       <c r="C13">
         <f>index!H16</f>
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1752,10 +1758,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>293</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1805,32 +1811,32 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
         <f>index!G19</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="C16">
         <f>index!H19</f>
-        <v>0</v>
-      </c>
-      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="D16" t="str">
         <f>index!I19</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E16" t="str">
         <f>index!J19</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1838,24 +1844,24 @@
         <f>index!G20</f>
         <v>1</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="str">
         <f>index!H20</f>
-        <v>0</v>
-      </c>
-      <c r="D17">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="D17" t="str">
         <f>index!I20</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
+        <v xml:space="preserve"> -   </v>
+      </c>
+      <c r="E17" t="str">
         <f>index!J20</f>
-        <v>0</v>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1880,17 +1886,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
@@ -1902,10 +1908,10 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1951,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1972,25 +1978,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1133</v>
+        <v>1258</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>948</v>
+        <v>1018</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>681</v>
+        <v>765</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1145</v>
+        <v>1130</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -1998,7 +2004,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>3907</v>
+        <v>4171</v>
       </c>
     </row>
   </sheetData>
@@ -2009,13 +2015,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2023,49 +2029,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>117</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>79565900</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>130361600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6781700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>102820500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>7968000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>121169800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8350000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>433917800</v>
+        <v>28099700</v>
       </c>
     </row>
   </sheetData>
@@ -2076,19 +2082,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
         <v>47</v>
@@ -2103,48 +2109,48 @@
         <v>49</v>
       </c>
       <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>124</v>
       </c>
-      <c r="H1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <f>index!R4</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>index!S4</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>index!T4</f>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>index!U4</f>
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f>SUM(B2:E2)</f>
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>11000</v>
       </c>
       <c r="H2">
         <f>F2*G2</f>
-        <v>4037000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2176,39 +2182,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!R6</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <f>index!S6</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <f>index!T6</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <f>index!U6</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>25000</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2240,39 +2246,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:H6" si="2">SUM(C2:C5)</f>
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <f t="shared" si="2"/>
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <f t="shared" si="2"/>
-        <v>372</v>
+        <v>60</v>
       </c>
       <c r="H6">
         <f t="shared" si="2"/>
-        <v>4162000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="45" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
@@ -2287,30 +2293,30 @@
         <v>49</v>
       </c>
       <c r="F8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" t="s">
         <v>123</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>124</v>
       </c>
-      <c r="H8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
         <f>index!R10</f>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <f>index!S10</f>
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f>index!T10</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>index!U10</f>
@@ -2318,17 +2324,17 @@
       </c>
       <c r="F9">
         <f>SUM(B9:E9)</f>
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
         <f>F9*G9</f>
-        <v>497400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2338,7 +2344,7 @@
       </c>
       <c r="C10">
         <f>index!S11</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f>index!T11</f>
@@ -2349,50 +2355,50 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:F21" si="3">SUM(B10:E10)</f>
-        <v>2</v>
+        <f t="shared" ref="F10:F22" si="3">SUM(B10:E10)</f>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>22500</v>
       </c>
       <c r="H10">
         <f t="shared" ref="H10:H21" si="4">F10*G10</f>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
       <c r="B11">
         <f>index!R12</f>
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <f>index!U12</f>
-        <v>215</v>
+        <v>10</v>
       </c>
       <c r="F11">
         <f t="shared" si="3"/>
-        <v>1187</v>
+        <v>20</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="4"/>
-        <v>15668400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>264000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2424,113 +2430,113 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13">
         <f>index!R14</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f>index!S14</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f>index!T14</f>
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <f>index!U14</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <f t="shared" si="3"/>
-        <v>184</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>14500</v>
       </c>
       <c r="H13">
         <f t="shared" si="4"/>
-        <v>2668000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>87000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14">
         <f>index!R15</f>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f>index!S15</f>
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <f t="shared" si="3"/>
-        <v>485</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="4"/>
-        <v>8366250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>103500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15">
         <f>index!R16</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <f>index!S16</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <f>index!T16</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>index!U16</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>23000</v>
       </c>
       <c r="H15">
         <f t="shared" si="4"/>
-        <v>1955000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
         <f>index!R17</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <f>index!S17</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <f>index!T17</f>
@@ -2542,23 +2548,23 @@
       </c>
       <c r="F16">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>30000</v>
       </c>
       <c r="H16">
         <f t="shared" si="4"/>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
         <f>index!R18</f>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <f>index!S18</f>
@@ -2574,17 +2580,17 @@
       </c>
       <c r="F17">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>6900</v>
       </c>
       <c r="H17">
         <f t="shared" si="4"/>
-        <v>289800</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2602,21 +2608,21 @@
       </c>
       <c r="E18">
         <f>index!U19</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>7000</v>
       </c>
       <c r="H18">
         <f t="shared" si="4"/>
-        <v>63000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2630,7 +2636,7 @@
       </c>
       <c r="D19">
         <f>index!T20</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <f>index!U20</f>
@@ -2638,49 +2644,49 @@
       </c>
       <c r="F19">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>12000</v>
       </c>
       <c r="H19">
         <f t="shared" si="4"/>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <f>index!T21</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <f>index!U21</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <f t="shared" si="3"/>
-        <v>385</v>
+        <v>30</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="4"/>
-        <v>3696000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>288000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2712,33 +2718,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22">
         <f>SUM(B9:B21)</f>
-        <v>772</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <f t="shared" ref="C22:H22" si="5">SUM(C9:C21)</f>
-        <v>1394</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <f t="shared" si="5"/>
-        <v>686</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <f t="shared" si="5"/>
-        <v>382</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <f t="shared" si="5"/>
-        <v>3234</v>
+        <v>62</v>
       </c>
       <c r="H22">
         <f t="shared" si="5"/>
-        <v>33920850</v>
+        <v>742500</v>
       </c>
     </row>
   </sheetData>
@@ -2752,20 +2758,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -2779,7 +2785,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>55</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2984,7 +2990,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
         <v>1749</v>
@@ -3030,19 +3036,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -3099,7 +3105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -3130,7 +3136,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3161,7 +3167,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -3192,7 +3198,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3226,19 +3232,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.87109375" customWidth="1"/>
+    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
@@ -3273,7 +3279,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3303,7 +3309,7 @@
       </c>
       <c r="H2" s="8">
         <f>index!AT3</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I2" s="5">
         <f>index!AU3</f>
@@ -3315,7 +3321,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3345,11 +3351,11 @@
       </c>
       <c r="H3" s="8">
         <f>index!AT4</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I3" s="5">
         <f>index!AU4</f>
-        <v>0</v>
+        <v>46176</v>
       </c>
       <c r="J3" s="4" t="str">
         <f>index!AV4</f>
@@ -3357,7 +3363,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3387,7 +3393,7 @@
       </c>
       <c r="H4" s="8">
         <f>index!AT5</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I4" s="5">
         <f>index!AU5</f>
@@ -3402,7 +3408,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3432,7 +3438,7 @@
       </c>
       <c r="H5" s="8">
         <f>index!AT6</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I5" s="5">
         <f>index!AU6</f>
@@ -3444,7 +3450,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3474,7 +3480,7 @@
       </c>
       <c r="H6" s="9">
         <f>index!AT7</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I6" s="5">
         <f>index!AU7</f>
@@ -3486,7 +3492,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3516,11 +3522,11 @@
       </c>
       <c r="H7" s="9">
         <f>index!AT8</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I7" s="5">
         <f>index!AU8</f>
-        <v>0</v>
+        <v>46176</v>
       </c>
       <c r="J7" s="4" t="str">
         <f>index!AV8</f>
@@ -3528,7 +3534,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3558,7 +3564,7 @@
       </c>
       <c r="H8" s="8">
         <f>index!AT9</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I8" s="5">
         <f>index!AU9</f>
@@ -3570,7 +3576,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3600,7 +3606,7 @@
       </c>
       <c r="H9" s="8">
         <f>index!AT10</f>
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="I9" s="5">
         <f>index!AU10</f>
@@ -3612,7 +3618,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3654,7 +3660,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3696,7 +3702,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3735,7 +3741,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3774,7 +3780,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3813,7 +3819,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3852,7 +3858,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3891,7 +3897,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3930,7 +3936,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>93</v>
       </c>
@@ -3942,18 +3948,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
-  <dimension ref="A1:AW27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AW26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -3973,7 +3979,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
@@ -4074,7 +4080,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A3" s="39"/>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -4089,9 +4095,9 @@
       <c r="N3" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="27">
-        <f>65965900+O9+O14+O19+O24</f>
-        <v>79565900</v>
+      <c r="O3" s="33">
+        <f>O9</f>
+        <v>5000000</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4161,15 +4167,15 @@
         <v>88</v>
       </c>
       <c r="AT3" s="8">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="AU3" s="5"/>
       <c r="AV3" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4207,38 +4213,38 @@
       <c r="N4" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="27">
-        <f>101851400+O10+O15+O20+O25</f>
-        <v>130361600</v>
+      <c r="O4" s="33">
+        <f t="shared" ref="O4:O6" si="0">O10</f>
+        <v>6781700</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="S4" s="27">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="T4" s="27">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="U4" s="27">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="V4" s="27">
         <v>0</v>
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>4037000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="s">
         <v>63</v>
@@ -4295,15 +4301,17 @@
         <v>90</v>
       </c>
       <c r="AT4" s="8">
-        <v>410000</v>
-      </c>
-      <c r="AU4" s="5"/>
+        <v>310000</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>46176</v>
+      </c>
       <c r="AV4" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4314,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="13">
-        <f t="shared" ref="D5:D22" si="0">C5+B5</f>
+        <f t="shared" ref="D5:D22" si="1">C5+B5</f>
         <v>0</v>
       </c>
       <c r="F5" s="20" t="s">
@@ -4323,8 +4331,8 @@
       <c r="G5" s="21">
         <v>37</v>
       </c>
-      <c r="H5" s="21">
-        <v>0</v>
+      <c r="H5" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I5" s="21">
         <v>5</v>
@@ -4342,9 +4350,9 @@
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="27">
-        <f>81582500+O11+O16+O21+O26</f>
-        <v>102820500</v>
+      <c r="O5" s="33">
+        <f t="shared" si="0"/>
+        <v>7968000</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4365,14 +4373,14 @@
         <v>0</v>
       </c>
       <c r="W5" s="27">
-        <f t="shared" ref="W5:W22" si="1">SUM(R5:V5)</f>
+        <f t="shared" ref="W5:W22" si="2">SUM(R5:V5)</f>
         <v>0</v>
       </c>
       <c r="X5" s="4">
         <v>30000</v>
       </c>
       <c r="Y5" s="27">
-        <f t="shared" ref="Y5:Y22" si="2">W5*X5</f>
+        <f t="shared" ref="Y5:Y22" si="3">W5*X5</f>
         <v>0</v>
       </c>
       <c r="AA5" t="s">
@@ -4430,15 +4438,15 @@
         <v>92</v>
       </c>
       <c r="AT5" s="8">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="AU5" s="5"/>
       <c r="AV5" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4449,66 +4457,66 @@
         <v>1445</v>
       </c>
       <c r="D6" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2970</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21">
-        <v>0</v>
-      </c>
-      <c r="J6" s="21">
-        <v>0</v>
+      <c r="G6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K6" s="21">
         <v>0</v>
       </c>
       <c r="L6" s="22">
-        <f t="shared" ref="L6:L25" si="3">SUM(G6:K6)</f>
+        <f t="shared" ref="L6:L25" si="4">SUM(G6:K6)</f>
         <v>0</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="27">
-        <f>98259500+O12+O17+O22+O27</f>
-        <v>121169800</v>
+      <c r="O6" s="33">
+        <f t="shared" si="0"/>
+        <v>8350000</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S6" s="27">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" s="27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U6" s="27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V6" s="27">
         <v>0</v>
       </c>
       <c r="W6" s="27">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>60</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
-        <f t="shared" si="2"/>
-        <v>125000</v>
+        <f t="shared" si="3"/>
+        <v>1500000</v>
       </c>
       <c r="AA6" t="s">
         <v>41</v>
@@ -4565,15 +4573,15 @@
         <v>95</v>
       </c>
       <c r="AT6" s="8">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="AU6" s="5"/>
       <c r="AV6" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4584,37 +4592,37 @@
         <v>0</v>
       </c>
       <c r="D7" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="H7" s="21">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="I7" s="21">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="J7" s="21">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" si="3"/>
-        <v>1348</v>
+        <f t="shared" si="4"/>
+        <v>1288</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(O3:O6)</f>
-        <v>433917800</v>
+        <v>28099700</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4635,14 +4643,14 @@
         <v>0</v>
       </c>
       <c r="W7" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X7" s="4">
         <v>30000</v>
       </c>
       <c r="Y7" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA7" t="s">
@@ -4699,16 +4707,16 @@
       <c r="AS7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AT7" s="9">
-        <v>410000</v>
+      <c r="AT7" s="8">
+        <v>310000</v>
       </c>
       <c r="AU7" s="5"/>
       <c r="AV7" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4717,30 +4725,30 @@
         <v>0</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>7</v>
       </c>
       <c r="G8" s="21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8" s="21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" s="21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" s="21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8" s="21">
         <v>0</v>
       </c>
       <c r="L8" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="27">
@@ -4759,12 +4767,12 @@
         <v>0</v>
       </c>
       <c r="W8" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X8" s="19"/>
       <c r="Y8" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC8" s="28">
@@ -4786,19 +4794,19 @@
         <v>145</v>
       </c>
       <c r="AH8">
-        <f t="shared" ref="AH8:AK8" si="4">SUM(AH4:AH7)</f>
+        <f t="shared" ref="AH8:AK8" si="5">SUM(AH4:AH7)</f>
         <v>4</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>93</v>
       </c>
       <c r="AM8" s="4">
@@ -4822,16 +4830,18 @@
       <c r="AS8" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AT8" s="9">
-        <v>410000</v>
-      </c>
-      <c r="AU8" s="5"/>
+      <c r="AT8" s="8">
+        <v>310000</v>
+      </c>
+      <c r="AU8" s="5">
+        <v>46176</v>
+      </c>
       <c r="AV8" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4840,34 +4850,33 @@
         <v>0</v>
       </c>
       <c r="D9" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
-        <v>0</v>
+      <c r="G9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K9" s="21">
         <v>0</v>
       </c>
       <c r="L9" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="O9">
-        <v>6250000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="32"/>
+      <c r="O9" s="1">
+        <f>100000+4900000</f>
+        <v>5000000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4886,12 +4895,12 @@
         <v>0</v>
       </c>
       <c r="W9" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AM9" s="4">
@@ -4916,62 +4925,63 @@
         <v>101</v>
       </c>
       <c r="AT9" s="8">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="AU9" s="5"/>
       <c r="AV9" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="13">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
       <c r="D10" s="13">
-        <f t="shared" si="0"/>
-        <v>2250</v>
+        <f t="shared" si="1"/>
+        <v>2100</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21">
-        <v>0</v>
+      <c r="G10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K10" s="21">
         <v>0</v>
       </c>
       <c r="L10" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>13577100</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <f>1700000+5081700</f>
+        <v>6781700</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="S10" s="27">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="T10" s="27">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="U10" s="27">
         <v>0</v>
@@ -4981,14 +4991,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
-        <f t="shared" si="2"/>
-        <v>497400</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA10" t="s">
         <v>115</v>
@@ -5015,15 +5025,15 @@
         <v>103</v>
       </c>
       <c r="AT10" s="8">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="AU10" s="5"/>
       <c r="AV10" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5034,14 +5044,14 @@
         <v>1</v>
       </c>
       <c r="D11" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="H11" s="21">
         <v>300</v>
@@ -5056,11 +5066,12 @@
         <v>0</v>
       </c>
       <c r="L11" s="22">
-        <f t="shared" si="3"/>
-        <v>732</v>
-      </c>
-      <c r="O11">
-        <v>8700000</v>
+        <f t="shared" si="4"/>
+        <v>882</v>
+      </c>
+      <c r="O11" s="1">
+        <f>2450000+5518000</f>
+        <v>7968000</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5069,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" s="27">
         <v>0</v>
@@ -5081,15 +5092,15 @@
         <v>0</v>
       </c>
       <c r="W11" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X11" s="4">
         <v>22500</v>
       </c>
       <c r="Y11" s="27">
-        <f t="shared" si="2"/>
-        <v>45000</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA11" t="s">
         <v>66</v>
@@ -5143,19 +5154,19 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="13">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C12" s="14">
         <v>981</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1011</v>
+        <v>1131</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5163,8 +5174,8 @@
       <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="21">
-        <v>0</v>
+      <c r="H12" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="I12" s="21">
         <v>4</v>
@@ -5176,40 +5187,41 @@
         <v>0</v>
       </c>
       <c r="L12" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="O12">
-        <v>9626800</v>
+      <c r="O12" s="1">
+        <f>1600000+6750000</f>
+        <v>8350000</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="S12" s="27">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="T12" s="27">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="U12" s="27">
-        <v>215</v>
+        <v>10</v>
       </c>
       <c r="V12" s="27">
         <v>0</v>
       </c>
       <c r="W12" s="27">
-        <f t="shared" si="1"/>
-        <v>1187</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
-        <f t="shared" si="2"/>
-        <v>15668400</v>
+        <f t="shared" si="3"/>
+        <v>264000</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
@@ -5263,7 +5275,7 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5274,7 +5286,7 @@
         <v>300</v>
       </c>
       <c r="D13" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="F13" s="20" t="s">
@@ -5284,20 +5296,20 @@
         <v>107</v>
       </c>
       <c r="H13" s="21">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I13" s="21">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J13" s="21">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="K13" s="21">
         <v>21</v>
       </c>
       <c r="L13" s="22">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" si="4"/>
+        <v>460</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5318,14 +5330,14 @@
         <v>0</v>
       </c>
       <c r="W13" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
         <v>20000</v>
       </c>
       <c r="Y13" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA13" t="s">
@@ -5366,7 +5378,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5374,65 +5386,62 @@
         <v>0</v>
       </c>
       <c r="C14" s="14">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" si="0"/>
-        <v>457</v>
+        <f t="shared" si="1"/>
+        <v>397</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="21">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21">
-        <v>0</v>
+      <c r="G14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K14" s="21">
         <v>0</v>
       </c>
       <c r="L14" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>4050000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q14" s="20" t="s">
         <v>34</v>
       </c>
       <c r="R14" s="27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S14" s="27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="T14" s="27">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="U14" s="27">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="V14" s="27">
         <v>0</v>
       </c>
       <c r="W14" s="27">
-        <f t="shared" si="1"/>
-        <v>184</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="X14" s="4">
         <v>14500</v>
       </c>
       <c r="Y14" s="27">
-        <f t="shared" si="2"/>
-        <v>2668000</v>
+        <f t="shared" si="3"/>
+        <v>87000</v>
       </c>
       <c r="AA14" t="s">
         <v>73</v>
@@ -5472,19 +5481,19 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="13">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C15" s="14">
         <v>3</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>42</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>34</v>
@@ -5493,10 +5502,10 @@
         <v>44</v>
       </c>
       <c r="H15" s="21">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I15" s="21">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J15" s="21">
         <v>57</v>
@@ -5505,40 +5514,37 @@
         <v>0</v>
       </c>
       <c r="L15" s="22">
-        <f t="shared" si="3"/>
-        <v>131</v>
-      </c>
-      <c r="O15">
-        <v>4048900</v>
+        <f t="shared" si="4"/>
+        <v>185</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="R15" s="27">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="S15" s="27">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="T15" s="27">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="U15" s="27">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="V15" s="27">
         <v>0</v>
       </c>
       <c r="W15" s="27">
-        <f t="shared" si="1"/>
-        <v>485</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
-        <f t="shared" si="2"/>
-        <v>8366250</v>
+        <f t="shared" si="3"/>
+        <v>103500</v>
       </c>
       <c r="AA15" t="s">
         <v>74</v>
@@ -5578,19 +5584,19 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="13">
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="C16" s="14">
         <v>6</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" si="0"/>
-        <v>66</v>
+        <f t="shared" si="1"/>
+        <v>516</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>35</v>
@@ -5599,10 +5605,10 @@
         <v>114</v>
       </c>
       <c r="H16" s="21">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="I16" s="21">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
@@ -5611,63 +5617,60 @@
         <v>21</v>
       </c>
       <c r="L16" s="22">
-        <f t="shared" si="3"/>
-        <v>314</v>
-      </c>
-      <c r="O16">
-        <v>3938000</v>
+        <f t="shared" si="4"/>
+        <v>419</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
       </c>
       <c r="R16" s="27">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S16" s="27">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="T16" s="27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U16" s="27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="27">
         <v>0</v>
       </c>
       <c r="W16" s="27">
-        <f t="shared" si="1"/>
-        <v>85</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X16" s="4">
         <v>23000</v>
       </c>
       <c r="Y16" s="27">
-        <f t="shared" si="2"/>
-        <v>1955000</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC16">
         <f>SUM(AC12:AC15)</f>
         <v>252</v>
       </c>
       <c r="AD16">
-        <f t="shared" ref="AD16:AH16" si="5">SUM(AD12:AD15)</f>
+        <f t="shared" ref="AD16:AH16" si="6">SUM(AD12:AD15)</f>
         <v>2520000</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2520000</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>252</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>252</v>
       </c>
       <c r="AM16" s="4">
@@ -5684,7 +5687,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5695,7 +5698,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>405</v>
       </c>
       <c r="F17" s="20" t="s">
@@ -5717,20 +5720,17 @@
         <v>22</v>
       </c>
       <c r="L17" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>301</v>
-      </c>
-      <c r="O17">
-        <v>3263400</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
       </c>
       <c r="R17" s="27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" s="27">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T17" s="27">
         <v>0</v>
@@ -5742,15 +5742,15 @@
         <v>0</v>
       </c>
       <c r="W17" s="27">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X17" s="4">
         <v>30000</v>
       </c>
       <c r="Y17" s="27">
-        <f t="shared" si="2"/>
-        <v>600000</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AM17" s="4">
         <v>15</v>
@@ -5766,7 +5766,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5774,11 +5774,11 @@
         <v>0</v>
       </c>
       <c r="C18" s="14">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" si="0"/>
-        <v>198</v>
+        <f t="shared" si="1"/>
+        <v>183</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>15</v>
@@ -5799,14 +5799,14 @@
         <v>0</v>
       </c>
       <c r="L18" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>118</v>
       </c>
       <c r="Q18" s="20" t="s">
         <v>16</v>
       </c>
       <c r="R18" s="27">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S18" s="27">
         <v>0</v>
@@ -5821,15 +5821,15 @@
         <v>0</v>
       </c>
       <c r="W18" s="27">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X18" s="4">
         <v>6900</v>
       </c>
       <c r="Y18" s="27">
-        <f t="shared" si="2"/>
-        <v>289800</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AM18" s="4">
         <v>16</v>
@@ -5845,7 +5845,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5856,33 +5856,30 @@
         <v>0</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="21">
-        <v>0</v>
+      <c r="G19" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="H19" s="21">
-        <v>0</v>
-      </c>
-      <c r="I19" s="21">
-        <v>0</v>
-      </c>
-      <c r="J19" s="21">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K19" s="21">
         <v>0</v>
       </c>
       <c r="L19" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>3200000</v>
+        <f t="shared" si="4"/>
+        <v>15</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>17</v>
@@ -5897,24 +5894,24 @@
         <v>0</v>
       </c>
       <c r="U19" s="27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V19" s="27">
         <v>0</v>
       </c>
       <c r="W19" s="27">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X19" s="4">
         <v>7000</v>
       </c>
       <c r="Y19" s="27">
-        <f t="shared" si="2"/>
-        <v>63000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5925,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F20" s="20" t="s">
@@ -5934,24 +5931,21 @@
       <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="21">
-        <v>0</v>
-      </c>
-      <c r="I20" s="21">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21">
-        <v>0</v>
+      <c r="H20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="K20" s="21">
         <v>0</v>
       </c>
       <c r="L20" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
-      </c>
-      <c r="O20">
-        <v>9184200</v>
       </c>
       <c r="Q20" s="20" t="s">
         <v>18</v>
@@ -5963,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U20" s="27">
         <v>0</v>
@@ -5972,30 +5966,30 @@
         <v>0</v>
       </c>
       <c r="W20" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="X20" s="4">
         <v>12000</v>
       </c>
       <c r="Y20" s="27">
-        <f t="shared" si="2"/>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="13">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="C21" s="14">
         <v>1002</v>
       </c>
       <c r="D21" s="13">
-        <f t="shared" si="0"/>
-        <v>1092</v>
+        <f t="shared" si="1"/>
+        <v>1392</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
@@ -6016,64 +6010,61 @@
         <v>0</v>
       </c>
       <c r="L21" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>108</v>
-      </c>
-      <c r="O21">
-        <v>6150000</v>
       </c>
       <c r="Q21" s="20" t="s">
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="S21" s="27">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="T21" s="27">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U21" s="27">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="V21" s="27">
         <v>0</v>
       </c>
       <c r="W21" s="27">
-        <f t="shared" si="1"/>
-        <v>385</v>
+        <f t="shared" si="2"/>
+        <v>30</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
-        <f t="shared" si="2"/>
-        <v>3696000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>288000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="13">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="C22" s="14">
         <v>0</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" si="0"/>
-        <v>72</v>
+        <f t="shared" si="1"/>
+        <v>222</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H22" s="21">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I22" s="21">
         <v>64</v>
@@ -6085,11 +6076,8 @@
         <v>12</v>
       </c>
       <c r="L22" s="22">
-        <f t="shared" si="3"/>
-        <v>343</v>
-      </c>
-      <c r="O22">
-        <v>8420100</v>
+        <f t="shared" si="4"/>
+        <v>313</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6110,18 +6098,18 @@
         <v>0</v>
       </c>
       <c r="W22" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X22" s="4">
         <v>13200</v>
       </c>
       <c r="Y22" s="27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6141,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="L23" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="Q23" s="20"/>
@@ -6168,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6186,11 +6174,8 @@
         <v>0</v>
       </c>
       <c r="L24" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>100000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q24" s="20"/>
       <c r="R24" s="27">
@@ -6216,7 +6201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6234,80 +6219,69 @@
         <v>0</v>
       </c>
       <c r="L25" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>1700000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q25" s="23" t="s">
         <v>50</v>
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>836</v>
+        <v>30</v>
       </c>
       <c r="S25" s="19">
-        <f t="shared" ref="S25:Y25" si="6">SUM(S4:S24)</f>
-        <v>1459</v>
+        <f t="shared" ref="S25:Y25" si="7">SUM(S4:S24)</f>
+        <v>40</v>
       </c>
       <c r="T25" s="19">
-        <f t="shared" si="6"/>
-        <v>781</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="U25" s="19">
-        <f t="shared" si="6"/>
-        <v>530</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="V25" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W25" s="19">
-        <f t="shared" si="6"/>
-        <v>3606</v>
+        <f t="shared" si="7"/>
+        <v>122</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
-        <f t="shared" si="6"/>
-        <v>38082850</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>2242500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
-        <f t="shared" ref="G26:K26" si="7">SUM(G5:G25)</f>
-        <v>1133</v>
+        <f t="shared" ref="G26:K26" si="8">SUM(G5:G25)</f>
+        <v>1258</v>
       </c>
       <c r="H26" s="24">
-        <f t="shared" si="7"/>
-        <v>948</v>
+        <f t="shared" si="8"/>
+        <v>1018</v>
       </c>
       <c r="I26" s="24">
-        <f t="shared" si="7"/>
-        <v>681</v>
+        <f t="shared" si="8"/>
+        <v>765</v>
       </c>
       <c r="J26" s="24">
-        <f t="shared" si="7"/>
-        <v>1145</v>
+        <f t="shared" si="8"/>
+        <v>1130</v>
       </c>
       <c r="K26" s="24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>117</v>
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4024</v>
-      </c>
-      <c r="O26">
-        <v>2450000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="O27">
-        <v>1600000</v>
+        <v>4288</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52040D7D-2062-5E48-AB67-46D7CEE52431}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E41156-C8F0-4A58-B272-6EBD29E3D12D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
@@ -27,23 +27,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="128">
   <si>
     <t>nama barang</t>
   </si>
@@ -424,6 +416,9 @@
   </si>
   <si>
     <t>VOUCHER</t>
+  </si>
+  <si>
+    <t>LUNAS</t>
   </si>
 </sst>
 </file>
@@ -431,8 +426,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
@@ -654,8 +649,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
@@ -721,16 +716,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -754,13 +752,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
-    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
@@ -789,9 +784,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -829,7 +824,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -935,7 +930,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1077,7 +1072,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1086,15 +1081,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1125,7 +1120,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1142,7 +1137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1159,7 +1154,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1176,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1190,7 +1185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1204,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1221,7 +1216,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1238,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1248,14 +1243,14 @@
       </c>
       <c r="C11">
         <f>index!C12</f>
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1272,7 +1267,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1282,14 +1277,14 @@
       </c>
       <c r="C13">
         <f>index!C14</f>
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>397</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1306,7 +1301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1323,7 +1318,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1340,7 +1335,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1350,14 +1345,14 @@
       </c>
       <c r="C17">
         <f>index!C18</f>
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1374,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1391,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1408,7 +1403,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1433,18 +1428,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1467,7 +1462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1475,13 +1470,13 @@
         <f>index!G5</f>
         <v>37</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2">
         <f>index!H5</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>index!I5</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>index!J5</f>
@@ -1489,60 +1484,60 @@
       </c>
       <c r="G2">
         <f>SUM(B2:F2)</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3">
         <f>index!G6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C3" t="str">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <f>index!H6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D3" t="str">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <f>index!I6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E3" t="str">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <f>index!J6</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G22" si="0">SUM(B3:F3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!G7</f>
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="C4">
         <f>index!H7</f>
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D4">
         <f>index!I7</f>
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="E4">
         <f>index!J7</f>
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1567,57 +1562,57 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" t="str">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6">
         <f>index!G9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C6" t="str">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <f>index!H9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D6" t="str">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <f>index!I9</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E6" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <f>index!J9</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" t="str">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7">
         <f>index!G10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C7" t="str">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <f>index!H10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <f>index!I10</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <f>index!J10</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f>index!G11</f>
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C8">
         <f>index!H11</f>
@@ -1633,10 +1628,10 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>882</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1644,9 +1639,9 @@
         <f>index!G12</f>
         <v>5</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9">
         <f>index!H12</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f>index!I12</f>
@@ -1661,17 +1656,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
       <c r="B10">
         <f>index!G13</f>
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C10">
         <f>index!H13</f>
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D10">
         <f>index!I13</f>
@@ -1679,39 +1674,39 @@
       </c>
       <c r="E10">
         <f>index!J13</f>
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>439</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11">
         <f>index!G14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="C11" t="str">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <f>index!H14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D11" t="str">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <f>index!I14</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E11" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <f>index!J14</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1721,22 +1716,22 @@
       </c>
       <c r="C12">
         <f>index!H15</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <f>index!I15</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <f>index!J15</f>
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1750,7 +1745,7 @@
       </c>
       <c r="D13">
         <f>index!I16</f>
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <f>index!J16</f>
@@ -1758,10 +1753,10 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1786,7 +1781,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1811,32 +1806,32 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B16">
         <f>index!G19</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="C16">
         <f>index!H19</f>
-        <v>15</v>
-      </c>
-      <c r="D16" t="str">
+        <v>6</v>
+      </c>
+      <c r="D16">
         <f>index!I19</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E16" t="str">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <f>index!J19</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1844,24 +1839,24 @@
         <f>index!G20</f>
         <v>1</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17">
         <f>index!H20</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="D17" t="str">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <f>index!I20</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="E17" t="str">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <f>index!J20</f>
-        <v xml:space="preserve"> -   </v>
+        <v>0</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1886,21 +1881,21 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>index!G22</f>
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C19">
         <f>index!H22</f>
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <f>index!I22</f>
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <f>index!J22</f>
@@ -1908,10 +1903,10 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1936,7 +1931,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1957,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1978,25 +1973,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23">
         <f>SUM(B2:B22)</f>
-        <v>1258</v>
+        <v>1207</v>
       </c>
       <c r="C23">
         <f t="shared" ref="C23:G23" si="1">SUM(C2:C22)</f>
-        <v>1018</v>
+        <v>956</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>765</v>
+        <v>720</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1130</v>
+        <v>1144</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
@@ -2004,7 +1999,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4171</v>
+        <v>4027</v>
       </c>
     </row>
   </sheetData>
@@ -2015,13 +2010,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2029,49 +2024,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>117</v>
       </c>
       <c r="B2">
         <f>index!O3</f>
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3">
         <f>index!O4</f>
-        <v>6781700</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>12009700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
         <f>index!O5</f>
-        <v>7968000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>13178500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
       <c r="B5">
         <f>index!O6</f>
-        <v>8350000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>16733500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>28099700</v>
+        <v>49421700</v>
       </c>
     </row>
   </sheetData>
@@ -2082,17 +2077,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>121</v>
       </c>
@@ -2118,7 +2113,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2132,7 +2127,7 @@
       </c>
       <c r="D2">
         <f>index!T4</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <f>index!U4</f>
@@ -2140,17 +2135,17 @@
       </c>
       <c r="F2">
         <f>SUM(B2:E2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>11000</v>
       </c>
       <c r="H2">
         <f>F2*G2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2182,13 +2177,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4">
         <f>index!R6</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <f>index!S6</f>
@@ -2196,25 +2191,25 @@
       </c>
       <c r="D4">
         <f>index!T6</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <f>index!U6</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>25000</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2250000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2246,13 +2241,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>125</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:H6" si="2">SUM(C2:C5)</f>
@@ -2260,23 +2255,23 @@
       </c>
       <c r="D6">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H6">
         <f t="shared" si="2"/>
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="45" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2305000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -2302,13 +2297,13 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
         <f>index!R10</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <f>index!S10</f>
@@ -2324,17 +2319,17 @@
       </c>
       <c r="F9">
         <f>SUM(B9:E9)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>600</v>
       </c>
       <c r="H9">
         <f>F9*G9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2355,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:F22" si="3">SUM(B10:E10)</f>
+        <f t="shared" ref="F10:F21" si="3">SUM(B10:E10)</f>
         <v>0</v>
       </c>
       <c r="G10">
@@ -2366,17 +2361,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
       <c r="B11">
         <f>index!R12</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <f>index!S12</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <f>index!T12</f>
@@ -2384,21 +2379,21 @@
       </c>
       <c r="E11">
         <f>index!U12</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G11">
         <v>13200</v>
       </c>
       <c r="H11">
         <f t="shared" si="4"/>
-        <v>264000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>594000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2430,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2462,7 +2457,7 @@
         <v>87000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2476,7 +2471,7 @@
       </c>
       <c r="D14">
         <f>index!T15</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <f>index!U15</f>
@@ -2484,17 +2479,17 @@
       </c>
       <c r="F14">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>17250</v>
       </c>
       <c r="H14">
         <f t="shared" si="4"/>
-        <v>103500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>207000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2526,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2558,7 +2553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2590,7 +2585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2622,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2654,21 +2649,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
         <f>index!R21</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <f>index!S21</f>
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D20">
         <f>index!T21</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E20">
         <f>index!U21</f>
@@ -2676,17 +2671,17 @@
       </c>
       <c r="F20">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>9600</v>
       </c>
       <c r="H20">
         <f t="shared" si="4"/>
-        <v>288000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>739200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2718,33 +2713,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22">
         <f>SUM(B9:B21)</f>
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <f t="shared" ref="C22:H22" si="5">SUM(C9:C21)</f>
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D22">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E22">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F22">
         <f t="shared" si="5"/>
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="H22">
         <f t="shared" si="5"/>
-        <v>742500</v>
+        <v>1639200</v>
       </c>
     </row>
   </sheetData>
@@ -2758,20 +2753,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.78125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -2785,7 +2780,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>55</v>
       </c>
@@ -2814,7 +2809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -2858,7 +2853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -2902,7 +2897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2946,7 +2941,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2990,7 +2985,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C7" s="28">
         <f>SUM(C3:C6)</f>
         <v>1749</v>
@@ -3036,19 +3031,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -3074,7 +3069,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -3105,7 +3100,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -3136,7 +3131,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3167,7 +3162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -3198,7 +3193,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3232,19 +3227,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.87109375" customWidth="1"/>
-    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
@@ -3279,7 +3274,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3359,11 +3354,11 @@
       </c>
       <c r="J3" s="4" t="str">
         <f>index!AV4</f>
-        <v>On Hand Dse</v>
+        <v>LUNAS</v>
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3397,18 +3392,18 @@
       </c>
       <c r="I4" s="5">
         <f>index!AU5</f>
-        <v>0</v>
+        <v>46177</v>
       </c>
       <c r="J4" s="4" t="str">
         <f>index!AV5</f>
-        <v>On Hand Dse</v>
+        <v>LUNAS</v>
       </c>
       <c r="K4" s="5"/>
       <c r="M4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3450,7 +3445,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3492,7 +3487,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3530,11 +3525,11 @@
       </c>
       <c r="J7" s="4" t="str">
         <f>index!AV8</f>
-        <v>On Hand Dse</v>
+        <v>LUNAS</v>
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3568,15 +3563,15 @@
       </c>
       <c r="I8" s="5">
         <f>index!AU9</f>
-        <v>0</v>
+        <v>46177</v>
       </c>
       <c r="J8" s="4" t="str">
         <f>index!AV9</f>
-        <v>On Hand Dse</v>
+        <v>LUNAS</v>
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3618,7 +3613,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3660,7 +3655,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3702,7 +3697,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3741,7 +3736,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3780,7 +3775,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3819,7 +3814,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3858,7 +3853,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3936,7 +3931,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J19" t="s">
         <v>93</v>
       </c>
@@ -3949,17 +3944,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -3979,28 +3974,28 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="38" t="s">
+    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="43"/>
       <c r="N2" s="29" t="s">
         <v>37</v>
       </c>
@@ -4025,13 +4020,13 @@
       <c r="V2" s="26">
         <v>8</v>
       </c>
-      <c r="W2" s="43" t="s">
+      <c r="W2" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="34" t="s">
+      <c r="X2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="36" t="s">
+      <c r="Y2" s="37" t="s">
         <v>46</v>
       </c>
       <c r="AA2" t="s">
@@ -4080,11 +4075,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
       <c r="F3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17"/>
@@ -4097,7 +4092,7 @@
       </c>
       <c r="O3" s="33">
         <f>O9</f>
-        <v>5000000</v>
+        <v>7500000</v>
       </c>
       <c r="Q3" s="25"/>
       <c r="R3" s="26" t="s">
@@ -4115,9 +4110,9 @@
       <c r="V3" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="W3" s="44"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="37"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="38"/>
       <c r="AC3" t="s">
         <v>55</v>
       </c>
@@ -4175,7 +4170,7 @@
       </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4215,7 +4210,7 @@
       </c>
       <c r="O4" s="33">
         <f t="shared" ref="O4:O6" si="0">O10</f>
-        <v>6781700</v>
+        <v>12009700</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>4</v>
@@ -4227,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U4" s="27">
         <v>0</v>
@@ -4237,14 +4232,14 @@
       </c>
       <c r="W4" s="27">
         <f>SUM(R4:V4)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X4" s="4">
         <v>11000</v>
       </c>
       <c r="Y4" s="27">
         <f>W4*X4</f>
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="AA4" t="s">
         <v>63</v>
@@ -4307,11 +4302,11 @@
         <v>46176</v>
       </c>
       <c r="AV4" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4331,11 +4326,11 @@
       <c r="G5" s="21">
         <v>37</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>28</v>
+      <c r="H5" s="21">
+        <v>0</v>
       </c>
       <c r="I5" s="21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="21">
         <v>19</v>
@@ -4345,14 +4340,14 @@
       </c>
       <c r="L5" s="22">
         <f>SUM(G5:K5)</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="N5" s="31" t="s">
         <v>41</v>
       </c>
       <c r="O5" s="33">
         <f t="shared" si="0"/>
-        <v>7968000</v>
+        <v>13178500</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>29</v>
@@ -4440,13 +4435,15 @@
       <c r="AT5" s="8">
         <v>310000</v>
       </c>
-      <c r="AU5" s="5"/>
+      <c r="AU5" s="5">
+        <v>46177</v>
+      </c>
       <c r="AV5" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4463,17 +4460,17 @@
       <c r="F6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>28</v>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21">
+        <v>0</v>
       </c>
       <c r="K6" s="21">
         <v>0</v>
@@ -4487,36 +4484,36 @@
       </c>
       <c r="O6" s="33">
         <f t="shared" si="0"/>
-        <v>8350000</v>
+        <v>16733500</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="27">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S6" s="27">
         <v>10</v>
       </c>
       <c r="T6" s="27">
+        <v>30</v>
+      </c>
+      <c r="U6" s="27">
         <v>20</v>
-      </c>
-      <c r="U6" s="27">
-        <v>10</v>
       </c>
       <c r="V6" s="27">
         <v>0</v>
       </c>
       <c r="W6" s="27">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="X6" s="4">
         <v>25000</v>
       </c>
       <c r="Y6" s="27">
         <f t="shared" si="3"/>
-        <v>1500000</v>
+        <v>2250000</v>
       </c>
       <c r="AA6" t="s">
         <v>41</v>
@@ -4581,7 +4578,7 @@
       </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4599,30 +4596,30 @@
         <v>30</v>
       </c>
       <c r="G7" s="21">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="H7" s="21">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I7" s="21">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="J7" s="21">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="K7" s="21">
         <v>10</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="4"/>
-        <v>1288</v>
+        <v>1237</v>
       </c>
       <c r="N7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="O7" s="27">
+      <c r="O7" s="8">
         <f>SUM(O3:O6)</f>
-        <v>28099700</v>
+        <v>49421700</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>7</v>
@@ -4716,7 +4713,7 @@
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4837,11 +4834,11 @@
         <v>46176</v>
       </c>
       <c r="AV8" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4854,17 +4851,17 @@
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>28</v>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21">
+        <v>0</v>
       </c>
       <c r="K9" s="21">
         <v>0</v>
@@ -4875,8 +4872,8 @@
       </c>
       <c r="N9" s="32"/>
       <c r="O9" s="1">
-        <f>100000+4900000</f>
-        <v>5000000</v>
+        <f>100000+4900000+2500000</f>
+        <v>7500000</v>
       </c>
       <c r="Q9" s="20"/>
       <c r="R9" s="27">
@@ -4927,13 +4924,15 @@
       <c r="AT9" s="8">
         <v>310000</v>
       </c>
-      <c r="AU9" s="5"/>
+      <c r="AU9" s="5">
+        <v>46177</v>
+      </c>
       <c r="AV9" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -4948,17 +4947,17 @@
         <v>2100</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>28</v>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0</v>
       </c>
       <c r="K10" s="21">
         <v>0</v>
@@ -4968,14 +4967,14 @@
         <v>0</v>
       </c>
       <c r="O10" s="1">
-        <f>1700000+5081700</f>
-        <v>6781700</v>
+        <f>1700000+5081700+5228000</f>
+        <v>12009700</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="R10" s="27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S10" s="27">
         <v>0</v>
@@ -4991,14 +4990,14 @@
       </c>
       <c r="W10" s="27">
         <f>SUM(R10:V10)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X10" s="4">
         <v>600</v>
       </c>
       <c r="Y10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AA10" t="s">
         <v>115</v>
@@ -5033,7 +5032,7 @@
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5051,7 +5050,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="21">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H11" s="21">
         <v>300</v>
@@ -5067,11 +5066,11 @@
       </c>
       <c r="L11" s="22">
         <f t="shared" si="4"/>
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="O11" s="1">
-        <f>2450000+5518000</f>
-        <v>7968000</v>
+        <f>2450000+5518000+5210500</f>
+        <v>13178500</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>31</v>
@@ -5154,7 +5153,7 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
@@ -5162,11 +5161,11 @@
         <v>150</v>
       </c>
       <c r="C12" s="14">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="D12" s="13">
         <f>C12+B12</f>
-        <v>1131</v>
+        <v>1111</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>31</v>
@@ -5174,8 +5173,8 @@
       <c r="G12" s="21">
         <v>5</v>
       </c>
-      <c r="H12" s="21" t="s">
-        <v>28</v>
+      <c r="H12" s="21">
+        <v>0</v>
       </c>
       <c r="I12" s="21">
         <v>4</v>
@@ -5191,37 +5190,37 @@
         <v>13</v>
       </c>
       <c r="O12" s="1">
-        <f>1600000+6750000</f>
-        <v>8350000</v>
+        <f>1600000+6750000+8383500</f>
+        <v>16733500</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>32</v>
       </c>
       <c r="R12" s="27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S12" s="27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" s="27">
         <v>0</v>
       </c>
       <c r="U12" s="27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V12" s="27">
         <v>0</v>
       </c>
       <c r="W12" s="27">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="X12" s="4">
         <v>13200</v>
       </c>
       <c r="Y12" s="27">
         <f t="shared" si="3"/>
-        <v>264000</v>
+        <v>594000</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
@@ -5275,7 +5274,7 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5293,23 +5292,23 @@
         <v>32</v>
       </c>
       <c r="G13" s="21">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H13" s="21">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I13" s="21">
         <v>90</v>
       </c>
       <c r="J13" s="21">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K13" s="21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L13" s="22">
         <f t="shared" si="4"/>
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="Q13" s="20" t="s">
         <v>33</v>
@@ -5378,7 +5377,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5386,26 +5385,26 @@
         <v>0</v>
       </c>
       <c r="C14" s="14">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="1"/>
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>28</v>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>0</v>
       </c>
       <c r="K14" s="21">
         <v>0</v>
@@ -5481,7 +5480,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5502,20 +5501,20 @@
         <v>44</v>
       </c>
       <c r="H15" s="21">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I15" s="21">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J15" s="21">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="K15" s="21">
         <v>0</v>
       </c>
       <c r="L15" s="22">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>35</v>
@@ -5527,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U15" s="27">
         <v>0</v>
@@ -5537,14 +5536,14 @@
       </c>
       <c r="W15" s="27">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X15" s="4">
         <v>17250</v>
       </c>
       <c r="Y15" s="27">
         <f t="shared" si="3"/>
-        <v>103500</v>
+        <v>207000</v>
       </c>
       <c r="AA15" t="s">
         <v>74</v>
@@ -5584,7 +5583,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5608,17 +5607,17 @@
         <v>110</v>
       </c>
       <c r="I16" s="21">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J16" s="21">
         <v>116</v>
       </c>
       <c r="K16" s="21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L16" s="22">
         <f t="shared" si="4"/>
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="Q16" s="20" t="s">
         <v>36</v>
@@ -5687,7 +5686,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5717,11 +5716,11 @@
         <v>93</v>
       </c>
       <c r="K17" s="21">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L17" s="22">
         <f t="shared" si="4"/>
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Q17" s="20" t="s">
         <v>15</v>
@@ -5766,7 +5765,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5774,11 +5773,11 @@
         <v>0</v>
       </c>
       <c r="C18" s="14">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D18" s="13">
         <f t="shared" si="1"/>
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>15</v>
@@ -5845,7 +5844,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5862,24 +5861,24 @@
       <c r="F19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="21" t="s">
-        <v>28</v>
+      <c r="G19" s="21">
+        <v>0</v>
       </c>
       <c r="H19" s="21">
-        <v>15</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="I19" s="21">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21">
+        <v>0</v>
       </c>
       <c r="K19" s="21">
         <v>0</v>
       </c>
       <c r="L19" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>17</v>
@@ -5911,7 +5910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5931,14 +5930,14 @@
       <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>28</v>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <v>0</v>
       </c>
       <c r="K20" s="21">
         <v>0</v>
@@ -5977,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -6017,13 +6016,13 @@
         <v>19</v>
       </c>
       <c r="R21" s="27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S21" s="27">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="T21" s="27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U21" s="27">
         <v>0</v>
@@ -6033,17 +6032,17 @@
       </c>
       <c r="W21" s="27">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="X21" s="4">
         <v>9600</v>
       </c>
       <c r="Y21" s="27">
         <f t="shared" si="3"/>
-        <v>288000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+        <v>739200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6061,13 +6060,13 @@
         <v>19</v>
       </c>
       <c r="G22" s="21">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H22" s="21">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="I22" s="21">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="J22" s="21">
         <v>61</v>
@@ -6077,7 +6076,7 @@
       </c>
       <c r="L22" s="22">
         <f t="shared" si="4"/>
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>20</v>
@@ -6109,7 +6108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6156,7 +6155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6201,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6227,19 +6226,19 @@
       </c>
       <c r="R25" s="19">
         <f>SUM(R4:R24)</f>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="S25" s="19">
         <f t="shared" ref="S25:Y25" si="7">SUM(S4:S24)</f>
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="T25" s="19">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="V25" s="19">
         <f t="shared" si="7"/>
@@ -6247,41 +6246,41 @@
       </c>
       <c r="W25" s="19">
         <f t="shared" si="7"/>
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
         <f t="shared" si="7"/>
-        <v>2242500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+        <v>3944200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
         <f t="shared" ref="G26:K26" si="8">SUM(G5:G25)</f>
-        <v>1258</v>
+        <v>1207</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="8"/>
-        <v>1018</v>
+        <v>956</v>
       </c>
       <c r="I26" s="24">
         <f t="shared" si="8"/>
-        <v>765</v>
+        <v>720</v>
       </c>
       <c r="J26" s="24">
         <f t="shared" si="8"/>
-        <v>1130</v>
+        <v>1144</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="8"/>
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L26" s="24">
         <f>SUM(L5:L25)</f>
-        <v>4288</v>
+        <v>4132</v>
       </c>
     </row>
   </sheetData>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5918695882615f9/Project/Mc-Sagaranten/develope-mobile-sagaranten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{9F82AD4D-DC67-1C4D-A5DD-D2653976B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46E41156-C8F0-4A58-B272-6EBD29E3D12D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A68C8C10-5CC6-0546-870F-240369AE7AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
     <sheet name="stok-barang-dse" sheetId="2" r:id="rId2"/>
     <sheet name="penjualan-salmo" sheetId="3" r:id="rId3"/>
     <sheet name="penjualan-reguler-new" sheetId="4" r:id="rId4"/>
-    <sheet name="penjualan-paket-tm" sheetId="5" r:id="rId5"/>
+    <sheet name="penjualan-paket-jupiter" sheetId="5" r:id="rId5"/>
     <sheet name="penjualan-direct-selling" sheetId="6" r:id="rId6"/>
     <sheet name="penjualan-hifi" sheetId="7" r:id="rId7"/>
     <sheet name="index" sheetId="8" r:id="rId8"/>
@@ -27,15 +27,49 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>LENOVO</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{96EF6D8D-13DC-40DB-9CFE-AD2182A8E497}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">yg diinput manual warna kuning,
+nama cso di copy dari data jgn di ketik manual
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="148">
   <si>
     <t>nama barang</t>
   </si>
@@ -419,21 +453,82 @@
   </si>
   <si>
     <t>LUNAS</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Tanggal Pengambilan</t>
+  </si>
+  <si>
+    <t>PAKET</t>
+  </si>
+  <si>
+    <t>Micro Cluster</t>
+  </si>
+  <si>
+    <t>Id  Outlet</t>
+  </si>
+  <si>
+    <t>Nama Outlet</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Tagihan</t>
+  </si>
+  <si>
+    <t>Jumlah Pembayaran</t>
+  </si>
+  <si>
+    <t>Selisih</t>
+  </si>
+  <si>
+    <t>Keterangan Setoran</t>
+  </si>
+  <si>
+    <t>PAKET1</t>
+  </si>
+  <si>
+    <t>PAKET4</t>
+  </si>
+  <si>
+    <t>Cuf cell</t>
+  </si>
+  <si>
+    <t>Amel cell</t>
+  </si>
+  <si>
+    <t>GIAN ABDULLAH CELL</t>
+  </si>
+  <si>
+    <t>ALKHA CELL</t>
+  </si>
+  <si>
+    <t>Nazila cell</t>
+  </si>
+  <si>
+    <t>Yasmin Cell</t>
+  </si>
+  <si>
+    <t>Bahagia cell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,8 +575,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,6 +631,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,11 +771,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -716,19 +838,54 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -754,12 +911,22 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{27F0E25F-2FC2-4FA2-85C5-647DEB95F14E}"/>
+    <cellStyle name="Koma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8F2B6BF2-7FD2-4FA0-9F55-2107D04465A9}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -784,9 +951,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -824,7 +991,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -930,7 +1097,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1072,7 +1239,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1081,15 +1248,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EA215D-50DE-4902-AC8C-D667D0BE309C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1103,7 +1270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1287,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1137,7 +1304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1154,7 +1321,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1171,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!B8</f>
         <v>0</v>
@@ -1185,7 +1352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>index!B9</f>
         <v>0</v>
@@ -1199,7 +1366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1216,7 +1383,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1233,7 +1400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1250,7 +1417,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1267,7 +1434,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1284,7 +1451,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1301,7 +1468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1318,7 +1485,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1335,7 +1502,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1352,7 +1519,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1369,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1403,7 +1570,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1428,18 +1595,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662D1FDC-0336-462A-A043-91B508E2B511}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.16796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1462,7 +1629,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1487,7 +1654,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1512,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1537,7 +1704,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1562,7 +1729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <f>index!G9</f>
         <v>0</v>
@@ -1584,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>index!G10</f>
         <v>0</v>
@@ -1606,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1631,7 +1798,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1656,7 +1823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1681,7 +1848,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1706,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1731,7 +1898,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1756,7 +1923,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1781,7 +1948,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1806,7 +1973,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1831,7 +1998,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1856,7 +2023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1881,7 +2048,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1906,7 +2073,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1931,7 +2098,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>28</v>
       </c>
@@ -1952,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -1973,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2010,13 +2177,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3633B40A-92CD-4728-BD2C-3FD996AF2E99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -2024,7 +2191,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -2033,7 +2200,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2042,7 +2209,7 @@
         <v>12009700</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -2051,7 +2218,7 @@
         <v>13178500</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2060,7 +2227,7 @@
         <v>16733500</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2077,17 +2244,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF492372-7161-41F4-99F8-CC7A23014CAA}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>121</v>
       </c>
@@ -2113,7 +2280,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2145,7 +2312,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2177,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -2209,7 +2376,7 @@
         <v>2250000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2241,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -2270,8 +2437,8 @@
         <v>2305000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" s="47" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -2297,7 +2464,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2329,7 +2496,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2361,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2393,7 +2560,7 @@
         <v>594000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2425,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2457,7 +2624,7 @@
         <v>87000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2489,7 +2656,7 @@
         <v>207000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2521,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2553,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2585,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2617,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2649,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2681,7 +2848,7 @@
         <v>739200</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2713,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2751,299 +2918,1293 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92B1183-B6CD-4DBC-9962-CF06051A507E}">
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.80078125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.73828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" s="46" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H1" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="39">
+        <v>1</v>
+      </c>
+      <c r="B2" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="31">
+        <v>17588141</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="44">
+        <v>115800</v>
+      </c>
+      <c r="J2" s="44">
+        <v>115800</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="39">
+        <v>2</v>
+      </c>
+      <c r="B3" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="31">
+        <v>17459415</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="44">
+        <v>118200</v>
+      </c>
+      <c r="J3" s="44">
+        <v>118200</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="39">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="31">
+        <v>17197757</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="44">
+        <v>118200</v>
+      </c>
+      <c r="J4" s="44">
+        <v>118200</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="39">
+        <v>4</v>
+      </c>
+      <c r="B5" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="31">
+        <v>17438405</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="44">
+        <v>115800</v>
+      </c>
+      <c r="J5" s="44">
+        <v>115800</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="39">
+        <v>5</v>
+      </c>
+      <c r="B6" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="31">
+        <v>17187147</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="44">
+        <v>118200</v>
+      </c>
+      <c r="J6" s="44">
+        <v>118200</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="39">
+        <v>6</v>
+      </c>
+      <c r="B7" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="31">
+        <v>17798355</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="44">
+        <v>118200</v>
+      </c>
+      <c r="J7" s="44">
+        <v>118200</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="40">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="39">
+        <v>7</v>
+      </c>
+      <c r="B8" s="40">
+        <v>46176</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="31">
+        <v>572672</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1</v>
+      </c>
+      <c r="I8" s="44">
+        <v>115800</v>
+      </c>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44">
+        <v>115800</v>
+      </c>
+      <c r="L8" s="44"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="39">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G9" s="43"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="44"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="39">
+        <v>9</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G10" s="43"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="44"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="39">
+        <v>10</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G11" s="43"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="44"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="39">
+        <v>11</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G12" s="43"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="44"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="39">
+        <v>12</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="43"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="44"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="39">
+        <v>13</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="43"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L14" s="44"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="39">
+        <v>14</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="43"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L15" s="44"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="39">
+        <v>15</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="43"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L16" s="44"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="39">
+        <v>16</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="43"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L17" s="44"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="39">
+        <v>17</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="43"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L18" s="44"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="39">
+        <v>18</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G19" s="43"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L19" s="44"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="39">
+        <v>19</v>
+      </c>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G20" s="43"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L20" s="44"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="39">
+        <v>20</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L21" s="44"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="39">
+        <v>21</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G22" s="43"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L22" s="44"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="39">
+        <v>22</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G23" s="43"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L23" s="44"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="39">
+        <v>23</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G24" s="43"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L24" s="44"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="39">
+        <v>24</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G25" s="43"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L25" s="44"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="39">
+        <v>25</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="31"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L26" s="44"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="39">
+        <v>26</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G27" s="31"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L27" s="44"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="39">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3">
-        <f>index!AC4</f>
-        <v>385</v>
-      </c>
-      <c r="D3" s="28">
-        <f>index!AD4</f>
-        <v>8750000</v>
-      </c>
-      <c r="E3" s="28">
-        <f>index!AE4</f>
-        <v>8750000</v>
-      </c>
-      <c r="F3" s="28" t="str">
-        <f>index!AF4</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="G3">
-        <f>index!AG4</f>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G28" s="31"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L28" s="44"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="39">
+        <v>28</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G29" s="31"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L29" s="44"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="39">
+        <v>29</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" s="31"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L30" s="44"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="39">
+        <v>30</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L31" s="44"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="39">
+        <v>31</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" s="31"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L32" s="44"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="39">
+        <v>32</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" s="31"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L33" s="44"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="39">
+        <v>33</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L34" s="44"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="39">
+        <v>34</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" s="31"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L35" s="44"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="39">
         <v>35</v>
       </c>
-      <c r="H3">
-        <f>index!AH4</f>
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <f>index!AI4</f>
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <f>index!AJ4</f>
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <f>SUM(G3:J3)</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4">
-        <f>index!AC5</f>
-        <v>372</v>
-      </c>
-      <c r="D4" s="28">
-        <f>index!AD5</f>
-        <v>8335000</v>
-      </c>
-      <c r="E4" s="28">
-        <f>index!AE5</f>
-        <v>8335000</v>
-      </c>
-      <c r="F4" s="28" t="str">
-        <f>index!AF5</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="G4">
-        <f>index!AG5</f>
-        <v>30</v>
-      </c>
-      <c r="H4">
-        <f>index!AH5</f>
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <f>index!AI5</f>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f>index!AJ5</f>
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <f t="shared" ref="K4:K6" si="0">SUM(G4:J4)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" s="31"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L36" s="44"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="39">
+        <v>36</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" s="31"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L37" s="44"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="39">
+        <v>37</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L38" s="44"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="44"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="39">
+        <v>39</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L40" s="44"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="39">
+        <v>40</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L41" s="44"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="39">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5">
-        <f>index!AC6</f>
-        <v>457</v>
-      </c>
-      <c r="D5" s="28">
-        <f>index!AD6</f>
-        <v>10170000</v>
-      </c>
-      <c r="E5" s="28">
-        <f>index!AE6</f>
-        <v>10170000</v>
-      </c>
-      <c r="F5" s="28" t="str">
-        <f>index!AF6</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="G5">
-        <f>index!AG6</f>
-        <v>39</v>
-      </c>
-      <c r="H5">
-        <f>index!AH6</f>
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <f>index!AI6</f>
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <f>index!AJ6</f>
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" s="31"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L42" s="44"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="39">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6">
-        <f>index!AC7</f>
-        <v>535</v>
-      </c>
-      <c r="D6" s="28">
-        <f>index!AD7</f>
-        <v>12125000</v>
-      </c>
-      <c r="E6" s="28">
-        <f>index!AE7</f>
-        <v>12125000</v>
-      </c>
-      <c r="F6" s="28" t="str">
-        <f>index!AF7</f>
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="G6">
-        <f>index!AG7</f>
-        <v>41</v>
-      </c>
-      <c r="H6">
-        <f>index!AH7</f>
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <f>index!AI7</f>
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <f>index!AJ7</f>
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" s="31"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L43" s="44"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="39">
+        <v>43</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" s="31"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L44" s="44"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="39">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C7" s="28">
-        <f>SUM(C3:C6)</f>
-        <v>1749</v>
-      </c>
-      <c r="D7" s="28">
-        <f>SUM(D3:D6)</f>
-        <v>39380000</v>
-      </c>
-      <c r="E7" s="28">
-        <f t="shared" ref="E7:F7" si="1">SUM(E3:E6)</f>
-        <v>39380000</v>
-      </c>
-      <c r="F7" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" ref="G7" si="2">SUM(G3:G6)</f>
-        <v>145</v>
-      </c>
-      <c r="H7" s="1">
-        <f t="shared" ref="H7" si="3">SUM(H3:H6)</f>
-        <v>4</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" ref="I7" si="4">SUM(I3:I6)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <f t="shared" ref="J7" si="5">SUM(J3:J6)</f>
-        <v>3</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" ref="K7" si="6">SUM(K3:K6)</f>
-        <v>152</v>
-      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" s="43"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L45" s="44"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="39">
+        <v>45</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" s="43"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L46" s="44"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="39">
+        <v>46</v>
+      </c>
+      <c r="B47" s="40"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" s="43"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L47" s="44"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="39">
+        <v>47</v>
+      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" s="43"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L48" s="44"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="39">
+        <v>48</v>
+      </c>
+      <c r="B49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" s="43"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L49" s="44"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="39">
+        <v>49</v>
+      </c>
+      <c r="B50" s="40"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" s="43"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L50" s="44"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="39">
+        <v>50</v>
+      </c>
+      <c r="B51" s="40"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" s="43"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L51" s="44"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E51">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1600DCE8-6448-4A3A-8492-4A393F719B5E}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.09375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -3069,7 +4230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -3100,7 +4261,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -3131,7 +4292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3162,7 +4323,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -3193,7 +4354,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>SUM(C2:C5)</f>
         <v>252</v>
@@ -3227,19 +4388,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4FCA9-A1AA-40B8-899C-39858A4BC2FF}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.87109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.87109375" customWidth="1"/>
+    <col min="9" max="9" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.98828125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
@@ -3274,7 +4435,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3316,7 +4477,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3358,7 +4519,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3403,7 +4564,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3445,7 +4606,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3487,7 +4648,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3529,7 +4690,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3571,7 +4732,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3613,7 +4774,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3655,7 +4816,7 @@
       </c>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3697,7 +4858,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3736,7 +4897,7 @@
       </c>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3775,7 +4936,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3814,7 +4975,7 @@
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3853,7 +5014,7 @@
       </c>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3892,7 +5053,7 @@
       </c>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3931,7 +5092,7 @@
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>93</v>
       </c>
@@ -3944,17 +5105,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
   <dimension ref="A1:AW26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -3974,28 +5135,28 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="43"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="56"/>
       <c r="N2" s="29" t="s">
         <v>37</v>
       </c>
@@ -4020,13 +5181,13 @@
       <c r="V2" s="26">
         <v>8</v>
       </c>
-      <c r="W2" s="44" t="s">
+      <c r="W2" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="X2" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="Y2" s="50" t="s">
         <v>46</v>
       </c>
       <c r="AA2" t="s">
@@ -4075,11 +5236,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="F3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17"/>
@@ -4110,9 +5271,9 @@
       <c r="V3" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="W3" s="45"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="38"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="51"/>
       <c r="AC3" t="s">
         <v>55</v>
       </c>
@@ -4170,7 +5331,7 @@
       </c>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -4306,7 +5467,7 @@
       </c>
       <c r="AW4" s="5"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -4443,7 +5604,7 @@
       </c>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -4578,7 +5739,7 @@
       </c>
       <c r="AW6" s="5"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -4713,7 +5874,7 @@
       </c>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -4838,7 +5999,7 @@
       </c>
       <c r="AW8" s="5"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -4932,7 +6093,7 @@
       </c>
       <c r="AW9" s="5"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -5032,7 +6193,7 @@
       </c>
       <c r="AW10" s="5"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -5153,7 +6314,7 @@
       </c>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
@@ -5274,7 +6435,7 @@
       </c>
       <c r="AW12" s="5"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -5377,7 +6538,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -5480,7 +6641,7 @@
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -5583,7 +6744,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -5686,7 +6847,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -5765,7 +6926,7 @@
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -5844,7 +7005,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -5910,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -5976,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -6042,7 +7203,7 @@
         <v>739200</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -6108,7 +7269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -6155,7 +7316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -6200,7 +7361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -6254,7 +7415,7 @@
         <v>3944200</v>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>

--- a/index-data.xlsx
+++ b/index-data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{A68C8C10-5CC6-0546-870F-240369AE7AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="7" xr2:uid="{FCA0993B-22C0-40F9-A77C-47A9D00BA9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="stok-gudang" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="161">
   <si>
     <t>nama barang</t>
   </si>
@@ -513,6 +513,45 @@
   </si>
   <si>
     <t>Bahagia cell</t>
+  </si>
+  <si>
+    <t>paket jupiter</t>
+  </si>
+  <si>
+    <t>SP 6GB</t>
+  </si>
+  <si>
+    <t>V 2.5 GB</t>
+  </si>
+  <si>
+    <t>V 3 GB</t>
+  </si>
+  <si>
+    <t>V 3.5 GB</t>
+  </si>
+  <si>
+    <t>V 1.5 GB</t>
+  </si>
+  <si>
+    <t>VCR 5GB 3</t>
+  </si>
+  <si>
+    <t>Tanggal Pembayaran</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Metode  Pembayaran</t>
+  </si>
+  <si>
+    <t>SALDO</t>
+  </si>
+  <si>
+    <t>GAP</t>
+  </si>
+  <si>
+    <t>CASH</t>
   </si>
 </sst>
 </file>
@@ -775,7 +814,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -873,9 +912,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -908,6 +945,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2437,7 +2477,7 @@
         <v>2305000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="47" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>126</v>
@@ -2977,36 +3017,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="40">
+        <f>index!AZ3</f>
         <v>46176</v>
       </c>
-      <c r="C2" s="41" t="s">
-        <v>139</v>
+      <c r="C2" s="41" t="str">
+        <f>index!BA3</f>
+        <v>PAKET1</v>
       </c>
       <c r="D2" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E2" s="31">
+        <f>index!BC3</f>
         <v>17588141</v>
       </c>
-      <c r="F2" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>63</v>
+      <c r="F2" s="31" t="str">
+        <f>index!BD3</f>
+        <v>Cuf cell</v>
+      </c>
+      <c r="G2" s="43" t="str">
+        <f>index!BE3</f>
+        <v>Muhamad Parhan</v>
       </c>
       <c r="H2" s="6">
+        <f>index!BF3</f>
         <v>1</v>
       </c>
       <c r="I2" s="44">
+        <f>index!BM3</f>
         <v>115800</v>
       </c>
       <c r="J2" s="44">
+        <f>index!BP3</f>
         <v>115800</v>
       </c>
-      <c r="K2" s="44" t="s">
-        <v>28</v>
+      <c r="K2" s="44" t="str">
+        <f>index!BR3</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L2" s="40">
+        <f>index!BS3</f>
         <v>46177</v>
       </c>
     </row>
@@ -3015,36 +3065,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="40">
+        <f>index!AZ4</f>
         <v>46176</v>
       </c>
-      <c r="C3" s="41" t="s">
-        <v>140</v>
+      <c r="C3" s="41" t="str">
+        <f>index!BA4</f>
+        <v>PAKET4</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E3" s="31">
+        <f>index!BC4</f>
         <v>17459415</v>
       </c>
-      <c r="F3" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>63</v>
+      <c r="F3" s="31" t="str">
+        <f>index!BD4</f>
+        <v>Amel cell</v>
+      </c>
+      <c r="G3" s="43" t="str">
+        <f>index!BE4</f>
+        <v>Muhamad Parhan</v>
       </c>
       <c r="H3" s="6">
+        <f>index!BF4</f>
         <v>1</v>
       </c>
       <c r="I3" s="44">
+        <f>index!BM4</f>
         <v>118200</v>
       </c>
       <c r="J3" s="44">
+        <f>index!BP4</f>
         <v>118200</v>
       </c>
-      <c r="K3" s="44" t="s">
-        <v>28</v>
+      <c r="K3" s="44" t="str">
+        <f>index!BR4</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L3" s="40">
+        <f>index!BS4</f>
         <v>46177</v>
       </c>
     </row>
@@ -3053,36 +3113,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="40">
+        <f>index!AZ5</f>
         <v>46176</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>140</v>
+      <c r="C4" s="41" t="str">
+        <f>index!BA5</f>
+        <v>PAKET4</v>
       </c>
       <c r="D4" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E4" s="31">
+        <f>index!BC5</f>
         <v>17197757</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>63</v>
+      <c r="F4" s="31" t="str">
+        <f>index!BD5</f>
+        <v>GIAN ABDULLAH CELL</v>
+      </c>
+      <c r="G4" s="43" t="str">
+        <f>index!BE5</f>
+        <v>Muhamad Parhan</v>
       </c>
       <c r="H4" s="6">
+        <f>index!BF5</f>
         <v>1</v>
       </c>
       <c r="I4" s="44">
+        <f>index!BM5</f>
         <v>118200</v>
       </c>
       <c r="J4" s="44">
+        <f>index!BP5</f>
         <v>118200</v>
       </c>
-      <c r="K4" s="44" t="s">
-        <v>28</v>
+      <c r="K4" s="44" t="str">
+        <f>index!BR5</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L4" s="40">
+        <f>index!BS5</f>
         <v>46177</v>
       </c>
     </row>
@@ -3091,36 +3161,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="40">
+        <f>index!AZ6</f>
         <v>46176</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>139</v>
+      <c r="C5" s="41" t="str">
+        <f>index!BA6</f>
+        <v>PAKET1</v>
       </c>
       <c r="D5" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="31">
+        <f>index!BC6</f>
         <v>17438405</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>65</v>
+      <c r="F5" s="31" t="str">
+        <f>index!BD6</f>
+        <v>ALKHA CELL</v>
+      </c>
+      <c r="G5" s="43" t="str">
+        <f>index!BE6</f>
+        <v>Andi Sutiawan</v>
       </c>
       <c r="H5" s="6">
+        <f>index!BF6</f>
         <v>1</v>
       </c>
       <c r="I5" s="44">
+        <f>index!BM6</f>
         <v>115800</v>
       </c>
       <c r="J5" s="44">
+        <f>index!BP6</f>
         <v>115800</v>
       </c>
-      <c r="K5" s="44" t="s">
-        <v>28</v>
+      <c r="K5" s="44" t="str">
+        <f>index!BR6</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L5" s="40">
+        <f>index!BS6</f>
         <v>46177</v>
       </c>
     </row>
@@ -3129,36 +3209,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="40">
+        <f>index!AZ7</f>
         <v>46176</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>140</v>
+      <c r="C6" s="41" t="str">
+        <f>index!BA7</f>
+        <v>PAKET4</v>
       </c>
       <c r="D6" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="31">
+        <f>index!BC7</f>
         <v>17187147</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>41</v>
+      <c r="F6" s="31" t="str">
+        <f>index!BD7</f>
+        <v>Nazila cell</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f>index!BE7</f>
+        <v>M. Enden Abdul Latif</v>
       </c>
       <c r="H6" s="6">
+        <f>index!BF7</f>
         <v>1</v>
       </c>
       <c r="I6" s="44">
+        <f>index!BM7</f>
         <v>118200</v>
       </c>
       <c r="J6" s="44">
+        <f>index!BP7</f>
         <v>118200</v>
       </c>
-      <c r="K6" s="44" t="s">
-        <v>28</v>
+      <c r="K6" s="44" t="str">
+        <f>index!BR7</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L6" s="40">
+        <f>index!BS7</f>
         <v>46177</v>
       </c>
     </row>
@@ -3167,36 +3257,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="40">
+        <f>index!AZ8</f>
         <v>46176</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>140</v>
+      <c r="C7" s="41" t="str">
+        <f>index!BA8</f>
+        <v>PAKET4</v>
       </c>
       <c r="D7" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E7" s="31">
+        <f>index!BC8</f>
         <v>17798355</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>41</v>
+      <c r="F7" s="31" t="str">
+        <f>index!BD8</f>
+        <v>Yasmin Cell</v>
+      </c>
+      <c r="G7" s="43" t="str">
+        <f>index!BE8</f>
+        <v>M. Enden Abdul Latif</v>
       </c>
       <c r="H7" s="6">
+        <f>index!BF8</f>
         <v>1</v>
       </c>
       <c r="I7" s="44">
+        <f>index!BM8</f>
         <v>118200</v>
       </c>
       <c r="J7" s="44">
+        <f>index!BP8</f>
         <v>118200</v>
       </c>
-      <c r="K7" s="44" t="s">
-        <v>28</v>
+      <c r="K7" s="44" t="str">
+        <f>index!BR8</f>
+        <v xml:space="preserve"> -   </v>
       </c>
       <c r="L7" s="40">
+        <f>index!BS8</f>
         <v>46177</v>
       </c>
     </row>
@@ -3205,430 +3305,876 @@
         <v>7</v>
       </c>
       <c r="B8" s="40">
+        <f>index!AZ9</f>
         <v>46176</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>139</v>
+      <c r="C8" s="41" t="str">
+        <f>index!BA9</f>
+        <v>PAKET1</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E8" s="31">
+        <f>index!BC9</f>
         <v>572672</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>42</v>
+      <c r="F8" s="31" t="str">
+        <f>index!BD9</f>
+        <v>Bahagia cell</v>
+      </c>
+      <c r="G8" s="43" t="str">
+        <f>index!BE9</f>
+        <v>Pebrian Sahri Ramdani</v>
       </c>
       <c r="H8" s="6">
+        <f>index!BF9</f>
         <v>1</v>
       </c>
       <c r="I8" s="44">
+        <f>index!BM9</f>
         <v>115800</v>
       </c>
-      <c r="J8" s="44"/>
+      <c r="J8" s="44">
+        <f>index!BP9</f>
+        <v>0</v>
+      </c>
       <c r="K8" s="44">
+        <f>index!BR9</f>
         <v>115800</v>
       </c>
-      <c r="L8" s="44"/>
+      <c r="L8" s="40">
+        <f>index!BS9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="39">
         <v>8</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="40">
+        <f>index!AZ10</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="41">
+        <f>index!BA10</f>
+        <v>0</v>
+      </c>
       <c r="D9" s="42"/>
-      <c r="E9" s="31"/>
+      <c r="E9" s="31">
+        <f>index!BC10</f>
+        <v>0</v>
+      </c>
       <c r="F9" s="31" t="e">
+        <f>index!BD10</f>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="6"/>
+      <c r="G9" s="43">
+        <f>index!BE10</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <f>index!BF10</f>
+        <v>0</v>
+      </c>
       <c r="I9" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="44"/>
+        <f>index!BM10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="44">
+        <f>index!BP10</f>
+        <v>0</v>
+      </c>
       <c r="K9" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L9" s="44"/>
+        <f>index!BR10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="40">
+        <f>index!BS10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="39">
         <v>9</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="40">
+        <f>index!AZ11</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="41">
+        <f>index!BA11</f>
+        <v>0</v>
+      </c>
       <c r="D10" s="42"/>
-      <c r="E10" s="31"/>
+      <c r="E10" s="31">
+        <f>index!BC11</f>
+        <v>0</v>
+      </c>
       <c r="F10" s="31" t="e">
+        <f>index!BD11</f>
         <v>#N/A</v>
       </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="6"/>
+      <c r="G10" s="43">
+        <f>index!BE11</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <f>index!BF11</f>
+        <v>0</v>
+      </c>
       <c r="I10" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="44"/>
+        <f>index!BM11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="44">
+        <f>index!BP11</f>
+        <v>0</v>
+      </c>
       <c r="K10" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L10" s="44"/>
+        <f>index!BR11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="40">
+        <f>index!BS11</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="39">
         <v>10</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
+      <c r="B11" s="40">
+        <f>index!AZ12</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="41">
+        <f>index!BA12</f>
+        <v>0</v>
+      </c>
       <c r="D11" s="42"/>
-      <c r="E11" s="31"/>
+      <c r="E11" s="31">
+        <f>index!BC12</f>
+        <v>0</v>
+      </c>
       <c r="F11" s="31" t="e">
+        <f>index!BD12</f>
         <v>#N/A</v>
       </c>
-      <c r="G11" s="43"/>
-      <c r="H11" s="6"/>
+      <c r="G11" s="43">
+        <f>index!BE12</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <f>index!BF12</f>
+        <v>0</v>
+      </c>
       <c r="I11" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="44"/>
+        <f>index!BM12</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="44">
+        <f>index!BP12</f>
+        <v>0</v>
+      </c>
       <c r="K11" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L11" s="44"/>
+        <f>index!BR12</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="40">
+        <f>index!BS12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="39">
         <v>11</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="40">
+        <f>index!AZ13</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="41">
+        <f>index!BA13</f>
+        <v>0</v>
+      </c>
       <c r="D12" s="42"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31">
+        <f>index!BC13</f>
+        <v>0</v>
+      </c>
       <c r="F12" s="31" t="e">
+        <f>index!BD13</f>
         <v>#N/A</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="6"/>
+      <c r="G12" s="43">
+        <f>index!BE13</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <f>index!BF13</f>
+        <v>0</v>
+      </c>
       <c r="I12" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="44"/>
+        <f>index!BM13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="44">
+        <f>index!BP13</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L12" s="44"/>
+        <f>index!BR13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="40">
+        <f>index!BS13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="39">
         <v>12</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="40">
+        <f>index!AZ14</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="41">
+        <f>index!BA14</f>
+        <v>0</v>
+      </c>
       <c r="D13" s="42"/>
-      <c r="E13" s="31"/>
+      <c r="E13" s="31">
+        <f>index!BC14</f>
+        <v>0</v>
+      </c>
       <c r="F13" s="31" t="e">
+        <f>index!BD14</f>
         <v>#N/A</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="6"/>
+      <c r="G13" s="43">
+        <f>index!BE14</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <f>index!BF14</f>
+        <v>0</v>
+      </c>
       <c r="I13" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J13" s="44"/>
+        <f>index!BM14</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="44">
+        <f>index!BP14</f>
+        <v>0</v>
+      </c>
       <c r="K13" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L13" s="44"/>
+        <f>index!BR14</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="40">
+        <f>index!BS14</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="39">
         <v>13</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
+      <c r="B14" s="40">
+        <f>index!AZ15</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="41">
+        <f>index!BA15</f>
+        <v>0</v>
+      </c>
       <c r="D14" s="42"/>
-      <c r="E14" s="31"/>
+      <c r="E14" s="31">
+        <f>index!BC15</f>
+        <v>0</v>
+      </c>
       <c r="F14" s="31" t="e">
+        <f>index!BD15</f>
         <v>#N/A</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="6"/>
+      <c r="G14" s="43">
+        <f>index!BE15</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f>index!BF15</f>
+        <v>0</v>
+      </c>
       <c r="I14" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J14" s="44"/>
+        <f>index!BM15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="44">
+        <f>index!BP15</f>
+        <v>0</v>
+      </c>
       <c r="K14" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L14" s="44"/>
+        <f>index!BR15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L14" s="40">
+        <f>index!BS15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="39">
         <v>14</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="40">
+        <f>index!AZ16</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="41">
+        <f>index!BA16</f>
+        <v>0</v>
+      </c>
       <c r="D15" s="42"/>
-      <c r="E15" s="31"/>
+      <c r="E15" s="31">
+        <f>index!BC16</f>
+        <v>0</v>
+      </c>
       <c r="F15" s="31" t="e">
+        <f>index!BD16</f>
         <v>#N/A</v>
       </c>
-      <c r="G15" s="43"/>
-      <c r="H15" s="6"/>
+      <c r="G15" s="43">
+        <f>index!BE16</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <f>index!BF16</f>
+        <v>0</v>
+      </c>
       <c r="I15" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J15" s="44"/>
+        <f>index!BM16</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="44">
+        <f>index!BP16</f>
+        <v>0</v>
+      </c>
       <c r="K15" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L15" s="44"/>
+        <f>index!BR16</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L15" s="40">
+        <f>index!BS16</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="39">
         <v>15</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="40">
+        <f>index!AZ17</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="41">
+        <f>index!BA17</f>
+        <v>0</v>
+      </c>
       <c r="D16" s="42"/>
-      <c r="E16" s="31"/>
+      <c r="E16" s="31">
+        <f>index!BC17</f>
+        <v>0</v>
+      </c>
       <c r="F16" s="31" t="e">
+        <f>index!BD17</f>
         <v>#N/A</v>
       </c>
-      <c r="G16" s="43"/>
-      <c r="H16" s="6"/>
+      <c r="G16" s="43">
+        <f>index!BE17</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <f>index!BF17</f>
+        <v>0</v>
+      </c>
       <c r="I16" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="44"/>
+        <f>index!BM17</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J16" s="44">
+        <f>index!BP17</f>
+        <v>0</v>
+      </c>
       <c r="K16" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L16" s="44"/>
+        <f>index!BR17</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L16" s="40">
+        <f>index!BS17</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="39">
         <v>16</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="40">
+        <f>index!AZ18</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="41">
+        <f>index!BA18</f>
+        <v>0</v>
+      </c>
       <c r="D17" s="42"/>
-      <c r="E17" s="31"/>
+      <c r="E17" s="31">
+        <f>index!BC18</f>
+        <v>0</v>
+      </c>
       <c r="F17" s="31" t="e">
+        <f>index!BD18</f>
         <v>#N/A</v>
       </c>
-      <c r="G17" s="43"/>
-      <c r="H17" s="6"/>
+      <c r="G17" s="43">
+        <f>index!BE18</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <f>index!BF18</f>
+        <v>0</v>
+      </c>
       <c r="I17" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J17" s="44"/>
+        <f>index!BM18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J17" s="44">
+        <f>index!BP18</f>
+        <v>0</v>
+      </c>
       <c r="K17" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L17" s="44"/>
+        <f>index!BR18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L17" s="40">
+        <f>index!BS18</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="39">
         <v>17</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="40">
+        <f>index!AZ19</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="41">
+        <f>index!BA19</f>
+        <v>0</v>
+      </c>
       <c r="D18" s="42"/>
-      <c r="E18" s="31"/>
+      <c r="E18" s="31">
+        <f>index!BC19</f>
+        <v>0</v>
+      </c>
       <c r="F18" s="31" t="e">
+        <f>index!BD19</f>
         <v>#N/A</v>
       </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="6"/>
+      <c r="G18" s="43">
+        <f>index!BE19</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <f>index!BF19</f>
+        <v>0</v>
+      </c>
       <c r="I18" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J18" s="44"/>
+        <f>index!BM19</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J18" s="44">
+        <f>index!BP19</f>
+        <v>0</v>
+      </c>
       <c r="K18" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L18" s="44"/>
+        <f>index!BR19</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L18" s="40">
+        <f>index!BS19</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="39">
         <v>18</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="40">
+        <f>index!AZ20</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="41">
+        <f>index!BA20</f>
+        <v>0</v>
+      </c>
       <c r="D19" s="42"/>
-      <c r="E19" s="31"/>
+      <c r="E19" s="31">
+        <f>index!BC20</f>
+        <v>0</v>
+      </c>
       <c r="F19" s="31" t="e">
+        <f>index!BD20</f>
         <v>#N/A</v>
       </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="6"/>
+      <c r="G19" s="43">
+        <f>index!BE20</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <f>index!BF20</f>
+        <v>0</v>
+      </c>
       <c r="I19" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J19" s="44"/>
+        <f>index!BM20</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="44">
+        <f>index!BP20</f>
+        <v>0</v>
+      </c>
       <c r="K19" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L19" s="44"/>
+        <f>index!BR20</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L19" s="40">
+        <f>index!BS20</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="39">
         <v>19</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="40">
+        <f>index!AZ21</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="41">
+        <f>index!BA21</f>
+        <v>0</v>
+      </c>
       <c r="D20" s="42"/>
-      <c r="E20" s="31"/>
+      <c r="E20" s="31">
+        <f>index!BC21</f>
+        <v>0</v>
+      </c>
       <c r="F20" s="31" t="e">
+        <f>index!BD21</f>
         <v>#N/A</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="6"/>
+      <c r="G20" s="43">
+        <f>index!BE21</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <f>index!BF21</f>
+        <v>0</v>
+      </c>
       <c r="I20" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J20" s="44"/>
+        <f>index!BM21</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J20" s="44">
+        <f>index!BP21</f>
+        <v>0</v>
+      </c>
       <c r="K20" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L20" s="44"/>
+        <f>index!BR21</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L20" s="40">
+        <f>index!BS21</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="39">
         <v>20</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
+      <c r="B21" s="40">
+        <f>index!AZ22</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="41">
+        <f>index!BA22</f>
+        <v>0</v>
+      </c>
       <c r="D21" s="42"/>
-      <c r="E21" s="31"/>
+      <c r="E21" s="31">
+        <f>index!BC22</f>
+        <v>0</v>
+      </c>
       <c r="F21" s="31" t="e">
+        <f>index!BD22</f>
         <v>#N/A</v>
       </c>
-      <c r="G21" s="43"/>
-      <c r="H21" s="6"/>
+      <c r="G21" s="43">
+        <f>index!BE22</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <f>index!BF22</f>
+        <v>0</v>
+      </c>
       <c r="I21" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J21" s="44"/>
+        <f>index!BM22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J21" s="44">
+        <f>index!BP22</f>
+        <v>0</v>
+      </c>
       <c r="K21" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L21" s="44"/>
+        <f>index!BR22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L21" s="40">
+        <f>index!BS22</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="39">
         <v>21</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
+      <c r="B22" s="40">
+        <f>index!AZ23</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="41">
+        <f>index!BA23</f>
+        <v>0</v>
+      </c>
       <c r="D22" s="42"/>
-      <c r="E22" s="31"/>
+      <c r="E22" s="31">
+        <f>index!BC23</f>
+        <v>0</v>
+      </c>
       <c r="F22" s="31" t="e">
+        <f>index!BD23</f>
         <v>#N/A</v>
       </c>
-      <c r="G22" s="43"/>
-      <c r="H22" s="6"/>
+      <c r="G22" s="43">
+        <f>index!BE23</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
+        <f>index!BF23</f>
+        <v>0</v>
+      </c>
       <c r="I22" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J22" s="44"/>
+        <f>index!BM23</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J22" s="44">
+        <f>index!BP23</f>
+        <v>0</v>
+      </c>
       <c r="K22" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L22" s="44"/>
+        <f>index!BR23</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L22" s="40">
+        <f>index!BS23</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="39">
         <v>22</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
+      <c r="B23" s="40">
+        <f>index!AZ24</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="41">
+        <f>index!BA24</f>
+        <v>0</v>
+      </c>
       <c r="D23" s="42"/>
-      <c r="E23" s="31"/>
+      <c r="E23" s="31">
+        <f>index!BC24</f>
+        <v>0</v>
+      </c>
       <c r="F23" s="31" t="e">
+        <f>index!BD24</f>
         <v>#N/A</v>
       </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="6"/>
+      <c r="G23" s="43">
+        <f>index!BE24</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
+        <f>index!BF24</f>
+        <v>0</v>
+      </c>
       <c r="I23" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J23" s="44"/>
+        <f>index!BM24</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J23" s="44">
+        <f>index!BP24</f>
+        <v>0</v>
+      </c>
       <c r="K23" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L23" s="44"/>
+        <f>index!BR24</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L23" s="40">
+        <f>index!BS24</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="39">
         <v>23</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="40">
+        <f>index!AZ25</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="41">
+        <f>index!BA25</f>
+        <v>0</v>
+      </c>
       <c r="D24" s="42"/>
-      <c r="E24" s="31"/>
+      <c r="E24" s="31">
+        <f>index!BC25</f>
+        <v>0</v>
+      </c>
       <c r="F24" s="31" t="e">
+        <f>index!BD25</f>
         <v>#N/A</v>
       </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="6"/>
+      <c r="G24" s="43">
+        <f>index!BE25</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <f>index!BF25</f>
+        <v>0</v>
+      </c>
       <c r="I24" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J24" s="44"/>
+        <f>index!BM25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J24" s="44">
+        <f>index!BP25</f>
+        <v>0</v>
+      </c>
       <c r="K24" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L24" s="44"/>
+        <f>index!BR25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L24" s="40">
+        <f>index!BS25</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="39">
         <v>24</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
+      <c r="B25" s="40">
+        <f>index!AZ26</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="41">
+        <f>index!BA26</f>
+        <v>0</v>
+      </c>
       <c r="D25" s="42"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L25" s="44"/>
+      <c r="E25" s="31">
+        <f>index!BC26</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="31">
+        <f>index!BD26</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="43">
+        <f>index!BE26</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <f>index!BF26</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="44">
+        <f>index!BM26</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="44">
+        <f>index!BP26</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="44">
+        <f>index!BR26</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="40">
+        <f>index!BS26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="39">
         <v>25</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="40">
+        <f>index!AZ27</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="41">
+        <f>index!BA27</f>
+        <v>0</v>
+      </c>
       <c r="D26" s="42"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L26" s="44"/>
+      <c r="E26" s="31">
+        <f>index!BC27</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="31">
+        <f>index!BD27</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="43">
+        <f>index!BE27</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
+        <f>index!BF27</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="44">
+        <f>index!BM27</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="44">
+        <f>index!BP27</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="44">
+        <f>index!BR27</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="40">
+        <f>index!BS27</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="39">
@@ -4239,18 +4785,19 @@
       </c>
       <c r="C2">
         <f>index!AC12</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <f>index!AD12</f>
-        <v>630000</v>
+        <v>375000</v>
       </c>
       <c r="E2">
-        <v>630000</v>
+        <f>index!AE12</f>
+        <v>0</v>
       </c>
       <c r="F2">
         <f>index!AF12</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <f>index!AG12</f>
@@ -4258,7 +4805,7 @@
       </c>
       <c r="H2">
         <f>index!AH12</f>
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -4270,18 +4817,19 @@
       </c>
       <c r="C3">
         <f>index!AC13</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <f>index!AD13</f>
-        <v>630000</v>
+        <v>375000</v>
       </c>
       <c r="E3">
-        <v>630000</v>
+        <f>index!AE13</f>
+        <v>0</v>
       </c>
       <c r="F3">
         <f>index!AF13</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <f>index!AG13</f>
@@ -4289,7 +4837,7 @@
       </c>
       <c r="H3">
         <f>index!AH13</f>
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -4301,18 +4849,19 @@
       </c>
       <c r="C4">
         <f>index!AC14</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <f>index!AD14</f>
-        <v>630000</v>
+        <v>375000</v>
       </c>
       <c r="E4">
-        <v>630000</v>
+        <f>index!AE14</f>
+        <v>0</v>
       </c>
       <c r="F4">
         <f>index!AF14</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G4">
         <f>index!AG14</f>
@@ -4320,7 +4869,7 @@
       </c>
       <c r="H4">
         <f>index!AH14</f>
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -4332,18 +4881,19 @@
       </c>
       <c r="C5">
         <f>index!AC15</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <f>index!AD15</f>
-        <v>630000</v>
+        <v>375000</v>
       </c>
       <c r="E5">
-        <v>630000</v>
+        <f>index!AE15</f>
+        <v>0</v>
       </c>
       <c r="F5">
         <f>index!AF15</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <f>index!AG15</f>
@@ -4351,25 +4901,25 @@
       </c>
       <c r="H5">
         <f>index!AH15</f>
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>SUM(C2:C5)</f>
-        <v>252</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:H6" si="0">SUM(D2:D5)</f>
-        <v>2520000</v>
+        <v>1500000</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>2520000</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
@@ -4377,7 +4927,7 @@
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5104,7 +5654,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978FC411-0E9B-4587-8457-DC4C81104AEC}">
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:BU26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="13.5859375" bestFit="1" customWidth="1"/>
@@ -5113,9 +5663,13 @@
     <col min="40" max="40" width="11.703125" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="9.68359375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="9.14453125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.14453125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="9.14453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -5134,8 +5688,11 @@
       <c r="AM1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="2" spans="1:49" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AY1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:73" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>0</v>
       </c>
@@ -5235,8 +5792,77 @@
       <c r="AW2" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>51</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A3" s="53"/>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -5330,8 +5956,77 @@
         <v>120</v>
       </c>
       <c r="AW3" s="5"/>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY3">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC3">
+        <v>17588141</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BF3">
+        <v>1</v>
+      </c>
+      <c r="BG3">
+        <v>3</v>
+      </c>
+      <c r="BH3">
+        <v>3</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK3">
+        <v>3</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM3" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BN3" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO3">
+        <v>1</v>
+      </c>
+      <c r="BP3" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS3" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>500000</v>
+      </c>
+      <c r="BU3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -5466,8 +6161,77 @@
         <v>127</v>
       </c>
       <c r="AW4" s="5"/>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY4">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC4">
+        <v>17459415</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>142</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>63</v>
+      </c>
+      <c r="BF4">
+        <v>1</v>
+      </c>
+      <c r="BG4">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ4">
+        <v>3</v>
+      </c>
+      <c r="BK4">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM4" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BN4" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO4">
+        <v>1</v>
+      </c>
+      <c r="BP4" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS4" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>200000</v>
+      </c>
+      <c r="BU4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
@@ -5603,8 +6367,77 @@
         <v>127</v>
       </c>
       <c r="AW5" s="5"/>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY5">
+        <v>3</v>
+      </c>
+      <c r="AZ5" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC5">
+        <v>17197757</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>63</v>
+      </c>
+      <c r="BF5">
+        <v>1</v>
+      </c>
+      <c r="BG5">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ5">
+        <v>3</v>
+      </c>
+      <c r="BK5">
+        <v>3</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM5" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BN5" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO5">
+        <v>1</v>
+      </c>
+      <c r="BP5" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS5" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>500000</v>
+      </c>
+      <c r="BU5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -5738,8 +6571,77 @@
         <v>120</v>
       </c>
       <c r="AW6" s="5"/>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY6">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>139</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC6">
+        <v>17438405</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>144</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BF6">
+        <v>1</v>
+      </c>
+      <c r="BG6">
+        <v>3</v>
+      </c>
+      <c r="BH6">
+        <v>3</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK6">
+        <v>3</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM6" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BN6" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO6">
+        <v>1</v>
+      </c>
+      <c r="BP6" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS6" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>500000</v>
+      </c>
+      <c r="BU6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -5873,8 +6775,77 @@
         <v>120</v>
       </c>
       <c r="AW7" s="5"/>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY7">
+        <v>5</v>
+      </c>
+      <c r="AZ7" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC7">
+        <v>17187147</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF7">
+        <v>1</v>
+      </c>
+      <c r="BG7">
+        <v>3</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ7">
+        <v>3</v>
+      </c>
+      <c r="BK7">
+        <v>3</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM7" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BN7" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO7">
+        <v>1</v>
+      </c>
+      <c r="BP7" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS7" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>100000</v>
+      </c>
+      <c r="BU7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="13">
         <v>0</v>
@@ -5998,8 +6969,77 @@
         <v>127</v>
       </c>
       <c r="AW8" s="5"/>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY8">
+        <v>6</v>
+      </c>
+      <c r="AZ8" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC8">
+        <v>17798355</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>146</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF8">
+        <v>1</v>
+      </c>
+      <c r="BG8">
+        <v>3</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ8">
+        <v>3</v>
+      </c>
+      <c r="BK8">
+        <v>3</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM8" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BN8" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BO8">
+        <v>1</v>
+      </c>
+      <c r="BP8" s="1">
+        <v>118200</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS8" s="47">
+        <v>46177</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>500000</v>
+      </c>
+      <c r="BU8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13">
         <v>0</v>
@@ -6092,8 +7132,62 @@
         <v>127</v>
       </c>
       <c r="AW9" s="5"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY9">
+        <v>7</v>
+      </c>
+      <c r="AZ9" s="47">
+        <v>46176</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC9">
+        <v>572672</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>147</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF9">
+        <v>1</v>
+      </c>
+      <c r="BG9">
+        <v>3</v>
+      </c>
+      <c r="BH9">
+        <v>3</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK9">
+        <v>3</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM9" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>115800</v>
+      </c>
+      <c r="BT9" s="1">
+        <v>300000</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>8</v>
       </c>
@@ -6192,8 +7286,44 @@
         <v>120</v>
       </c>
       <c r="AW10" s="5"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY10">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM10" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR10" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>9</v>
       </c>
@@ -6313,8 +7443,44 @@
         <v>118</v>
       </c>
       <c r="AW11" s="5"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY11">
+        <v>9</v>
+      </c>
+      <c r="BD11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM11" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR11" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU11" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>10</v>
       </c>
@@ -6390,22 +7556,22 @@
         <v>63</v>
       </c>
       <c r="AC12">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="AD12">
-        <v>630000</v>
-      </c>
-      <c r="AE12">
-        <v>630000</v>
+        <f>15000*AC12</f>
+        <v>375000</v>
       </c>
       <c r="AF12">
-        <v>63</v>
+        <f>AC12</f>
+        <v>25</v>
       </c>
       <c r="AG12">
         <v>0</v>
       </c>
       <c r="AH12">
-        <v>63</v>
+        <f>AF12</f>
+        <v>25</v>
       </c>
       <c r="AM12" s="4">
         <v>10</v>
@@ -6434,8 +7600,44 @@
         <v>119</v>
       </c>
       <c r="AW12" s="5"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="BD12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -6507,22 +7709,22 @@
         <v>65</v>
       </c>
       <c r="AC13">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="AD13">
-        <v>630000</v>
-      </c>
-      <c r="AE13">
-        <v>630000</v>
+        <f t="shared" ref="AD13:AD15" si="6">15000*AC13</f>
+        <v>375000</v>
       </c>
       <c r="AF13">
-        <v>63</v>
+        <f t="shared" ref="AF13:AF15" si="7">AC13</f>
+        <v>25</v>
       </c>
       <c r="AG13">
         <v>0</v>
       </c>
       <c r="AH13">
-        <v>63</v>
+        <f t="shared" ref="AH13:AH15" si="8">AF13</f>
+        <v>25</v>
       </c>
       <c r="AM13" s="4">
         <v>11</v>
@@ -6537,8 +7739,44 @@
       <c r="AU13" s="5"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY13">
+        <v>11</v>
+      </c>
+      <c r="BD13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM13" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR13" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>12</v>
       </c>
@@ -6610,22 +7848,22 @@
         <v>41</v>
       </c>
       <c r="AC14">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="AD14">
-        <v>630000</v>
-      </c>
-      <c r="AE14">
-        <v>630000</v>
+        <f t="shared" si="6"/>
+        <v>375000</v>
       </c>
       <c r="AF14">
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="AG14">
         <v>0</v>
       </c>
       <c r="AH14">
-        <v>63</v>
+        <f t="shared" si="8"/>
+        <v>25</v>
       </c>
       <c r="AM14" s="4">
         <v>12</v>
@@ -6640,8 +7878,44 @@
       <c r="AU14" s="5"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY14">
+        <v>12</v>
+      </c>
+      <c r="BD14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
@@ -6713,22 +7987,22 @@
         <v>42</v>
       </c>
       <c r="AC15">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="AD15">
-        <v>630000</v>
-      </c>
-      <c r="AE15">
-        <v>630000</v>
+        <f t="shared" si="6"/>
+        <v>375000</v>
       </c>
       <c r="AF15">
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="AG15">
         <v>0</v>
       </c>
       <c r="AH15">
-        <v>63</v>
+        <f t="shared" si="8"/>
+        <v>25</v>
       </c>
       <c r="AM15" s="4">
         <v>13</v>
@@ -6743,8 +8017,44 @@
       <c r="AU15" s="5"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY15">
+        <v>13</v>
+      </c>
+      <c r="BD15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM15" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR15" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
@@ -6811,27 +8121,27 @@
       </c>
       <c r="AC16">
         <f>SUM(AC12:AC15)</f>
-        <v>252</v>
+        <v>100</v>
       </c>
       <c r="AD16">
-        <f t="shared" ref="AD16:AH16" si="6">SUM(AD12:AD15)</f>
-        <v>2520000</v>
+        <f t="shared" ref="AD16:AH16" si="9">SUM(AD12:AD15)</f>
+        <v>1500000</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="6"/>
-        <v>2520000</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="6"/>
-        <v>252</v>
+        <f t="shared" si="9"/>
+        <v>100</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="6"/>
-        <v>252</v>
+        <f t="shared" si="9"/>
+        <v>100</v>
       </c>
       <c r="AM16" s="4">
         <v>14</v>
@@ -6846,8 +8156,44 @@
       <c r="AU16" s="10"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="10"/>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY16">
+        <v>14</v>
+      </c>
+      <c r="BD16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
@@ -6925,8 +8271,44 @@
       <c r="AU17" s="10"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="10"/>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY17">
+        <v>15</v>
+      </c>
+      <c r="BD17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM17" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR17" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT17" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU17" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>16</v>
       </c>
@@ -7004,8 +8386,44 @@
       <c r="AU18" s="10"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="10"/>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY18">
+        <v>16</v>
+      </c>
+      <c r="BD18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM18" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR18" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT18" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -7070,8 +8488,44 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY19">
+        <v>17</v>
+      </c>
+      <c r="BD19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM19" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR19" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
@@ -7136,8 +8590,44 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY20">
+        <v>18</v>
+      </c>
+      <c r="BD20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM20" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR20" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT20" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
@@ -7202,8 +8692,44 @@
         <f t="shared" si="3"/>
         <v>739200</v>
       </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY21">
+        <v>19</v>
+      </c>
+      <c r="BD21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM21" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR21" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT21" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>20</v>
       </c>
@@ -7268,8 +8794,44 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY22">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM22" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR22" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT22" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:73" x14ac:dyDescent="0.2">
       <c r="F23" s="20" t="s">
         <v>20</v>
       </c>
@@ -7315,8 +8877,44 @@
       <c r="Y23" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY23">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM23" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR23" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT23" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:73" x14ac:dyDescent="0.2">
       <c r="F24" s="20"/>
       <c r="G24" s="21">
         <v>0</v>
@@ -7360,8 +8958,44 @@
       <c r="Y24" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY24">
+        <v>22</v>
+      </c>
+      <c r="BD24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM24" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR24" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT24" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:73" x14ac:dyDescent="0.2">
       <c r="F25" s="20"/>
       <c r="G25" s="21">
         <v>0</v>
@@ -7390,53 +9024,89 @@
         <v>75</v>
       </c>
       <c r="S25" s="19">
-        <f t="shared" ref="S25:Y25" si="7">SUM(S4:S24)</f>
+        <f t="shared" ref="S25:Y25" si="10">SUM(S4:S24)</f>
         <v>75</v>
       </c>
       <c r="T25" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>65</v>
       </c>
       <c r="U25" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="V25" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W25" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>255</v>
       </c>
       <c r="X25" s="19"/>
       <c r="Y25" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3944200</v>
       </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AY25">
+        <v>23</v>
+      </c>
+      <c r="BD25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BH25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BK25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM25" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR25" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT25" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:73" x14ac:dyDescent="0.2">
       <c r="F26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="24">
-        <f t="shared" ref="G26:K26" si="8">SUM(G5:G25)</f>
+        <f t="shared" ref="G26:K26" si="11">SUM(G5:G25)</f>
         <v>1207</v>
       </c>
       <c r="H26" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>956</v>
       </c>
       <c r="I26" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>720</v>
       </c>
       <c r="J26" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1144</v>
       </c>
       <c r="K26" s="24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="L26" s="24">
